--- a/data/ams_weekly_data/Nexlev/ads_report_week23.xlsx
+++ b/data/ams_weekly_data/Nexlev/ads_report_week23.xlsx
@@ -479,7 +479,7 @@
         <v>55</v>
       </c>
       <c r="F2" t="n">
-        <v>29955</v>
+        <v>29828</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -507,7 +507,7 @@
         <v>21</v>
       </c>
       <c r="F3" t="n">
-        <v>4213</v>
+        <v>4146</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -535,7 +535,7 @@
         <v>1</v>
       </c>
       <c r="F4" t="n">
-        <v>350</v>
+        <v>344</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -563,7 +563,7 @@
         <v>14</v>
       </c>
       <c r="F5" t="n">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -591,7 +591,7 @@
         <v>5</v>
       </c>
       <c r="F6" t="n">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -647,7 +647,7 @@
         <v>9</v>
       </c>
       <c r="F8" t="n">
-        <v>2384</v>
+        <v>2373</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -675,7 +675,7 @@
         <v>9</v>
       </c>
       <c r="F9" t="n">
-        <v>1466</v>
+        <v>1463</v>
       </c>
       <c r="G9" t="n">
         <v>846.61</v>
@@ -731,7 +731,7 @@
         <v>4</v>
       </c>
       <c r="F11" t="n">
-        <v>1154</v>
+        <v>1146</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
         <v>53</v>
       </c>
       <c r="F13" t="n">
-        <v>2948</v>
+        <v>2935</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -927,7 +927,7 @@
         <v>24</v>
       </c>
       <c r="F18" t="n">
-        <v>2676</v>
+        <v>2535</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -983,7 +983,7 @@
         <v>6</v>
       </c>
       <c r="F20" t="n">
-        <v>1336</v>
+        <v>1332</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -1011,7 +1011,7 @@
         <v>73</v>
       </c>
       <c r="F21" t="n">
-        <v>10956</v>
+        <v>10878</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -1039,7 +1039,7 @@
         <v>12</v>
       </c>
       <c r="F22" t="n">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1067,7 +1067,7 @@
         <v>22</v>
       </c>
       <c r="F23" t="n">
-        <v>2593</v>
+        <v>2571</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1095,7 +1095,7 @@
         <v>15</v>
       </c>
       <c r="F24" t="n">
-        <v>12859</v>
+        <v>12824</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1123,7 +1123,7 @@
         <v>49</v>
       </c>
       <c r="F25" t="n">
-        <v>7193</v>
+        <v>7184</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -1151,7 +1151,7 @@
         <v>2</v>
       </c>
       <c r="F26" t="n">
-        <v>511</v>
+        <v>489</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -1207,7 +1207,7 @@
         <v>291</v>
       </c>
       <c r="F28" t="n">
-        <v>20718</v>
+        <v>20613</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -1235,7 +1235,7 @@
         <v>18</v>
       </c>
       <c r="F29" t="n">
-        <v>1499</v>
+        <v>1456</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -1291,7 +1291,7 @@
         <v>15</v>
       </c>
       <c r="F31" t="n">
-        <v>488</v>
+        <v>484</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
         <v>20</v>
       </c>
       <c r="F32" t="n">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -1347,7 +1347,7 @@
         <v>46</v>
       </c>
       <c r="F33" t="n">
-        <v>2565</v>
+        <v>2556</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -1375,7 +1375,7 @@
         <v>19</v>
       </c>
       <c r="F34" t="n">
-        <v>601</v>
+        <v>586</v>
       </c>
       <c r="G34" t="n">
         <v>2541.53</v>
@@ -1403,7 +1403,7 @@
         <v>20</v>
       </c>
       <c r="F35" t="n">
-        <v>2951</v>
+        <v>2936</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -1459,7 +1459,7 @@
         <v>0</v>
       </c>
       <c r="F37" t="n">
-        <v>807</v>
+        <v>754</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -1487,7 +1487,7 @@
         <v>25</v>
       </c>
       <c r="F38" t="n">
-        <v>2079</v>
+        <v>2009</v>
       </c>
       <c r="G38" t="n">
         <v>3812.72</v>
@@ -1515,7 +1515,7 @@
         <v>26</v>
       </c>
       <c r="F39" t="n">
-        <v>3274</v>
+        <v>3228</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -1599,7 +1599,7 @@
         <v>17</v>
       </c>
       <c r="F42" t="n">
-        <v>883</v>
+        <v>871</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -1683,7 +1683,7 @@
         <v>25</v>
       </c>
       <c r="F45" t="n">
-        <v>2771</v>
+        <v>2768</v>
       </c>
       <c r="G45" t="n">
         <v>1046.67</v>
@@ -1739,7 +1739,7 @@
         <v>16</v>
       </c>
       <c r="F47" t="n">
-        <v>4401</v>
+        <v>4399</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
@@ -1767,7 +1767,7 @@
         <v>15</v>
       </c>
       <c r="F48" t="n">
-        <v>1773</v>
+        <v>1756</v>
       </c>
       <c r="G48" t="n">
         <v>1814.4</v>
@@ -1795,7 +1795,7 @@
         <v>2</v>
       </c>
       <c r="F49" t="n">
-        <v>442</v>
+        <v>415</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -1823,7 +1823,7 @@
         <v>12</v>
       </c>
       <c r="F50" t="n">
-        <v>2629</v>
+        <v>2619</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
@@ -1851,7 +1851,7 @@
         <v>30</v>
       </c>
       <c r="F51" t="n">
-        <v>11947</v>
+        <v>11888</v>
       </c>
       <c r="G51" t="n">
         <v>2880.51</v>
@@ -1907,7 +1907,7 @@
         <v>14</v>
       </c>
       <c r="F53" t="n">
-        <v>3768</v>
+        <v>3762</v>
       </c>
       <c r="G53" t="n">
         <v>2380</v>
@@ -1935,13 +1935,13 @@
         <v>37</v>
       </c>
       <c r="F54" t="n">
-        <v>8231</v>
+        <v>8195</v>
       </c>
       <c r="G54" t="n">
-        <v>0</v>
+        <v>5083.9</v>
       </c>
       <c r="H54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -1963,7 +1963,7 @@
         <v>62</v>
       </c>
       <c r="F55" t="n">
-        <v>1978</v>
+        <v>1977</v>
       </c>
       <c r="G55" t="n">
         <v>5083.9</v>
@@ -1991,7 +1991,7 @@
         <v>38</v>
       </c>
       <c r="F56" t="n">
-        <v>1655</v>
+        <v>1650</v>
       </c>
       <c r="G56" t="n">
         <v>5185.59</v>
@@ -2019,7 +2019,7 @@
         <v>26</v>
       </c>
       <c r="F57" t="n">
-        <v>3628</v>
+        <v>3602</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
@@ -2047,7 +2047,7 @@
         <v>30</v>
       </c>
       <c r="F58" t="n">
-        <v>4645</v>
+        <v>4628</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
@@ -2075,7 +2075,7 @@
         <v>67</v>
       </c>
       <c r="F59" t="n">
-        <v>30139</v>
+        <v>30108</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
@@ -2103,7 +2103,7 @@
         <v>36</v>
       </c>
       <c r="F60" t="n">
-        <v>5891</v>
+        <v>5855</v>
       </c>
       <c r="G60" t="n">
         <v>15082.2</v>
@@ -2187,7 +2187,7 @@
         <v>1</v>
       </c>
       <c r="F63" t="n">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
@@ -2215,7 +2215,7 @@
         <v>92</v>
       </c>
       <c r="F64" t="n">
-        <v>18008</v>
+        <v>17898</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
@@ -2243,7 +2243,7 @@
         <v>51</v>
       </c>
       <c r="F65" t="n">
-        <v>28796</v>
+        <v>28590</v>
       </c>
       <c r="G65" t="n">
         <v>2033.05</v>
@@ -2271,7 +2271,7 @@
         <v>65</v>
       </c>
       <c r="F66" t="n">
-        <v>18654</v>
+        <v>18243</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
@@ -2299,7 +2299,7 @@
         <v>28</v>
       </c>
       <c r="F67" t="n">
-        <v>3822</v>
+        <v>3811</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -2411,7 +2411,7 @@
         <v>1</v>
       </c>
       <c r="F71" t="n">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
@@ -2467,7 +2467,7 @@
         <v>0</v>
       </c>
       <c r="F73" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -2523,7 +2523,7 @@
         <v>0</v>
       </c>
       <c r="F75" t="n">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
@@ -2551,7 +2551,7 @@
         <v>0</v>
       </c>
       <c r="F76" t="n">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -2635,7 +2635,7 @@
         <v>0</v>
       </c>
       <c r="F79" t="n">
-        <v>130</v>
+        <v>118</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
@@ -2663,7 +2663,7 @@
         <v>2</v>
       </c>
       <c r="F80" t="n">
-        <v>446</v>
+        <v>427</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -2747,7 +2747,7 @@
         <v>0</v>
       </c>
       <c r="F83" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -2803,7 +2803,7 @@
         <v>1</v>
       </c>
       <c r="F85" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -2915,7 +2915,7 @@
         <v>2</v>
       </c>
       <c r="F89" t="n">
-        <v>513</v>
+        <v>502</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -2943,7 +2943,7 @@
         <v>2</v>
       </c>
       <c r="F90" t="n">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -3083,7 +3083,7 @@
         <v>15</v>
       </c>
       <c r="F95" t="n">
-        <v>990</v>
+        <v>941</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -3111,7 +3111,7 @@
         <v>1</v>
       </c>
       <c r="F96" t="n">
-        <v>1050</v>
+        <v>984</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
@@ -3391,7 +3391,7 @@
         <v>1</v>
       </c>
       <c r="F106" t="n">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="G106" t="n">
         <v>0</v>
@@ -3531,7 +3531,7 @@
         <v>0</v>
       </c>
       <c r="F111" t="n">
-        <v>94</v>
+        <v>75</v>
       </c>
       <c r="G111" t="n">
         <v>0</v>
@@ -3559,7 +3559,7 @@
         <v>1</v>
       </c>
       <c r="F112" t="n">
-        <v>1707</v>
+        <v>1698</v>
       </c>
       <c r="G112" t="n">
         <v>0</v>
@@ -3643,7 +3643,7 @@
         <v>0</v>
       </c>
       <c r="F115" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G115" t="n">
         <v>0</v>
@@ -3755,7 +3755,7 @@
         <v>4</v>
       </c>
       <c r="F119" t="n">
-        <v>437</v>
+        <v>393</v>
       </c>
       <c r="G119" t="n">
         <v>0</v>
@@ -3783,7 +3783,7 @@
         <v>0</v>
       </c>
       <c r="F120" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G120" t="n">
         <v>0</v>
@@ -3811,7 +3811,7 @@
         <v>0</v>
       </c>
       <c r="F121" t="n">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="G121" t="n">
         <v>0</v>
@@ -3839,7 +3839,7 @@
         <v>0</v>
       </c>
       <c r="F122" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G122" t="n">
         <v>0</v>
@@ -3867,7 +3867,7 @@
         <v>4</v>
       </c>
       <c r="F123" t="n">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="G123" t="n">
         <v>677.12</v>
@@ -3895,7 +3895,7 @@
         <v>2</v>
       </c>
       <c r="F124" t="n">
-        <v>7429</v>
+        <v>5674</v>
       </c>
       <c r="G124" t="n">
         <v>0</v>
@@ -3923,7 +3923,7 @@
         <v>1</v>
       </c>
       <c r="F125" t="n">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="G125" t="n">
         <v>0</v>
@@ -4007,7 +4007,7 @@
         <v>0</v>
       </c>
       <c r="F128" t="n">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="G128" t="n">
         <v>0</v>
@@ -4035,7 +4035,7 @@
         <v>2</v>
       </c>
       <c r="F129" t="n">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="G129" t="n">
         <v>0</v>
@@ -4063,7 +4063,7 @@
         <v>0</v>
       </c>
       <c r="F130" t="n">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="G130" t="n">
         <v>0</v>
@@ -4091,7 +4091,7 @@
         <v>1</v>
       </c>
       <c r="F131" t="n">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="G131" t="n">
         <v>0</v>
@@ -4119,7 +4119,7 @@
         <v>2</v>
       </c>
       <c r="F132" t="n">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="G132" t="n">
         <v>0</v>
@@ -4147,7 +4147,7 @@
         <v>1</v>
       </c>
       <c r="F133" t="n">
-        <v>170</v>
+        <v>156</v>
       </c>
       <c r="G133" t="n">
         <v>0</v>
@@ -4175,7 +4175,7 @@
         <v>6</v>
       </c>
       <c r="F134" t="n">
-        <v>1157</v>
+        <v>1108</v>
       </c>
       <c r="G134" t="n">
         <v>0</v>
@@ -4231,7 +4231,7 @@
         <v>0</v>
       </c>
       <c r="F136" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G136" t="n">
         <v>0</v>
@@ -4259,7 +4259,7 @@
         <v>0</v>
       </c>
       <c r="F137" t="n">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="G137" t="n">
         <v>0</v>
@@ -4287,7 +4287,7 @@
         <v>1</v>
       </c>
       <c r="F138" t="n">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="G138" t="n">
         <v>0</v>
@@ -4343,7 +4343,7 @@
         <v>104</v>
       </c>
       <c r="F140" t="n">
-        <v>12650</v>
+        <v>12574</v>
       </c>
       <c r="G140" t="n">
         <v>1778.81</v>
@@ -4371,7 +4371,7 @@
         <v>0</v>
       </c>
       <c r="F141" t="n">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="G141" t="n">
         <v>0</v>
@@ -4399,7 +4399,7 @@
         <v>4</v>
       </c>
       <c r="F142" t="n">
-        <v>804</v>
+        <v>792</v>
       </c>
       <c r="G142" t="n">
         <v>0</v>
@@ -4427,7 +4427,7 @@
         <v>1</v>
       </c>
       <c r="F143" t="n">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="G143" t="n">
         <v>0</v>
@@ -4455,7 +4455,7 @@
         <v>8</v>
       </c>
       <c r="F144" t="n">
-        <v>18289</v>
+        <v>11779</v>
       </c>
       <c r="G144" t="n">
         <v>0</v>
@@ -4483,7 +4483,7 @@
         <v>4</v>
       </c>
       <c r="F145" t="n">
-        <v>1164</v>
+        <v>1041</v>
       </c>
       <c r="G145" t="n">
         <v>0</v>
@@ -4511,7 +4511,7 @@
         <v>0</v>
       </c>
       <c r="F146" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G146" t="n">
         <v>0</v>
@@ -4539,7 +4539,7 @@
         <v>1</v>
       </c>
       <c r="F147" t="n">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="G147" t="n">
         <v>0</v>
@@ -4595,7 +4595,7 @@
         <v>1</v>
       </c>
       <c r="F149" t="n">
-        <v>911</v>
+        <v>895</v>
       </c>
       <c r="G149" t="n">
         <v>0</v>
@@ -4651,7 +4651,7 @@
         <v>0</v>
       </c>
       <c r="F151" t="n">
-        <v>545</v>
+        <v>542</v>
       </c>
       <c r="G151" t="n">
         <v>0</v>
@@ -4679,7 +4679,7 @@
         <v>0</v>
       </c>
       <c r="F152" t="n">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="G152" t="n">
         <v>0</v>
@@ -4707,7 +4707,7 @@
         <v>2</v>
       </c>
       <c r="F153" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G153" t="n">
         <v>1380</v>
@@ -4735,7 +4735,7 @@
         <v>0</v>
       </c>
       <c r="F154" t="n">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="G154" t="n">
         <v>0</v>
@@ -4763,7 +4763,7 @@
         <v>0</v>
       </c>
       <c r="F155" t="n">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="G155" t="n">
         <v>0</v>
@@ -4847,7 +4847,7 @@
         <v>1</v>
       </c>
       <c r="F158" t="n">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="G158" t="n">
         <v>0</v>
@@ -4875,7 +4875,7 @@
         <v>0</v>
       </c>
       <c r="F159" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G159" t="n">
         <v>0</v>
@@ -4903,7 +4903,7 @@
         <v>2</v>
       </c>
       <c r="F160" t="n">
-        <v>405</v>
+        <v>394</v>
       </c>
       <c r="G160" t="n">
         <v>0</v>
@@ -4931,7 +4931,7 @@
         <v>1</v>
       </c>
       <c r="F161" t="n">
-        <v>304</v>
+        <v>299</v>
       </c>
       <c r="G161" t="n">
         <v>0</v>
@@ -4987,7 +4987,7 @@
         <v>1</v>
       </c>
       <c r="F163" t="n">
-        <v>629</v>
+        <v>614</v>
       </c>
       <c r="G163" t="n">
         <v>0</v>
@@ -5015,7 +5015,7 @@
         <v>1</v>
       </c>
       <c r="F164" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G164" t="n">
         <v>0</v>
@@ -5043,7 +5043,7 @@
         <v>0</v>
       </c>
       <c r="F165" t="n">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="G165" t="n">
         <v>0</v>
@@ -5071,7 +5071,7 @@
         <v>1</v>
       </c>
       <c r="F166" t="n">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="G166" t="n">
         <v>0</v>
@@ -5099,7 +5099,7 @@
         <v>17</v>
       </c>
       <c r="F167" t="n">
-        <v>1286</v>
+        <v>1214</v>
       </c>
       <c r="G167" t="n">
         <v>0</v>
@@ -5351,7 +5351,7 @@
         <v>0</v>
       </c>
       <c r="F176" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="G176" t="n">
         <v>0</v>
@@ -5407,7 +5407,7 @@
         <v>0</v>
       </c>
       <c r="F178" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G178" t="n">
         <v>0</v>
@@ -5438,10 +5438,10 @@
         <v>29</v>
       </c>
       <c r="G179" t="n">
-        <v>0</v>
+        <v>1651.69</v>
       </c>
       <c r="H179" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="180">
@@ -5519,7 +5519,7 @@
         <v>0</v>
       </c>
       <c r="F182" t="n">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="G182" t="n">
         <v>0</v>
@@ -5547,7 +5547,7 @@
         <v>0</v>
       </c>
       <c r="F183" t="n">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G183" t="n">
         <v>0</v>
@@ -5911,7 +5911,7 @@
         <v>0</v>
       </c>
       <c r="F196" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G196" t="n">
         <v>0</v>
@@ -6051,7 +6051,7 @@
         <v>50</v>
       </c>
       <c r="F201" t="n">
-        <v>9859</v>
+        <v>9806</v>
       </c>
       <c r="G201" t="n">
         <v>0</v>
@@ -6135,7 +6135,7 @@
         <v>2</v>
       </c>
       <c r="F204" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G204" t="n">
         <v>0</v>
@@ -6163,7 +6163,7 @@
         <v>3</v>
       </c>
       <c r="F205" t="n">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G205" t="n">
         <v>0</v>
@@ -6219,7 +6219,7 @@
         <v>17</v>
       </c>
       <c r="F207" t="n">
-        <v>2289</v>
+        <v>2269</v>
       </c>
       <c r="G207" t="n">
         <v>0</v>
@@ -6247,7 +6247,7 @@
         <v>17</v>
       </c>
       <c r="F208" t="n">
-        <v>888</v>
+        <v>725</v>
       </c>
       <c r="G208" t="n">
         <v>0</v>
@@ -6303,7 +6303,7 @@
         <v>76</v>
       </c>
       <c r="F210" t="n">
-        <v>9838</v>
+        <v>9490</v>
       </c>
       <c r="G210" t="n">
         <v>3557.62</v>
@@ -6387,7 +6387,7 @@
         <v>42</v>
       </c>
       <c r="F213" t="n">
-        <v>4059</v>
+        <v>4039</v>
       </c>
       <c r="G213" t="n">
         <v>0</v>
@@ -6415,7 +6415,7 @@
         <v>25</v>
       </c>
       <c r="F214" t="n">
-        <v>8116</v>
+        <v>8089</v>
       </c>
       <c r="G214" t="n">
         <v>0</v>
@@ -6443,7 +6443,7 @@
         <v>17</v>
       </c>
       <c r="F215" t="n">
-        <v>1961</v>
+        <v>1958</v>
       </c>
       <c r="G215" t="n">
         <v>0</v>
@@ -6499,7 +6499,7 @@
         <v>41</v>
       </c>
       <c r="F217" t="n">
-        <v>16156</v>
+        <v>16131</v>
       </c>
       <c r="G217" t="n">
         <v>0</v>
@@ -6527,7 +6527,7 @@
         <v>19</v>
       </c>
       <c r="F218" t="n">
-        <v>5554</v>
+        <v>5544</v>
       </c>
       <c r="G218" t="n">
         <v>0</v>
@@ -6555,7 +6555,7 @@
         <v>16</v>
       </c>
       <c r="F219" t="n">
-        <v>8704</v>
+        <v>8652</v>
       </c>
       <c r="G219" t="n">
         <v>0</v>
@@ -6583,7 +6583,7 @@
         <v>128</v>
       </c>
       <c r="F220" t="n">
-        <v>11228</v>
+        <v>10918</v>
       </c>
       <c r="G220" t="n">
         <v>0</v>
@@ -6611,7 +6611,7 @@
         <v>8</v>
       </c>
       <c r="F221" t="n">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="G221" t="n">
         <v>0</v>
@@ -6639,7 +6639,7 @@
         <v>33</v>
       </c>
       <c r="F222" t="n">
-        <v>10213</v>
+        <v>10178</v>
       </c>
       <c r="G222" t="n">
         <v>0</v>
@@ -6661,13 +6661,13 @@
         </is>
       </c>
       <c r="D223" t="n">
-        <v>1481.95</v>
+        <v>1498.75</v>
       </c>
       <c r="E223" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F223" t="n">
-        <v>21825</v>
+        <v>21637</v>
       </c>
       <c r="G223" t="n">
         <v>4066.1</v>
@@ -6695,7 +6695,7 @@
         <v>56</v>
       </c>
       <c r="F224" t="n">
-        <v>12334</v>
+        <v>12307</v>
       </c>
       <c r="G224" t="n">
         <v>4066.1</v>
@@ -6751,7 +6751,7 @@
         <v>1</v>
       </c>
       <c r="F226" t="n">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="G226" t="n">
         <v>0</v>
@@ -6779,13 +6779,13 @@
         <v>5</v>
       </c>
       <c r="F227" t="n">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="G227" t="n">
         <v>1008.57</v>
       </c>
       <c r="H227" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="228">
@@ -6807,7 +6807,7 @@
         <v>40</v>
       </c>
       <c r="F228" t="n">
-        <v>9809</v>
+        <v>9758</v>
       </c>
       <c r="G228" t="n">
         <v>5083.9</v>
@@ -6835,7 +6835,7 @@
         <v>0</v>
       </c>
       <c r="F229" t="n">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="G229" t="n">
         <v>0</v>
@@ -6863,7 +6863,7 @@
         <v>1</v>
       </c>
       <c r="F230" t="n">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="G230" t="n">
         <v>0</v>
@@ -6891,7 +6891,7 @@
         <v>32</v>
       </c>
       <c r="F231" t="n">
-        <v>4775</v>
+        <v>4746</v>
       </c>
       <c r="G231" t="n">
         <v>0</v>
@@ -6947,7 +6947,7 @@
         <v>12</v>
       </c>
       <c r="F233" t="n">
-        <v>2013</v>
+        <v>1972</v>
       </c>
       <c r="G233" t="n">
         <v>0</v>
@@ -6975,7 +6975,7 @@
         <v>24</v>
       </c>
       <c r="F234" t="n">
-        <v>2512</v>
+        <v>2501</v>
       </c>
       <c r="G234" t="n">
         <v>0</v>
@@ -7031,7 +7031,7 @@
         <v>36</v>
       </c>
       <c r="F236" t="n">
-        <v>6702</v>
+        <v>6670</v>
       </c>
       <c r="G236" t="n">
         <v>0</v>
@@ -7059,7 +7059,7 @@
         <v>4</v>
       </c>
       <c r="F237" t="n">
-        <v>1017</v>
+        <v>1015</v>
       </c>
       <c r="G237" t="n">
         <v>0</v>
@@ -7087,7 +7087,7 @@
         <v>20</v>
       </c>
       <c r="F238" t="n">
-        <v>1350</v>
+        <v>1342</v>
       </c>
       <c r="G238" t="n">
         <v>0</v>
@@ -7115,7 +7115,7 @@
         <v>33</v>
       </c>
       <c r="F239" t="n">
-        <v>4596</v>
+        <v>4594</v>
       </c>
       <c r="G239" t="n">
         <v>0</v>
@@ -7143,7 +7143,7 @@
         <v>14</v>
       </c>
       <c r="F240" t="n">
-        <v>1393</v>
+        <v>1386</v>
       </c>
       <c r="G240" t="n">
         <v>0</v>
@@ -7163,7 +7163,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:H55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7212,12 +7212,12 @@
       <c r="A2" t="inlineStr"/>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Nex_HnK_SD_GS-02_B0CDPMX152_PRM_30</t>
+          <t>Nex_HPC_SD_CFM-03_B0FPGDVVCX_VRM_14_30</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>B0CDPMX152</t>
+          <t>B0DM6BB3VT</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -7240,12 +7240,12 @@
       <c r="A3" t="inlineStr"/>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Nexlev -B0DNJS23HS- Steam Cleaner-SD-PT</t>
+          <t>Nex_HPC_SD_CFM-03_B0FPGDVVCX_VRM_14_30</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0FPGDVVCX</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -7255,7 +7255,7 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>1082</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -7268,12 +7268,12 @@
       <c r="A4" t="inlineStr"/>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Nexlev -B0DVC7VJP1-  Stand Mixer -SD-Audience</t>
+          <t>Nex_HPC_SD_CM-02_B0DFCDZWND_VRM_7_14</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>B0DVC7VJP1</t>
+          <t>B0DFCDKMWR</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -7296,12 +7296,12 @@
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Nexlev-SD-Steam Cleaner- Defensive</t>
+          <t>Nex_HPC_SD_CM-02_B0DFCDZWND_VRM_7_14</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0DFCDZWND</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -7311,7 +7311,7 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -7324,12 +7324,12 @@
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Nexlev-SD-Steam Cleaner- Defensive</t>
+          <t>Nex_HPC_SD_CT_V-02_IM_Styling Audience</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0DT6Y7KJM</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -7339,7 +7339,7 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>171</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -7352,12 +7352,12 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Nexlev-SD-Vaccum Cleaner- Defensive01</t>
+          <t>Nex_HPC_SD_ET-01/ET-02/ETC-07_PRM_30</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0CS69T7HF</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -7367,7 +7367,7 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>196</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -7380,22 +7380,22 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Nexlev-SD-Vaccum Cleaner- Defensive01</t>
+          <t>Nex_HPC_SD_ET-01/ET-02/ETC-07_PRM_30</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>B0DCK7ZH5P</t>
+          <t>B0CSG2JZ19</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>11.38</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>185</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -7408,27 +7408,1315 @@
       <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
+          <t>Nex_HPC_SD_ET-01/ET-02/ETC-07_PRM_30</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>B0D25LNDSY</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr"/>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Nex_HPC_SD_ET-01/ET-02/ETC-07_PRM_30</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>B0D2P5TGWK</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr"/>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Nex_HPC_SD_ET-01/ET-02/ETC-07_PRM_30</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>B0D2P6KF4N</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr"/>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Nex_HPC_SD_ET-01/ET-02/ETC-07_PRM_30</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>B0D2P7WLJB</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr"/>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Nex_HPC_SD_ET-01/ET-02/ETC-07_PRM_30</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>B0D9KCNVNM</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr"/>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Nex_HPC_SD_ET-01/ET-02/ETC-07_PRM_30</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>B0FJ1ZB4G9</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr"/>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Nex_HPC_SD_ET-01/ET-02/ETC-07_PRM_30</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>B0FJG5PFGQ</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr"/>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Nex_HPC_SD_FS-01_B0D9KFZYG8_VRM_14</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>B0D9KFZYG8</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr"/>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Nex_HPC_SD_LE-02_B0DCGHKRXX_VRM_14</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>B0DCGHKRXX</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr"/>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Nex_HPC_SD_V-03_Comp_PT_B0DQCWRG3H</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>B0DQCWRG3H</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr"/>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Nex_HPC_Toothbrush_SD_CT_AI Image</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>B0D2P5TGWK</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr"/>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Nex_HPC_Toothbrush_SD_CT_AI Image</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>B0D2P7WLJB</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr"/>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Nex_HPC_Toothbrush_SD_CT_AI Image</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>B0D9KCNVNM</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr"/>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Nex_HPC_Toothbrush_SD_CT_AI Image</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>B0FJ1ZB4G9</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr"/>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Nex_HPC_Toothbrush_SD_CT_AI Image</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>B0FJG5PFGQ</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr"/>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Nex_HnK_SD_AP-03_B0DVC58QPZ_VRM_14</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>B0DVC58QPZ</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr"/>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Nex_HnK_SD_Comp_PT_AP-03_B0DVC58QPZ</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>B0DVC58QPZ</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr"/>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Nex_HnK_SD_Comp_PT_GS-02_B0CDPMX152</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>B0CDPMX152</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr"/>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Nex_HnK_SD_Comp_PT_GS-05_B0D383WQPB</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>B0D383WQPB</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr"/>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Nex_HnK_SD_Comp_PT_SC-01_B0CDPP45BM</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>B0CDPP45BM</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr"/>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Nex_HnK_SD_Comp_PT_SC-05_B0F43P6D23</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>B0F43P6D23</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr"/>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Nex_HnK_SD_GS-02_B0CDPMX152_PRM_30</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>B0CDPMX152</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr"/>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Nex_HnK_SD_GS-02_B0CDPMX152_PRM_30</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>B0D383WQPB</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr"/>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Nex_HnK_SD_GS-02_B0CDPMX152_PRM_30_60_90</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>B0DVC58QPZ</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr"/>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Nex_HnK_SD_GS-02_B0CDPMX152_VRM_14</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>B0CDPMX152</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr"/>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Nex_HnK_SD_KE-03_B0FJ8SFNRH_VRM_14</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>B0FJ8SFNRH</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr"/>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Nex_HnK_SD_MR-01/02_B0CYSLCRQS_B0DCK7ZH5P_VRM_14</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>B0CYSLCRQS</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr"/>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Nex_HnK_SD_MR-01/02_B0CYSLCRQS_B0DCK7ZH5P_VRM_14</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>B0DCK7ZH5P</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr"/>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Nex_HnK_SD_SC-01/SC-04/SC-05_VRM_7_14</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>B0CDPP45BM</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr"/>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Nex_HnK_SD_SC-01/SC-04/SC-05_VRM_7_14</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>B0DNJS23HS</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr"/>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Nex_HnK_SD_SC-01/SC-04/SC-05_VRM_7_14</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>B0F43P6D23</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr"/>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Nex_HnK_SD_SC-04_B0DNJS23HS_VRM_7_14</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>B0DNJS23HS</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr"/>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Nex_HnK_SD_SC-05_B0F43P6D23_VRM_7_14_30</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>B0F43P6D23</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>0</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr"/>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Nex_Hnk_SD_Comp_PT_ST-01_B0DVC7VJP1</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>B0DVC7VJP1</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>0</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" t="n">
+        <v>0</v>
+      </c>
+      <c r="G42" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr"/>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Nexlev -B0DNJS23HS- Steam Cleaner-SD-PT</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>B0DNJS23HS</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>0</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" t="n">
+        <v>1082</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr"/>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Nexlev -B0DVC7VJP1-  Stand Mixer -SD-Audience</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>B0DVC7VJP1</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0</v>
+      </c>
+      <c r="G44" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr"/>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Nexlev-B0DQCWRG3H-Hot Air Brush-SD-Audience</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>B0DQCWRG3H</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>0</v>
+      </c>
+      <c r="E45" t="n">
+        <v>0</v>
+      </c>
+      <c r="F45" t="n">
+        <v>0</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr"/>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Nexlev-Catch All-Garment Steamer-SD-Audience</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>B0CDPMX152</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>0</v>
+      </c>
+      <c r="E46" t="n">
+        <v>0</v>
+      </c>
+      <c r="F46" t="n">
+        <v>0</v>
+      </c>
+      <c r="G46" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr"/>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Nexlev-Catch All-Garment Steamer-SD-Audience</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>B0D383WQPB</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>0</v>
+      </c>
+      <c r="E47" t="n">
+        <v>0</v>
+      </c>
+      <c r="F47" t="n">
+        <v>0</v>
+      </c>
+      <c r="G47" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr"/>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Nexlev-Catch All-Vacuum Cleaner-SD-PT</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>B0CYSLCRQS</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>0</v>
+      </c>
+      <c r="E48" t="n">
+        <v>0</v>
+      </c>
+      <c r="F48" t="n">
+        <v>0</v>
+      </c>
+      <c r="G48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr"/>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Nexlev-Catch All-Vacuum Cleaner-SD-PT</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>B0DCK7ZH5P</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>0</v>
+      </c>
+      <c r="E49" t="n">
+        <v>0</v>
+      </c>
+      <c r="F49" t="n">
+        <v>0</v>
+      </c>
+      <c r="G49" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr"/>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Nexlev-SD-Steam Cleaner- Defensive</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>B0CDPP45BM</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>0</v>
+      </c>
+      <c r="E50" t="n">
+        <v>0</v>
+      </c>
+      <c r="F50" t="n">
+        <v>0</v>
+      </c>
+      <c r="G50" t="n">
+        <v>0</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr"/>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Nexlev-SD-Steam Cleaner- Defensive</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>B0DNJS23HS</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>0</v>
+      </c>
+      <c r="E51" t="n">
+        <v>0</v>
+      </c>
+      <c r="F51" t="n">
+        <v>46</v>
+      </c>
+      <c r="G51" t="n">
+        <v>0</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr"/>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Nexlev-SD-Steam Cleaner- Defensive</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>B0F43P6D23</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>0</v>
+      </c>
+      <c r="E52" t="n">
+        <v>0</v>
+      </c>
+      <c r="F52" t="n">
+        <v>171</v>
+      </c>
+      <c r="G52" t="n">
+        <v>0</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr"/>
+      <c r="B53" t="inlineStr">
+        <is>
           <t>Nexlev-SD-Vaccum Cleaner- Defensive01</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>B0CYSLCRQS</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>0</v>
+      </c>
+      <c r="E53" t="n">
+        <v>0</v>
+      </c>
+      <c r="F53" t="n">
+        <v>196</v>
+      </c>
+      <c r="G53" t="n">
+        <v>0</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr"/>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Nexlev-SD-Vaccum Cleaner- Defensive01</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>B0DCK7ZH5P</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>11.38</v>
+      </c>
+      <c r="E54" t="n">
+        <v>1</v>
+      </c>
+      <c r="F54" t="n">
+        <v>185</v>
+      </c>
+      <c r="G54" t="n">
+        <v>0</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr"/>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Nexlev-SD-Vaccum Cleaner- Defensive01</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
         <is>
           <t>B0FS6TB7CP</t>
         </is>
       </c>
-      <c r="D9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="n">
+      <c r="D55" t="n">
+        <v>0</v>
+      </c>
+      <c r="E55" t="n">
+        <v>0</v>
+      </c>
+      <c r="F55" t="n">
         <v>4</v>
       </c>
-      <c r="G9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" t="n">
+      <c r="G55" t="n">
+        <v>0</v>
+      </c>
+      <c r="H55" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7506,7 +8794,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1952</v>
+        <v>1948</v>
       </c>
       <c r="E2" t="n">
         <v>18</v>
@@ -7539,7 +8827,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1952</v>
+        <v>1948</v>
       </c>
       <c r="E3" t="n">
         <v>18</v>
@@ -7572,7 +8860,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1952</v>
+        <v>1948</v>
       </c>
       <c r="E4" t="n">
         <v>18</v>
@@ -7605,7 +8893,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1358</v>
+        <v>1352</v>
       </c>
       <c r="E5" t="n">
         <v>50</v>
@@ -7638,7 +8926,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1358</v>
+        <v>1352</v>
       </c>
       <c r="E6" t="n">
         <v>50</v>
@@ -7671,7 +8959,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2230</v>
+        <v>2205</v>
       </c>
       <c r="E7" t="n">
         <v>12</v>
@@ -7704,7 +8992,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>2230</v>
+        <v>2205</v>
       </c>
       <c r="E8" t="n">
         <v>12</v>
@@ -7737,7 +9025,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2230</v>
+        <v>2205</v>
       </c>
       <c r="E9" t="n">
         <v>12</v>
@@ -7770,7 +9058,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1532</v>
+        <v>1519</v>
       </c>
       <c r="E10" t="n">
         <v>17</v>
@@ -7803,7 +9091,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>3483</v>
+        <v>3454</v>
       </c>
       <c r="E11" t="n">
         <v>38</v>
@@ -7836,7 +9124,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>886</v>
+        <v>881</v>
       </c>
       <c r="E12" t="n">
         <v>6</v>
@@ -7869,7 +9157,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>886</v>
+        <v>881</v>
       </c>
       <c r="E13" t="n">
         <v>6</v>
@@ -7902,7 +9190,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>886</v>
+        <v>881</v>
       </c>
       <c r="E14" t="n">
         <v>6</v>
@@ -7968,7 +9256,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>4547</v>
+        <v>4528</v>
       </c>
       <c r="E16" t="n">
         <v>58</v>
@@ -8232,7 +9520,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E24" t="n">
         <v>2</v>
@@ -8265,7 +9553,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E25" t="n">
         <v>2</v>
@@ -8298,7 +9586,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E26" t="n">
         <v>2</v>
@@ -8331,7 +9619,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>880</v>
+        <v>875</v>
       </c>
       <c r="E27" t="n">
         <v>5</v>
@@ -8364,7 +9652,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>880</v>
+        <v>875</v>
       </c>
       <c r="E28" t="n">
         <v>5</v>
@@ -8397,7 +9685,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>880</v>
+        <v>875</v>
       </c>
       <c r="E29" t="n">
         <v>5</v>
@@ -8430,7 +9718,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="E30" t="n">
         <v>14</v>
@@ -8463,7 +9751,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="E31" t="n">
         <v>14</v>
@@ -8496,7 +9784,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="E32" t="n">
         <v>14</v>
@@ -8595,7 +9883,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>1668</v>
+        <v>1666</v>
       </c>
       <c r="E35" t="n">
         <v>82</v>
@@ -8628,7 +9916,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="E36" t="n">
         <v>46</v>

--- a/data/ams_weekly_data/Nexlev/ads_report_week23.xlsx
+++ b/data/ams_weekly_data/Nexlev/ads_report_week23.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H240"/>
+  <dimension ref="A1:H293"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -464,22 +464,22 @@
       <c r="A2" t="inlineStr"/>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Campaign - 20/5/2026 16:32:01.948</t>
+          <t>Nex_HnK_SP_KT_SC-04_B0DNJS23HS_HV_Exact</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>B0GKNGWLJ2</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>625.36</v>
+        <v>833.6299999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>55</v>
+        <v>31</v>
       </c>
       <c r="F2" t="n">
-        <v>29828</v>
+        <v>5773</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -492,22 +492,22 @@
       <c r="A3" t="inlineStr"/>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Nex_HnK_SP_KT_SC-04_B0DNJS23HS_HV_Exact</t>
+          <t>Nexlev - B0CDPP45BM - Exact/BM</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0CDPP45BM</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>512.92</v>
+        <v>6.03</v>
       </c>
       <c r="E3" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>4146</v>
+        <v>353</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -520,7 +520,7 @@
       <c r="A4" t="inlineStr"/>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Nexlev - B0CDPP45BM - Exact/BM</t>
+          <t>Nexlev - B0CDPP45BM - Steam Cleaner - CT</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -529,13 +529,13 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>6.03</v>
+        <v>446.45</v>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="F4" t="n">
-        <v>344</v>
+        <v>861</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -548,7 +548,7 @@
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Nexlev - B0CDPP45BM - Steam Cleaner - CT</t>
+          <t>Nexlev - B0CDPP45BM - Steam Cleaner - PT</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -557,13 +557,13 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>282.91</v>
+        <v>107.42</v>
       </c>
       <c r="E5" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F5" t="n">
-        <v>596</v>
+        <v>273</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -576,7 +576,7 @@
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Nexlev - B0CDPP45BM - Steam Cleaner - PT</t>
+          <t>Nexlev - B0CDPP45BM - Steam Cleaner - PT 2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -585,13 +585,13 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>58.67</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>171</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -604,22 +604,22 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Nexlev - B0CDPP45BM - Steam Cleaner - PT 2</t>
+          <t>Nexlev - B0D383WQPB - Garment Steamer - PT</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>B0CDPP45BM</t>
+          <t>B0D383WQPB</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>914.0799999999999</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>4828</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -632,22 +632,22 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Nexlev - B0D383WQPB - Garment Steamer - PT</t>
+          <t>Nexlev - B0D81DLSFT - Blow Dryer - BM 2</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>B0D383WQPB</t>
+          <t>B0D81DLSFT</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>195.25</v>
+        <v>311.98</v>
       </c>
       <c r="E8" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="F8" t="n">
-        <v>2373</v>
+        <v>4183</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -660,50 +660,50 @@
       <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Nexlev - B0D81DLSFT - Blow Dryer - BM 2</t>
+          <t>Nexlev - B0DCGHKRXX - Therapy Comb - SP - AT</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>B0D81DLSFT</t>
+          <t>B0DCGHKRXX</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>135.64</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>1463</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>846.61</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Nexlev - B0DCGHKRXX - Therapy Comb - SP - AT</t>
+          <t>Nexlev - B0DCK4DR1B - Skin Lift Device - Auto</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>B0DCGHKRXX</t>
+          <t>B0DCK4DR1B</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>158.73</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>3498</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -716,22 +716,22 @@
       <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Nexlev - B0DCK4DR1B - Skin Lift Device - Auto</t>
+          <t>Nexlev - B0DCK7ZH5P - Carpet &amp; Car Seat Vacuum Cleaner - KT - Broad1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>B0DCK4DR1B</t>
+          <t>B0DCK7ZH5P</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>44.95</v>
+        <v>1740.08</v>
       </c>
       <c r="E11" t="n">
-        <v>4</v>
+        <v>126</v>
       </c>
       <c r="F11" t="n">
-        <v>1146</v>
+        <v>10415</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -744,7 +744,7 @@
       <c r="A12" t="inlineStr"/>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Nexlev - B0DCK7ZH5P - Carpet &amp; Car Seat Vacuum Cleaner - KT - Broad1</t>
+          <t>Nexlev - B0DCK7ZH5P - Sofa Cleaning Machine - Auto</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -753,13 +753,13 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>473.75</v>
+        <v>997.3099999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>38</v>
+        <v>114</v>
       </c>
       <c r="F12" t="n">
-        <v>4028</v>
+        <v>8086</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -772,7 +772,7 @@
       <c r="A13" t="inlineStr"/>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Nexlev - B0DCK7ZH5P - Sofa Cleaning Machine - Auto</t>
+          <t>Nexlev - B0DCK7ZH5P - Sofa Cleaning Machine - PT</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -781,13 +781,13 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>484.83</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>2935</v>
+        <v>0</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -800,7 +800,7 @@
       <c r="A14" t="inlineStr"/>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Nexlev - B0DCK7ZH5P - Sofa Cleaning Machine - PT</t>
+          <t>Nexlev - B0DCK7ZH5P - Sofa Cleaning Machine - PT 2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -828,7 +828,7 @@
       <c r="A15" t="inlineStr"/>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Nexlev - B0DCK7ZH5P - Sofa Cleaning Machine - PT 2</t>
+          <t>Nexlev - B0DCK7ZH5P - Sofa Cleaning Machine- Exact</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -856,7 +856,7 @@
       <c r="A16" t="inlineStr"/>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Nexlev - B0DCK7ZH5P - Sofa Cleaning Machine- Exact</t>
+          <t>Nexlev - B0DCK7ZH5P - Sofa Cleaning Machine- PT/CT</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -884,7 +884,7 @@
       <c r="A17" t="inlineStr"/>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Nexlev - B0DCK7ZH5P - Sofa Cleaning Machine- PT/CT</t>
+          <t>Nexlev - B0DCK7ZH5P- Sofa Cleaning Machine - Auto</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -893,13 +893,13 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>584.65</v>
       </c>
       <c r="E17" t="n">
-        <v>0</v>
+        <v>123</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>14872</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -912,22 +912,22 @@
       <c r="A18" t="inlineStr"/>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Nexlev - B0DCK7ZH5P- Sofa Cleaning Machine - Auto</t>
+          <t>Nexlev - B0DDC3GVZW - Cordless Vacuum Cleaner - Phrase</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>B0DCK7ZH5P</t>
+          <t>B0DDC3GVZW</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>94.98999999999999</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>2535</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -940,12 +940,12 @@
       <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Nexlev - B0DM6BB3VT - Calf Massager - SP - KT - Exact</t>
+          <t>Nexlev - B0DKK15YNJ - Oil Applicator Comb - SP - AT</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>B0DM6BB3VT</t>
+          <t>B0DKK15YNJ</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -968,22 +968,22 @@
       <c r="A20" t="inlineStr"/>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Nexlev - B0DNJS23HS - Steam Cleaner - BM</t>
+          <t>Nexlev - B0DM6BB3VT - Calf Massager - SP - KT - Exact</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0DM6BB3VT</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>93.70999999999999</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>1332</v>
+        <v>0</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -996,22 +996,22 @@
       <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Nexlev - B0DVC7VJP1 - Stand Mixer - Broad</t>
+          <t>Nexlev - B0DNJP9T35 - Spin Scrubber- SP - PT</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>B0DVC7VJP1</t>
+          <t>B0DNJP9T35</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>1016.37</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>10878</v>
+        <v>1</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -1024,50 +1024,50 @@
       <c r="A22" t="inlineStr"/>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Nexlev - B0F43P6D23 - Steam Cleaner - CT</t>
+          <t>Nexlev - B0DNJS23HS - Steam Cleaner - BM</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>210.81</v>
+        <v>1747.54</v>
       </c>
       <c r="E22" t="n">
-        <v>12</v>
+        <v>103</v>
       </c>
       <c r="F22" t="n">
-        <v>346</v>
+        <v>8217</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>10167.8</v>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Nexlev - B0F43P6D23 - Steam Cleaner - SP - KT - Exact</t>
+          <t>Nexlev - B0DNJS23HS - Steam Cleaner - CT</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>478.48</v>
+        <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>2571</v>
+        <v>0</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1080,22 +1080,22 @@
       <c r="A24" t="inlineStr"/>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Nexlev - B0FS6TB7CP - Portable Blender - BM</t>
+          <t>Nexlev - B0DNJS23HS - Steam Cleaner - CT - On Other</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>B0FS6TB7CP</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>202.44</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>12824</v>
+        <v>0</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1108,22 +1108,22 @@
       <c r="A25" t="inlineStr"/>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Nexlev - B0FS6TB7CP - Portable Blender - PT</t>
+          <t>Nexlev - B0DNJS23HS - Steam Cleaner - PT</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>B0FS6TB7CP</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>744.08</v>
+        <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>7184</v>
+        <v>0</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -1136,22 +1136,22 @@
       <c r="A26" t="inlineStr"/>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Nexlev - SP- B0GN86G345 -  Car Air Purifier - BM</t>
+          <t>Nexlev - B0DNJS23HS - Steam Cleaner - Phrase/BM</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>B0GN86G345</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>17.44</v>
+        <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>489</v>
+        <v>0</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -1164,50 +1164,50 @@
       <c r="A27" t="inlineStr"/>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Nexlev - SP-B0GN94YDY2 - Stand Mixer with Digital Timer - BM</t>
+          <t>Nexlev - B0DVC7VJP1 - Stand Mixer - Broad</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>B0GN94YDY2</t>
+          <t>B0DVC7VJP1</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>0</v>
+        <v>2535.56</v>
       </c>
       <c r="E27" t="n">
-        <v>0</v>
+        <v>173</v>
       </c>
       <c r="F27" t="n">
-        <v>37</v>
+        <v>23958</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>5083.9</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr"/>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Nexlev -B0CDPP45BM-Steam Cleaner-SP-KT-Exact/Phrase</t>
+          <t>Nexlev - B0DVC7VJP1 - Stand Mixer - CT</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>B0CDPP45BM</t>
+          <t>B0DVC7VJP1</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>6391.89</v>
+        <v>395.18</v>
       </c>
       <c r="E28" t="n">
-        <v>291</v>
+        <v>39</v>
       </c>
       <c r="F28" t="n">
-        <v>20613</v>
+        <v>3691</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -1220,22 +1220,22 @@
       <c r="A29" t="inlineStr"/>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Nexlev -B0CYSLCRQS- Vacuum Cleaner -SP-PT</t>
+          <t>Nexlev - B0DVC7VJP1 - Stand Mixer - PT</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0DVC7VJP1</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>342.41</v>
+        <v>26.67</v>
       </c>
       <c r="E29" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="F29" t="n">
-        <v>1456</v>
+        <v>106</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -1248,12 +1248,12 @@
       <c r="A30" t="inlineStr"/>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Nexlev -B0CYSLCRQS- Vacuum Cleaner-SP-KT-Exact</t>
+          <t>Nexlev - B0DVC7VJP1 - Stand Mixer - PT -SP</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0DVC7VJP1</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1263,7 +1263,7 @@
         <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -1276,22 +1276,22 @@
       <c r="A31" t="inlineStr"/>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Nexlev -B0CYSLCRQS-Vacuum Cleaner-SP-KT-Broad</t>
+          <t>Nexlev - B0F43P6D23 - Steam Cleaner - BM</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>164.45</v>
+        <v>0</v>
       </c>
       <c r="E31" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>484</v>
+        <v>0</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -1304,22 +1304,22 @@
       <c r="A32" t="inlineStr"/>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Nexlev -B0DNJS23HS-Steam Cleaner-SP-PT</t>
+          <t>Nexlev - B0F43P6D23 - Steam Cleaner - CT</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>533.27</v>
+        <v>239.94</v>
       </c>
       <c r="E32" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F32" t="n">
-        <v>446</v>
+        <v>547</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -1332,7 +1332,7 @@
       <c r="A33" t="inlineStr"/>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Nexlev -B0F43P6D23 - Steam Cleaner-SP-KT -Broad</t>
+          <t>Nexlev - B0F43P6D23 - Steam Cleaner - SP - KT - Exact</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1341,13 +1341,13 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>596.23</v>
+        <v>1044.75</v>
       </c>
       <c r="E33" t="n">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="F33" t="n">
-        <v>2556</v>
+        <v>4018</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -1360,78 +1360,78 @@
       <c r="A34" t="inlineStr"/>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Nexlev -B0F43P6D23-Steam Cleaner-SP-PT</t>
+          <t>Nexlev - B0FS6TB7CP - Portable Blender - BM</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0FS6TB7CP</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>287.29</v>
+        <v>1258.55</v>
       </c>
       <c r="E34" t="n">
-        <v>19</v>
+        <v>94</v>
       </c>
       <c r="F34" t="n">
-        <v>586</v>
+        <v>46051</v>
       </c>
       <c r="G34" t="n">
-        <v>2541.53</v>
+        <v>6099.15</v>
       </c>
       <c r="H34" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr"/>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Nexlev -B0GKNGWLJ2- Cordless Spin -SP-KT-Exact</t>
+          <t>Nexlev - B0FS6TB7CP - Portable Blender - PT</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>B0GKNGWLJ2</t>
+          <t>B0FS6TB7CP</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>256.65</v>
+        <v>2362.24</v>
       </c>
       <c r="E35" t="n">
-        <v>20</v>
+        <v>159</v>
       </c>
       <c r="F35" t="n">
-        <v>2936</v>
+        <v>27314</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>10165.25</v>
       </c>
       <c r="H35" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr"/>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Nexlev -Catch All-Tyre Inflator-SP-CT</t>
+          <t>Nexlev - B0FS6TB7CP - Portable Blender - PT(1)</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>B0DJFH6RTL</t>
+          <t>B0FS6TB7CP</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>0</v>
+        <v>10.56</v>
       </c>
       <c r="E36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F36" t="n">
-        <v>0</v>
+        <v>168</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -1444,12 +1444,12 @@
       <c r="A37" t="inlineStr"/>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Nexlev -SP- B0GN8N96R5 - Smart Air Purifier - BM</t>
+          <t>Nexlev - B0FS6TB7CP - Portable Blender - PT(2)</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>B0GN8N96R5</t>
+          <t>B0FS6TB7CP</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1459,7 +1459,7 @@
         <v>0</v>
       </c>
       <c r="F37" t="n">
-        <v>754</v>
+        <v>64</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -1472,50 +1472,50 @@
       <c r="A38" t="inlineStr"/>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Nexlev-B0CDPP45BM- Steam Cleaner-SP-KT-Exact-Branded</t>
+          <t>Nexlev - B0GN8WW6BC - Stand Mixer with Stainless Steel Bowl  - AT</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>B0CDPP45BM</t>
+          <t>B0GN8WW6BC</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>300.49</v>
+        <v>38.67</v>
       </c>
       <c r="E38" t="n">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="F38" t="n">
-        <v>2009</v>
+        <v>371</v>
       </c>
       <c r="G38" t="n">
-        <v>3812.72</v>
+        <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr"/>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Nexlev-B0CYSLCRQS- Vacuum Cleaner -SP -KT-Exact</t>
+          <t>Nexlev - B0GN8WW6BC - Stand Mixer with Stainless Steel Bowl  - PT</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0GN8WW6BC</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>272.97</v>
+        <v>8.99</v>
       </c>
       <c r="E39" t="n">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="F39" t="n">
-        <v>3228</v>
+        <v>211</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -1528,12 +1528,12 @@
       <c r="A40" t="inlineStr"/>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Nexlev-B0CYSLCRQS- Vacuum Cleaner-SP-CT</t>
+          <t>Nexlev - B0GN8WW6BC - Stand Mixer with Stainless Steel Bowl - PT(1)</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0GN8WW6BC</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1543,7 +1543,7 @@
         <v>0</v>
       </c>
       <c r="F40" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -1556,22 +1556,22 @@
       <c r="A41" t="inlineStr"/>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Nexlev-B0CYSLCRQS- Vacuum Cleaner-SP-KT-Phrase/Broad</t>
+          <t>Nexlev - B0GN8WW6BC - Stand Mixer with Stainless Steel Bowl - Phrase</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0GN8WW6BC</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>0</v>
+        <v>22.38</v>
       </c>
       <c r="E41" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F41" t="n">
-        <v>0</v>
+        <v>1413</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -1584,22 +1584,22 @@
       <c r="A42" t="inlineStr"/>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner -SP-KT-Phrase</t>
+          <t>Nexlev - B0GN94YDY2 - Stand Mixer with Digital Timer - AT</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0GN94YDY2</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>294.29</v>
+        <v>3.32</v>
       </c>
       <c r="E42" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="F42" t="n">
-        <v>871</v>
+        <v>292</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -1612,12 +1612,12 @@
       <c r="A43" t="inlineStr"/>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Nexlev-B0D2LHNS9B- Callus Remover -SP-CT</t>
+          <t>Nexlev - B0GN94YDY2 - Stand Mixer with Digital Timer - PT</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>B0D2LHNS9B</t>
+          <t>B0GN94YDY2</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1627,7 +1627,7 @@
         <v>0</v>
       </c>
       <c r="F43" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -1640,22 +1640,22 @@
       <c r="A44" t="inlineStr"/>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Nexlev-B0D672NXC8-Steam Cleaner-SP-KT-Exact/Phrase</t>
+          <t>Nexlev - SP- B0GN86G345 -  Car Air Purifier - BM</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>B0D672NXC8</t>
+          <t>B0GN86G345</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>0</v>
+        <v>39.64</v>
       </c>
       <c r="E44" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F44" t="n">
-        <v>0</v>
+        <v>984</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -1668,78 +1668,78 @@
       <c r="A45" t="inlineStr"/>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Nexlev-B0D67727VG-Oil Applicator-SP-KT-Phrase</t>
+          <t>Nexlev - SP-B0GN94YDY2 - Stand Mixer with Digital Timer - BM</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>B0D67727VG</t>
+          <t>B0GN94YDY2</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>270.73</v>
+        <v>0</v>
       </c>
       <c r="E45" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F45" t="n">
-        <v>2768</v>
+        <v>137</v>
       </c>
       <c r="G45" t="n">
-        <v>1046.67</v>
+        <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr"/>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Nexlev-B0D67727VG-Oil Applicator-SP-PT</t>
+          <t>Nexlev -B0CDPP45BM-Steam Cleaner-SP-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>B0D67727VG</t>
+          <t>B0CDPP45BM</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>0</v>
+        <v>9049.040000000001</v>
       </c>
       <c r="E46" t="n">
-        <v>0</v>
+        <v>424</v>
       </c>
       <c r="F46" t="n">
-        <v>44</v>
+        <v>30950</v>
       </c>
       <c r="G46" t="n">
-        <v>0</v>
+        <v>7625.42</v>
       </c>
       <c r="H46" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr"/>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Nexlev-B0D9KFZYG8- Face Steam-SP-KT-Exact/Phrase</t>
+          <t>Nexlev -B0CYSLCRQS- Vacuum Cleaner -SP-CT</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>B0D9KFZYG8</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>329.26</v>
+        <v>355.17</v>
       </c>
       <c r="E47" t="n">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="F47" t="n">
-        <v>4399</v>
+        <v>1201</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
@@ -1752,50 +1752,50 @@
       <c r="A48" t="inlineStr"/>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Nexlev-B0DCGHVN81-Vacuum Cleaner -Exact</t>
+          <t>Nexlev -B0CYSLCRQS- Vacuum Cleaner -SP-PT</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>B0DCGHVN81</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>199.73</v>
+        <v>1088.35</v>
       </c>
       <c r="E48" t="n">
-        <v>15</v>
+        <v>70</v>
       </c>
       <c r="F48" t="n">
-        <v>1756</v>
+        <v>2935</v>
       </c>
       <c r="G48" t="n">
-        <v>1814.4</v>
+        <v>5083.06</v>
       </c>
       <c r="H48" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr"/>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Nexlev-B0DCK3N2JJ-Hair Straightener--SP-KT-Phrase</t>
+          <t>Nexlev -B0CYSLCRQS- Vacuum Cleaner-SP-KT-Exact</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>B0DCK3N2JJ</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>13.89</v>
+        <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F49" t="n">
-        <v>415</v>
+        <v>0</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -1808,22 +1808,22 @@
       <c r="A50" t="inlineStr"/>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Nexlev-B0DCK3N2JJ-Hair Straightener-SP-PT</t>
+          <t>Nexlev -B0CYSLCRQS-Vacuum Cleaner-SP-KT-Broad</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>B0DCK3N2JJ</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>315.6</v>
+        <v>697.9299999999999</v>
       </c>
       <c r="E50" t="n">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="F50" t="n">
-        <v>2619</v>
+        <v>1523</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
@@ -1836,50 +1836,50 @@
       <c r="A51" t="inlineStr"/>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Nexlev-B0DCK7ZH5P-Vacuum Cleaner-SP-KT-Exact</t>
+          <t>Nexlev -B0DNJS23HS-Steam Cleaner-SP-PT</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>B0DCK7ZH5P</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>884.2</v>
+        <v>1883.91</v>
       </c>
       <c r="E51" t="n">
-        <v>30</v>
+        <v>75</v>
       </c>
       <c r="F51" t="n">
-        <v>11888</v>
+        <v>2073</v>
       </c>
       <c r="G51" t="n">
-        <v>2880.51</v>
+        <v>11099.15</v>
       </c>
       <c r="H51" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr"/>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Nexlev-B0DKK15YNJ- Oil Applicator--SP-KT-Phrase</t>
+          <t>Nexlev -B0F43P6D23 - Steam Cleaner-SP-KT -Broad</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>B0DKK15YNJ</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>0</v>
+        <v>789.15</v>
       </c>
       <c r="E52" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="F52" t="n">
-        <v>0</v>
+        <v>3550</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -1892,25 +1892,25 @@
       <c r="A53" t="inlineStr"/>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Nexlev-B0DKK15YNJ-Oil Applicator-SP-KT-Exact/Phrase</t>
+          <t>Nexlev -B0F43P6D23-Steam Cleaner-SP-PT</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>B0DKK15YNJ</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>164.4</v>
+        <v>432.64</v>
       </c>
       <c r="E53" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="F53" t="n">
-        <v>3762</v>
+        <v>758</v>
       </c>
       <c r="G53" t="n">
-        <v>2380</v>
+        <v>2541.53</v>
       </c>
       <c r="H53" t="n">
         <v>1</v>
@@ -1920,106 +1920,106 @@
       <c r="A54" t="inlineStr"/>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Nexlev-B0DNJS23HS -Steam Cleaner-SP-KT-Branded</t>
+          <t>Nexlev -B0FPGDVVCX- Calf Massager-SP-Auto</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0FPGDVVCX</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>809.47</v>
+        <v>73.36</v>
       </c>
       <c r="E54" t="n">
-        <v>37</v>
+        <v>7</v>
       </c>
       <c r="F54" t="n">
-        <v>8195</v>
+        <v>888</v>
       </c>
       <c r="G54" t="n">
-        <v>5083.9</v>
+        <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr"/>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Nexlev-B0DNJS23HS- Steam Cleaner-SP-KT-Broad</t>
+          <t>Nexlev -B0GKNGWLJ2- Cordless Spin - AT</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0GKNGWLJ2</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>1335.75</v>
+        <v>11.93</v>
       </c>
       <c r="E55" t="n">
-        <v>62</v>
+        <v>4</v>
       </c>
       <c r="F55" t="n">
-        <v>1977</v>
+        <v>267</v>
       </c>
       <c r="G55" t="n">
-        <v>5083.9</v>
+        <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr"/>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Nexlev-B0DNJS23HS-Steam Cleaner-SP-KT -Exact/Phrase</t>
+          <t>Nexlev -B0GKNGWLJ2- Cordless Spin - CT</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0GKNGWLJ2</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>1341.84</v>
+        <v>38.31</v>
       </c>
       <c r="E56" t="n">
-        <v>38</v>
+        <v>5</v>
       </c>
       <c r="F56" t="n">
-        <v>1650</v>
+        <v>1110</v>
       </c>
       <c r="G56" t="n">
-        <v>5185.59</v>
+        <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr"/>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Nexlev-B0DQCWRG3H- Hot Air Brush-SP-KT-Exact</t>
+          <t>Nexlev -B0GKNGWLJ2- Cordless Spin -SP-KT-Exact</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>B0DQCWRG3H</t>
+          <t>B0GKNGWLJ2</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>269.43</v>
+        <v>443.03</v>
       </c>
       <c r="E57" t="n">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="F57" t="n">
-        <v>3602</v>
+        <v>4458</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
@@ -2032,22 +2032,22 @@
       <c r="A58" t="inlineStr"/>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Nexlev-B0DQCWRG3H-Hot Air Brush- SP-KT-Phrase</t>
+          <t>Nexlev -Catch All-Tyre Inflator-SP-CT</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>B0DQCWRG3H</t>
+          <t>B0DJFH6RTL</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>335.85</v>
+        <v>0</v>
       </c>
       <c r="E58" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="F58" t="n">
-        <v>4628</v>
+        <v>0</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
@@ -2060,22 +2060,22 @@
       <c r="A59" t="inlineStr"/>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Nexlev-B0DVC7VJP1- Stand Mixer- SP-Auto</t>
+          <t>Nexlev -SP- B0GN8N96R5 - Smart Air Purifier - BM</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>B0DVC7VJP1</t>
+          <t>B0GN8N96R5</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>759.53</v>
+        <v>0</v>
       </c>
       <c r="E59" t="n">
-        <v>67</v>
+        <v>0</v>
       </c>
       <c r="F59" t="n">
-        <v>30108</v>
+        <v>1251</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
@@ -2088,40 +2088,40 @@
       <c r="A60" t="inlineStr"/>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Nexlev-B0DVC7VJP1-Stand Mixer-SP-KT-Exact/Phrase</t>
+          <t>Nexlev-B0CDPP45BM- Steam Cleaner-SP-KT-Exact-Branded</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>B0DVC7VJP1</t>
+          <t>B0CDPP45BM</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>675.85</v>
+        <v>544.12</v>
       </c>
       <c r="E60" t="n">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="F60" t="n">
-        <v>5855</v>
+        <v>3210</v>
       </c>
       <c r="G60" t="n">
-        <v>15082.2</v>
+        <v>3812.72</v>
       </c>
       <c r="H60" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr"/>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Nexlev-B0DVC7VJP1-Stand Mixer-SP-PT</t>
+          <t>Nexlev-B0CDPP45BM-Steam Cleaner-SP-Auto</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>B0DVC7VJP1</t>
+          <t>B0CDPP45BM</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2144,50 +2144,50 @@
       <c r="A62" t="inlineStr"/>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Nexlev-B0F43P6D23 -Steam Cleaner- SP-KT-Exact</t>
+          <t>Nexlev-B0CYSLCRQS- Vacuum Cleaner -SP -KT-Exact</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>300.12</v>
+        <v>686.0500000000001</v>
       </c>
       <c r="E62" t="n">
-        <v>16</v>
+        <v>67</v>
       </c>
       <c r="F62" t="n">
-        <v>969</v>
+        <v>9079</v>
       </c>
       <c r="G62" t="n">
-        <v>0</v>
+        <v>2965.25</v>
       </c>
       <c r="H62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr"/>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Nexlev-B0F43P6D23-Steam Cleaner -SP-CT</t>
+          <t>Nexlev-B0CYSLCRQS- Vacuum Cleaner-SP-CT</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>13.96</v>
+        <v>0</v>
       </c>
       <c r="E63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F63" t="n">
-        <v>113</v>
+        <v>0</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
@@ -2200,22 +2200,22 @@
       <c r="A64" t="inlineStr"/>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Nexlev-B0F43P6D23-Steam Cleaner-SP-KT-Exact/Phrase</t>
+          <t>Nexlev-B0CYSLCRQS- Vacuum Cleaner-SP-KT-Phrase/Broad</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>1959.31</v>
+        <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>92</v>
+        <v>0</v>
       </c>
       <c r="F64" t="n">
-        <v>17898</v>
+        <v>0</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
@@ -2228,50 +2228,50 @@
       <c r="A65" t="inlineStr"/>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Nexlev-B0FS6TB7CP-Portable Blender -SP-KT-Exact/Phrase</t>
+          <t>Nexlev-B0CYSLCRQS-Sofa Cleaning Machine-SP-CT</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>B0FS6TB7CP</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>691.1799999999999</v>
+        <v>280.06</v>
       </c>
       <c r="E65" t="n">
-        <v>51</v>
+        <v>27</v>
       </c>
       <c r="F65" t="n">
-        <v>28590</v>
+        <v>1019</v>
       </c>
       <c r="G65" t="n">
-        <v>2033.05</v>
+        <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr"/>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Nexlev-B0FS6TB7CP-Portable Blender-SP-Auto</t>
+          <t>Nexlev-B0CYSLCRQS-Sofa Cleaning Machine-SP-CT-Refine</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>B0FS6TB7CP</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>641.15</v>
+        <v>25.96</v>
       </c>
       <c r="E66" t="n">
-        <v>65</v>
+        <v>3</v>
       </c>
       <c r="F66" t="n">
-        <v>18243</v>
+        <v>148</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
@@ -2284,22 +2284,22 @@
       <c r="A67" t="inlineStr"/>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Nexlev-B0GKNGWLJ2-Cordless Spin-SP-KT-Exact</t>
+          <t>Nexlev-B0CYSLCRQS-Sofa Cleaning Machine-SP-PT</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>B0GKNGWLJ2</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>183.23</v>
+        <v>11.53</v>
       </c>
       <c r="E67" t="n">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="F67" t="n">
-        <v>3811</v>
+        <v>71</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -2312,40 +2312,40 @@
       <c r="A68" t="inlineStr"/>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Nexlev-B0GKNGWLJ2-Cordless Spin-SP-KT-Exact/Phrase</t>
+          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner -SP-KT-Phrase</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>B0GKNGWLJ2</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>394.26</v>
+        <v>1011.78</v>
       </c>
       <c r="E68" t="n">
-        <v>28</v>
+        <v>59</v>
       </c>
       <c r="F68" t="n">
-        <v>1538</v>
+        <v>3440</v>
       </c>
       <c r="G68" t="n">
-        <v>0</v>
+        <v>2541.53</v>
       </c>
       <c r="H68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr"/>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Nexlev-B0GKNGWLJ2-Cordless Spin-SP-KT-PT</t>
+          <t>Nexlev-B0D2LHNS9B- Callus Remover -SP-CT</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>B0GKNGWLJ2</t>
+          <t>B0D2LHNS9B</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2368,50 +2368,50 @@
       <c r="A70" t="inlineStr"/>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Nexlev-Branded-All Products</t>
+          <t>Nexlev-B0D672NXC8-Steam Cleaner-SP-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>B0CDQ55W2M</t>
+          <t>B0D672NXC8</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>0</v>
+        <v>867.59</v>
       </c>
       <c r="E70" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="F70" t="n">
+        <v>4061</v>
+      </c>
+      <c r="G70" t="n">
+        <v>6100.85</v>
+      </c>
+      <c r="H70" t="n">
         <v>1</v>
-      </c>
-      <c r="G70" t="n">
-        <v>0</v>
-      </c>
-      <c r="H70" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr"/>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Nexlev-Branded-All Products</t>
+          <t>Nexlev-B0D672NXC8-Steam Cleaner-SP-PT</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>B0CQX9ZZMH</t>
+          <t>B0D672NXC8</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>6.12</v>
+        <v>64.62</v>
       </c>
       <c r="E71" t="n">
         <v>1</v>
       </c>
       <c r="F71" t="n">
-        <v>249</v>
+        <v>40</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
@@ -2424,50 +2424,50 @@
       <c r="A72" t="inlineStr"/>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Nexlev-Branded-All Products</t>
+          <t>Nexlev-B0D67727VG-Oil Applicator-SP-KT-Phrase</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>B0CW1JJP9S</t>
+          <t>B0D67727VG</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>0</v>
+        <v>614.4100000000001</v>
       </c>
       <c r="E72" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="F72" t="n">
-        <v>15</v>
+        <v>8343</v>
       </c>
       <c r="G72" t="n">
-        <v>0</v>
+        <v>1046.67</v>
       </c>
       <c r="H72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr"/>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Nexlev-Branded-All Products</t>
+          <t>Nexlev-B0D67727VG-Oil Applicator-SP-PT</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>B0D25LNDSY</t>
+          <t>B0D67727VG</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>0</v>
+        <v>30.5</v>
       </c>
       <c r="E73" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F73" t="n">
-        <v>24</v>
+        <v>90</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -2480,68 +2480,68 @@
       <c r="A74" t="inlineStr"/>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Nexlev-Branded-All Products</t>
+          <t>Nexlev-B0D9KFZYG8- Face Steam-SP-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>B0D2LD6BYJ</t>
+          <t>B0D9KFZYG8</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>0</v>
+        <v>823.0999999999999</v>
       </c>
       <c r="E74" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="F74" t="n">
-        <v>5</v>
+        <v>12982</v>
       </c>
       <c r="G74" t="n">
-        <v>0</v>
+        <v>2879.66</v>
       </c>
       <c r="H74" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr"/>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Nexlev-Branded-All Products</t>
+          <t>Nexlev-B0DCGHVN81-Vacuum Cleaner -Exact</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>B0D2LFMY48</t>
+          <t>B0DCGHVN81</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>0</v>
+        <v>558.51</v>
       </c>
       <c r="E75" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="F75" t="n">
-        <v>79</v>
+        <v>6879</v>
       </c>
       <c r="G75" t="n">
-        <v>0</v>
+        <v>1814.4</v>
       </c>
       <c r="H75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr"/>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Nexlev-Branded-All Products</t>
+          <t>Nexlev-B0DCGHVN81-Vacuum Cleaner -SP-Auto</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>B0D2LKB4BJ</t>
+          <t>B0DCGHVN81</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -2551,7 +2551,7 @@
         <v>0</v>
       </c>
       <c r="F76" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -2564,22 +2564,22 @@
       <c r="A77" t="inlineStr"/>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Nexlev-Branded-All Products</t>
+          <t>Nexlev-B0DCK3N2JJ-Hair Straightener--SP-KT-Phrase</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>B0D63FKYZ5</t>
+          <t>B0DCK3N2JJ</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>9.49</v>
+        <v>13.89</v>
       </c>
       <c r="E77" t="n">
         <v>2</v>
       </c>
       <c r="F77" t="n">
-        <v>32</v>
+        <v>492</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
@@ -2592,22 +2592,22 @@
       <c r="A78" t="inlineStr"/>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Nexlev-Branded-All Products</t>
+          <t>Nexlev-B0DCK3N2JJ-Hair Straightener-SP-PT</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>B0D81DLSFT</t>
+          <t>B0DCK3N2JJ</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>0</v>
+        <v>618.76</v>
       </c>
       <c r="E78" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="F78" t="n">
-        <v>2</v>
+        <v>2880</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
@@ -2620,12 +2620,12 @@
       <c r="A79" t="inlineStr"/>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Nexlev-Branded-All Products</t>
+          <t>Nexlev-B0DCK7ZH5P-Sofa Cleaning Machine-SP-PT</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>B0D83Q7L8W</t>
+          <t>B0DCK7ZH5P</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -2635,7 +2635,7 @@
         <v>0</v>
       </c>
       <c r="F79" t="n">
-        <v>118</v>
+        <v>19</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
@@ -2648,40 +2648,40 @@
       <c r="A80" t="inlineStr"/>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Nexlev-Branded-All Products</t>
+          <t>Nexlev-B0DCK7ZH5P-Vacuum Cleaner-SP-KT-Exact</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>B0D8445KJN</t>
+          <t>B0DCK7ZH5P</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>12.12</v>
+        <v>2529.64</v>
       </c>
       <c r="E80" t="n">
-        <v>2</v>
+        <v>86</v>
       </c>
       <c r="F80" t="n">
-        <v>427</v>
+        <v>37852</v>
       </c>
       <c r="G80" t="n">
-        <v>0</v>
+        <v>8302.549999999999</v>
       </c>
       <c r="H80" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr"/>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Nexlev-Branded-All Products</t>
+          <t>Nexlev-B0DCK7ZH5P-Vacuum Cleaner-SP-PT</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>B0D86Y2V7V</t>
+          <t>B0DCK7ZH5P</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -2691,7 +2691,7 @@
         <v>0</v>
       </c>
       <c r="F81" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
@@ -2704,22 +2704,22 @@
       <c r="A82" t="inlineStr"/>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Nexlev-Branded-All Products</t>
+          <t>Nexlev-B0DKK15YNJ- Oil Applicator--SP-KT-Phrase</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>B0D86ZC9YT</t>
+          <t>B0DKK15YNJ</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>7.68</v>
+        <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F82" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -2732,78 +2732,78 @@
       <c r="A83" t="inlineStr"/>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Nexlev-Branded-All Products</t>
+          <t>Nexlev-B0DKK15YNJ-Oil Applicator-SP-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>B0D9KCNVNM</t>
+          <t>B0DKK15YNJ</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>0</v>
+        <v>520.38</v>
       </c>
       <c r="E83" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="F83" t="n">
-        <v>16</v>
+        <v>9740</v>
       </c>
       <c r="G83" t="n">
-        <v>0</v>
+        <v>11900</v>
       </c>
       <c r="H83" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr"/>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Nexlev-Branded-All Products</t>
+          <t>Nexlev-B0DM6BB3VT-Calf Massager-SP-CT</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>B0D9KFP4MG</t>
+          <t>B0DM6BB3VT</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>29.58</v>
+        <v>0</v>
       </c>
       <c r="E84" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F84" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="G84" t="n">
-        <v>1651.7</v>
+        <v>0</v>
       </c>
       <c r="H84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr"/>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Nexlev-Branded-All Products</t>
+          <t>Nexlev-B0DNJS23HS -Steam Cleaner-SP-AT</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>B0D9KFQG8Q</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>7.7</v>
+        <v>60.73999999999999</v>
       </c>
       <c r="E85" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="F85" t="n">
-        <v>33</v>
+        <v>882</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -2816,106 +2816,106 @@
       <c r="A86" t="inlineStr"/>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Nexlev-Branded-All Products</t>
+          <t>Nexlev-B0DNJS23HS -Steam Cleaner-SP-KT-Branded</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>B0DCK4DR1B</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>0</v>
+        <v>3736.95</v>
       </c>
       <c r="E86" t="n">
-        <v>0</v>
+        <v>163</v>
       </c>
       <c r="F86" t="n">
-        <v>17</v>
+        <v>33859</v>
       </c>
       <c r="G86" t="n">
-        <v>0</v>
+        <v>5083.9</v>
       </c>
       <c r="H86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr"/>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Nexlev-Branded-All Products</t>
+          <t>Nexlev-B0DNJS23HS- Steam Cleaner-SP-KT-Broad</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>B0DFCDKMWR</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>7.62</v>
+        <v>2862.35</v>
       </c>
       <c r="E87" t="n">
-        <v>1</v>
+        <v>146</v>
       </c>
       <c r="F87" t="n">
-        <v>32</v>
+        <v>9574</v>
       </c>
       <c r="G87" t="n">
-        <v>0</v>
+        <v>10167.8</v>
       </c>
       <c r="H87" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr"/>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Nexlev-Branded-All Products</t>
+          <t>Nexlev-B0DNJS23HS-Steam Cleaner-SP-KT -Exact/Phrase</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>B0DFCDZWND</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>0</v>
+        <v>3867.51</v>
       </c>
       <c r="E88" t="n">
-        <v>0</v>
+        <v>144</v>
       </c>
       <c r="F88" t="n">
-        <v>7</v>
+        <v>18739</v>
       </c>
       <c r="G88" t="n">
-        <v>0</v>
+        <v>12811.02</v>
       </c>
       <c r="H88" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr"/>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Nexlev-Branded-All Products</t>
+          <t>Nexlev-B0DNJS23HS-Steam Mop cleaner-SP-PT</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>B0DFCG2VGS</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>7.76</v>
+        <v>12</v>
       </c>
       <c r="E89" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F89" t="n">
-        <v>502</v>
+        <v>20</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -2928,124 +2928,124 @@
       <c r="A90" t="inlineStr"/>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Nexlev-Branded-All Products</t>
+          <t>Nexlev-B0DQCWRG3H- Hot Air Brush-SP-KT-Exact</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>B0DFD123P5</t>
+          <t>B0DQCWRG3H</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>13.7</v>
+        <v>857.28</v>
       </c>
       <c r="E90" t="n">
-        <v>2</v>
+        <v>95</v>
       </c>
       <c r="F90" t="n">
-        <v>328</v>
+        <v>14098</v>
       </c>
       <c r="G90" t="n">
-        <v>0</v>
+        <v>1736.44</v>
       </c>
       <c r="H90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr"/>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Nexlev-Branded-All Products</t>
+          <t>Nexlev-B0DQCWRG3H-Hot Air Brush- SP-KT-Phrase</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>B0DFM4JZV9</t>
+          <t>B0DQCWRG3H</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>0</v>
+        <v>1285.19</v>
       </c>
       <c r="E91" t="n">
-        <v>0</v>
+        <v>124</v>
       </c>
       <c r="F91" t="n">
+        <v>25169</v>
+      </c>
+      <c r="G91" t="n">
+        <v>3472.88</v>
+      </c>
+      <c r="H91" t="n">
         <v>2</v>
-      </c>
-      <c r="G91" t="n">
-        <v>0</v>
-      </c>
-      <c r="H91" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr"/>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Nexlev-Branded-All Products</t>
+          <t>Nexlev-B0DVC7VJP1- Stand Mixer- SP-Auto</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>B0DJFH4K8B</t>
+          <t>B0DVC7VJP1</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>0</v>
+        <v>3483.49</v>
       </c>
       <c r="E92" t="n">
-        <v>0</v>
+        <v>299</v>
       </c>
       <c r="F92" t="n">
-        <v>6</v>
+        <v>153606</v>
       </c>
       <c r="G92" t="n">
-        <v>0</v>
+        <v>10167.8</v>
       </c>
       <c r="H92" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr"/>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Nexlev-Branded-All Products</t>
+          <t>Nexlev-B0DVC7VJP1-Stand Mixer-SP-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>B0DJFH6RTL</t>
+          <t>B0DVC7VJP1</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>0</v>
+        <v>1567.32</v>
       </c>
       <c r="E93" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="F93" t="n">
-        <v>2</v>
+        <v>15981</v>
       </c>
       <c r="G93" t="n">
-        <v>0</v>
+        <v>25080.51</v>
       </c>
       <c r="H93" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr"/>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Nexlev-Branded-All Products</t>
+          <t>Nexlev-B0DVC7VJP1-Stand Mixer-SP-PT</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>B0DK9LYT4P</t>
+          <t>B0DVC7VJP1</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3055,7 +3055,7 @@
         <v>0</v>
       </c>
       <c r="F94" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -3068,50 +3068,50 @@
       <c r="A95" t="inlineStr"/>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Nexlev-Branded-All Products</t>
+          <t>Nexlev-B0F43P6D23 -Steam Cleaner- SP-KT-Exact</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>B0DKJSCLBD</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>112.08</v>
+        <v>404.21</v>
       </c>
       <c r="E95" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F95" t="n">
-        <v>941</v>
+        <v>1382</v>
       </c>
       <c r="G95" t="n">
-        <v>0</v>
+        <v>3050</v>
       </c>
       <c r="H95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr"/>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Nexlev-Branded-All Products</t>
+          <t>Nexlev-B0F43P6D23-Steam Cleaner -SP-CT</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>B0DNJF1BLS</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>7.7</v>
+        <v>27.66</v>
       </c>
       <c r="E96" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F96" t="n">
-        <v>984</v>
+        <v>152</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
@@ -3124,106 +3124,106 @@
       <c r="A97" t="inlineStr"/>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Nexlev-Branded-All Products</t>
+          <t>Nexlev-B0F43P6D23-Steam Cleaner-SP-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>B0DNJJKBKG</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>0</v>
+        <v>3090.23</v>
       </c>
       <c r="E97" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="F97" t="n">
-        <v>11</v>
+        <v>27343</v>
       </c>
       <c r="G97" t="n">
-        <v>0</v>
+        <v>3050</v>
       </c>
       <c r="H97" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr"/>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Nexlev-Branded-All Products</t>
+          <t>Nexlev-B0FS6TB7CP-Portable Blender -SP-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>B0DNJP9T35</t>
+          <t>B0FS6TB7CP</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>0</v>
+        <v>2412.39</v>
       </c>
       <c r="E98" t="n">
-        <v>0</v>
+        <v>186</v>
       </c>
       <c r="F98" t="n">
-        <v>2</v>
+        <v>99533</v>
       </c>
       <c r="G98" t="n">
-        <v>0</v>
+        <v>2033.05</v>
       </c>
       <c r="H98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr"/>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Nexlev-Branded-All Products</t>
+          <t>Nexlev-B0FS6TB7CP-Portable Blender-SP-Auto</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>B0DT6Y7KJM</t>
+          <t>B0FS6TB7CP</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>0</v>
+        <v>1643.43</v>
       </c>
       <c r="E99" t="n">
-        <v>0</v>
+        <v>176</v>
       </c>
       <c r="F99" t="n">
-        <v>20</v>
+        <v>47590</v>
       </c>
       <c r="G99" t="n">
-        <v>0</v>
+        <v>2033.06</v>
       </c>
       <c r="H99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr"/>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Nexlev-Branded-All Products</t>
+          <t>Nexlev-B0GGHZWMVW-Vacuum-BM</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>B0DV9CY3XR</t>
+          <t>B0GGHZWMVW</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>0</v>
+        <v>488.17</v>
       </c>
       <c r="E100" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="F100" t="n">
-        <v>13</v>
+        <v>4599</v>
       </c>
       <c r="G100" t="n">
         <v>0</v>
@@ -3236,22 +3236,22 @@
       <c r="A101" t="inlineStr"/>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Nexlev-Branded-All Products</t>
+          <t>Nexlev-B0GGHZWMVW-Vacuum-PT</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>B0DVC58QPZ</t>
+          <t>B0GGHZWMVW</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>9.24</v>
+        <v>0</v>
       </c>
       <c r="E101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F101" t="n">
-        <v>48</v>
+        <v>21</v>
       </c>
       <c r="G101" t="n">
         <v>0</v>
@@ -3264,22 +3264,22 @@
       <c r="A102" t="inlineStr"/>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Nexlev-Branded-All Products</t>
+          <t>Nexlev-B0GKNGWLJ2-Cordless Spin-SP-KT-Exact</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>B0DVC968P1</t>
+          <t>B0GKNGWLJ2</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>0</v>
+        <v>485.44</v>
       </c>
       <c r="E102" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="F102" t="n">
-        <v>1</v>
+        <v>9244</v>
       </c>
       <c r="G102" t="n">
         <v>0</v>
@@ -3292,22 +3292,22 @@
       <c r="A103" t="inlineStr"/>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Nexlev-Branded-All Products</t>
+          <t>Nexlev-B0GKNGWLJ2-Cordless Spin-SP-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>B0DVC9PRSD</t>
+          <t>B0GKNGWLJ2</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>0</v>
+        <v>853.15</v>
       </c>
       <c r="E103" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="F103" t="n">
-        <v>3</v>
+        <v>4727</v>
       </c>
       <c r="G103" t="n">
         <v>0</v>
@@ -3320,12 +3320,12 @@
       <c r="A104" t="inlineStr"/>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Nexlev-Branded-All Products</t>
+          <t>Nexlev-B0GKNGWLJ2-Cordless Spin-SP-KT-PT</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>B0DVSZ2VVJ</t>
+          <t>B0GKNGWLJ2</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -3335,7 +3335,7 @@
         <v>0</v>
       </c>
       <c r="F104" t="n">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
@@ -3353,17 +3353,17 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>B0F29SZCVF</t>
+          <t>B0CDQ55W2M</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>23.92</v>
+        <v>0</v>
       </c>
       <c r="E105" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F105" t="n">
-        <v>40</v>
+        <v>9</v>
       </c>
       <c r="G105" t="n">
         <v>0</v>
@@ -3381,17 +3381,17 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>B0F2MZ8CG9</t>
+          <t>B0CQX9ZZMH</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>7.66</v>
+        <v>29.45</v>
       </c>
       <c r="E106" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F106" t="n">
-        <v>135</v>
+        <v>888</v>
       </c>
       <c r="G106" t="n">
         <v>0</v>
@@ -3409,7 +3409,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>B0F2N11VTN</t>
+          <t>B0CW1JJP9S</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -3419,7 +3419,7 @@
         <v>0</v>
       </c>
       <c r="F107" t="n">
-        <v>1607</v>
+        <v>80</v>
       </c>
       <c r="G107" t="n">
         <v>0</v>
@@ -3437,23 +3437,23 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>B0F2N37819</t>
+          <t>B0D25LNDSY</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>0</v>
+        <v>21.08</v>
       </c>
       <c r="E108" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F108" t="n">
-        <v>13</v>
+        <v>123</v>
       </c>
       <c r="G108" t="n">
-        <v>0</v>
+        <v>1354.24</v>
       </c>
       <c r="H108" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="109">
@@ -3465,17 +3465,17 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>B0F2N4N83Y</t>
+          <t>B0D2LD6BYJ</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="E109" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F109" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="G109" t="n">
         <v>0</v>
@@ -3493,7 +3493,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>B0F678L8YT</t>
+          <t>B0D2LFMY48</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -3503,7 +3503,7 @@
         <v>0</v>
       </c>
       <c r="F110" t="n">
-        <v>17</v>
+        <v>167</v>
       </c>
       <c r="G110" t="n">
         <v>0</v>
@@ -3521,17 +3521,17 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>B0F679QJH4</t>
+          <t>B0D2LKB4BJ</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>0</v>
+        <v>7.69</v>
       </c>
       <c r="E111" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F111" t="n">
-        <v>75</v>
+        <v>173</v>
       </c>
       <c r="G111" t="n">
         <v>0</v>
@@ -3549,17 +3549,17 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>B0F67BSF2R</t>
+          <t>B0D63FKYZ5</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>6.36</v>
+        <v>23.03</v>
       </c>
       <c r="E112" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F112" t="n">
-        <v>1698</v>
+        <v>103</v>
       </c>
       <c r="G112" t="n">
         <v>0</v>
@@ -3577,7 +3577,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>B0F67BW7SF</t>
+          <t>B0D81DLSFT</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -3587,7 +3587,7 @@
         <v>0</v>
       </c>
       <c r="F113" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="G113" t="n">
         <v>0</v>
@@ -3605,17 +3605,17 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>B0FJ1ZB4G9</t>
+          <t>B0D83Q7L8W</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="E114" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F114" t="n">
-        <v>32</v>
+        <v>240</v>
       </c>
       <c r="G114" t="n">
         <v>0</v>
@@ -3633,17 +3633,17 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>B0FJG5PFGQ</t>
+          <t>B0D8445KJN</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>0</v>
+        <v>23.21</v>
       </c>
       <c r="E115" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F115" t="n">
-        <v>41</v>
+        <v>3168</v>
       </c>
       <c r="G115" t="n">
         <v>0</v>
@@ -3661,17 +3661,17 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>B0FMF1D9NV</t>
+          <t>B0D86Y2V7V</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>0</v>
+        <v>7.16</v>
       </c>
       <c r="E116" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F116" t="n">
-        <v>28</v>
+        <v>82</v>
       </c>
       <c r="G116" t="n">
         <v>0</v>
@@ -3689,17 +3689,17 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>B0FS7T8151</t>
+          <t>B0D86ZC9YT</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>0</v>
+        <v>7.68</v>
       </c>
       <c r="E117" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F117" t="n">
-        <v>7</v>
+        <v>38</v>
       </c>
       <c r="G117" t="n">
         <v>0</v>
@@ -3717,17 +3717,17 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>B0FYNKYJFN</t>
+          <t>B0D9KCNVNM</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="E118" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F118" t="n">
-        <v>86</v>
+        <v>53</v>
       </c>
       <c r="G118" t="n">
         <v>0</v>
@@ -3745,45 +3745,45 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>B0GGHZWMVW</t>
+          <t>B0D9KFP4MG</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>27.8</v>
+        <v>43.39</v>
       </c>
       <c r="E119" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F119" t="n">
-        <v>393</v>
+        <v>278</v>
       </c>
       <c r="G119" t="n">
-        <v>0</v>
+        <v>1651.7</v>
       </c>
       <c r="H119" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr"/>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-AT</t>
+          <t>Nexlev-Branded-All Products</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>B0CDQ55W2M</t>
+          <t>B0D9KFQG8Q</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>0</v>
+        <v>15.28</v>
       </c>
       <c r="E120" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F120" t="n">
-        <v>8</v>
+        <v>857</v>
       </c>
       <c r="G120" t="n">
         <v>0</v>
@@ -3796,22 +3796,22 @@
       <c r="A121" t="inlineStr"/>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-AT</t>
+          <t>Nexlev-Branded-All Products</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>B0CQX9ZZMH</t>
+          <t>B0DCK4DR1B</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>0</v>
+        <v>13.92</v>
       </c>
       <c r="E121" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F121" t="n">
-        <v>152</v>
+        <v>76</v>
       </c>
       <c r="G121" t="n">
         <v>0</v>
@@ -3824,22 +3824,22 @@
       <c r="A122" t="inlineStr"/>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-AT</t>
+          <t>Nexlev-Branded-All Products</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>B0CW1JJP9S</t>
+          <t>B0DFCDKMWR</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>0</v>
+        <v>21.27</v>
       </c>
       <c r="E122" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F122" t="n">
-        <v>52</v>
+        <v>89</v>
       </c>
       <c r="G122" t="n">
         <v>0</v>
@@ -3852,50 +3852,50 @@
       <c r="A123" t="inlineStr"/>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-AT</t>
+          <t>Nexlev-Branded-All Products</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>B0D25LNDSY</t>
+          <t>B0DFCDZWND</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>15.27</v>
+        <v>0</v>
       </c>
       <c r="E123" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F123" t="n">
-        <v>364</v>
+        <v>37</v>
       </c>
       <c r="G123" t="n">
-        <v>677.12</v>
+        <v>0</v>
       </c>
       <c r="H123" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr"/>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-AT</t>
+          <t>Nexlev-Branded-All Products</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>B0D2LD6BYJ</t>
+          <t>B0DFCG2VGS</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>4.61</v>
+        <v>27.38</v>
       </c>
       <c r="E124" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F124" t="n">
-        <v>5674</v>
+        <v>1218</v>
       </c>
       <c r="G124" t="n">
         <v>0</v>
@@ -3908,22 +3908,22 @@
       <c r="A125" t="inlineStr"/>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-AT</t>
+          <t>Nexlev-Branded-All Products</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>B0D2LFMY48</t>
+          <t>B0DFD123P5</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>3.67</v>
+        <v>40.97</v>
       </c>
       <c r="E125" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F125" t="n">
-        <v>547</v>
+        <v>905</v>
       </c>
       <c r="G125" t="n">
         <v>0</v>
@@ -3936,22 +3936,22 @@
       <c r="A126" t="inlineStr"/>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-AT</t>
+          <t>Nexlev-Branded-All Products</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>B0D2LKB4BJ</t>
+          <t>B0DFM4JZV9</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>3.19</v>
+        <v>3.13</v>
       </c>
       <c r="E126" t="n">
         <v>1</v>
       </c>
       <c r="F126" t="n">
-        <v>321</v>
+        <v>5</v>
       </c>
       <c r="G126" t="n">
         <v>0</v>
@@ -3964,22 +3964,22 @@
       <c r="A127" t="inlineStr"/>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-AT</t>
+          <t>Nexlev-Branded-All Products</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>B0D63FKYZ5</t>
+          <t>B0DJFH4K8B</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>3.67</v>
+        <v>0</v>
       </c>
       <c r="E127" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F127" t="n">
-        <v>229</v>
+        <v>11</v>
       </c>
       <c r="G127" t="n">
         <v>0</v>
@@ -3992,22 +3992,22 @@
       <c r="A128" t="inlineStr"/>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-AT</t>
+          <t>Nexlev-Branded-All Products</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>B0D81DLSFT</t>
+          <t>B0DJFH6RTL</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="E128" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F128" t="n">
-        <v>243</v>
+        <v>15</v>
       </c>
       <c r="G128" t="n">
         <v>0</v>
@@ -4020,22 +4020,22 @@
       <c r="A129" t="inlineStr"/>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-AT</t>
+          <t>Nexlev-Branded-All Products</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>B0D83Q7L8W</t>
+          <t>B0DK9LYT4P</t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>4.43</v>
+        <v>4.03</v>
       </c>
       <c r="E129" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F129" t="n">
-        <v>249</v>
+        <v>14</v>
       </c>
       <c r="G129" t="n">
         <v>0</v>
@@ -4048,22 +4048,22 @@
       <c r="A130" t="inlineStr"/>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-AT</t>
+          <t>Nexlev-Branded-All Products</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>B0D8445KJN</t>
+          <t>B0DKJSCLBD</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>0</v>
+        <v>257.98</v>
       </c>
       <c r="E130" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="F130" t="n">
-        <v>312</v>
+        <v>6321</v>
       </c>
       <c r="G130" t="n">
         <v>0</v>
@@ -4076,22 +4076,22 @@
       <c r="A131" t="inlineStr"/>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-AT</t>
+          <t>Nexlev-Branded-All Products</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>B0D86Y2V7V</t>
+          <t>B0DNJF1BLS</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>3.57</v>
+        <v>55.32</v>
       </c>
       <c r="E131" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F131" t="n">
-        <v>132</v>
+        <v>2580</v>
       </c>
       <c r="G131" t="n">
         <v>0</v>
@@ -4104,22 +4104,22 @@
       <c r="A132" t="inlineStr"/>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-AT</t>
+          <t>Nexlev-Branded-All Products</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>B0D86ZC9YT</t>
+          <t>B0DNJJKBKG</t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="E132" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F132" t="n">
-        <v>159</v>
+        <v>53</v>
       </c>
       <c r="G132" t="n">
         <v>0</v>
@@ -4132,22 +4132,22 @@
       <c r="A133" t="inlineStr"/>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-AT</t>
+          <t>Nexlev-Branded-All Products</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>B0D9KCNVNM</t>
+          <t>B0DNJP9T35</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>3.67</v>
+        <v>0</v>
       </c>
       <c r="E133" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F133" t="n">
-        <v>156</v>
+        <v>2</v>
       </c>
       <c r="G133" t="n">
         <v>0</v>
@@ -4160,22 +4160,22 @@
       <c r="A134" t="inlineStr"/>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-AT</t>
+          <t>Nexlev-Branded-All Products</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>B0D9KFP4MG</t>
+          <t>B0DT6Y7KJM</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>21.41</v>
+        <v>7.7</v>
       </c>
       <c r="E134" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F134" t="n">
-        <v>1108</v>
+        <v>54</v>
       </c>
       <c r="G134" t="n">
         <v>0</v>
@@ -4188,22 +4188,22 @@
       <c r="A135" t="inlineStr"/>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-AT</t>
+          <t>Nexlev-Branded-All Products</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>B0D9KFQG8Q</t>
+          <t>B0DV9CY3XR</t>
         </is>
       </c>
       <c r="D135" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="E135" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F135" t="n">
-        <v>115</v>
+        <v>40</v>
       </c>
       <c r="G135" t="n">
         <v>0</v>
@@ -4216,22 +4216,22 @@
       <c r="A136" t="inlineStr"/>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-AT</t>
+          <t>Nexlev-Branded-All Products</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>B0DCK4DR1B</t>
+          <t>B0DVC58QPZ</t>
         </is>
       </c>
       <c r="D136" t="n">
-        <v>0</v>
+        <v>28.21</v>
       </c>
       <c r="E136" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F136" t="n">
-        <v>41</v>
+        <v>165</v>
       </c>
       <c r="G136" t="n">
         <v>0</v>
@@ -4244,12 +4244,12 @@
       <c r="A137" t="inlineStr"/>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-AT</t>
+          <t>Nexlev-Branded-All Products</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>B0DFCDKMWR</t>
+          <t>B0DVC968P1</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -4259,7 +4259,7 @@
         <v>0</v>
       </c>
       <c r="F137" t="n">
-        <v>91</v>
+        <v>3</v>
       </c>
       <c r="G137" t="n">
         <v>0</v>
@@ -4272,22 +4272,22 @@
       <c r="A138" t="inlineStr"/>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-AT</t>
+          <t>Nexlev-Branded-All Products</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>B0DFCDZWND</t>
+          <t>B0DVC9PRSD</t>
         </is>
       </c>
       <c r="D138" t="n">
-        <v>3.67</v>
+        <v>0</v>
       </c>
       <c r="E138" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F138" t="n">
-        <v>198</v>
+        <v>25</v>
       </c>
       <c r="G138" t="n">
         <v>0</v>
@@ -4300,22 +4300,22 @@
       <c r="A139" t="inlineStr"/>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-AT</t>
+          <t>Nexlev-Branded-All Products</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>B0DFCG2VGS</t>
+          <t>B0DVSZ2VVJ</t>
         </is>
       </c>
       <c r="D139" t="n">
-        <v>0</v>
+        <v>15.4</v>
       </c>
       <c r="E139" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F139" t="n">
-        <v>0</v>
+        <v>126</v>
       </c>
       <c r="G139" t="n">
         <v>0</v>
@@ -4328,78 +4328,78 @@
       <c r="A140" t="inlineStr"/>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-AT</t>
+          <t>Nexlev-Branded-All Products</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>B0DFD123P5</t>
+          <t>B0F29SZCVF</t>
         </is>
       </c>
       <c r="D140" t="n">
-        <v>349.67</v>
+        <v>31.43</v>
       </c>
       <c r="E140" t="n">
-        <v>104</v>
+        <v>4</v>
       </c>
       <c r="F140" t="n">
-        <v>12574</v>
+        <v>156</v>
       </c>
       <c r="G140" t="n">
-        <v>1778.81</v>
+        <v>0</v>
       </c>
       <c r="H140" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr"/>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-AT</t>
+          <t>Nexlev-Branded-All Products</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>B0DFM4JZV9</t>
+          <t>B0F2MZ8CG9</t>
         </is>
       </c>
       <c r="D141" t="n">
-        <v>0</v>
+        <v>13.64</v>
       </c>
       <c r="E141" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F141" t="n">
-        <v>245</v>
+        <v>285</v>
       </c>
       <c r="G141" t="n">
-        <v>0</v>
+        <v>676.28</v>
       </c>
       <c r="H141" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr"/>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-AT</t>
+          <t>Nexlev-Branded-All Products</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>B0DJFH4K8B</t>
+          <t>B0F2N11VTN</t>
         </is>
       </c>
       <c r="D142" t="n">
-        <v>13.21</v>
+        <v>22.9</v>
       </c>
       <c r="E142" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F142" t="n">
-        <v>792</v>
+        <v>4357</v>
       </c>
       <c r="G142" t="n">
         <v>0</v>
@@ -4412,22 +4412,22 @@
       <c r="A143" t="inlineStr"/>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-AT</t>
+          <t>Nexlev-Branded-All Products</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>B0DJFH6RTL</t>
+          <t>B0F2N1HTBT</t>
         </is>
       </c>
       <c r="D143" t="n">
-        <v>4.51</v>
+        <v>0</v>
       </c>
       <c r="E143" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F143" t="n">
-        <v>408</v>
+        <v>343</v>
       </c>
       <c r="G143" t="n">
         <v>0</v>
@@ -4440,22 +4440,22 @@
       <c r="A144" t="inlineStr"/>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-AT</t>
+          <t>Nexlev-Branded-All Products</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>B0DK9LYT4P</t>
+          <t>B0F2N37819</t>
         </is>
       </c>
       <c r="D144" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="E144" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F144" t="n">
-        <v>11779</v>
+        <v>69</v>
       </c>
       <c r="G144" t="n">
         <v>0</v>
@@ -4468,22 +4468,22 @@
       <c r="A145" t="inlineStr"/>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-AT</t>
+          <t>Nexlev-Branded-All Products</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>B0DKJSCLBD</t>
+          <t>B0F2N4N83Y</t>
         </is>
       </c>
       <c r="D145" t="n">
-        <v>12.87</v>
+        <v>15.4</v>
       </c>
       <c r="E145" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F145" t="n">
-        <v>1041</v>
+        <v>99</v>
       </c>
       <c r="G145" t="n">
         <v>0</v>
@@ -4496,12 +4496,12 @@
       <c r="A146" t="inlineStr"/>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-AT</t>
+          <t>Nexlev-Branded-All Products</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>B0DNJJKBKG</t>
+          <t>B0F678L8YT</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -4511,7 +4511,7 @@
         <v>0</v>
       </c>
       <c r="F146" t="n">
-        <v>35</v>
+        <v>467</v>
       </c>
       <c r="G146" t="n">
         <v>0</v>
@@ -4524,22 +4524,22 @@
       <c r="A147" t="inlineStr"/>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-AT</t>
+          <t>Nexlev-Branded-All Products</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>B0DT6Y7KJM</t>
+          <t>B0F679QJH4</t>
         </is>
       </c>
       <c r="D147" t="n">
-        <v>3.57</v>
+        <v>14.26</v>
       </c>
       <c r="E147" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F147" t="n">
-        <v>164</v>
+        <v>1466</v>
       </c>
       <c r="G147" t="n">
         <v>0</v>
@@ -4552,22 +4552,22 @@
       <c r="A148" t="inlineStr"/>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-AT</t>
+          <t>Nexlev-Branded-All Products</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>B0DV9CY3XR</t>
+          <t>B0F67BSF2R</t>
         </is>
       </c>
       <c r="D148" t="n">
-        <v>0</v>
+        <v>19.88</v>
       </c>
       <c r="E148" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F148" t="n">
-        <v>26</v>
+        <v>13533</v>
       </c>
       <c r="G148" t="n">
         <v>0</v>
@@ -4580,22 +4580,22 @@
       <c r="A149" t="inlineStr"/>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-AT</t>
+          <t>Nexlev-Branded-All Products</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>B0DVC58QPZ</t>
+          <t>B0F67BW7SF</t>
         </is>
       </c>
       <c r="D149" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="E149" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F149" t="n">
-        <v>895</v>
+        <v>78</v>
       </c>
       <c r="G149" t="n">
         <v>0</v>
@@ -4608,12 +4608,12 @@
       <c r="A150" t="inlineStr"/>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-AT</t>
+          <t>Nexlev-Branded-All Products</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>B0DVC968P1</t>
+          <t>B0F74DJYG6</t>
         </is>
       </c>
       <c r="D150" t="n">
@@ -4623,7 +4623,7 @@
         <v>0</v>
       </c>
       <c r="F150" t="n">
-        <v>2</v>
+        <v>822</v>
       </c>
       <c r="G150" t="n">
         <v>0</v>
@@ -4636,12 +4636,12 @@
       <c r="A151" t="inlineStr"/>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-AT</t>
+          <t>Nexlev-Branded-All Products</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>B0DVC9PRSD</t>
+          <t>B0FJ1ZB4G9</t>
         </is>
       </c>
       <c r="D151" t="n">
@@ -4651,7 +4651,7 @@
         <v>0</v>
       </c>
       <c r="F151" t="n">
-        <v>542</v>
+        <v>102</v>
       </c>
       <c r="G151" t="n">
         <v>0</v>
@@ -4664,22 +4664,22 @@
       <c r="A152" t="inlineStr"/>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-AT</t>
+          <t>Nexlev-Branded-All Products</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>B0DVSZ2VVJ</t>
+          <t>B0FJG5PFGQ</t>
         </is>
       </c>
       <c r="D152" t="n">
-        <v>0</v>
+        <v>7.32</v>
       </c>
       <c r="E152" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F152" t="n">
-        <v>107</v>
+        <v>190</v>
       </c>
       <c r="G152" t="n">
         <v>0</v>
@@ -4692,40 +4692,40 @@
       <c r="A153" t="inlineStr"/>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-AT</t>
+          <t>Nexlev-Branded-All Products</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>B0F29SZCVF</t>
+          <t>B0FMF1D9NV</t>
         </is>
       </c>
       <c r="D153" t="n">
-        <v>7.34</v>
+        <v>14.65</v>
       </c>
       <c r="E153" t="n">
         <v>2</v>
       </c>
       <c r="F153" t="n">
-        <v>45</v>
+        <v>196</v>
       </c>
       <c r="G153" t="n">
-        <v>1380</v>
+        <v>0</v>
       </c>
       <c r="H153" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr"/>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-AT</t>
+          <t>Nexlev-Branded-All Products</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>B0F2MZ8CG9</t>
+          <t>B0FS7T8151</t>
         </is>
       </c>
       <c r="D154" t="n">
@@ -4735,7 +4735,7 @@
         <v>0</v>
       </c>
       <c r="F154" t="n">
-        <v>129</v>
+        <v>37</v>
       </c>
       <c r="G154" t="n">
         <v>0</v>
@@ -4748,22 +4748,22 @@
       <c r="A155" t="inlineStr"/>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-AT</t>
+          <t>Nexlev-Branded-All Products</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>B0F2N11VTN</t>
+          <t>B0FYNKYJFN</t>
         </is>
       </c>
       <c r="D155" t="n">
-        <v>0</v>
+        <v>15.35</v>
       </c>
       <c r="E155" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F155" t="n">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="G155" t="n">
         <v>0</v>
@@ -4776,22 +4776,22 @@
       <c r="A156" t="inlineStr"/>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-AT</t>
+          <t>Nexlev-Branded-All Products</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>B0F2N37819</t>
+          <t>B0GGHZWMVW</t>
         </is>
       </c>
       <c r="D156" t="n">
-        <v>0</v>
+        <v>119.84</v>
       </c>
       <c r="E156" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="F156" t="n">
-        <v>11</v>
+        <v>5694</v>
       </c>
       <c r="G156" t="n">
         <v>0</v>
@@ -4809,17 +4809,17 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>B0F2N4N83Y</t>
+          <t>B0CDQ55W2M</t>
         </is>
       </c>
       <c r="D157" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="E157" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F157" t="n">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="G157" t="n">
         <v>0</v>
@@ -4837,17 +4837,17 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>B0F678L8YT</t>
+          <t>B0CQX9ZZMH</t>
         </is>
       </c>
       <c r="D158" t="n">
-        <v>3.64</v>
+        <v>3.67</v>
       </c>
       <c r="E158" t="n">
         <v>1</v>
       </c>
       <c r="F158" t="n">
-        <v>192</v>
+        <v>408</v>
       </c>
       <c r="G158" t="n">
         <v>0</v>
@@ -4865,17 +4865,17 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>B0F679QJH4</t>
+          <t>B0CW1JJP9S</t>
         </is>
       </c>
       <c r="D159" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="E159" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F159" t="n">
-        <v>63</v>
+        <v>185</v>
       </c>
       <c r="G159" t="n">
         <v>0</v>
@@ -4893,23 +4893,23 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>B0F67BSF2R</t>
+          <t>B0D25LNDSY</t>
         </is>
       </c>
       <c r="D160" t="n">
-        <v>4.74</v>
+        <v>49.34</v>
       </c>
       <c r="E160" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="F160" t="n">
-        <v>394</v>
+        <v>1238</v>
       </c>
       <c r="G160" t="n">
-        <v>0</v>
+        <v>677.12</v>
       </c>
       <c r="H160" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="161">
@@ -4921,17 +4921,17 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>B0F67BW7SF</t>
+          <t>B0D2LD6BYJ</t>
         </is>
       </c>
       <c r="D161" t="n">
-        <v>3.26</v>
+        <v>8.98</v>
       </c>
       <c r="E161" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F161" t="n">
-        <v>299</v>
+        <v>8627</v>
       </c>
       <c r="G161" t="n">
         <v>0</v>
@@ -4949,17 +4949,17 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>B0FJ1ZB4G9</t>
+          <t>B0D2LFMY48</t>
         </is>
       </c>
       <c r="D162" t="n">
-        <v>0</v>
+        <v>12.21</v>
       </c>
       <c r="E162" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F162" t="n">
-        <v>193</v>
+        <v>2585</v>
       </c>
       <c r="G162" t="n">
         <v>0</v>
@@ -4977,17 +4977,17 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>B0FJG5PFGQ</t>
+          <t>B0D2LKB4BJ</t>
         </is>
       </c>
       <c r="D163" t="n">
-        <v>3.67</v>
+        <v>11.52</v>
       </c>
       <c r="E163" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F163" t="n">
-        <v>614</v>
+        <v>1009</v>
       </c>
       <c r="G163" t="n">
         <v>0</v>
@@ -5005,17 +5005,17 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>B0FMF1D9NV</t>
+          <t>B0D63FKYZ5</t>
         </is>
       </c>
       <c r="D164" t="n">
-        <v>3.57</v>
+        <v>4.9</v>
       </c>
       <c r="E164" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F164" t="n">
-        <v>98</v>
+        <v>873</v>
       </c>
       <c r="G164" t="n">
         <v>0</v>
@@ -5033,7 +5033,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>B0FS7T8151</t>
+          <t>B0D81DLSFT</t>
         </is>
       </c>
       <c r="D165" t="n">
@@ -5043,7 +5043,7 @@
         <v>0</v>
       </c>
       <c r="F165" t="n">
-        <v>170</v>
+        <v>870</v>
       </c>
       <c r="G165" t="n">
         <v>0</v>
@@ -5061,17 +5061,17 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>B0FYNKYJFN</t>
+          <t>B0D83Q7L8W</t>
         </is>
       </c>
       <c r="D166" t="n">
-        <v>3.66</v>
+        <v>16.28</v>
       </c>
       <c r="E166" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F166" t="n">
-        <v>82</v>
+        <v>709</v>
       </c>
       <c r="G166" t="n">
         <v>0</v>
@@ -5089,17 +5089,17 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>B0GGHZWMVW</t>
+          <t>B0D8445KJN</t>
         </is>
       </c>
       <c r="D167" t="n">
-        <v>58.23</v>
+        <v>4.73</v>
       </c>
       <c r="E167" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="F167" t="n">
-        <v>1214</v>
+        <v>1154</v>
       </c>
       <c r="G167" t="n">
         <v>0</v>
@@ -5112,22 +5112,22 @@
       <c r="A168" t="inlineStr"/>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Nexlev-Defensive-AT</t>
+          <t>Nexlev-Catch All-AT</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>B0CQX9ZZMH</t>
+          <t>B0D86Y2V7V</t>
         </is>
       </c>
       <c r="D168" t="n">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="E168" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F168" t="n">
-        <v>2</v>
+        <v>450</v>
       </c>
       <c r="G168" t="n">
         <v>0</v>
@@ -5140,22 +5140,22 @@
       <c r="A169" t="inlineStr"/>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Nexlev-Defensive-AT</t>
+          <t>Nexlev-Catch All-AT</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>B0D25LNDSY</t>
+          <t>B0D86ZC9YT</t>
         </is>
       </c>
       <c r="D169" t="n">
-        <v>0</v>
+        <v>13.46</v>
       </c>
       <c r="E169" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F169" t="n">
-        <v>4</v>
+        <v>1207</v>
       </c>
       <c r="G169" t="n">
         <v>0</v>
@@ -5168,22 +5168,22 @@
       <c r="A170" t="inlineStr"/>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Nexlev-Defensive-AT</t>
+          <t>Nexlev-Catch All-AT</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>B0D2LD6BYJ</t>
+          <t>B0D9KCNVNM</t>
         </is>
       </c>
       <c r="D170" t="n">
-        <v>0</v>
+        <v>4.67</v>
       </c>
       <c r="E170" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F170" t="n">
-        <v>3</v>
+        <v>395</v>
       </c>
       <c r="G170" t="n">
         <v>0</v>
@@ -5196,50 +5196,50 @@
       <c r="A171" t="inlineStr"/>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Nexlev-Defensive-AT</t>
+          <t>Nexlev-Catch All-AT</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>B0D2LFMY48</t>
+          <t>B0D9KFP4MG</t>
         </is>
       </c>
       <c r="D171" t="n">
-        <v>0</v>
+        <v>75.37</v>
       </c>
       <c r="E171" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="F171" t="n">
-        <v>26</v>
+        <v>5612</v>
       </c>
       <c r="G171" t="n">
-        <v>0</v>
+        <v>1651.7</v>
       </c>
       <c r="H171" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr"/>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Nexlev-Defensive-AT</t>
+          <t>Nexlev-Catch All-AT</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>B0D2LKB4BJ</t>
+          <t>B0D9KFQG8Q</t>
         </is>
       </c>
       <c r="D172" t="n">
-        <v>9.6</v>
+        <v>4.5</v>
       </c>
       <c r="E172" t="n">
         <v>2</v>
       </c>
       <c r="F172" t="n">
-        <v>17</v>
+        <v>298</v>
       </c>
       <c r="G172" t="n">
         <v>0</v>
@@ -5252,12 +5252,12 @@
       <c r="A173" t="inlineStr"/>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Nexlev-Defensive-AT</t>
+          <t>Nexlev-Catch All-AT</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>B0D81DLSFT</t>
+          <t>B0DCK4DR1B</t>
         </is>
       </c>
       <c r="D173" t="n">
@@ -5267,7 +5267,7 @@
         <v>0</v>
       </c>
       <c r="F173" t="n">
-        <v>1</v>
+        <v>129</v>
       </c>
       <c r="G173" t="n">
         <v>0</v>
@@ -5280,22 +5280,22 @@
       <c r="A174" t="inlineStr"/>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Nexlev-Defensive-AT</t>
+          <t>Nexlev-Catch All-AT</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>B0D83Q7L8W</t>
+          <t>B0DFCDKMWR</t>
         </is>
       </c>
       <c r="D174" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="E174" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F174" t="n">
-        <v>4</v>
+        <v>201</v>
       </c>
       <c r="G174" t="n">
         <v>0</v>
@@ -5308,22 +5308,22 @@
       <c r="A175" t="inlineStr"/>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Nexlev-Defensive-AT</t>
+          <t>Nexlev-Catch All-AT</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>B0D8445KJN</t>
+          <t>B0DFCDZWND</t>
         </is>
       </c>
       <c r="D175" t="n">
-        <v>0</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="E175" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F175" t="n">
-        <v>13</v>
+        <v>667</v>
       </c>
       <c r="G175" t="n">
         <v>0</v>
@@ -5336,12 +5336,12 @@
       <c r="A176" t="inlineStr"/>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Nexlev-Defensive-AT</t>
+          <t>Nexlev-Catch All-AT</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>B0D86Y2V7V</t>
+          <t>B0DFCG2VGS</t>
         </is>
       </c>
       <c r="D176" t="n">
@@ -5351,7 +5351,7 @@
         <v>0</v>
       </c>
       <c r="F176" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="G176" t="n">
         <v>0</v>
@@ -5364,50 +5364,50 @@
       <c r="A177" t="inlineStr"/>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Nexlev-Defensive-AT</t>
+          <t>Nexlev-Catch All-AT</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>B0D86ZC9YT</t>
+          <t>B0DFD123P5</t>
         </is>
       </c>
       <c r="D177" t="n">
-        <v>0</v>
+        <v>887.36</v>
       </c>
       <c r="E177" t="n">
-        <v>0</v>
+        <v>263</v>
       </c>
       <c r="F177" t="n">
+        <v>31340</v>
+      </c>
+      <c r="G177" t="n">
+        <v>3550</v>
+      </c>
+      <c r="H177" t="n">
         <v>2</v>
-      </c>
-      <c r="G177" t="n">
-        <v>0</v>
-      </c>
-      <c r="H177" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr"/>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Nexlev-Defensive-AT</t>
+          <t>Nexlev-Catch All-AT</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>B0D9KCNVNM</t>
+          <t>B0DFM4JZV9</t>
         </is>
       </c>
       <c r="D178" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="E178" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F178" t="n">
-        <v>7</v>
+        <v>704</v>
       </c>
       <c r="G178" t="n">
         <v>0</v>
@@ -5420,50 +5420,50 @@
       <c r="A179" t="inlineStr"/>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Nexlev-Defensive-AT</t>
+          <t>Nexlev-Catch All-AT</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>B0D9KFP4MG</t>
+          <t>B0DJFH4K8B</t>
         </is>
       </c>
       <c r="D179" t="n">
-        <v>4.8</v>
+        <v>21.2</v>
       </c>
       <c r="E179" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F179" t="n">
-        <v>29</v>
+        <v>2073</v>
       </c>
       <c r="G179" t="n">
-        <v>1651.69</v>
+        <v>0</v>
       </c>
       <c r="H179" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr"/>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Nexlev-Defensive-AT</t>
+          <t>Nexlev-Catch All-AT</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>B0DCK4DR1B</t>
+          <t>B0DJFH6RTL</t>
         </is>
       </c>
       <c r="D180" t="n">
-        <v>0</v>
+        <v>11.81</v>
       </c>
       <c r="E180" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F180" t="n">
-        <v>4</v>
+        <v>1322</v>
       </c>
       <c r="G180" t="n">
         <v>0</v>
@@ -5476,22 +5476,22 @@
       <c r="A181" t="inlineStr"/>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Nexlev-Defensive-AT</t>
+          <t>Nexlev-Catch All-AT</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>B0DFCDZWND</t>
+          <t>B0DK9LYT4P</t>
         </is>
       </c>
       <c r="D181" t="n">
-        <v>0</v>
+        <v>81.89</v>
       </c>
       <c r="E181" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F181" t="n">
-        <v>2</v>
+        <v>17989</v>
       </c>
       <c r="G181" t="n">
         <v>0</v>
@@ -5504,40 +5504,40 @@
       <c r="A182" t="inlineStr"/>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Nexlev-Defensive-AT</t>
+          <t>Nexlev-Catch All-AT</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>B0DFCG2VGS</t>
+          <t>B0DKJSCLBD</t>
         </is>
       </c>
       <c r="D182" t="n">
-        <v>0</v>
+        <v>23.35</v>
       </c>
       <c r="E182" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F182" t="n">
-        <v>128</v>
+        <v>2791</v>
       </c>
       <c r="G182" t="n">
-        <v>0</v>
+        <v>2117.8</v>
       </c>
       <c r="H182" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr"/>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Nexlev-Defensive-AT</t>
+          <t>Nexlev-Catch All-AT</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>B0DFD123P5</t>
+          <t>B0DNJJKBKG</t>
         </is>
       </c>
       <c r="D183" t="n">
@@ -5560,22 +5560,22 @@
       <c r="A184" t="inlineStr"/>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Nexlev-Defensive-AT</t>
+          <t>Nexlev-Catch All-AT</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>B0DJFH4K8B</t>
+          <t>B0DT6Y7KJM</t>
         </is>
       </c>
       <c r="D184" t="n">
-        <v>0</v>
+        <v>10.91</v>
       </c>
       <c r="E184" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F184" t="n">
-        <v>2</v>
+        <v>430</v>
       </c>
       <c r="G184" t="n">
         <v>0</v>
@@ -5588,22 +5588,22 @@
       <c r="A185" t="inlineStr"/>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Nexlev-Defensive-AT</t>
+          <t>Nexlev-Catch All-AT</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>B0DJFH6RTL</t>
+          <t>B0DV9CY3XR</t>
         </is>
       </c>
       <c r="D185" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="E185" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F185" t="n">
-        <v>1</v>
+        <v>92</v>
       </c>
       <c r="G185" t="n">
         <v>0</v>
@@ -5616,22 +5616,22 @@
       <c r="A186" t="inlineStr"/>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Nexlev-Defensive-AT</t>
+          <t>Nexlev-Catch All-AT</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>B0DK9LYT4P</t>
+          <t>B0DVC58QPZ</t>
         </is>
       </c>
       <c r="D186" t="n">
-        <v>0</v>
+        <v>39.46</v>
       </c>
       <c r="E186" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F186" t="n">
-        <v>2</v>
+        <v>2474</v>
       </c>
       <c r="G186" t="n">
         <v>0</v>
@@ -5644,12 +5644,12 @@
       <c r="A187" t="inlineStr"/>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Nexlev-Defensive-AT</t>
+          <t>Nexlev-Catch All-AT</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>B0DKJSCLBD</t>
+          <t>B0DVC968P1</t>
         </is>
       </c>
       <c r="D187" t="n">
@@ -5659,7 +5659,7 @@
         <v>0</v>
       </c>
       <c r="F187" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="G187" t="n">
         <v>0</v>
@@ -5672,22 +5672,22 @@
       <c r="A188" t="inlineStr"/>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Nexlev-Defensive-AT</t>
+          <t>Nexlev-Catch All-AT</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>B0DNJF1BLS</t>
+          <t>B0DVC9PRSD</t>
         </is>
       </c>
       <c r="D188" t="n">
-        <v>4.64</v>
+        <v>14.28</v>
       </c>
       <c r="E188" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F188" t="n">
-        <v>4</v>
+        <v>957</v>
       </c>
       <c r="G188" t="n">
         <v>0</v>
@@ -5700,22 +5700,22 @@
       <c r="A189" t="inlineStr"/>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Nexlev-Defensive-AT</t>
+          <t>Nexlev-Catch All-AT</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>B0DT6Y7KJM</t>
+          <t>B0DVSZ2VVJ</t>
         </is>
       </c>
       <c r="D189" t="n">
-        <v>0</v>
+        <v>10.34</v>
       </c>
       <c r="E189" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F189" t="n">
-        <v>1</v>
+        <v>260</v>
       </c>
       <c r="G189" t="n">
         <v>0</v>
@@ -5728,78 +5728,78 @@
       <c r="A190" t="inlineStr"/>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Nexlev-Defensive-AT</t>
+          <t>Nexlev-Catch All-AT</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>B0DV9CY3XR</t>
+          <t>B0F29SZCVF</t>
         </is>
       </c>
       <c r="D190" t="n">
-        <v>0</v>
+        <v>14.67</v>
       </c>
       <c r="E190" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F190" t="n">
-        <v>2</v>
+        <v>146</v>
       </c>
       <c r="G190" t="n">
-        <v>0</v>
+        <v>1380</v>
       </c>
       <c r="H190" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr"/>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Nexlev-Defensive-AT</t>
+          <t>Nexlev-Catch All-AT</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>B0F2N11VTN</t>
+          <t>B0F2MZ8CG9</t>
         </is>
       </c>
       <c r="D191" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="E191" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F191" t="n">
-        <v>0</v>
+        <v>242</v>
       </c>
       <c r="G191" t="n">
-        <v>0</v>
+        <v>338.14</v>
       </c>
       <c r="H191" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr"/>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Nexlev-Defensive-AT</t>
+          <t>Nexlev-Catch All-AT</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>B0F678L8YT</t>
+          <t>B0F2N11VTN</t>
         </is>
       </c>
       <c r="D192" t="n">
-        <v>2.02</v>
+        <v>5.66</v>
       </c>
       <c r="E192" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F192" t="n">
-        <v>5</v>
+        <v>479</v>
       </c>
       <c r="G192" t="n">
         <v>0</v>
@@ -5812,22 +5812,22 @@
       <c r="A193" t="inlineStr"/>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Nexlev-Defensive-AT</t>
+          <t>Nexlev-Catch All-AT</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>B0F679QJH4</t>
+          <t>B0F2N1HTBT</t>
         </is>
       </c>
       <c r="D193" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="E193" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F193" t="n">
-        <v>1</v>
+        <v>135</v>
       </c>
       <c r="G193" t="n">
         <v>0</v>
@@ -5840,12 +5840,12 @@
       <c r="A194" t="inlineStr"/>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Nexlev-Defensive-AT</t>
+          <t>Nexlev-Catch All-AT</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>B0F67BSF2R</t>
+          <t>B0F2N37819</t>
         </is>
       </c>
       <c r="D194" t="n">
@@ -5855,7 +5855,7 @@
         <v>0</v>
       </c>
       <c r="F194" t="n">
-        <v>7</v>
+        <v>52</v>
       </c>
       <c r="G194" t="n">
         <v>0</v>
@@ -5868,22 +5868,22 @@
       <c r="A195" t="inlineStr"/>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Nexlev-Defensive-AT</t>
+          <t>Nexlev-Catch All-AT</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>B0FJ1ZB4G9</t>
+          <t>B0F2N4N83Y</t>
         </is>
       </c>
       <c r="D195" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="E195" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F195" t="n">
-        <v>0</v>
+        <v>121</v>
       </c>
       <c r="G195" t="n">
         <v>0</v>
@@ -5896,22 +5896,22 @@
       <c r="A196" t="inlineStr"/>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Nexlev-Defensive-AT</t>
+          <t>Nexlev-Catch All-AT</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>B0FJG5PFGQ</t>
+          <t>B0F678L8YT</t>
         </is>
       </c>
       <c r="D196" t="n">
-        <v>0</v>
+        <v>8.93</v>
       </c>
       <c r="E196" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F196" t="n">
-        <v>4</v>
+        <v>542</v>
       </c>
       <c r="G196" t="n">
         <v>0</v>
@@ -5924,22 +5924,22 @@
       <c r="A197" t="inlineStr"/>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Nexlev-Defensive-AT</t>
+          <t>Nexlev-Catch All-AT</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>B0FMF1D9NV</t>
+          <t>B0F679QJH4</t>
         </is>
       </c>
       <c r="D197" t="n">
-        <v>1.34</v>
+        <v>15.83</v>
       </c>
       <c r="E197" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F197" t="n">
-        <v>5</v>
+        <v>123</v>
       </c>
       <c r="G197" t="n">
         <v>0</v>
@@ -5952,22 +5952,22 @@
       <c r="A198" t="inlineStr"/>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Nexlev-Defensive-AT</t>
+          <t>Nexlev-Catch All-AT</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>B0FS7T8151</t>
+          <t>B0F67BSF2R</t>
         </is>
       </c>
       <c r="D198" t="n">
-        <v>0</v>
+        <v>9.09</v>
       </c>
       <c r="E198" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F198" t="n">
-        <v>0</v>
+        <v>1276</v>
       </c>
       <c r="G198" t="n">
         <v>0</v>
@@ -5980,22 +5980,22 @@
       <c r="A199" t="inlineStr"/>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Nexlev-Defensive-AT</t>
+          <t>Nexlev-Catch All-AT</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>B0FYNKYJFN</t>
+          <t>B0F67BW7SF</t>
         </is>
       </c>
       <c r="D199" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="E199" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F199" t="n">
-        <v>5</v>
+        <v>873</v>
       </c>
       <c r="G199" t="n">
         <v>0</v>
@@ -6008,22 +6008,22 @@
       <c r="A200" t="inlineStr"/>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Nexlev-Defensive-AT</t>
+          <t>Nexlev-Catch All-AT</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>B0GGHZWMVW</t>
+          <t>B0F74DJYG6</t>
         </is>
       </c>
       <c r="D200" t="n">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="E200" t="n">
+        <v>0</v>
+      </c>
+      <c r="F200" t="n">
         <v>2</v>
-      </c>
-      <c r="F200" t="n">
-        <v>60</v>
       </c>
       <c r="G200" t="n">
         <v>0</v>
@@ -6036,22 +6036,22 @@
       <c r="A201" t="inlineStr"/>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Nexlev-Multi Ad Group-Steam Cleaner -SP-KT -Exact/Phrase/Broad</t>
+          <t>Nexlev-Catch All-AT</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>B0CDPP45BM</t>
+          <t>B0FJ1ZB4G9</t>
         </is>
       </c>
       <c r="D201" t="n">
-        <v>1374.42</v>
+        <v>0</v>
       </c>
       <c r="E201" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F201" t="n">
-        <v>9806</v>
+        <v>555</v>
       </c>
       <c r="G201" t="n">
         <v>0</v>
@@ -6064,22 +6064,22 @@
       <c r="A202" t="inlineStr"/>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Nexlev-SP- B0GN8WW6BC - Stand Mixer with Stainless Steel Bowl - BM</t>
+          <t>Nexlev-Catch All-AT</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>B0GN8WW6BC</t>
+          <t>B0FJG5PFGQ</t>
         </is>
       </c>
       <c r="D202" t="n">
-        <v>0</v>
+        <v>23.86</v>
       </c>
       <c r="E202" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F202" t="n">
-        <v>33</v>
+        <v>1842</v>
       </c>
       <c r="G202" t="n">
         <v>0</v>
@@ -6092,22 +6092,22 @@
       <c r="A203" t="inlineStr"/>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Nexlev-Steamer-PT(SEAHELTON)</t>
+          <t>Nexlev-Catch All-AT</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>B0CDPP45BM</t>
+          <t>B0FMF1D9NV</t>
         </is>
       </c>
       <c r="D203" t="n">
-        <v>7.36</v>
+        <v>7.24</v>
       </c>
       <c r="E203" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F203" t="n">
-        <v>39</v>
+        <v>219</v>
       </c>
       <c r="G203" t="n">
         <v>0</v>
@@ -6120,22 +6120,22 @@
       <c r="A204" t="inlineStr"/>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Nexlev-Steamer-PT(SEAHELTON)</t>
+          <t>Nexlev-Catch All-AT</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0FS7T8151</t>
         </is>
       </c>
       <c r="D204" t="n">
-        <v>29.2</v>
+        <v>0</v>
       </c>
       <c r="E204" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F204" t="n">
-        <v>54</v>
+        <v>408</v>
       </c>
       <c r="G204" t="n">
         <v>0</v>
@@ -6148,22 +6148,22 @@
       <c r="A205" t="inlineStr"/>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Nexlev-steam Cleaner For Home-B0CDPP45BM-BM-SP</t>
+          <t>Nexlev-Catch All-AT</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>B0CDPP45BM</t>
+          <t>B0FYNKYJFN</t>
         </is>
       </c>
       <c r="D205" t="n">
-        <v>39.51</v>
+        <v>4.8</v>
       </c>
       <c r="E205" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F205" t="n">
-        <v>194</v>
+        <v>175</v>
       </c>
       <c r="G205" t="n">
         <v>0</v>
@@ -6176,22 +6176,22 @@
       <c r="A206" t="inlineStr"/>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Nexlev-steam Cleaner For Home-B0CDPP45BM-Exact-SP</t>
+          <t>Nexlev-Catch All-AT</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>B0CDPP45BM</t>
+          <t>B0GGHZWMVW</t>
         </is>
       </c>
       <c r="D206" t="n">
-        <v>0</v>
+        <v>148.29</v>
       </c>
       <c r="E206" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="F206" t="n">
-        <v>2</v>
+        <v>7248</v>
       </c>
       <c r="G206" t="n">
         <v>0</v>
@@ -6204,22 +6204,22 @@
       <c r="A207" t="inlineStr"/>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Nexliv- Steam Mop-B0D2LJSQXZ-AT-SP</t>
+          <t>Nexlev-Defensive-AT</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>B0D2LJSQXZ</t>
+          <t>B0CQX9ZZMH</t>
         </is>
       </c>
       <c r="D207" t="n">
-        <v>142.84</v>
+        <v>0</v>
       </c>
       <c r="E207" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="F207" t="n">
-        <v>2269</v>
+        <v>5</v>
       </c>
       <c r="G207" t="n">
         <v>0</v>
@@ -6232,22 +6232,22 @@
       <c r="A208" t="inlineStr"/>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Nexliv- Steam Mop-B0D2LJSQXZ-PT-SP</t>
+          <t>Nexlev-Defensive-AT</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>B0D2LJSQXZ</t>
+          <t>B0CW1JJP9S</t>
         </is>
       </c>
       <c r="D208" t="n">
-        <v>152.66</v>
+        <v>0</v>
       </c>
       <c r="E208" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="F208" t="n">
-        <v>725</v>
+        <v>1</v>
       </c>
       <c r="G208" t="n">
         <v>0</v>
@@ -6260,12 +6260,12 @@
       <c r="A209" t="inlineStr"/>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Nexliv--Steam Cleaner--B0F43P6D23-AT-SP</t>
+          <t>Nexlev-Defensive-AT</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0D25LNDSY</t>
         </is>
       </c>
       <c r="D209" t="n">
@@ -6275,7 +6275,7 @@
         <v>0</v>
       </c>
       <c r="F209" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="G209" t="n">
         <v>0</v>
@@ -6288,40 +6288,40 @@
       <c r="A210" t="inlineStr"/>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Nexliv-2 in 1 Stick Vacuum Cleaner-B0DCGHVN81-AT</t>
+          <t>Nexlev-Defensive-AT</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>B0DCGHVN81</t>
+          <t>B0D2LD6BYJ</t>
         </is>
       </c>
       <c r="D210" t="n">
-        <v>481.73</v>
+        <v>0</v>
       </c>
       <c r="E210" t="n">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="F210" t="n">
-        <v>9490</v>
+        <v>3</v>
       </c>
       <c r="G210" t="n">
-        <v>3557.62</v>
+        <v>0</v>
       </c>
       <c r="H210" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr"/>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Nexliv-2 in 1 Stick Vacuum Cleaner-B0DCGHVN81-BM-SP</t>
+          <t>Nexlev-Defensive-AT</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>B0DCGHVN81</t>
+          <t>B0D2LFMY48</t>
         </is>
       </c>
       <c r="D211" t="n">
@@ -6331,7 +6331,7 @@
         <v>0</v>
       </c>
       <c r="F211" t="n">
-        <v>0</v>
+        <v>115</v>
       </c>
       <c r="G211" t="n">
         <v>0</v>
@@ -6344,22 +6344,22 @@
       <c r="A212" t="inlineStr"/>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Nexliv-2 in 1 Stick Vacuum Cleaner-B0DCGHVN81-PT(2)-SP</t>
+          <t>Nexlev-Defensive-AT</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>B0DCGHVN81</t>
+          <t>B0D2LKB4BJ</t>
         </is>
       </c>
       <c r="D212" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="E212" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F212" t="n">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="G212" t="n">
         <v>0</v>
@@ -6372,22 +6372,22 @@
       <c r="A213" t="inlineStr"/>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Nexliv-2 in 1 Stick Vacuum Cleaner-B0DCGHVN81-PT-SP</t>
+          <t>Nexlev-Defensive-AT</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>B0DCGHVN81</t>
+          <t>B0D81DLSFT</t>
         </is>
       </c>
       <c r="D213" t="n">
-        <v>541</v>
+        <v>0</v>
       </c>
       <c r="E213" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="F213" t="n">
-        <v>4039</v>
+        <v>12</v>
       </c>
       <c r="G213" t="n">
         <v>0</v>
@@ -6400,22 +6400,22 @@
       <c r="A214" t="inlineStr"/>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Nexliv-2 in 1 Stick Vacuum Cleaner-B0DCGHVN81-Phrase-SP(2)</t>
+          <t>Nexlev-Defensive-AT</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>B0DCGHVN81</t>
+          <t>B0D83Q7L8W</t>
         </is>
       </c>
       <c r="D214" t="n">
-        <v>324.25</v>
+        <v>0</v>
       </c>
       <c r="E214" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F214" t="n">
-        <v>8089</v>
+        <v>80</v>
       </c>
       <c r="G214" t="n">
         <v>0</v>
@@ -6428,22 +6428,22 @@
       <c r="A215" t="inlineStr"/>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Nexliv-B0D9KDQCCM-Portable Sewing Machine-AT-SP</t>
+          <t>Nexlev-Defensive-AT</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>B0D9KDQCCM</t>
+          <t>B0D8445KJN</t>
         </is>
       </c>
       <c r="D215" t="n">
-        <v>141.64</v>
+        <v>0</v>
       </c>
       <c r="E215" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="F215" t="n">
-        <v>1958</v>
+        <v>19</v>
       </c>
       <c r="G215" t="n">
         <v>0</v>
@@ -6456,12 +6456,12 @@
       <c r="A216" t="inlineStr"/>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Nexliv-B0DCK4DR1B-Skin Lift Device-PT-SP</t>
+          <t>Nexlev-Defensive-AT</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>B0DCK4DR1B</t>
+          <t>B0D86Y2V7V</t>
         </is>
       </c>
       <c r="D216" t="n">
@@ -6471,7 +6471,7 @@
         <v>0</v>
       </c>
       <c r="F216" t="n">
-        <v>90</v>
+        <v>76</v>
       </c>
       <c r="G216" t="n">
         <v>0</v>
@@ -6484,22 +6484,22 @@
       <c r="A217" t="inlineStr"/>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Nexliv-Electric Food Kettle-B0DFCG2VGS-BM-SP</t>
+          <t>Nexlev-Defensive-AT</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>B0DFCG2VGS</t>
+          <t>B0D86ZC9YT</t>
         </is>
       </c>
       <c r="D217" t="n">
-        <v>442.05</v>
+        <v>0</v>
       </c>
       <c r="E217" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="F217" t="n">
-        <v>16131</v>
+        <v>9</v>
       </c>
       <c r="G217" t="n">
         <v>0</v>
@@ -6512,22 +6512,22 @@
       <c r="A218" t="inlineStr"/>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Nexliv-Handheld Steamer-B0D383WQPB-BM-SP</t>
+          <t>Nexlev-Defensive-AT</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>B0D383WQPB</t>
+          <t>B0D9KCNVNM</t>
         </is>
       </c>
       <c r="D218" t="n">
-        <v>413.79</v>
+        <v>0</v>
       </c>
       <c r="E218" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="F218" t="n">
-        <v>5544</v>
+        <v>15</v>
       </c>
       <c r="G218" t="n">
         <v>0</v>
@@ -6540,50 +6540,50 @@
       <c r="A219" t="inlineStr"/>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Nexliv-Handheld Steamer-B0D383WQPB-CT</t>
+          <t>Nexlev-Defensive-AT</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>B0D383WQPB</t>
+          <t>B0D9KFP4MG</t>
         </is>
       </c>
       <c r="D219" t="n">
-        <v>329.07</v>
+        <v>4.8</v>
       </c>
       <c r="E219" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="F219" t="n">
-        <v>8652</v>
+        <v>122</v>
       </c>
       <c r="G219" t="n">
-        <v>0</v>
+        <v>1651.69</v>
       </c>
       <c r="H219" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr"/>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Nexliv-Mattress Sofa-B0CYSLCRQS-AT-SP</t>
+          <t>Nexlev-Defensive-AT</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0D9KFQG8Q</t>
         </is>
       </c>
       <c r="D220" t="n">
-        <v>460.99</v>
+        <v>0</v>
       </c>
       <c r="E220" t="n">
-        <v>128</v>
+        <v>0</v>
       </c>
       <c r="F220" t="n">
-        <v>10918</v>
+        <v>0</v>
       </c>
       <c r="G220" t="n">
         <v>0</v>
@@ -6596,22 +6596,22 @@
       <c r="A221" t="inlineStr"/>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Nexliv-Mattress Sofa-B0CYSLCRQS-Exact-SP</t>
+          <t>Nexlev-Defensive-AT</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0DCK4DR1B</t>
         </is>
       </c>
       <c r="D221" t="n">
-        <v>39.35</v>
+        <v>0</v>
       </c>
       <c r="E221" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F221" t="n">
-        <v>185</v>
+        <v>15</v>
       </c>
       <c r="G221" t="n">
         <v>0</v>
@@ -6624,22 +6624,22 @@
       <c r="A222" t="inlineStr"/>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Nexliv-Portable Blender-B0FS6TB7CP-BM</t>
+          <t>Nexlev-Defensive-AT</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>B0FS6TB7CP</t>
+          <t>B0DFCDZWND</t>
         </is>
       </c>
       <c r="D222" t="n">
-        <v>474.63</v>
+        <v>0</v>
       </c>
       <c r="E222" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="F222" t="n">
-        <v>10178</v>
+        <v>8</v>
       </c>
       <c r="G222" t="n">
         <v>0</v>
@@ -6652,78 +6652,78 @@
       <c r="A223" t="inlineStr"/>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Nexliv-Portable Blender-B0FS6TB7CP-CT</t>
+          <t>Nexlev-Defensive-AT</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>B0FS6TB7CP</t>
+          <t>B0DFCG2VGS</t>
         </is>
       </c>
       <c r="D223" t="n">
-        <v>1498.75</v>
+        <v>4.8</v>
       </c>
       <c r="E223" t="n">
-        <v>87</v>
+        <v>1</v>
       </c>
       <c r="F223" t="n">
-        <v>21637</v>
+        <v>281</v>
       </c>
       <c r="G223" t="n">
-        <v>4066.1</v>
+        <v>0</v>
       </c>
       <c r="H223" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr"/>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Nexliv-Portable Blender-B0FS6TB7CP-PT(2)-SP</t>
+          <t>Nexlev-Defensive-AT</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>B0FS6TB7CP</t>
+          <t>B0DFD123P5</t>
         </is>
       </c>
       <c r="D224" t="n">
-        <v>922.1800000000001</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="E224" t="n">
-        <v>56</v>
+        <v>2</v>
       </c>
       <c r="F224" t="n">
-        <v>12307</v>
+        <v>251</v>
       </c>
       <c r="G224" t="n">
-        <v>4066.1</v>
+        <v>0</v>
       </c>
       <c r="H224" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr"/>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Nexliv-Portable Blender-B0FS6TB7CP-PT-SP</t>
+          <t>Nexlev-Defensive-AT</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>B08L46ZKKZ</t>
+          <t>B0DJFH4K8B</t>
         </is>
       </c>
       <c r="D225" t="n">
-        <v>442.58</v>
+        <v>0</v>
       </c>
       <c r="E225" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="F225" t="n">
-        <v>989</v>
+        <v>3</v>
       </c>
       <c r="G225" t="n">
         <v>0</v>
@@ -6736,22 +6736,22 @@
       <c r="A226" t="inlineStr"/>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Nexliv-Portable Blender-B0FS6TB7CP-PT-SP</t>
+          <t>Nexlev-Defensive-AT</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>B0FNQS4RRD</t>
+          <t>B0DJFH6RTL</t>
         </is>
       </c>
       <c r="D226" t="n">
-        <v>15.19</v>
+        <v>0</v>
       </c>
       <c r="E226" t="n">
+        <v>0</v>
+      </c>
+      <c r="F226" t="n">
         <v>1</v>
-      </c>
-      <c r="F226" t="n">
-        <v>599</v>
       </c>
       <c r="G226" t="n">
         <v>0</v>
@@ -6764,78 +6764,78 @@
       <c r="A227" t="inlineStr"/>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Nexliv-Portable Sewing Machine-B0D9KDQCCM-Phrase-SP</t>
+          <t>Nexlev-Defensive-AT</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>B0D9KDQCCM</t>
+          <t>B0DK9LYT4P</t>
         </is>
       </c>
       <c r="D227" t="n">
-        <v>42.95</v>
+        <v>0</v>
       </c>
       <c r="E227" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F227" t="n">
-        <v>183</v>
+        <v>7</v>
       </c>
       <c r="G227" t="n">
-        <v>1008.57</v>
+        <v>0</v>
       </c>
       <c r="H227" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr"/>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Nexliv-Stand Mixer-B0DVC7VJP1-BM-SP</t>
+          <t>Nexlev-Defensive-AT</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>B0DVC7VJP1</t>
+          <t>B0DKJSCLBD</t>
         </is>
       </c>
       <c r="D228" t="n">
-        <v>574.9400000000001</v>
+        <v>6.52</v>
       </c>
       <c r="E228" t="n">
-        <v>40</v>
+        <v>2</v>
       </c>
       <c r="F228" t="n">
-        <v>9758</v>
+        <v>60</v>
       </c>
       <c r="G228" t="n">
-        <v>5083.9</v>
+        <v>0</v>
       </c>
       <c r="H228" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr"/>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Nexliv-Stand Mixer-B0DVC7VJP1-CT-SP</t>
+          <t>Nexlev-Defensive-AT</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>B0DVC7VJP1</t>
+          <t>B0DNJF1BLS</t>
         </is>
       </c>
       <c r="D229" t="n">
-        <v>0</v>
+        <v>4.64</v>
       </c>
       <c r="E229" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F229" t="n">
-        <v>171</v>
+        <v>17</v>
       </c>
       <c r="G229" t="n">
         <v>0</v>
@@ -6848,22 +6848,22 @@
       <c r="A230" t="inlineStr"/>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Nexliv-Steam Cleaner,B0F43P6D23-KW-SP-Exact</t>
+          <t>Nexlev-Defensive-AT</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0DNJJKBKG</t>
         </is>
       </c>
       <c r="D230" t="n">
-        <v>10.41</v>
+        <v>0</v>
       </c>
       <c r="E230" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F230" t="n">
-        <v>521</v>
+        <v>11</v>
       </c>
       <c r="G230" t="n">
         <v>0</v>
@@ -6876,22 +6876,22 @@
       <c r="A231" t="inlineStr"/>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Nexliv-Steam Cleaner---B0F43P6D23-PT-SP</t>
+          <t>Nexlev-Defensive-AT</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0DT6Y7KJM</t>
         </is>
       </c>
       <c r="D231" t="n">
-        <v>517.9300000000001</v>
+        <v>0</v>
       </c>
       <c r="E231" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="F231" t="n">
-        <v>4746</v>
+        <v>7</v>
       </c>
       <c r="G231" t="n">
         <v>0</v>
@@ -6904,22 +6904,22 @@
       <c r="A232" t="inlineStr"/>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Nexliv-Steam Cleaner-B0F43P6D23-BM-SP</t>
+          <t>Nexlev-Defensive-AT</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0DV9CY3XR</t>
         </is>
       </c>
       <c r="D232" t="n">
-        <v>140.36</v>
+        <v>0</v>
       </c>
       <c r="E232" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="F232" t="n">
-        <v>322</v>
+        <v>15</v>
       </c>
       <c r="G232" t="n">
         <v>0</v>
@@ -6932,22 +6932,22 @@
       <c r="A233" t="inlineStr"/>
       <c r="B233" t="inlineStr">
         <is>
-          <t>Nexliv-Steam Mop Floor Cleaner-B0DNJS23HS-CT-SP</t>
+          <t>Nexlev-Defensive-AT</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0DVC58QPZ</t>
         </is>
       </c>
       <c r="D233" t="n">
-        <v>257.79</v>
+        <v>0</v>
       </c>
       <c r="E233" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="F233" t="n">
-        <v>1972</v>
+        <v>4</v>
       </c>
       <c r="G233" t="n">
         <v>0</v>
@@ -6960,22 +6960,22 @@
       <c r="A234" t="inlineStr"/>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Nexliv-Steam Mop Floor Cleaner-B0DNJS23HS-Exact</t>
+          <t>Nexlev-Defensive-AT</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0DVC9PRSD</t>
         </is>
       </c>
       <c r="D234" t="n">
-        <v>500.36</v>
+        <v>0</v>
       </c>
       <c r="E234" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="F234" t="n">
-        <v>2501</v>
+        <v>1</v>
       </c>
       <c r="G234" t="n">
         <v>0</v>
@@ -6988,22 +6988,22 @@
       <c r="A235" t="inlineStr"/>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Nexliv/Steam Cleaner-B0F43P6D23-Exact(1)-SP</t>
+          <t>Nexlev-Defensive-AT</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0DVSZ2VVJ</t>
         </is>
       </c>
       <c r="D235" t="n">
-        <v>13.07</v>
+        <v>0</v>
       </c>
       <c r="E235" t="n">
+        <v>0</v>
+      </c>
+      <c r="F235" t="n">
         <v>1</v>
-      </c>
-      <c r="F235" t="n">
-        <v>34</v>
       </c>
       <c r="G235" t="n">
         <v>0</v>
@@ -7016,22 +7016,22 @@
       <c r="A236" t="inlineStr"/>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Nexlive-Cordless Spin Mop-B0GKNGWLJ2-Exact-SP</t>
+          <t>Nexlev-Defensive-AT</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>B0GKNGWLJ2</t>
+          <t>B0F29SZCVF</t>
         </is>
       </c>
       <c r="D236" t="n">
-        <v>376.66</v>
+        <v>0</v>
       </c>
       <c r="E236" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="F236" t="n">
-        <v>6670</v>
+        <v>7</v>
       </c>
       <c r="G236" t="n">
         <v>0</v>
@@ -7044,22 +7044,22 @@
       <c r="A237" t="inlineStr"/>
       <c r="B237" t="inlineStr">
         <is>
-          <t>Nexlive-Oil Applicator Comb-B0DKK15YNJ-PH-SP</t>
+          <t>Nexlev-Defensive-AT</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>B0DKK15YNJ</t>
+          <t>B0F2N11VTN</t>
         </is>
       </c>
       <c r="D237" t="n">
-        <v>39.29</v>
+        <v>0</v>
       </c>
       <c r="E237" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F237" t="n">
-        <v>1015</v>
+        <v>2</v>
       </c>
       <c r="G237" t="n">
         <v>0</v>
@@ -7072,22 +7072,22 @@
       <c r="A238" t="inlineStr"/>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Nexlive-Steam Mop Flor Cleaner-B0DNJS23HS-PT/-SP</t>
+          <t>Nexlev-Defensive-AT</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0F2N37819</t>
         </is>
       </c>
       <c r="D238" t="n">
-        <v>383.34</v>
+        <v>4.26</v>
       </c>
       <c r="E238" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="F238" t="n">
-        <v>1342</v>
+        <v>5</v>
       </c>
       <c r="G238" t="n">
         <v>0</v>
@@ -7100,22 +7100,22 @@
       <c r="A239" t="inlineStr"/>
       <c r="B239" t="inlineStr">
         <is>
-          <t>Nexllev-Vacuum Cleaner-B0DCK7ZH5P-Exact</t>
+          <t>Nexlev-Defensive-AT</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>B0DCK7ZH5P</t>
+          <t>B0F678L8YT</t>
         </is>
       </c>
       <c r="D239" t="n">
-        <v>356.99</v>
+        <v>2.02</v>
       </c>
       <c r="E239" t="n">
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="F239" t="n">
-        <v>4594</v>
+        <v>12</v>
       </c>
       <c r="G239" t="n">
         <v>0</v>
@@ -7128,27 +7128,1511 @@
       <c r="A240" t="inlineStr"/>
       <c r="B240" t="inlineStr">
         <is>
+          <t>Nexlev-Defensive-AT</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>B0F679QJH4</t>
+        </is>
+      </c>
+      <c r="D240" t="n">
+        <v>0</v>
+      </c>
+      <c r="E240" t="n">
+        <v>0</v>
+      </c>
+      <c r="F240" t="n">
+        <v>1</v>
+      </c>
+      <c r="G240" t="n">
+        <v>0</v>
+      </c>
+      <c r="H240" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr"/>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>Nexlev-Defensive-AT</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>B0F67BSF2R</t>
+        </is>
+      </c>
+      <c r="D241" t="n">
+        <v>0</v>
+      </c>
+      <c r="E241" t="n">
+        <v>0</v>
+      </c>
+      <c r="F241" t="n">
+        <v>11</v>
+      </c>
+      <c r="G241" t="n">
+        <v>0</v>
+      </c>
+      <c r="H241" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr"/>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>Nexlev-Defensive-AT</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>B0FJ1ZB4G9</t>
+        </is>
+      </c>
+      <c r="D242" t="n">
+        <v>0</v>
+      </c>
+      <c r="E242" t="n">
+        <v>0</v>
+      </c>
+      <c r="F242" t="n">
+        <v>1</v>
+      </c>
+      <c r="G242" t="n">
+        <v>0</v>
+      </c>
+      <c r="H242" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr"/>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>Nexlev-Defensive-AT</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>B0FJG5PFGQ</t>
+        </is>
+      </c>
+      <c r="D243" t="n">
+        <v>0</v>
+      </c>
+      <c r="E243" t="n">
+        <v>0</v>
+      </c>
+      <c r="F243" t="n">
+        <v>19</v>
+      </c>
+      <c r="G243" t="n">
+        <v>0</v>
+      </c>
+      <c r="H243" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr"/>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>Nexlev-Defensive-AT</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>B0FMF1D9NV</t>
+        </is>
+      </c>
+      <c r="D244" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="E244" t="n">
+        <v>1</v>
+      </c>
+      <c r="F244" t="n">
+        <v>10</v>
+      </c>
+      <c r="G244" t="n">
+        <v>0</v>
+      </c>
+      <c r="H244" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr"/>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>Nexlev-Defensive-AT</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>B0FS7T8151</t>
+        </is>
+      </c>
+      <c r="D245" t="n">
+        <v>0</v>
+      </c>
+      <c r="E245" t="n">
+        <v>0</v>
+      </c>
+      <c r="F245" t="n">
+        <v>0</v>
+      </c>
+      <c r="G245" t="n">
+        <v>0</v>
+      </c>
+      <c r="H245" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr"/>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>Nexlev-Defensive-AT</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>B0FYNKYJFN</t>
+        </is>
+      </c>
+      <c r="D246" t="n">
+        <v>0</v>
+      </c>
+      <c r="E246" t="n">
+        <v>0</v>
+      </c>
+      <c r="F246" t="n">
+        <v>17</v>
+      </c>
+      <c r="G246" t="n">
+        <v>0</v>
+      </c>
+      <c r="H246" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr"/>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>Nexlev-Defensive-AT</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>B0GGHZWMVW</t>
+        </is>
+      </c>
+      <c r="D247" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E247" t="n">
+        <v>3</v>
+      </c>
+      <c r="F247" t="n">
+        <v>206</v>
+      </c>
+      <c r="G247" t="n">
+        <v>0</v>
+      </c>
+      <c r="H247" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr"/>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>Nexlev-Multi Ad Group-Steam Cleaner -SP-KT -Exact/Phrase/Broad</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>B0CDPP45BM</t>
+        </is>
+      </c>
+      <c r="D248" t="n">
+        <v>2241.97</v>
+      </c>
+      <c r="E248" t="n">
+        <v>79</v>
+      </c>
+      <c r="F248" t="n">
+        <v>16749</v>
+      </c>
+      <c r="G248" t="n">
+        <v>5083.9</v>
+      </c>
+      <c r="H248" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr"/>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>Nexlev-SP- B0GN8WW6BC - Stand Mixer with Stainless Steel Bowl - BM</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>B0GN8WW6BC</t>
+        </is>
+      </c>
+      <c r="D249" t="n">
+        <v>0</v>
+      </c>
+      <c r="E249" t="n">
+        <v>0</v>
+      </c>
+      <c r="F249" t="n">
+        <v>169</v>
+      </c>
+      <c r="G249" t="n">
+        <v>0</v>
+      </c>
+      <c r="H249" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr"/>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>Nexlev-Steamer-PT(SEAHELTON)</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>B0CDPP45BM</t>
+        </is>
+      </c>
+      <c r="D250" t="n">
+        <v>7.36</v>
+      </c>
+      <c r="E250" t="n">
+        <v>1</v>
+      </c>
+      <c r="F250" t="n">
+        <v>43</v>
+      </c>
+      <c r="G250" t="n">
+        <v>0</v>
+      </c>
+      <c r="H250" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr"/>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>Nexlev-Steamer-PT(SEAHELTON)</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>B0F43P6D23</t>
+        </is>
+      </c>
+      <c r="D251" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="E251" t="n">
+        <v>2</v>
+      </c>
+      <c r="F251" t="n">
+        <v>68</v>
+      </c>
+      <c r="G251" t="n">
+        <v>0</v>
+      </c>
+      <c r="H251" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr"/>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>Nexlev-steam Cleaner For Home-B0CDPP45BM-BM-SP</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>B0CDPP45BM</t>
+        </is>
+      </c>
+      <c r="D252" t="n">
+        <v>39.51</v>
+      </c>
+      <c r="E252" t="n">
+        <v>3</v>
+      </c>
+      <c r="F252" t="n">
+        <v>264</v>
+      </c>
+      <c r="G252" t="n">
+        <v>0</v>
+      </c>
+      <c r="H252" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr"/>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>Nexlev-steam Cleaner For Home-B0CDPP45BM-Exact-SP</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>B0CDPP45BM</t>
+        </is>
+      </c>
+      <c r="D253" t="n">
+        <v>0</v>
+      </c>
+      <c r="E253" t="n">
+        <v>0</v>
+      </c>
+      <c r="F253" t="n">
+        <v>2</v>
+      </c>
+      <c r="G253" t="n">
+        <v>0</v>
+      </c>
+      <c r="H253" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr"/>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>Nexliv- Steam Mop-B0D2LJSQXZ-AT-SP</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>B0D2LJSQXZ</t>
+        </is>
+      </c>
+      <c r="D254" t="n">
+        <v>450.78</v>
+      </c>
+      <c r="E254" t="n">
+        <v>52</v>
+      </c>
+      <c r="F254" t="n">
+        <v>5523</v>
+      </c>
+      <c r="G254" t="n">
+        <v>0</v>
+      </c>
+      <c r="H254" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr"/>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>Nexliv- Steam Mop-B0D2LJSQXZ-PT-SP</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>B0D2LJSQXZ</t>
+        </is>
+      </c>
+      <c r="D255" t="n">
+        <v>454.82</v>
+      </c>
+      <c r="E255" t="n">
+        <v>50</v>
+      </c>
+      <c r="F255" t="n">
+        <v>3580</v>
+      </c>
+      <c r="G255" t="n">
+        <v>3219.49</v>
+      </c>
+      <c r="H255" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr"/>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>Nexliv--Steam Cleaner--B0F43P6D23-AT-SP</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>B0F43P6D23</t>
+        </is>
+      </c>
+      <c r="D256" t="n">
+        <v>0</v>
+      </c>
+      <c r="E256" t="n">
+        <v>0</v>
+      </c>
+      <c r="F256" t="n">
+        <v>0</v>
+      </c>
+      <c r="G256" t="n">
+        <v>0</v>
+      </c>
+      <c r="H256" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr"/>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>Nexliv-2 in 1 Stick Vacuum Cleaner-B0DCGHVN81-AT</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>B0DCGHVN81</t>
+        </is>
+      </c>
+      <c r="D257" t="n">
+        <v>1220.51</v>
+      </c>
+      <c r="E257" t="n">
+        <v>186</v>
+      </c>
+      <c r="F257" t="n">
+        <v>33400</v>
+      </c>
+      <c r="G257" t="n">
+        <v>7115.24</v>
+      </c>
+      <c r="H257" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr"/>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>Nexliv-2 in 1 Stick Vacuum Cleaner-B0DCGHVN81-BM-SP</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>B0DCGHVN81</t>
+        </is>
+      </c>
+      <c r="D258" t="n">
+        <v>0</v>
+      </c>
+      <c r="E258" t="n">
+        <v>0</v>
+      </c>
+      <c r="F258" t="n">
+        <v>0</v>
+      </c>
+      <c r="G258" t="n">
+        <v>0</v>
+      </c>
+      <c r="H258" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr"/>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>Nexliv-2 in 1 Stick Vacuum Cleaner-B0DCGHVN81-PT(2)-SP</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>B0DCGHVN81</t>
+        </is>
+      </c>
+      <c r="D259" t="n">
+        <v>0</v>
+      </c>
+      <c r="E259" t="n">
+        <v>0</v>
+      </c>
+      <c r="F259" t="n">
+        <v>0</v>
+      </c>
+      <c r="G259" t="n">
+        <v>0</v>
+      </c>
+      <c r="H259" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr"/>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>Nexliv-2 in 1 Stick Vacuum Cleaner-B0DCGHVN81-PT-SP</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>B0DCGHVN81</t>
+        </is>
+      </c>
+      <c r="D260" t="n">
+        <v>1132.5</v>
+      </c>
+      <c r="E260" t="n">
+        <v>90</v>
+      </c>
+      <c r="F260" t="n">
+        <v>8370</v>
+      </c>
+      <c r="G260" t="n">
+        <v>0</v>
+      </c>
+      <c r="H260" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr"/>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>Nexliv-2 in 1 Stick Vacuum Cleaner-B0DCGHVN81-PT-SP(1)</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>B0DCGHVN81</t>
+        </is>
+      </c>
+      <c r="D261" t="n">
+        <v>0</v>
+      </c>
+      <c r="E261" t="n">
+        <v>0</v>
+      </c>
+      <c r="F261" t="n">
+        <v>1</v>
+      </c>
+      <c r="G261" t="n">
+        <v>0</v>
+      </c>
+      <c r="H261" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr"/>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>Nexliv-2 in 1 Stick Vacuum Cleaner-B0DCGHVN81-PT-SP(2)</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>B0DCGHVN81</t>
+        </is>
+      </c>
+      <c r="D262" t="n">
+        <v>0</v>
+      </c>
+      <c r="E262" t="n">
+        <v>0</v>
+      </c>
+      <c r="F262" t="n">
+        <v>14</v>
+      </c>
+      <c r="G262" t="n">
+        <v>0</v>
+      </c>
+      <c r="H262" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr"/>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>Nexliv-2 in 1 Stick Vacuum Cleaner-B0DCGHVN81-Phrase-SP(2)</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>B0DCGHVN81</t>
+        </is>
+      </c>
+      <c r="D263" t="n">
+        <v>692.85</v>
+      </c>
+      <c r="E263" t="n">
+        <v>52</v>
+      </c>
+      <c r="F263" t="n">
+        <v>33195</v>
+      </c>
+      <c r="G263" t="n">
+        <v>1778.81</v>
+      </c>
+      <c r="H263" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr"/>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>Nexliv-B0D9KDQCCM-Portable Sewing Machine-AT-SP</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>B0D9KDQCCM</t>
+        </is>
+      </c>
+      <c r="D264" t="n">
+        <v>460.82</v>
+      </c>
+      <c r="E264" t="n">
+        <v>57</v>
+      </c>
+      <c r="F264" t="n">
+        <v>4935</v>
+      </c>
+      <c r="G264" t="n">
+        <v>0</v>
+      </c>
+      <c r="H264" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr"/>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>Nexliv-B0DCK4DR1B-Skin Lift Device-PT-SP</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>B0DCK4DR1B</t>
+        </is>
+      </c>
+      <c r="D265" t="n">
+        <v>13.12</v>
+      </c>
+      <c r="E265" t="n">
+        <v>1</v>
+      </c>
+      <c r="F265" t="n">
+        <v>284</v>
+      </c>
+      <c r="G265" t="n">
+        <v>0</v>
+      </c>
+      <c r="H265" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr"/>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>Nexliv-B0F43P6D23-KW-SP-Exact(111)</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>B0F43P6D23</t>
+        </is>
+      </c>
+      <c r="D266" t="n">
+        <v>0</v>
+      </c>
+      <c r="E266" t="n">
+        <v>0</v>
+      </c>
+      <c r="F266" t="n">
+        <v>0</v>
+      </c>
+      <c r="G266" t="n">
+        <v>0</v>
+      </c>
+      <c r="H266" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr"/>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>Nexliv-Electric Food Kettle-B0DFCG2VGS-BM-SP</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>B0DFCG2VGS</t>
+        </is>
+      </c>
+      <c r="D267" t="n">
+        <v>1342.73</v>
+      </c>
+      <c r="E267" t="n">
+        <v>131</v>
+      </c>
+      <c r="F267" t="n">
+        <v>44449</v>
+      </c>
+      <c r="G267" t="n">
+        <v>0</v>
+      </c>
+      <c r="H267" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr"/>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>Nexliv-Handheld Steamer-B0D383WQPB-BM-SP</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>B0D383WQPB</t>
+        </is>
+      </c>
+      <c r="D268" t="n">
+        <v>1235.63</v>
+      </c>
+      <c r="E268" t="n">
+        <v>55</v>
+      </c>
+      <c r="F268" t="n">
+        <v>14735</v>
+      </c>
+      <c r="G268" t="n">
+        <v>3388.14</v>
+      </c>
+      <c r="H268" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr"/>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>Nexliv-Handheld Steamer-B0D383WQPB-CT</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>B0D383WQPB</t>
+        </is>
+      </c>
+      <c r="D269" t="n">
+        <v>1289.87</v>
+      </c>
+      <c r="E269" t="n">
+        <v>64</v>
+      </c>
+      <c r="F269" t="n">
+        <v>23133</v>
+      </c>
+      <c r="G269" t="n">
+        <v>2033.05</v>
+      </c>
+      <c r="H269" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr"/>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>Nexliv-Mattress Sofa-B0CYSLCRQS-AT-SP</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>B0CYSLCRQS</t>
+        </is>
+      </c>
+      <c r="D270" t="n">
+        <v>1718.82</v>
+      </c>
+      <c r="E270" t="n">
+        <v>475</v>
+      </c>
+      <c r="F270" t="n">
+        <v>45128</v>
+      </c>
+      <c r="G270" t="n">
+        <v>2880.51</v>
+      </c>
+      <c r="H270" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr"/>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>Nexliv-Mattress Sofa-B0CYSLCRQS-Exact-SP</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>B0CYSLCRQS</t>
+        </is>
+      </c>
+      <c r="D271" t="n">
+        <v>119.08</v>
+      </c>
+      <c r="E271" t="n">
+        <v>21</v>
+      </c>
+      <c r="F271" t="n">
+        <v>934</v>
+      </c>
+      <c r="G271" t="n">
+        <v>0</v>
+      </c>
+      <c r="H271" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr"/>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>Nexliv-Portable Blender-B0FS6TB7CP-BM</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>B0FS6TB7CP</t>
+        </is>
+      </c>
+      <c r="D272" t="n">
+        <v>1278.43</v>
+      </c>
+      <c r="E272" t="n">
+        <v>89</v>
+      </c>
+      <c r="F272" t="n">
+        <v>19247</v>
+      </c>
+      <c r="G272" t="n">
+        <v>0</v>
+      </c>
+      <c r="H272" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr"/>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>Nexliv-Portable Blender-B0FS6TB7CP-CT</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>B0FS6TB7CP</t>
+        </is>
+      </c>
+      <c r="D273" t="n">
+        <v>2850.7</v>
+      </c>
+      <c r="E273" t="n">
+        <v>167</v>
+      </c>
+      <c r="F273" t="n">
+        <v>35788</v>
+      </c>
+      <c r="G273" t="n">
+        <v>6099.15</v>
+      </c>
+      <c r="H273" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr"/>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>Nexliv-Portable Blender-B0FS6TB7CP-PT(2)-SP</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>B0FS6TB7CP</t>
+        </is>
+      </c>
+      <c r="D274" t="n">
+        <v>2953.95</v>
+      </c>
+      <c r="E274" t="n">
+        <v>182</v>
+      </c>
+      <c r="F274" t="n">
+        <v>38573</v>
+      </c>
+      <c r="G274" t="n">
+        <v>6099.15</v>
+      </c>
+      <c r="H274" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr"/>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>Nexliv-Portable Blender-B0FS6TB7CP-PT-SP</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>B08L46ZKKZ</t>
+        </is>
+      </c>
+      <c r="D275" t="n">
+        <v>2354.57</v>
+      </c>
+      <c r="E275" t="n">
+        <v>173</v>
+      </c>
+      <c r="F275" t="n">
+        <v>7512</v>
+      </c>
+      <c r="G275" t="n">
+        <v>15586.48</v>
+      </c>
+      <c r="H275" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr"/>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>Nexliv-Portable Blender-B0FS6TB7CP-PT-SP</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>B0FNQS4RRD</t>
+        </is>
+      </c>
+      <c r="D276" t="n">
+        <v>252.5</v>
+      </c>
+      <c r="E276" t="n">
+        <v>16</v>
+      </c>
+      <c r="F276" t="n">
+        <v>4743</v>
+      </c>
+      <c r="G276" t="n">
+        <v>5083.9</v>
+      </c>
+      <c r="H276" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr"/>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>Nexliv-Portable Sewing Machine-B0D9KDQCCM-Phrase-SP</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>B0D9KDQCCM</t>
+        </is>
+      </c>
+      <c r="D277" t="n">
+        <v>135.41</v>
+      </c>
+      <c r="E277" t="n">
+        <v>15</v>
+      </c>
+      <c r="F277" t="n">
+        <v>1361</v>
+      </c>
+      <c r="G277" t="n">
+        <v>1979.05</v>
+      </c>
+      <c r="H277" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr"/>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>Nexliv-Stand Mixer-B0DVC7VJP1-BM-SP</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>B0DVC7VJP1</t>
+        </is>
+      </c>
+      <c r="D278" t="n">
+        <v>1512.75</v>
+      </c>
+      <c r="E278" t="n">
+        <v>103</v>
+      </c>
+      <c r="F278" t="n">
+        <v>26908</v>
+      </c>
+      <c r="G278" t="n">
+        <v>10167.8</v>
+      </c>
+      <c r="H278" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr"/>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>Nexliv-Stand Mixer-B0DVC7VJP1-CT-SP</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>B0DVC7VJP1</t>
+        </is>
+      </c>
+      <c r="D279" t="n">
+        <v>61.65</v>
+      </c>
+      <c r="E279" t="n">
+        <v>5</v>
+      </c>
+      <c r="F279" t="n">
+        <v>546</v>
+      </c>
+      <c r="G279" t="n">
+        <v>0</v>
+      </c>
+      <c r="H279" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr"/>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>Nexliv-Steam Cleaner,B0F43P6D23-KW-SP-Exact</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>B0F43P6D23</t>
+        </is>
+      </c>
+      <c r="D280" t="n">
+        <v>79.96000000000001</v>
+      </c>
+      <c r="E280" t="n">
+        <v>5</v>
+      </c>
+      <c r="F280" t="n">
+        <v>1396</v>
+      </c>
+      <c r="G280" t="n">
+        <v>0</v>
+      </c>
+      <c r="H280" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr"/>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>Nexliv-Steam Cleaner---B0F43P6D23-PT-SP</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>B0F43P6D23</t>
+        </is>
+      </c>
+      <c r="D281" t="n">
+        <v>950.6900000000001</v>
+      </c>
+      <c r="E281" t="n">
+        <v>55</v>
+      </c>
+      <c r="F281" t="n">
+        <v>8009</v>
+      </c>
+      <c r="G281" t="n">
+        <v>0</v>
+      </c>
+      <c r="H281" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr"/>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>Nexliv-Steam Cleaner-B0F43P6D23-AT-SP</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>B0F43P6D23</t>
+        </is>
+      </c>
+      <c r="D282" t="n">
+        <v>0</v>
+      </c>
+      <c r="E282" t="n">
+        <v>0</v>
+      </c>
+      <c r="F282" t="n">
+        <v>15</v>
+      </c>
+      <c r="G282" t="n">
+        <v>0</v>
+      </c>
+      <c r="H282" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr"/>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>Nexliv-Steam Cleaner-B0F43P6D23-BM-SP</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>B0F43P6D23</t>
+        </is>
+      </c>
+      <c r="D283" t="n">
+        <v>292.84</v>
+      </c>
+      <c r="E283" t="n">
+        <v>21</v>
+      </c>
+      <c r="F283" t="n">
+        <v>484</v>
+      </c>
+      <c r="G283" t="n">
+        <v>0</v>
+      </c>
+      <c r="H283" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr"/>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>Nexliv-Steam Mop Floor Cleaner-B0DNJS23HS-BM-and exact-SP</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>B0DNJS23HS</t>
+        </is>
+      </c>
+      <c r="D284" t="n">
+        <v>0</v>
+      </c>
+      <c r="E284" t="n">
+        <v>0</v>
+      </c>
+      <c r="F284" t="n">
+        <v>0</v>
+      </c>
+      <c r="G284" t="n">
+        <v>0</v>
+      </c>
+      <c r="H284" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr"/>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>Nexliv-Steam Mop Floor Cleaner-B0DNJS23HS-CT-SP</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>B0DNJS23HS</t>
+        </is>
+      </c>
+      <c r="D285" t="n">
+        <v>1217.12</v>
+      </c>
+      <c r="E285" t="n">
+        <v>56</v>
+      </c>
+      <c r="F285" t="n">
+        <v>4378</v>
+      </c>
+      <c r="G285" t="n">
+        <v>0</v>
+      </c>
+      <c r="H285" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr"/>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>Nexliv-Steam Mop Floor Cleaner-B0DNJS23HS-Exact</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>B0DNJS23HS</t>
+        </is>
+      </c>
+      <c r="D286" t="n">
+        <v>1705</v>
+      </c>
+      <c r="E286" t="n">
+        <v>85</v>
+      </c>
+      <c r="F286" t="n">
+        <v>9629</v>
+      </c>
+      <c r="G286" t="n">
+        <v>0</v>
+      </c>
+      <c r="H286" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr"/>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>Nexliv/Steam Cleaner-B0F43P6D23-Exact(1)-SP</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>B0F43P6D23</t>
+        </is>
+      </c>
+      <c r="D287" t="n">
+        <v>13.07</v>
+      </c>
+      <c r="E287" t="n">
+        <v>1</v>
+      </c>
+      <c r="F287" t="n">
+        <v>66</v>
+      </c>
+      <c r="G287" t="n">
+        <v>0</v>
+      </c>
+      <c r="H287" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr"/>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>Nexlive-Cordless Spin Mop-B0GKNGWLJ2-Exact-SP</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>B0GKNGWLJ2</t>
+        </is>
+      </c>
+      <c r="D288" t="n">
+        <v>932.8200000000001</v>
+      </c>
+      <c r="E288" t="n">
+        <v>83</v>
+      </c>
+      <c r="F288" t="n">
+        <v>14930</v>
+      </c>
+      <c r="G288" t="n">
+        <v>0</v>
+      </c>
+      <c r="H288" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr"/>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>Nexlive-Cordless Spin Mop-B0GKNGWLJ2-PT-SP</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>B0GKNGWLJ2</t>
+        </is>
+      </c>
+      <c r="D289" t="n">
+        <v>1881.89</v>
+      </c>
+      <c r="E289" t="n">
+        <v>156</v>
+      </c>
+      <c r="F289" t="n">
+        <v>74239</v>
+      </c>
+      <c r="G289" t="n">
+        <v>3304.24</v>
+      </c>
+      <c r="H289" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr"/>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>Nexlive-Oil Applicator Comb-B0DKK15YNJ-PH-SP</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>B0DKK15YNJ</t>
+        </is>
+      </c>
+      <c r="D290" t="n">
+        <v>289.25</v>
+      </c>
+      <c r="E290" t="n">
+        <v>29</v>
+      </c>
+      <c r="F290" t="n">
+        <v>4022</v>
+      </c>
+      <c r="G290" t="n">
+        <v>0</v>
+      </c>
+      <c r="H290" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr"/>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>Nexlive-Steam Mop Flor Cleaner-B0DNJS23HS-PT/-SP</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>B0DNJS23HS</t>
+        </is>
+      </c>
+      <c r="D291" t="n">
+        <v>567.24</v>
+      </c>
+      <c r="E291" t="n">
+        <v>30</v>
+      </c>
+      <c r="F291" t="n">
+        <v>2710</v>
+      </c>
+      <c r="G291" t="n">
+        <v>0</v>
+      </c>
+      <c r="H291" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr"/>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>Nexllev-Vacuum Cleaner-B0DCK7ZH5P-Exact</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>B0DCK7ZH5P</t>
+        </is>
+      </c>
+      <c r="D292" t="n">
+        <v>960.6600000000001</v>
+      </c>
+      <c r="E292" t="n">
+        <v>87</v>
+      </c>
+      <c r="F292" t="n">
+        <v>14650</v>
+      </c>
+      <c r="G292" t="n">
+        <v>2880.5</v>
+      </c>
+      <c r="H292" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr"/>
+      <c r="B293" t="inlineStr">
+        <is>
           <t>nexliv-Mattress Sofa Carpet B0DCK7ZH5P-Phrase-SP</t>
         </is>
       </c>
-      <c r="C240" t="inlineStr">
+      <c r="C293" t="inlineStr">
         <is>
           <t>B0DCK7ZH5P</t>
         </is>
       </c>
-      <c r="D240" t="n">
-        <v>294.05</v>
-      </c>
-      <c r="E240" t="n">
-        <v>14</v>
-      </c>
-      <c r="F240" t="n">
-        <v>1386</v>
-      </c>
-      <c r="G240" t="n">
-        <v>0</v>
-      </c>
-      <c r="H240" t="n">
+      <c r="D293" t="n">
+        <v>815.7</v>
+      </c>
+      <c r="E293" t="n">
+        <v>43</v>
+      </c>
+      <c r="F293" t="n">
+        <v>6117</v>
+      </c>
+      <c r="G293" t="n">
+        <v>0</v>
+      </c>
+      <c r="H293" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8369,13 +9853,13 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>0</v>
+        <v>253.79</v>
       </c>
       <c r="E43" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F43" t="n">
-        <v>1082</v>
+        <v>3524</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -8599,7 +10083,7 @@
         <v>0</v>
       </c>
       <c r="F51" t="n">
-        <v>46</v>
+        <v>770</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -8627,7 +10111,7 @@
         <v>0</v>
       </c>
       <c r="F52" t="n">
-        <v>171</v>
+        <v>457</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -8649,13 +10133,13 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>0</v>
+        <v>6.07</v>
       </c>
       <c r="E53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F53" t="n">
-        <v>196</v>
+        <v>466</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
@@ -8683,7 +10167,7 @@
         <v>1</v>
       </c>
       <c r="F54" t="n">
-        <v>185</v>
+        <v>753</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
@@ -8711,7 +10195,7 @@
         <v>0</v>
       </c>
       <c r="F55" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
@@ -8731,7 +10215,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I39"/>
+  <dimension ref="A1:I43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8794,16 +10278,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1948</v>
+        <v>7711</v>
       </c>
       <c r="E2" t="n">
-        <v>18</v>
+        <v>49</v>
       </c>
       <c r="F2" t="n">
-        <v>602.1633333333333</v>
+        <v>1947.11</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>960.1700000000001</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -8827,16 +10311,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1948</v>
+        <v>7711</v>
       </c>
       <c r="E3" t="n">
-        <v>18</v>
+        <v>49</v>
       </c>
       <c r="F3" t="n">
-        <v>602.1633333333333</v>
+        <v>1947.11</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>960.1700000000001</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -8860,16 +10344,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1948</v>
+        <v>7711</v>
       </c>
       <c r="E4" t="n">
-        <v>18</v>
+        <v>49</v>
       </c>
       <c r="F4" t="n">
-        <v>602.1633333333333</v>
+        <v>1947.11</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>960.1700000000001</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -8893,16 +10377,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1352</v>
+        <v>3726</v>
       </c>
       <c r="E5" t="n">
-        <v>50</v>
+        <v>122</v>
       </c>
       <c r="F5" t="n">
-        <v>393.585</v>
+        <v>1063.41</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>2118.22</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -8926,16 +10410,16 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1352</v>
+        <v>3726</v>
       </c>
       <c r="E6" t="n">
-        <v>50</v>
+        <v>122</v>
       </c>
       <c r="F6" t="n">
-        <v>393.585</v>
+        <v>1063.41</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>2118.22</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -8959,19 +10443,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2205</v>
+        <v>8601</v>
       </c>
       <c r="E7" t="n">
-        <v>12</v>
+        <v>47</v>
       </c>
       <c r="F7" t="n">
-        <v>187.01</v>
+        <v>588.5933333333334</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>1904.126666666667</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -8992,19 +10476,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>2205</v>
+        <v>8601</v>
       </c>
       <c r="E8" t="n">
-        <v>12</v>
+        <v>47</v>
       </c>
       <c r="F8" t="n">
-        <v>187.01</v>
+        <v>588.5933333333334</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>1904.126666666667</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -9025,19 +10509,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2205</v>
+        <v>8601</v>
       </c>
       <c r="E9" t="n">
-        <v>12</v>
+        <v>47</v>
       </c>
       <c r="F9" t="n">
-        <v>187.01</v>
+        <v>588.5933333333334</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>1904.126666666667</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -9058,16 +10542,16 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1519</v>
+        <v>4745</v>
       </c>
       <c r="E10" t="n">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="F10" t="n">
-        <v>162.2621420858796</v>
+        <v>480.6366666666667</v>
       </c>
       <c r="G10" t="n">
-        <v>1366.358235482948</v>
+        <v>1491.106666666667</v>
       </c>
       <c r="H10" t="n">
         <v>1</v>
@@ -9087,23 +10571,23 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>B0DKK15YNJ</t>
+          <t>B0DCGHKRXX</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>3454</v>
+        <v>4745</v>
       </c>
       <c r="E11" t="n">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="F11" t="n">
-        <v>368.9678579141205</v>
+        <v>480.6366666666667</v>
       </c>
       <c r="G11" t="n">
-        <v>3106.961764517052</v>
+        <v>1491.106666666667</v>
       </c>
       <c r="H11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -9115,28 +10599,28 @@
       <c r="A12" t="inlineStr"/>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Nexlev-B0CDPP45BM-Cleaning Machine-SB-PT</t>
+          <t>Nexlev -Catch All- Scalp Massager-SB-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>B0CDPP45BM</t>
+          <t>B0DKK15YNJ</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>881</v>
+        <v>4745</v>
       </c>
       <c r="E12" t="n">
-        <v>6</v>
+        <v>46</v>
       </c>
       <c r="F12" t="n">
-        <v>63.26666666666667</v>
+        <v>480.6366666666667</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>1491.106666666667</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -9153,17 +10637,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>B0D672NXC8</t>
+          <t>B0CDPP45BM</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>881</v>
+        <v>2647</v>
       </c>
       <c r="E13" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="F13" t="n">
-        <v>63.26666666666667</v>
+        <v>167.03</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -9186,17 +10670,17 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0D672NXC8</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>881</v>
+        <v>2647</v>
       </c>
       <c r="E14" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="F14" t="n">
-        <v>63.26666666666667</v>
+        <v>167.03</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -9214,28 +10698,28 @@
       <c r="A15" t="inlineStr"/>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Nexlev-B0CDPP45BM-Steam Cleaner-SBV-KT-Exact/Phrase</t>
+          <t>Nexlev-B0CDPP45BM-Cleaning Machine-SB-PT</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>B0CDPP45BM</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>739</v>
+        <v>2647</v>
       </c>
       <c r="E15" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="F15" t="n">
-        <v>83.31999999999999</v>
+        <v>167.03</v>
       </c>
       <c r="G15" t="n">
-        <v>3812.71</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -9252,23 +10736,23 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0CDPP45BM</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>4528</v>
+        <v>15655</v>
       </c>
       <c r="E16" t="n">
-        <v>58</v>
+        <v>203</v>
       </c>
       <c r="F16" t="n">
-        <v>1093.2</v>
+        <v>3781.31</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>14657.61</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -9289,13 +10773,13 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>194</v>
+        <v>594</v>
       </c>
       <c r="E17" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="F17" t="n">
-        <v>65.3</v>
+        <v>162.89</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -9322,13 +10806,13 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>194</v>
+        <v>594</v>
       </c>
       <c r="E18" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="F18" t="n">
-        <v>65.3</v>
+        <v>162.89</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -9355,13 +10839,13 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>194</v>
+        <v>594</v>
       </c>
       <c r="E19" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="F19" t="n">
-        <v>65.3</v>
+        <v>162.89</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -9388,13 +10872,13 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>624</v>
+        <v>1994</v>
       </c>
       <c r="E20" t="n">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="F20" t="n">
-        <v>154.69</v>
+        <v>455.98</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -9421,13 +10905,13 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>58</v>
+        <v>162</v>
       </c>
       <c r="E21" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F21" t="n">
-        <v>16</v>
+        <v>49.08</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -9454,13 +10938,13 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>58</v>
+        <v>162</v>
       </c>
       <c r="E22" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F22" t="n">
-        <v>16</v>
+        <v>49.08</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -9487,19 +10971,19 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>2609</v>
+        <v>5338</v>
       </c>
       <c r="E23" t="n">
-        <v>93</v>
+        <v>201</v>
       </c>
       <c r="F23" t="n">
-        <v>1113.06</v>
+        <v>2477.33</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>5083.9</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -9520,13 +11004,13 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>108</v>
+        <v>308</v>
       </c>
       <c r="E24" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F24" t="n">
-        <v>14.07</v>
+        <v>66.89999999999999</v>
       </c>
       <c r="G24" t="n">
         <v>1694.633333333333</v>
@@ -9553,13 +11037,13 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>108</v>
+        <v>308</v>
       </c>
       <c r="E25" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F25" t="n">
-        <v>14.07</v>
+        <v>66.89999999999999</v>
       </c>
       <c r="G25" t="n">
         <v>1694.633333333333</v>
@@ -9586,13 +11070,13 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>108</v>
+        <v>308</v>
       </c>
       <c r="E26" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F26" t="n">
-        <v>14.07</v>
+        <v>66.89999999999999</v>
       </c>
       <c r="G26" t="n">
         <v>1694.633333333333</v>
@@ -9619,16 +11103,16 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>875</v>
+        <v>3226</v>
       </c>
       <c r="E27" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="F27" t="n">
-        <v>50.85</v>
+        <v>153.2433333333333</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>2033.613333333333</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
@@ -9652,16 +11136,16 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>875</v>
+        <v>3226</v>
       </c>
       <c r="E28" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="F28" t="n">
-        <v>50.85</v>
+        <v>153.2433333333333</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>2033.613333333333</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
@@ -9685,16 +11169,16 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>875</v>
+        <v>3226</v>
       </c>
       <c r="E29" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="F29" t="n">
-        <v>50.85</v>
+        <v>153.2433333333333</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>2033.613333333333</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
@@ -9718,13 +11202,13 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>700</v>
+        <v>7548</v>
       </c>
       <c r="E30" t="n">
-        <v>14</v>
+        <v>51</v>
       </c>
       <c r="F30" t="n">
-        <v>167.79</v>
+        <v>505.4833333333333</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -9751,13 +11235,13 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>700</v>
+        <v>7548</v>
       </c>
       <c r="E31" t="n">
-        <v>14</v>
+        <v>51</v>
       </c>
       <c r="F31" t="n">
-        <v>167.79</v>
+        <v>505.4833333333333</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -9784,13 +11268,13 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>700</v>
+        <v>7548</v>
       </c>
       <c r="E32" t="n">
-        <v>14</v>
+        <v>51</v>
       </c>
       <c r="F32" t="n">
-        <v>167.79</v>
+        <v>505.4833333333333</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -9817,13 +11301,13 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>2622</v>
+        <v>8748</v>
       </c>
       <c r="E33" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F33" t="n">
-        <v>90.925</v>
+        <v>295.75</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -9850,13 +11334,13 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>2622</v>
+        <v>8748</v>
       </c>
       <c r="E34" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F34" t="n">
-        <v>90.925</v>
+        <v>295.75</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -9879,20 +11363,20 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0CDPP45BM</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>1666</v>
+        <v>2613</v>
       </c>
       <c r="E35" t="n">
-        <v>82</v>
+        <v>144</v>
       </c>
       <c r="F35" t="n">
-        <v>1117.647556983527</v>
+        <v>1922.106666666667</v>
       </c>
       <c r="G35" t="n">
-        <v>10269.49</v>
+        <v>11980.22333333333</v>
       </c>
       <c r="H35" t="n">
         <v>3</v>
@@ -9912,23 +11396,23 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>935</v>
+        <v>2613</v>
       </c>
       <c r="E36" t="n">
-        <v>46</v>
+        <v>144</v>
       </c>
       <c r="F36" t="n">
-        <v>626.9824430164731</v>
+        <v>1922.106666666667</v>
       </c>
       <c r="G36" t="n">
-        <v>5761.02</v>
+        <v>11980.22333333333</v>
       </c>
       <c r="H36" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -9940,28 +11424,28 @@
       <c r="A37" t="inlineStr"/>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Nexlev-Vacuum Cleaner-Branded</t>
+          <t>Nexlev-Steamer-PT(SEAHELTON)-SB</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>651</v>
+        <v>2613</v>
       </c>
       <c r="E37" t="n">
-        <v>2</v>
+        <v>144</v>
       </c>
       <c r="F37" t="n">
-        <v>26.12333333333333</v>
+        <v>1922.106666666667</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>11980.22333333333</v>
       </c>
       <c r="H37" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -9973,22 +11457,22 @@
       <c r="A38" t="inlineStr"/>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Nexlev-Vacuum Cleaner-Branded</t>
+          <t>Nexlev-Steamers-Branded</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>B0DCK7ZH5P</t>
+          <t>B0CDPP45BM</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>651</v>
+        <v>11</v>
       </c>
       <c r="E38" t="n">
         <v>2</v>
       </c>
       <c r="F38" t="n">
-        <v>26.12333333333333</v>
+        <v>16.74666666666667</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -10006,22 +11490,22 @@
       <c r="A39" t="inlineStr"/>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Nexlev-Vacuum Cleaner-Branded</t>
+          <t>Nexlev-Steamers-Branded</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>B0DKJSCLBD</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>651</v>
+        <v>11</v>
       </c>
       <c r="E39" t="n">
         <v>2</v>
       </c>
       <c r="F39" t="n">
-        <v>26.12333333333333</v>
+        <v>16.74666666666667</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -10030,6 +11514,138 @@
         <v>0</v>
       </c>
       <c r="I39" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr"/>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Nexlev-Steamers-Branded</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>B0F43P6D23</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>11</v>
+      </c>
+      <c r="E40" t="n">
+        <v>2</v>
+      </c>
+      <c r="F40" t="n">
+        <v>16.74666666666667</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr"/>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Nexlev-Vacuum Cleaner-Branded</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>B0CYSLCRQS</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>2077</v>
+      </c>
+      <c r="E41" t="n">
+        <v>6</v>
+      </c>
+      <c r="F41" t="n">
+        <v>92.00999999999999</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr"/>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Nexlev-Vacuum Cleaner-Branded</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>B0DCK7ZH5P</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>2077</v>
+      </c>
+      <c r="E42" t="n">
+        <v>6</v>
+      </c>
+      <c r="F42" t="n">
+        <v>92.00999999999999</v>
+      </c>
+      <c r="G42" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr"/>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Nexlev-Vacuum Cleaner-Branded</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>B0DKJSCLBD</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>2077</v>
+      </c>
+      <c r="E43" t="n">
+        <v>6</v>
+      </c>
+      <c r="F43" t="n">
+        <v>92.00999999999999</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" t="inlineStr">
         <is>
           <t>Nexlev</t>
         </is>

--- a/data/ams_weekly_data/Nexlev/ads_report_week23.xlsx
+++ b/data/ams_weekly_data/Nexlev/ads_report_week23.xlsx
@@ -3422,10 +3422,10 @@
         <v>107384</v>
       </c>
       <c r="G107" t="n">
-        <v>8132.21</v>
+        <v>10250.01</v>
       </c>
       <c r="H107" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="108">
@@ -10831,7 +10831,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I51"/>
+  <dimension ref="A1:I47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11484,23 +11484,23 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0DCK7ZH5P</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>1365</v>
+        <v>4095</v>
       </c>
       <c r="E20" t="n">
-        <v>35</v>
+        <v>106</v>
       </c>
       <c r="F20" t="n">
-        <v>369.0066666666667</v>
+        <v>1107.02</v>
       </c>
       <c r="G20" t="n">
-        <v>1807.343333333333</v>
+        <v>5422.030000000001</v>
       </c>
       <c r="H20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -11512,25 +11512,25 @@
       <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner -SB-KT-Exact</t>
+          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner -SB-KT-Phrase(Video)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>B0D672NXC8</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>1365</v>
+        <v>4485</v>
       </c>
       <c r="E21" t="n">
-        <v>35</v>
+        <v>93</v>
       </c>
       <c r="F21" t="n">
-        <v>369.0066666666667</v>
+        <v>1076.39</v>
       </c>
       <c r="G21" t="n">
-        <v>1807.343333333333</v>
+        <v>2541.53</v>
       </c>
       <c r="H21" t="n">
         <v>1</v>
@@ -11545,28 +11545,28 @@
       <c r="A22" t="inlineStr"/>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner -SB-KT-Exact</t>
+          <t>Nexlev-B0DKK15YNJ- Oil Applicator-SBV-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>B0DCK7ZH5P</t>
+          <t>B0DKK15YNJ</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>1365</v>
+        <v>721</v>
       </c>
       <c r="E22" t="n">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="F22" t="n">
-        <v>369.0066666666667</v>
+        <v>397.27</v>
       </c>
       <c r="G22" t="n">
-        <v>1807.343333333333</v>
+        <v>4760</v>
       </c>
       <c r="H22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -11578,28 +11578,28 @@
       <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner -SB-KT-Phrase(Video)</t>
+          <t>Nexlev-B0DNJS23HS-SBV-Phrase-Mop Cleaner-SP</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>4485</v>
+        <v>92</v>
       </c>
       <c r="E23" t="n">
-        <v>93</v>
+        <v>3</v>
       </c>
       <c r="F23" t="n">
-        <v>1076.39</v>
+        <v>42.07</v>
       </c>
       <c r="G23" t="n">
-        <v>2541.53</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -11611,28 +11611,28 @@
       <c r="A24" t="inlineStr"/>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Nexlev-B0DKK15YNJ- Oil Applicator-SBV-KT-Exact/Phrase</t>
+          <t>Nexlev-B0DNJS23HS-Steam Cleaner - SBV-KT-Exact</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>B0DKK15YNJ</t>
+          <t>B0D2LJSQXZ</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>721</v>
+        <v>2661</v>
       </c>
       <c r="E24" t="n">
-        <v>22</v>
+        <v>86</v>
       </c>
       <c r="F24" t="n">
-        <v>397.27</v>
+        <v>1037.514701556099</v>
       </c>
       <c r="G24" t="n">
-        <v>4760</v>
+        <v>4661.135641610127</v>
       </c>
       <c r="H24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -11644,7 +11644,7 @@
       <c r="A25" t="inlineStr"/>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Nexlev-B0DNJS23HS-SBV-Phrase-Mop Cleaner-SP</t>
+          <t>Nexlev-B0DNJS23HS-Steam Cleaner - SBV-KT-Exact</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -11653,19 +11653,19 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>92</v>
+        <v>4202</v>
       </c>
       <c r="E25" t="n">
-        <v>3</v>
+        <v>135</v>
       </c>
       <c r="F25" t="n">
-        <v>42.07</v>
+        <v>1638.34054189982</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>7360.404128722786</v>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -11682,20 +11682,20 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>B0D2LJSQXZ</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>2661</v>
+        <v>2521</v>
       </c>
       <c r="E26" t="n">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="F26" t="n">
-        <v>1037.514701556099</v>
+        <v>982.8947565440808</v>
       </c>
       <c r="G26" t="n">
-        <v>4661.135641610127</v>
+        <v>4415.750229667087</v>
       </c>
       <c r="H26" t="n">
         <v>1</v>
@@ -11710,7 +11710,7 @@
       <c r="A27" t="inlineStr"/>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Nexlev-B0DNJS23HS-Steam Cleaner - SBV-KT-Exact</t>
+          <t>Nexlev-B0DNJS23HS-Steam Mop-SB-KT-BM</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -11719,16 +11719,16 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>4202</v>
+        <v>1204</v>
       </c>
       <c r="E27" t="n">
-        <v>135</v>
+        <v>28</v>
       </c>
       <c r="F27" t="n">
-        <v>1638.34054189982</v>
+        <v>293.083034260277</v>
       </c>
       <c r="G27" t="n">
-        <v>7360.404128722786</v>
+        <v>8165.15987525244</v>
       </c>
       <c r="H27" t="n">
         <v>2</v>
@@ -11743,25 +11743,25 @@
       <c r="A28" t="inlineStr"/>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Nexlev-B0DNJS23HS-Steam Cleaner - SBV-KT-Exact</t>
+          <t>Nexlev-B0DNJS23HS-Steam Mop-SB-KT-BM</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0GKNGWLJ2</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>2521</v>
+        <v>782</v>
       </c>
       <c r="E28" t="n">
-        <v>81</v>
+        <v>18</v>
       </c>
       <c r="F28" t="n">
-        <v>982.8947565440808</v>
+        <v>190.486965739723</v>
       </c>
       <c r="G28" t="n">
-        <v>4415.750229667087</v>
+        <v>5306.88012474756</v>
       </c>
       <c r="H28" t="n">
         <v>1</v>
@@ -11776,28 +11776,28 @@
       <c r="A29" t="inlineStr"/>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Nexlev-B0DNJS23HS-Steam Mop-SB-KT-BM</t>
+          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- PT</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>B0D2LJSQXZ</t>
+          <t>B0DVC7VJP1</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>662</v>
+        <v>5397</v>
       </c>
       <c r="E29" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="F29" t="n">
-        <v>161.19</v>
+        <v>630.95</v>
       </c>
       <c r="G29" t="n">
-        <v>4490.68</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -11809,28 +11809,28 @@
       <c r="A30" t="inlineStr"/>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Nexlev-B0DNJS23HS-Steam Mop-SB-KT-BM</t>
+          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- PT01</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0DVC7VJP1</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>662</v>
+        <v>4467</v>
       </c>
       <c r="E30" t="n">
-        <v>15</v>
+        <v>48</v>
       </c>
       <c r="F30" t="n">
-        <v>161.19</v>
+        <v>637.5599999999999</v>
       </c>
       <c r="G30" t="n">
-        <v>4490.68</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -11842,28 +11842,28 @@
       <c r="A31" t="inlineStr"/>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Nexlev-B0DNJS23HS-Steam Mop-SB-KT-BM</t>
+          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- Phrase01</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>B0GKNGWLJ2</t>
+          <t>B0DVC7VJP1</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>662</v>
+        <v>10430</v>
       </c>
       <c r="E31" t="n">
-        <v>15</v>
+        <v>49</v>
       </c>
       <c r="F31" t="n">
-        <v>161.19</v>
+        <v>529.66</v>
       </c>
       <c r="G31" t="n">
-        <v>4490.68</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -11875,7 +11875,7 @@
       <c r="A32" t="inlineStr"/>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- PT</t>
+          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV-phrase</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -11884,13 +11884,13 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>5397</v>
+        <v>10840</v>
       </c>
       <c r="E32" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F32" t="n">
-        <v>630.95</v>
+        <v>509.86</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -11908,28 +11908,28 @@
       <c r="A33" t="inlineStr"/>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- PT01</t>
+          <t>Nexlev-B0F43P6D23-Steam Cleaner-SB-KT-Phrase</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>B0DVC7VJP1</t>
+          <t>B0D672NXC8</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>4467</v>
+        <v>15741</v>
       </c>
       <c r="E33" t="n">
-        <v>48</v>
+        <v>75</v>
       </c>
       <c r="F33" t="n">
-        <v>637.5599999999999</v>
+        <v>708.1391669398656</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>6100.84</v>
       </c>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -11941,28 +11941,28 @@
       <c r="A34" t="inlineStr"/>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- Phrase01</t>
+          <t>Nexlev-B0F43P6D23-Steam Cleaner-SB-KT-Phrase</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>B0DVC7VJP1</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>10430</v>
+        <v>7870</v>
       </c>
       <c r="E34" t="n">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="F34" t="n">
-        <v>529.66</v>
+        <v>354.0208330601344</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>3050</v>
       </c>
       <c r="H34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -11974,28 +11974,28 @@
       <c r="A35" t="inlineStr"/>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV-phrase</t>
+          <t>Nexlev-Catch All-Steam Cleaner -SB-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>B0DVC7VJP1</t>
+          <t>B0D672NXC8</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>10840</v>
+        <v>12012</v>
       </c>
       <c r="E35" t="n">
-        <v>48</v>
+        <v>111</v>
       </c>
       <c r="F35" t="n">
-        <v>509.86</v>
+        <v>946.1314232479821</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>6270.34</v>
       </c>
       <c r="H35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -12007,28 +12007,28 @@
       <c r="A36" t="inlineStr"/>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Nexlev-B0F43P6D23-Steam Cleaner-SB-KT-Phrase</t>
+          <t>Nexlev-Catch All-Steam Cleaner -SB-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>B0CDPP45BM</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>7870</v>
+        <v>29217</v>
       </c>
       <c r="E36" t="n">
-        <v>38</v>
+        <v>271</v>
       </c>
       <c r="F36" t="n">
-        <v>354.0533333333333</v>
+        <v>2301.328576752018</v>
       </c>
       <c r="G36" t="n">
-        <v>3050.28</v>
+        <v>15251.7</v>
       </c>
       <c r="H36" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -12040,28 +12040,28 @@
       <c r="A37" t="inlineStr"/>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Nexlev-B0F43P6D23-Steam Cleaner-SB-KT-Phrase</t>
+          <t>Nexlev-Catch All-Vacuum Cleaner-SB-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>B0D672NXC8</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>7870</v>
+        <v>9440</v>
       </c>
       <c r="E37" t="n">
-        <v>38</v>
+        <v>12</v>
       </c>
       <c r="F37" t="n">
-        <v>354.0533333333333</v>
+        <v>324.805</v>
       </c>
       <c r="G37" t="n">
-        <v>3050.28</v>
+        <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -12073,28 +12073,28 @@
       <c r="A38" t="inlineStr"/>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Nexlev-B0F43P6D23-Steam Cleaner-SB-KT-Phrase</t>
+          <t>Nexlev-Catch All-Vacuum Cleaner-SB-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0DCK7ZH5P</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>7870</v>
+        <v>9440</v>
       </c>
       <c r="E38" t="n">
-        <v>38</v>
+        <v>12</v>
       </c>
       <c r="F38" t="n">
-        <v>354.0533333333333</v>
+        <v>324.805</v>
       </c>
       <c r="G38" t="n">
-        <v>3050.28</v>
+        <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -12106,28 +12106,28 @@
       <c r="A39" t="inlineStr"/>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-Steam Cleaner -SB-KT-Exact/Phrase</t>
+          <t>Nexlev-Steamer-PT(SEAHELTON)-SB</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>B0D672NXC8</t>
+          <t>B0CDPP45BM</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>12012</v>
+        <v>3293</v>
       </c>
       <c r="E39" t="n">
-        <v>111</v>
+        <v>187</v>
       </c>
       <c r="F39" t="n">
-        <v>946.1314232479821</v>
+        <v>2337.229394220671</v>
       </c>
       <c r="G39" t="n">
-        <v>6270.34</v>
+        <v>13461.16317853616</v>
       </c>
       <c r="H39" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -12139,7 +12139,7 @@
       <c r="A40" t="inlineStr"/>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-Steam Cleaner -SB-KT-Exact/Phrase</t>
+          <t>Nexlev-Steamer-PT(SEAHELTON)-SB</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -12148,19 +12148,19 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>29217</v>
+        <v>4388</v>
       </c>
       <c r="E40" t="n">
-        <v>271</v>
+        <v>249</v>
       </c>
       <c r="F40" t="n">
-        <v>2301.328576752018</v>
+        <v>3114.188948494056</v>
       </c>
       <c r="G40" t="n">
-        <v>15251.7</v>
+        <v>17936.0253247416</v>
       </c>
       <c r="H40" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -12172,28 +12172,28 @@
       <c r="A41" t="inlineStr"/>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-Vacuum Cleaner-SB-KT-Exact/Phrase</t>
+          <t>Nexlev-Steamer-PT(SEAHELTON)-SB</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>9440</v>
+        <v>12761</v>
       </c>
       <c r="E41" t="n">
-        <v>12</v>
+        <v>724</v>
       </c>
       <c r="F41" t="n">
-        <v>324.805</v>
+        <v>9056.191657285275</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>52158.71149672224</v>
       </c>
       <c r="H41" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -12205,22 +12205,22 @@
       <c r="A42" t="inlineStr"/>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-Vacuum Cleaner-SB-KT-Exact/Phrase</t>
+          <t>Nexlev-Steamers-Branded</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>B0DCK7ZH5P</t>
+          <t>B0CDPP45BM</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>9440</v>
+        <v>30</v>
       </c>
       <c r="E42" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="F42" t="n">
-        <v>324.805</v>
+        <v>19.57333333333333</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -12238,28 +12238,28 @@
       <c r="A43" t="inlineStr"/>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Nexlev-Steamer-PT(SEAHELTON)-SB</t>
+          <t>Nexlev-Steamers-Branded</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>B0CDPP45BM</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>3293</v>
+        <v>30</v>
       </c>
       <c r="E43" t="n">
-        <v>187</v>
+        <v>3</v>
       </c>
       <c r="F43" t="n">
-        <v>2337.229394220671</v>
+        <v>19.57333333333333</v>
       </c>
       <c r="G43" t="n">
-        <v>13461.16317853616</v>
+        <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -12271,28 +12271,28 @@
       <c r="A44" t="inlineStr"/>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Nexlev-Steamer-PT(SEAHELTON)-SB</t>
+          <t>Nexlev-Steamers-Branded</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>4388</v>
+        <v>30</v>
       </c>
       <c r="E44" t="n">
-        <v>249</v>
+        <v>3</v>
       </c>
       <c r="F44" t="n">
-        <v>3114.188948494056</v>
+        <v>19.57333333333333</v>
       </c>
       <c r="G44" t="n">
-        <v>17936.0253247416</v>
+        <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -12304,28 +12304,28 @@
       <c r="A45" t="inlineStr"/>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Nexlev-Steamer-PT(SEAHELTON)-SB</t>
+          <t>Nexlev-Vacuum Cleaner-Branded</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>12761</v>
+        <v>2314</v>
       </c>
       <c r="E45" t="n">
-        <v>724</v>
+        <v>10</v>
       </c>
       <c r="F45" t="n">
-        <v>9056.191657285275</v>
+        <v>117.4133333333333</v>
       </c>
       <c r="G45" t="n">
-        <v>52158.71149672224</v>
+        <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -12337,22 +12337,22 @@
       <c r="A46" t="inlineStr"/>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Nexlev-Steamers-Branded</t>
+          <t>Nexlev-Vacuum Cleaner-Branded</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>B0CDPP45BM</t>
+          <t>B0DCK7ZH5P</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>30</v>
+        <v>2314</v>
       </c>
       <c r="E46" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F46" t="n">
-        <v>19.57333333333333</v>
+        <v>117.4133333333333</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -12370,22 +12370,22 @@
       <c r="A47" t="inlineStr"/>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Nexlev-Steamers-Branded</t>
+          <t>Nexlev-Vacuum Cleaner-Branded</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0DKJSCLBD</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>30</v>
+        <v>2314</v>
       </c>
       <c r="E47" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F47" t="n">
-        <v>19.57333333333333</v>
+        <v>117.4133333333333</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
@@ -12394,138 +12394,6 @@
         <v>0</v>
       </c>
       <c r="I47" t="inlineStr">
-        <is>
-          <t>Nexlev</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr"/>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>Nexlev-Steamers-Branded</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>B0F43P6D23</t>
-        </is>
-      </c>
-      <c r="D48" t="n">
-        <v>30</v>
-      </c>
-      <c r="E48" t="n">
-        <v>3</v>
-      </c>
-      <c r="F48" t="n">
-        <v>19.57333333333333</v>
-      </c>
-      <c r="G48" t="n">
-        <v>0</v>
-      </c>
-      <c r="H48" t="n">
-        <v>0</v>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>Nexlev</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr"/>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>Nexlev-Vacuum Cleaner-Branded</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>B0CYSLCRQS</t>
-        </is>
-      </c>
-      <c r="D49" t="n">
-        <v>2314</v>
-      </c>
-      <c r="E49" t="n">
-        <v>10</v>
-      </c>
-      <c r="F49" t="n">
-        <v>117.4133333333333</v>
-      </c>
-      <c r="G49" t="n">
-        <v>0</v>
-      </c>
-      <c r="H49" t="n">
-        <v>0</v>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>Nexlev</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr"/>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>Nexlev-Vacuum Cleaner-Branded</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>B0DCK7ZH5P</t>
-        </is>
-      </c>
-      <c r="D50" t="n">
-        <v>2314</v>
-      </c>
-      <c r="E50" t="n">
-        <v>10</v>
-      </c>
-      <c r="F50" t="n">
-        <v>117.4133333333333</v>
-      </c>
-      <c r="G50" t="n">
-        <v>0</v>
-      </c>
-      <c r="H50" t="n">
-        <v>0</v>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>Nexlev</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr"/>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>Nexlev-Vacuum Cleaner-Branded</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>B0DKJSCLBD</t>
-        </is>
-      </c>
-      <c r="D51" t="n">
-        <v>2314</v>
-      </c>
-      <c r="E51" t="n">
-        <v>10</v>
-      </c>
-      <c r="F51" t="n">
-        <v>117.4133333333333</v>
-      </c>
-      <c r="G51" t="n">
-        <v>0</v>
-      </c>
-      <c r="H51" t="n">
-        <v>0</v>
-      </c>
-      <c r="I51" t="inlineStr">
         <is>
           <t>Nexlev</t>
         </is>

--- a/data/ams_weekly_data/Nexlev/ads_report_week23.xlsx
+++ b/data/ams_weekly_data/Nexlev/ads_report_week23.xlsx
@@ -1543,13 +1543,13 @@
         <v>390</v>
       </c>
       <c r="F40" t="n">
-        <v>166023</v>
+        <v>166021</v>
       </c>
       <c r="G40" t="n">
         <v>24376.3</v>
       </c>
       <c r="H40" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="41">
@@ -2470,10 +2470,10 @@
         <v>10487</v>
       </c>
       <c r="G73" t="n">
-        <v>5255.940000000001</v>
+        <v>7373.74</v>
       </c>
       <c r="H73" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="74">
@@ -2663,7 +2663,7 @@
         <v>95</v>
       </c>
       <c r="F80" t="n">
-        <v>15726</v>
+        <v>15725</v>
       </c>
       <c r="G80" t="n">
         <v>3140.01</v>
@@ -3223,7 +3223,7 @@
         <v>814</v>
       </c>
       <c r="F100" t="n">
-        <v>414157</v>
+        <v>414156</v>
       </c>
       <c r="G100" t="n">
         <v>20335.6</v>
@@ -8151,7 +8151,7 @@
         <v>680</v>
       </c>
       <c r="F276" t="n">
-        <v>159352</v>
+        <v>159351</v>
       </c>
       <c r="G276" t="n">
         <v>25666.09</v>
@@ -8739,7 +8739,7 @@
         <v>300</v>
       </c>
       <c r="F297" t="n">
-        <v>75046</v>
+        <v>75045</v>
       </c>
       <c r="G297" t="n">
         <v>40672.03999999999</v>
@@ -10831,7 +10831,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I47"/>
+  <dimension ref="A1:I51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11484,23 +11484,23 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>B0DCK7ZH5P</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>4095</v>
+        <v>1365</v>
       </c>
       <c r="E20" t="n">
-        <v>106</v>
+        <v>35</v>
       </c>
       <c r="F20" t="n">
-        <v>1107.02</v>
+        <v>369.0066666666667</v>
       </c>
       <c r="G20" t="n">
-        <v>5422.030000000001</v>
+        <v>1807.343333333333</v>
       </c>
       <c r="H20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -11512,25 +11512,25 @@
       <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner -SB-KT-Phrase(Video)</t>
+          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner -SB-KT-Exact</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0D672NXC8</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>4485</v>
+        <v>1365</v>
       </c>
       <c r="E21" t="n">
-        <v>93</v>
+        <v>35</v>
       </c>
       <c r="F21" t="n">
-        <v>1076.39</v>
+        <v>369.0066666666667</v>
       </c>
       <c r="G21" t="n">
-        <v>2541.53</v>
+        <v>1807.343333333333</v>
       </c>
       <c r="H21" t="n">
         <v>1</v>
@@ -11545,28 +11545,28 @@
       <c r="A22" t="inlineStr"/>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Nexlev-B0DKK15YNJ- Oil Applicator-SBV-KT-Exact/Phrase</t>
+          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner -SB-KT-Exact</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>B0DKK15YNJ</t>
+          <t>B0DCK7ZH5P</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>721</v>
+        <v>1365</v>
       </c>
       <c r="E22" t="n">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="F22" t="n">
-        <v>397.27</v>
+        <v>369.0066666666667</v>
       </c>
       <c r="G22" t="n">
-        <v>4760</v>
+        <v>1807.343333333333</v>
       </c>
       <c r="H22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -11578,28 +11578,28 @@
       <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Nexlev-B0DNJS23HS-SBV-Phrase-Mop Cleaner-SP</t>
+          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner -SB-KT-Phrase(Video)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>92</v>
+        <v>4485</v>
       </c>
       <c r="E23" t="n">
-        <v>3</v>
+        <v>93</v>
       </c>
       <c r="F23" t="n">
-        <v>42.07</v>
+        <v>1076.39</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>2541.53</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -11611,28 +11611,28 @@
       <c r="A24" t="inlineStr"/>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Nexlev-B0DNJS23HS-Steam Cleaner - SBV-KT-Exact</t>
+          <t>Nexlev-B0DKK15YNJ- Oil Applicator-SBV-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>B0D2LJSQXZ</t>
+          <t>B0DKK15YNJ</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>2661</v>
+        <v>721</v>
       </c>
       <c r="E24" t="n">
-        <v>86</v>
+        <v>22</v>
       </c>
       <c r="F24" t="n">
-        <v>1037.514701556099</v>
+        <v>397.27</v>
       </c>
       <c r="G24" t="n">
-        <v>4661.135641610127</v>
+        <v>4760</v>
       </c>
       <c r="H24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -11644,7 +11644,7 @@
       <c r="A25" t="inlineStr"/>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Nexlev-B0DNJS23HS-Steam Cleaner - SBV-KT-Exact</t>
+          <t>Nexlev-B0DNJS23HS-SBV-Phrase-Mop Cleaner-SP</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -11653,19 +11653,19 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>4202</v>
+        <v>92</v>
       </c>
       <c r="E25" t="n">
-        <v>135</v>
+        <v>3</v>
       </c>
       <c r="F25" t="n">
-        <v>1638.34054189982</v>
+        <v>42.07</v>
       </c>
       <c r="G25" t="n">
-        <v>7360.404128722786</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -11682,20 +11682,20 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0D2LJSQXZ</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>2521</v>
+        <v>2661</v>
       </c>
       <c r="E26" t="n">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="F26" t="n">
-        <v>982.8947565440808</v>
+        <v>1037.514701556099</v>
       </c>
       <c r="G26" t="n">
-        <v>4415.750229667087</v>
+        <v>4661.135641610127</v>
       </c>
       <c r="H26" t="n">
         <v>1</v>
@@ -11710,7 +11710,7 @@
       <c r="A27" t="inlineStr"/>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Nexlev-B0DNJS23HS-Steam Mop-SB-KT-BM</t>
+          <t>Nexlev-B0DNJS23HS-Steam Cleaner - SBV-KT-Exact</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -11719,16 +11719,16 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>1204</v>
+        <v>4202</v>
       </c>
       <c r="E27" t="n">
-        <v>28</v>
+        <v>135</v>
       </c>
       <c r="F27" t="n">
-        <v>293.083034260277</v>
+        <v>1638.34054189982</v>
       </c>
       <c r="G27" t="n">
-        <v>8165.15987525244</v>
+        <v>7360.404128722786</v>
       </c>
       <c r="H27" t="n">
         <v>2</v>
@@ -11743,25 +11743,25 @@
       <c r="A28" t="inlineStr"/>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Nexlev-B0DNJS23HS-Steam Mop-SB-KT-BM</t>
+          <t>Nexlev-B0DNJS23HS-Steam Cleaner - SBV-KT-Exact</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>B0GKNGWLJ2</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>782</v>
+        <v>2521</v>
       </c>
       <c r="E28" t="n">
-        <v>18</v>
+        <v>81</v>
       </c>
       <c r="F28" t="n">
-        <v>190.486965739723</v>
+        <v>982.8947565440808</v>
       </c>
       <c r="G28" t="n">
-        <v>5306.88012474756</v>
+        <v>4415.750229667087</v>
       </c>
       <c r="H28" t="n">
         <v>1</v>
@@ -11776,28 +11776,28 @@
       <c r="A29" t="inlineStr"/>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- PT</t>
+          <t>Nexlev-B0DNJS23HS-Steam Mop-SB-KT-BM</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>B0DVC7VJP1</t>
+          <t>B0D2LJSQXZ</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>5397</v>
+        <v>662</v>
       </c>
       <c r="E29" t="n">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="F29" t="n">
-        <v>630.95</v>
+        <v>161.19</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>4490.68</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -11809,28 +11809,28 @@
       <c r="A30" t="inlineStr"/>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- PT01</t>
+          <t>Nexlev-B0DNJS23HS-Steam Mop-SB-KT-BM</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>B0DVC7VJP1</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>4467</v>
+        <v>662</v>
       </c>
       <c r="E30" t="n">
-        <v>48</v>
+        <v>15</v>
       </c>
       <c r="F30" t="n">
-        <v>637.5599999999999</v>
+        <v>161.19</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>4490.68</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -11842,28 +11842,28 @@
       <c r="A31" t="inlineStr"/>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- Phrase01</t>
+          <t>Nexlev-B0DNJS23HS-Steam Mop-SB-KT-BM</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>B0DVC7VJP1</t>
+          <t>B0GKNGWLJ2</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>10430</v>
+        <v>662</v>
       </c>
       <c r="E31" t="n">
-        <v>49</v>
+        <v>15</v>
       </c>
       <c r="F31" t="n">
-        <v>529.66</v>
+        <v>161.19</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>4490.68</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -11875,7 +11875,7 @@
       <c r="A32" t="inlineStr"/>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV-phrase</t>
+          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- PT</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -11884,13 +11884,13 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>10840</v>
+        <v>5397</v>
       </c>
       <c r="E32" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F32" t="n">
-        <v>509.86</v>
+        <v>630.95</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -11908,28 +11908,28 @@
       <c r="A33" t="inlineStr"/>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Nexlev-B0F43P6D23-Steam Cleaner-SB-KT-Phrase</t>
+          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- PT01</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>B0D672NXC8</t>
+          <t>B0DVC7VJP1</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>15741</v>
+        <v>4467</v>
       </c>
       <c r="E33" t="n">
-        <v>75</v>
+        <v>48</v>
       </c>
       <c r="F33" t="n">
-        <v>708.1391669398656</v>
+        <v>637.5599999999999</v>
       </c>
       <c r="G33" t="n">
-        <v>6100.84</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -11941,28 +11941,28 @@
       <c r="A34" t="inlineStr"/>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Nexlev-B0F43P6D23-Steam Cleaner-SB-KT-Phrase</t>
+          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- Phrase01</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0DVC7VJP1</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>7870</v>
+        <v>10430</v>
       </c>
       <c r="E34" t="n">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="F34" t="n">
-        <v>354.0208330601344</v>
+        <v>529.66</v>
       </c>
       <c r="G34" t="n">
-        <v>3050</v>
+        <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -11974,28 +11974,28 @@
       <c r="A35" t="inlineStr"/>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-Steam Cleaner -SB-KT-Exact/Phrase</t>
+          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV-phrase</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>B0D672NXC8</t>
+          <t>B0DVC7VJP1</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>12012</v>
+        <v>10840</v>
       </c>
       <c r="E35" t="n">
-        <v>111</v>
+        <v>48</v>
       </c>
       <c r="F35" t="n">
-        <v>946.1314232479821</v>
+        <v>509.86</v>
       </c>
       <c r="G35" t="n">
-        <v>6270.34</v>
+        <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -12007,28 +12007,28 @@
       <c r="A36" t="inlineStr"/>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-Steam Cleaner -SB-KT-Exact/Phrase</t>
+          <t>Nexlev-B0F43P6D23-Steam Cleaner-SB-KT-Phrase</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0CDPP45BM</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>29217</v>
+        <v>7870</v>
       </c>
       <c r="E36" t="n">
-        <v>271</v>
+        <v>38</v>
       </c>
       <c r="F36" t="n">
-        <v>2301.328576752018</v>
+        <v>354.0533333333333</v>
       </c>
       <c r="G36" t="n">
-        <v>15251.7</v>
+        <v>3050.28</v>
       </c>
       <c r="H36" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -12040,28 +12040,28 @@
       <c r="A37" t="inlineStr"/>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-Vacuum Cleaner-SB-KT-Exact/Phrase</t>
+          <t>Nexlev-B0F43P6D23-Steam Cleaner-SB-KT-Phrase</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0D672NXC8</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>9440</v>
+        <v>7870</v>
       </c>
       <c r="E37" t="n">
-        <v>12</v>
+        <v>38</v>
       </c>
       <c r="F37" t="n">
-        <v>324.805</v>
+        <v>354.0533333333333</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>3050.28</v>
       </c>
       <c r="H37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -12073,28 +12073,28 @@
       <c r="A38" t="inlineStr"/>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-Vacuum Cleaner-SB-KT-Exact/Phrase</t>
+          <t>Nexlev-B0F43P6D23-Steam Cleaner-SB-KT-Phrase</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>B0DCK7ZH5P</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>9440</v>
+        <v>7870</v>
       </c>
       <c r="E38" t="n">
-        <v>12</v>
+        <v>38</v>
       </c>
       <c r="F38" t="n">
-        <v>324.805</v>
+        <v>354.0533333333333</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>3050.28</v>
       </c>
       <c r="H38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -12106,28 +12106,28 @@
       <c r="A39" t="inlineStr"/>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Nexlev-Steamer-PT(SEAHELTON)-SB</t>
+          <t>Nexlev-Catch All-Steam Cleaner -SB-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>B0CDPP45BM</t>
+          <t>B0D672NXC8</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>3293</v>
+        <v>12012</v>
       </c>
       <c r="E39" t="n">
-        <v>187</v>
+        <v>111</v>
       </c>
       <c r="F39" t="n">
-        <v>2337.229394220671</v>
+        <v>946.1314232479821</v>
       </c>
       <c r="G39" t="n">
-        <v>13461.16317853616</v>
+        <v>6270.34</v>
       </c>
       <c r="H39" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -12139,7 +12139,7 @@
       <c r="A40" t="inlineStr"/>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Nexlev-Steamer-PT(SEAHELTON)-SB</t>
+          <t>Nexlev-Catch All-Steam Cleaner -SB-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -12148,19 +12148,19 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>4388</v>
+        <v>29217</v>
       </c>
       <c r="E40" t="n">
-        <v>249</v>
+        <v>271</v>
       </c>
       <c r="F40" t="n">
-        <v>3114.188948494056</v>
+        <v>2301.328576752018</v>
       </c>
       <c r="G40" t="n">
-        <v>17936.0253247416</v>
+        <v>15251.7</v>
       </c>
       <c r="H40" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -12172,28 +12172,28 @@
       <c r="A41" t="inlineStr"/>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Nexlev-Steamer-PT(SEAHELTON)-SB</t>
+          <t>Nexlev-Catch All-Vacuum Cleaner-SB-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>12761</v>
+        <v>9440</v>
       </c>
       <c r="E41" t="n">
-        <v>724</v>
+        <v>12</v>
       </c>
       <c r="F41" t="n">
-        <v>9056.191657285275</v>
+        <v>324.805</v>
       </c>
       <c r="G41" t="n">
-        <v>52158.71149672224</v>
+        <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -12205,22 +12205,22 @@
       <c r="A42" t="inlineStr"/>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Nexlev-Steamers-Branded</t>
+          <t>Nexlev-Catch All-Vacuum Cleaner-SB-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>B0CDPP45BM</t>
+          <t>B0DCK7ZH5P</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>30</v>
+        <v>9440</v>
       </c>
       <c r="E42" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="F42" t="n">
-        <v>19.57333333333333</v>
+        <v>324.805</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -12238,28 +12238,28 @@
       <c r="A43" t="inlineStr"/>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Nexlev-Steamers-Branded</t>
+          <t>Nexlev-Steamer-PT(SEAHELTON)-SB</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0CDPP45BM</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>30</v>
+        <v>3293</v>
       </c>
       <c r="E43" t="n">
-        <v>3</v>
+        <v>187</v>
       </c>
       <c r="F43" t="n">
-        <v>19.57333333333333</v>
+        <v>2337.229394220671</v>
       </c>
       <c r="G43" t="n">
-        <v>0</v>
+        <v>13461.16317853616</v>
       </c>
       <c r="H43" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -12271,28 +12271,28 @@
       <c r="A44" t="inlineStr"/>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Nexlev-Steamers-Branded</t>
+          <t>Nexlev-Steamer-PT(SEAHELTON)-SB</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>30</v>
+        <v>4388</v>
       </c>
       <c r="E44" t="n">
-        <v>3</v>
+        <v>249</v>
       </c>
       <c r="F44" t="n">
-        <v>19.57333333333333</v>
+        <v>3114.188948494056</v>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>17936.0253247416</v>
       </c>
       <c r="H44" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -12304,28 +12304,28 @@
       <c r="A45" t="inlineStr"/>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Nexlev-Vacuum Cleaner-Branded</t>
+          <t>Nexlev-Steamer-PT(SEAHELTON)-SB</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>2314</v>
+        <v>12761</v>
       </c>
       <c r="E45" t="n">
-        <v>10</v>
+        <v>724</v>
       </c>
       <c r="F45" t="n">
-        <v>117.4133333333333</v>
+        <v>9056.191657285275</v>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>52158.71149672224</v>
       </c>
       <c r="H45" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -12337,22 +12337,22 @@
       <c r="A46" t="inlineStr"/>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Nexlev-Vacuum Cleaner-Branded</t>
+          <t>Nexlev-Steamers-Branded</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>B0DCK7ZH5P</t>
+          <t>B0CDPP45BM</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>2314</v>
+        <v>30</v>
       </c>
       <c r="E46" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="F46" t="n">
-        <v>117.4133333333333</v>
+        <v>19.57333333333333</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -12370,30 +12370,162 @@
       <c r="A47" t="inlineStr"/>
       <c r="B47" t="inlineStr">
         <is>
+          <t>Nexlev-Steamers-Branded</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>B0DNJS23HS</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>30</v>
+      </c>
+      <c r="E47" t="n">
+        <v>3</v>
+      </c>
+      <c r="F47" t="n">
+        <v>19.57333333333333</v>
+      </c>
+      <c r="G47" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0</v>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr"/>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Nexlev-Steamers-Branded</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>B0F43P6D23</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>30</v>
+      </c>
+      <c r="E48" t="n">
+        <v>3</v>
+      </c>
+      <c r="F48" t="n">
+        <v>19.57333333333333</v>
+      </c>
+      <c r="G48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr"/>
+      <c r="B49" t="inlineStr">
+        <is>
           <t>Nexlev-Vacuum Cleaner-Branded</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>B0CYSLCRQS</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>2314</v>
+      </c>
+      <c r="E49" t="n">
+        <v>10</v>
+      </c>
+      <c r="F49" t="n">
+        <v>117.4133333333333</v>
+      </c>
+      <c r="G49" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0</v>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr"/>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Nexlev-Vacuum Cleaner-Branded</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>B0DCK7ZH5P</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>2314</v>
+      </c>
+      <c r="E50" t="n">
+        <v>10</v>
+      </c>
+      <c r="F50" t="n">
+        <v>117.4133333333333</v>
+      </c>
+      <c r="G50" t="n">
+        <v>0</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0</v>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr"/>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Nexlev-Vacuum Cleaner-Branded</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
         <is>
           <t>B0DKJSCLBD</t>
         </is>
       </c>
-      <c r="D47" t="n">
+      <c r="D51" t="n">
         <v>2314</v>
       </c>
-      <c r="E47" t="n">
+      <c r="E51" t="n">
         <v>10</v>
       </c>
-      <c r="F47" t="n">
+      <c r="F51" t="n">
         <v>117.4133333333333</v>
       </c>
-      <c r="G47" t="n">
-        <v>0</v>
-      </c>
-      <c r="H47" t="n">
-        <v>0</v>
-      </c>
-      <c r="I47" t="inlineStr">
+      <c r="G51" t="n">
+        <v>0</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0</v>
+      </c>
+      <c r="I51" t="inlineStr">
         <is>
           <t>Nexlev</t>
         </is>

--- a/data/ams_weekly_data/Nexlev/ads_report_week23.xlsx
+++ b/data/ams_weekly_data/Nexlev/ads_report_week23.xlsx
@@ -899,7 +899,7 @@
         <v>114</v>
       </c>
       <c r="F17" t="n">
-        <v>8085</v>
+        <v>8084</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -1039,7 +1039,7 @@
         <v>418</v>
       </c>
       <c r="F22" t="n">
-        <v>46552</v>
+        <v>46549</v>
       </c>
       <c r="G22" t="n">
         <v>2541.52</v>
@@ -1347,7 +1347,7 @@
         <v>168</v>
       </c>
       <c r="F33" t="n">
-        <v>15736</v>
+        <v>15735</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -1543,7 +1543,7 @@
         <v>390</v>
       </c>
       <c r="F40" t="n">
-        <v>166021</v>
+        <v>166017</v>
       </c>
       <c r="G40" t="n">
         <v>24376.3</v>
@@ -2047,7 +2047,7 @@
         <v>272</v>
       </c>
       <c r="F58" t="n">
-        <v>9560</v>
+        <v>9559</v>
       </c>
       <c r="G58" t="n">
         <v>31434.75</v>
@@ -2159,7 +2159,7 @@
         <v>109</v>
       </c>
       <c r="F62" t="n">
-        <v>9028</v>
+        <v>9027</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
@@ -2719,7 +2719,7 @@
         <v>82</v>
       </c>
       <c r="F82" t="n">
-        <v>28981</v>
+        <v>28979</v>
       </c>
       <c r="G82" t="n">
         <v>5759.32</v>
@@ -3027,7 +3027,7 @@
         <v>71</v>
       </c>
       <c r="F93" t="n">
-        <v>6970</v>
+        <v>6969</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -3055,7 +3055,7 @@
         <v>335</v>
       </c>
       <c r="F94" t="n">
-        <v>95680</v>
+        <v>95678</v>
       </c>
       <c r="G94" t="n">
         <v>18471.19</v>
@@ -3083,7 +3083,7 @@
         <v>285</v>
       </c>
       <c r="F95" t="n">
-        <v>18179</v>
+        <v>18177</v>
       </c>
       <c r="G95" t="n">
         <v>25822.04</v>
@@ -3195,7 +3195,7 @@
         <v>364</v>
       </c>
       <c r="F99" t="n">
-        <v>70026</v>
+        <v>70025</v>
       </c>
       <c r="G99" t="n">
         <v>11604.23</v>
@@ -3223,7 +3223,7 @@
         <v>814</v>
       </c>
       <c r="F100" t="n">
-        <v>414156</v>
+        <v>414143</v>
       </c>
       <c r="G100" t="n">
         <v>20335.6</v>
@@ -3391,7 +3391,7 @@
         <v>489</v>
       </c>
       <c r="F106" t="n">
-        <v>251806</v>
+        <v>251796</v>
       </c>
       <c r="G106" t="n">
         <v>8132.2</v>
@@ -3419,7 +3419,7 @@
         <v>365</v>
       </c>
       <c r="F107" t="n">
-        <v>107384</v>
+        <v>107382</v>
       </c>
       <c r="G107" t="n">
         <v>10250.01</v>
@@ -3447,7 +3447,7 @@
         <v>105</v>
       </c>
       <c r="F108" t="n">
-        <v>10071</v>
+        <v>10070</v>
       </c>
       <c r="G108" t="n">
         <v>0</v>
@@ -3475,7 +3475,7 @@
         <v>79</v>
       </c>
       <c r="F109" t="n">
-        <v>3820</v>
+        <v>3819</v>
       </c>
       <c r="G109" t="n">
         <v>0</v>
@@ -3643,7 +3643,7 @@
         <v>4</v>
       </c>
       <c r="F115" t="n">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="G115" t="n">
         <v>0</v>
@@ -3895,7 +3895,7 @@
         <v>4</v>
       </c>
       <c r="F124" t="n">
-        <v>3039</v>
+        <v>3037</v>
       </c>
       <c r="G124" t="n">
         <v>0</v>
@@ -4035,7 +4035,7 @@
         <v>2</v>
       </c>
       <c r="F129" t="n">
-        <v>801</v>
+        <v>799</v>
       </c>
       <c r="G129" t="n">
         <v>0</v>
@@ -4315,7 +4315,7 @@
         <v>37</v>
       </c>
       <c r="F139" t="n">
-        <v>6082</v>
+        <v>6080</v>
       </c>
       <c r="G139" t="n">
         <v>0</v>
@@ -4679,7 +4679,7 @@
         <v>6</v>
       </c>
       <c r="F152" t="n">
-        <v>1695</v>
+        <v>1694</v>
       </c>
       <c r="G152" t="n">
         <v>0</v>
@@ -4763,7 +4763,7 @@
         <v>1</v>
       </c>
       <c r="F155" t="n">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="G155" t="n">
         <v>0</v>
@@ -4819,7 +4819,7 @@
         <v>2</v>
       </c>
       <c r="F157" t="n">
-        <v>4689</v>
+        <v>4688</v>
       </c>
       <c r="G157" t="n">
         <v>0</v>
@@ -4847,7 +4847,7 @@
         <v>4</v>
       </c>
       <c r="F158" t="n">
-        <v>17545</v>
+        <v>17544</v>
       </c>
       <c r="G158" t="n">
         <v>0</v>
@@ -4987,7 +4987,7 @@
         <v>3</v>
       </c>
       <c r="F163" t="n">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="G163" t="n">
         <v>0</v>
@@ -5071,7 +5071,7 @@
         <v>39</v>
       </c>
       <c r="F166" t="n">
-        <v>11706</v>
+        <v>11704</v>
       </c>
       <c r="G166" t="n">
         <v>0</v>
@@ -5351,7 +5351,7 @@
         <v>4</v>
       </c>
       <c r="F176" t="n">
-        <v>2574</v>
+        <v>2573</v>
       </c>
       <c r="G176" t="n">
         <v>0</v>
@@ -5603,7 +5603,7 @@
         <v>62</v>
       </c>
       <c r="F185" t="n">
-        <v>13720</v>
+        <v>13718</v>
       </c>
       <c r="G185" t="n">
         <v>3303.39</v>
@@ -5858,10 +5858,10 @@
         <v>3530</v>
       </c>
       <c r="G194" t="n">
-        <v>0</v>
+        <v>1397.46</v>
       </c>
       <c r="H194" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="195">
@@ -6275,7 +6275,7 @@
         <v>2</v>
       </c>
       <c r="F209" t="n">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="G209" t="n">
         <v>0</v>
@@ -6359,7 +6359,7 @@
         <v>4</v>
       </c>
       <c r="F212" t="n">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="G212" t="n">
         <v>0</v>
@@ -6583,7 +6583,7 @@
         <v>5</v>
       </c>
       <c r="F220" t="n">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="G220" t="n">
         <v>8466.1</v>
@@ -6835,7 +6835,7 @@
         <v>2</v>
       </c>
       <c r="F229" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G229" t="n">
         <v>0</v>
@@ -8151,13 +8151,13 @@
         <v>680</v>
       </c>
       <c r="F276" t="n">
-        <v>159351</v>
+        <v>159346</v>
       </c>
       <c r="G276" t="n">
-        <v>25666.09</v>
+        <v>27480.5</v>
       </c>
       <c r="H276" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="277">
@@ -8235,7 +8235,7 @@
         <v>209</v>
       </c>
       <c r="F279" t="n">
-        <v>26212</v>
+        <v>26211</v>
       </c>
       <c r="G279" t="n">
         <v>3557.63</v>
@@ -8431,7 +8431,7 @@
         <v>132</v>
       </c>
       <c r="F286" t="n">
-        <v>44572</v>
+        <v>44571</v>
       </c>
       <c r="G286" t="n">
         <v>0</v>
@@ -8462,10 +8462,10 @@
         <v>21343</v>
       </c>
       <c r="G287" t="n">
-        <v>5082.209999999999</v>
+        <v>6776.28</v>
       </c>
       <c r="H287" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="288">
@@ -8515,7 +8515,7 @@
         <v>1036</v>
       </c>
       <c r="F289" t="n">
-        <v>119297</v>
+        <v>119294</v>
       </c>
       <c r="G289" t="n">
         <v>7709.320000000001</v>
@@ -8599,7 +8599,7 @@
         <v>241</v>
       </c>
       <c r="F292" t="n">
-        <v>48117</v>
+        <v>48115</v>
       </c>
       <c r="G292" t="n">
         <v>6099.15</v>
@@ -8658,10 +8658,10 @@
         <v>28933</v>
       </c>
       <c r="G294" t="n">
-        <v>70565.41</v>
+        <v>77597.62</v>
       </c>
       <c r="H294" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="295">
@@ -8742,10 +8742,10 @@
         <v>75045</v>
       </c>
       <c r="G297" t="n">
-        <v>40672.03999999999</v>
+        <v>45755.94</v>
       </c>
       <c r="H297" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="298">
@@ -9165,7 +9165,7 @@
         <v>2380</v>
       </c>
       <c r="H312" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="313">
@@ -10831,7 +10831,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I51"/>
+  <dimension ref="A1:I48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11092,16 +11092,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>34415</v>
+        <v>30136</v>
       </c>
       <c r="E8" t="n">
-        <v>196</v>
+        <v>171</v>
       </c>
       <c r="F8" t="n">
-        <v>2639.656507022944</v>
+        <v>2311.552196280246</v>
       </c>
       <c r="G8" t="n">
-        <v>11424.76</v>
+        <v>8568.570000000002</v>
       </c>
       <c r="H8" t="n">
         <v>3</v>
@@ -11125,19 +11125,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>25523</v>
+        <v>29800</v>
       </c>
       <c r="E9" t="n">
-        <v>145</v>
+        <v>170</v>
       </c>
       <c r="F9" t="n">
-        <v>1957.633492977056</v>
+        <v>2285.737803719754</v>
       </c>
       <c r="G9" t="n">
-        <v>8472.879999999999</v>
+        <v>8472.880000000001</v>
       </c>
       <c r="H9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -11158,16 +11158,16 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>14645</v>
+        <v>12314</v>
       </c>
       <c r="E10" t="n">
-        <v>148</v>
+        <v>125</v>
       </c>
       <c r="F10" t="n">
-        <v>1508.76638197942</v>
+        <v>1268.562638524461</v>
       </c>
       <c r="G10" t="n">
-        <v>4676.452789219664</v>
+        <v>4598.475136156199</v>
       </c>
       <c r="H10" t="n">
         <v>4</v>
@@ -11187,23 +11187,23 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>B0DKK15YNJ</t>
+          <t>B0DCGHKRXX</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16651</v>
+        <v>4982</v>
       </c>
       <c r="E11" t="n">
-        <v>169</v>
+        <v>50</v>
       </c>
       <c r="F11" t="n">
-        <v>1715.38361802058</v>
+        <v>513.3020649918427</v>
       </c>
       <c r="G11" t="n">
-        <v>5316.867210780336</v>
+        <v>1860.69391571247</v>
       </c>
       <c r="H11" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -11215,28 +11215,28 @@
       <c r="A12" t="inlineStr"/>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Nexlev-B0CDPP45BM-Cleaning Machine-SB-PT</t>
+          <t>Nexlev -Catch All- Scalp Massager-SB-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>B0CDPP45BM</t>
+          <t>B0DKK15YNJ</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>6885</v>
+        <v>14000</v>
       </c>
       <c r="E12" t="n">
-        <v>33</v>
+        <v>142</v>
       </c>
       <c r="F12" t="n">
-        <v>366.35</v>
+        <v>1442.285296483697</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>5228.21094813133</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -11253,11 +11253,11 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>B0D672NXC8</t>
+          <t>B0CDPP45BM</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>6885</v>
+        <v>6884</v>
       </c>
       <c r="E13" t="n">
         <v>33</v>
@@ -11286,11 +11286,11 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0D672NXC8</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>6885</v>
+        <v>6884</v>
       </c>
       <c r="E14" t="n">
         <v>33</v>
@@ -11314,28 +11314,28 @@
       <c r="A15" t="inlineStr"/>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Nexlev-B0CDPP45BM-Steam Cleaner-SBV-KT-Exact/Phrase</t>
+          <t>Nexlev-B0CDPP45BM-Cleaning Machine-SB-PT</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>B0CDPP45BM</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>15867</v>
+        <v>6884</v>
       </c>
       <c r="E15" t="n">
-        <v>225</v>
+        <v>33</v>
       </c>
       <c r="F15" t="n">
-        <v>4184.137889877319</v>
+        <v>366.35</v>
       </c>
       <c r="G15" t="n">
-        <v>17420.61236661249</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -11352,23 +11352,23 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0CDPP45BM</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>3341</v>
+        <v>15867</v>
       </c>
       <c r="E16" t="n">
-        <v>45</v>
+        <v>225</v>
       </c>
       <c r="F16" t="n">
-        <v>950.0321101226807</v>
+        <v>4184.137889877319</v>
       </c>
       <c r="G16" t="n">
-        <v>2320.897633387513</v>
+        <v>17420.61236661249</v>
       </c>
       <c r="H16" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -11380,28 +11380,28 @@
       <c r="A17" t="inlineStr"/>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner - SBV-PT</t>
+          <t>Nexlev-B0CDPP45BM-Steam Cleaner-SBV-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>4576</v>
+        <v>3340</v>
       </c>
       <c r="E17" t="n">
-        <v>74</v>
+        <v>45</v>
       </c>
       <c r="F17" t="n">
-        <v>863.8</v>
+        <v>950.0321101226807</v>
       </c>
       <c r="G17" t="n">
-        <v>5083.05</v>
+        <v>2320.897633387513</v>
       </c>
       <c r="H17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -11413,7 +11413,7 @@
       <c r="A18" t="inlineStr"/>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner - SBV-Phrase</t>
+          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner - SBV-PT</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -11422,19 +11422,19 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>2608</v>
+        <v>4576</v>
       </c>
       <c r="E18" t="n">
-        <v>28</v>
+        <v>74</v>
       </c>
       <c r="F18" t="n">
-        <v>319.34</v>
+        <v>863.8</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>5083.05</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -11446,7 +11446,7 @@
       <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner - SBV-Phrase01</t>
+          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner - SBV-Phrase</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -11455,13 +11455,13 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>5932</v>
+        <v>2608</v>
       </c>
       <c r="E19" t="n">
-        <v>51</v>
+        <v>28</v>
       </c>
       <c r="F19" t="n">
-        <v>585.65</v>
+        <v>319.34</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -11479,7 +11479,7 @@
       <c r="A20" t="inlineStr"/>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner -SB-KT-Exact</t>
+          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner - SBV-Phrase01</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -11488,19 +11488,19 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>1365</v>
+        <v>5932</v>
       </c>
       <c r="E20" t="n">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="F20" t="n">
-        <v>369.0066666666667</v>
+        <v>585.65</v>
       </c>
       <c r="G20" t="n">
-        <v>1807.343333333333</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -11517,23 +11517,23 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>B0D672NXC8</t>
+          <t>B0DCK7ZH5P</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>1365</v>
+        <v>4095</v>
       </c>
       <c r="E21" t="n">
-        <v>35</v>
+        <v>106</v>
       </c>
       <c r="F21" t="n">
-        <v>369.0066666666667</v>
+        <v>1107.02</v>
       </c>
       <c r="G21" t="n">
-        <v>1807.343333333333</v>
+        <v>5422.030000000001</v>
       </c>
       <c r="H21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -11545,28 +11545,28 @@
       <c r="A22" t="inlineStr"/>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner -SB-KT-Exact</t>
+          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner -SB-KT-Phrase(Video)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>B0DCK7ZH5P</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>1365</v>
+        <v>4485</v>
       </c>
       <c r="E22" t="n">
-        <v>35</v>
+        <v>93</v>
       </c>
       <c r="F22" t="n">
-        <v>369.0066666666667</v>
+        <v>1076.39</v>
       </c>
       <c r="G22" t="n">
-        <v>1807.343333333333</v>
+        <v>2541.53</v>
       </c>
       <c r="H22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -11578,28 +11578,28 @@
       <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner -SB-KT-Phrase(Video)</t>
+          <t>Nexlev-B0DKK15YNJ- Oil Applicator-SBV-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0DKK15YNJ</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>4485</v>
+        <v>721</v>
       </c>
       <c r="E23" t="n">
-        <v>93</v>
+        <v>22</v>
       </c>
       <c r="F23" t="n">
-        <v>1076.39</v>
+        <v>397.27</v>
       </c>
       <c r="G23" t="n">
-        <v>2541.53</v>
+        <v>4760</v>
       </c>
       <c r="H23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -11611,28 +11611,28 @@
       <c r="A24" t="inlineStr"/>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Nexlev-B0DKK15YNJ- Oil Applicator-SBV-KT-Exact/Phrase</t>
+          <t>Nexlev-B0DNJS23HS-SBV-Phrase-Mop Cleaner-SP</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>B0DKK15YNJ</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>721</v>
+        <v>92</v>
       </c>
       <c r="E24" t="n">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="F24" t="n">
-        <v>397.27</v>
+        <v>42.07</v>
       </c>
       <c r="G24" t="n">
-        <v>4760</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -11644,28 +11644,28 @@
       <c r="A25" t="inlineStr"/>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Nexlev-B0DNJS23HS-SBV-Phrase-Mop Cleaner-SP</t>
+          <t>Nexlev-B0DNJS23HS-Steam Cleaner - SBV-KT-Exact</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0D2LJSQXZ</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>92</v>
+        <v>2661</v>
       </c>
       <c r="E25" t="n">
-        <v>3</v>
+        <v>86</v>
       </c>
       <c r="F25" t="n">
-        <v>42.07</v>
+        <v>1037.514701556099</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>4661.135641610127</v>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -11682,23 +11682,23 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>B0D2LJSQXZ</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>2661</v>
+        <v>4202</v>
       </c>
       <c r="E26" t="n">
-        <v>86</v>
+        <v>135</v>
       </c>
       <c r="F26" t="n">
-        <v>1037.514701556099</v>
+        <v>1638.34054189982</v>
       </c>
       <c r="G26" t="n">
-        <v>4661.135641610127</v>
+        <v>7360.404128722786</v>
       </c>
       <c r="H26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -11715,23 +11715,23 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>4202</v>
+        <v>2521</v>
       </c>
       <c r="E27" t="n">
-        <v>135</v>
+        <v>81</v>
       </c>
       <c r="F27" t="n">
-        <v>1638.34054189982</v>
+        <v>982.8947565440808</v>
       </c>
       <c r="G27" t="n">
-        <v>7360.404128722786</v>
+        <v>4415.750229667087</v>
       </c>
       <c r="H27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -11743,28 +11743,28 @@
       <c r="A28" t="inlineStr"/>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Nexlev-B0DNJS23HS-Steam Cleaner - SBV-KT-Exact</t>
+          <t>Nexlev-B0DNJS23HS-Steam Mop-SB-KT-BM</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>2521</v>
+        <v>1204</v>
       </c>
       <c r="E28" t="n">
-        <v>81</v>
+        <v>28</v>
       </c>
       <c r="F28" t="n">
-        <v>982.8947565440808</v>
+        <v>293.083034260277</v>
       </c>
       <c r="G28" t="n">
-        <v>4415.750229667087</v>
+        <v>8165.15987525244</v>
       </c>
       <c r="H28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -11781,20 +11781,20 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>B0D2LJSQXZ</t>
+          <t>B0GKNGWLJ2</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>662</v>
+        <v>782</v>
       </c>
       <c r="E29" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F29" t="n">
-        <v>161.19</v>
+        <v>190.486965739723</v>
       </c>
       <c r="G29" t="n">
-        <v>4490.68</v>
+        <v>5306.88012474756</v>
       </c>
       <c r="H29" t="n">
         <v>1</v>
@@ -11809,28 +11809,28 @@
       <c r="A30" t="inlineStr"/>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Nexlev-B0DNJS23HS-Steam Mop-SB-KT-BM</t>
+          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- PT</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0DVC7VJP1</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>662</v>
+        <v>5397</v>
       </c>
       <c r="E30" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="F30" t="n">
-        <v>161.19</v>
+        <v>630.95</v>
       </c>
       <c r="G30" t="n">
-        <v>4490.68</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -11842,28 +11842,28 @@
       <c r="A31" t="inlineStr"/>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Nexlev-B0DNJS23HS-Steam Mop-SB-KT-BM</t>
+          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- PT01</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>B0GKNGWLJ2</t>
+          <t>B0DVC7VJP1</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>662</v>
+        <v>4467</v>
       </c>
       <c r="E31" t="n">
-        <v>15</v>
+        <v>48</v>
       </c>
       <c r="F31" t="n">
-        <v>161.19</v>
+        <v>637.5599999999999</v>
       </c>
       <c r="G31" t="n">
-        <v>4490.68</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -11875,7 +11875,7 @@
       <c r="A32" t="inlineStr"/>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- PT</t>
+          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- Phrase01</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -11884,13 +11884,13 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>5397</v>
+        <v>10430</v>
       </c>
       <c r="E32" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F32" t="n">
-        <v>630.95</v>
+        <v>529.66</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -11908,7 +11908,7 @@
       <c r="A33" t="inlineStr"/>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- PT01</t>
+          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV-phrase</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -11917,13 +11917,13 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>4467</v>
+        <v>10840</v>
       </c>
       <c r="E33" t="n">
         <v>48</v>
       </c>
       <c r="F33" t="n">
-        <v>637.5599999999999</v>
+        <v>509.86</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -11941,28 +11941,28 @@
       <c r="A34" t="inlineStr"/>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- Phrase01</t>
+          <t>Nexlev-B0F43P6D23-Steam Cleaner-SB-KT-Phrase</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>B0DVC7VJP1</t>
+          <t>B0D672NXC8</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>10430</v>
+        <v>15741</v>
       </c>
       <c r="E34" t="n">
-        <v>49</v>
+        <v>75</v>
       </c>
       <c r="F34" t="n">
-        <v>529.66</v>
+        <v>708.1391669398656</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>8162.514621215101</v>
       </c>
       <c r="H34" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -11974,28 +11974,28 @@
       <c r="A35" t="inlineStr"/>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV-phrase</t>
+          <t>Nexlev-B0F43P6D23-Steam Cleaner-SB-KT-Phrase</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>B0DVC7VJP1</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>10840</v>
+        <v>7870</v>
       </c>
       <c r="E35" t="n">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="F35" t="n">
-        <v>509.86</v>
+        <v>354.0208330601344</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>4080.695378784898</v>
       </c>
       <c r="H35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -12007,25 +12007,25 @@
       <c r="A36" t="inlineStr"/>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Nexlev-B0F43P6D23-Steam Cleaner-SB-KT-Phrase</t>
+          <t>Nexlev-Catch All-Steam Cleaner -SB-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>B0CDPP45BM</t>
+          <t>B0D672NXC8</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>7870</v>
+        <v>12012</v>
       </c>
       <c r="E36" t="n">
-        <v>38</v>
+        <v>111</v>
       </c>
       <c r="F36" t="n">
-        <v>354.0533333333333</v>
+        <v>946.1314232479821</v>
       </c>
       <c r="G36" t="n">
-        <v>3050.28</v>
+        <v>7455.225785130034</v>
       </c>
       <c r="H36" t="n">
         <v>1</v>
@@ -12040,28 +12040,28 @@
       <c r="A37" t="inlineStr"/>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Nexlev-B0F43P6D23-Steam Cleaner-SB-KT-Phrase</t>
+          <t>Nexlev-Catch All-Steam Cleaner -SB-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>B0D672NXC8</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>7870</v>
+        <v>29217</v>
       </c>
       <c r="E37" t="n">
-        <v>38</v>
+        <v>271</v>
       </c>
       <c r="F37" t="n">
-        <v>354.0533333333333</v>
+        <v>2301.328576752018</v>
       </c>
       <c r="G37" t="n">
-        <v>3050.28</v>
+        <v>18133.76421486997</v>
       </c>
       <c r="H37" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -12073,28 +12073,28 @@
       <c r="A38" t="inlineStr"/>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Nexlev-B0F43P6D23-Steam Cleaner-SB-KT-Phrase</t>
+          <t>Nexlev-Catch All-Vacuum Cleaner-SB-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>7870</v>
+        <v>9440</v>
       </c>
       <c r="E38" t="n">
-        <v>38</v>
+        <v>12</v>
       </c>
       <c r="F38" t="n">
-        <v>354.0533333333333</v>
+        <v>324.805</v>
       </c>
       <c r="G38" t="n">
-        <v>3050.28</v>
+        <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -12106,28 +12106,28 @@
       <c r="A39" t="inlineStr"/>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-Steam Cleaner -SB-KT-Exact/Phrase</t>
+          <t>Nexlev-Catch All-Vacuum Cleaner-SB-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>B0D672NXC8</t>
+          <t>B0DCK7ZH5P</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>12012</v>
+        <v>9440</v>
       </c>
       <c r="E39" t="n">
-        <v>111</v>
+        <v>12</v>
       </c>
       <c r="F39" t="n">
-        <v>946.1314232479821</v>
+        <v>324.805</v>
       </c>
       <c r="G39" t="n">
-        <v>6270.34</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -12139,28 +12139,28 @@
       <c r="A40" t="inlineStr"/>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-Steam Cleaner -SB-KT-Exact/Phrase</t>
+          <t>Nexlev-Steamer-PT(SEAHELTON)-SB</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0CDPP45BM</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>29217</v>
+        <v>3293</v>
       </c>
       <c r="E40" t="n">
-        <v>271</v>
+        <v>187</v>
       </c>
       <c r="F40" t="n">
-        <v>2301.328576752018</v>
+        <v>2337.229394220671</v>
       </c>
       <c r="G40" t="n">
-        <v>15251.7</v>
+        <v>13979.83487307437</v>
       </c>
       <c r="H40" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -12172,28 +12172,28 @@
       <c r="A41" t="inlineStr"/>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-Vacuum Cleaner-SB-KT-Exact/Phrase</t>
+          <t>Nexlev-Steamer-PT(SEAHELTON)-SB</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>9440</v>
+        <v>4388</v>
       </c>
       <c r="E41" t="n">
-        <v>12</v>
+        <v>249</v>
       </c>
       <c r="F41" t="n">
-        <v>324.805</v>
+        <v>3114.188948494056</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>18627.1178050183</v>
       </c>
       <c r="H41" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -12205,28 +12205,28 @@
       <c r="A42" t="inlineStr"/>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-Vacuum Cleaner-SB-KT-Exact/Phrase</t>
+          <t>Nexlev-Steamer-PT(SEAHELTON)-SB</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>B0DCK7ZH5P</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>9440</v>
+        <v>12761</v>
       </c>
       <c r="E42" t="n">
-        <v>12</v>
+        <v>724</v>
       </c>
       <c r="F42" t="n">
-        <v>324.805</v>
+        <v>9056.191657285275</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>54168.43732190733</v>
       </c>
       <c r="H42" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -12238,7 +12238,7 @@
       <c r="A43" t="inlineStr"/>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Nexlev-Steamer-PT(SEAHELTON)-SB</t>
+          <t>Nexlev-Steamers-Branded</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -12247,19 +12247,19 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>3293</v>
+        <v>30</v>
       </c>
       <c r="E43" t="n">
-        <v>187</v>
+        <v>3</v>
       </c>
       <c r="F43" t="n">
-        <v>2337.229394220671</v>
+        <v>19.57333333333333</v>
       </c>
       <c r="G43" t="n">
-        <v>13461.16317853616</v>
+        <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -12271,7 +12271,7 @@
       <c r="A44" t="inlineStr"/>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Nexlev-Steamer-PT(SEAHELTON)-SB</t>
+          <t>Nexlev-Steamers-Branded</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -12280,19 +12280,19 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>4388</v>
+        <v>30</v>
       </c>
       <c r="E44" t="n">
-        <v>249</v>
+        <v>3</v>
       </c>
       <c r="F44" t="n">
-        <v>3114.188948494056</v>
+        <v>19.57333333333333</v>
       </c>
       <c r="G44" t="n">
-        <v>17936.0253247416</v>
+        <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -12304,7 +12304,7 @@
       <c r="A45" t="inlineStr"/>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Nexlev-Steamer-PT(SEAHELTON)-SB</t>
+          <t>Nexlev-Steamers-Branded</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -12313,19 +12313,19 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>12761</v>
+        <v>30</v>
       </c>
       <c r="E45" t="n">
-        <v>724</v>
+        <v>3</v>
       </c>
       <c r="F45" t="n">
-        <v>9056.191657285275</v>
+        <v>19.57333333333333</v>
       </c>
       <c r="G45" t="n">
-        <v>52158.71149672224</v>
+        <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -12337,22 +12337,22 @@
       <c r="A46" t="inlineStr"/>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Nexlev-Steamers-Branded</t>
+          <t>Nexlev-Vacuum Cleaner-Branded</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>B0CDPP45BM</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>30</v>
+        <v>2314</v>
       </c>
       <c r="E46" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F46" t="n">
-        <v>19.57333333333333</v>
+        <v>117.4133333333333</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -12370,22 +12370,22 @@
       <c r="A47" t="inlineStr"/>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Nexlev-Steamers-Branded</t>
+          <t>Nexlev-Vacuum Cleaner-Branded</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0DCK7ZH5P</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>30</v>
+        <v>2314</v>
       </c>
       <c r="E47" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F47" t="n">
-        <v>19.57333333333333</v>
+        <v>117.4133333333333</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
@@ -12403,22 +12403,22 @@
       <c r="A48" t="inlineStr"/>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Nexlev-Steamers-Branded</t>
+          <t>Nexlev-Vacuum Cleaner-Branded</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0DKJSCLBD</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>30</v>
+        <v>2314</v>
       </c>
       <c r="E48" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F48" t="n">
-        <v>19.57333333333333</v>
+        <v>117.4133333333333</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -12427,105 +12427,6 @@
         <v>0</v>
       </c>
       <c r="I48" t="inlineStr">
-        <is>
-          <t>Nexlev</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr"/>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>Nexlev-Vacuum Cleaner-Branded</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>B0CYSLCRQS</t>
-        </is>
-      </c>
-      <c r="D49" t="n">
-        <v>2314</v>
-      </c>
-      <c r="E49" t="n">
-        <v>10</v>
-      </c>
-      <c r="F49" t="n">
-        <v>117.4133333333333</v>
-      </c>
-      <c r="G49" t="n">
-        <v>0</v>
-      </c>
-      <c r="H49" t="n">
-        <v>0</v>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>Nexlev</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr"/>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>Nexlev-Vacuum Cleaner-Branded</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>B0DCK7ZH5P</t>
-        </is>
-      </c>
-      <c r="D50" t="n">
-        <v>2314</v>
-      </c>
-      <c r="E50" t="n">
-        <v>10</v>
-      </c>
-      <c r="F50" t="n">
-        <v>117.4133333333333</v>
-      </c>
-      <c r="G50" t="n">
-        <v>0</v>
-      </c>
-      <c r="H50" t="n">
-        <v>0</v>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>Nexlev</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr"/>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>Nexlev-Vacuum Cleaner-Branded</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>B0DKJSCLBD</t>
-        </is>
-      </c>
-      <c r="D51" t="n">
-        <v>2314</v>
-      </c>
-      <c r="E51" t="n">
-        <v>10</v>
-      </c>
-      <c r="F51" t="n">
-        <v>117.4133333333333</v>
-      </c>
-      <c r="G51" t="n">
-        <v>0</v>
-      </c>
-      <c r="H51" t="n">
-        <v>0</v>
-      </c>
-      <c r="I51" t="inlineStr">
         <is>
           <t>Nexlev</t>
         </is>

--- a/data/ams_weekly_data/Nexlev/ads_report_week23.xlsx
+++ b/data/ams_weekly_data/Nexlev/ads_report_week23.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H315"/>
+  <dimension ref="A1:H310"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,13 +473,13 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>833.6299999999999</v>
+        <v>320.71</v>
       </c>
       <c r="E2" t="n">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="F2" t="n">
-        <v>5773</v>
+        <v>1718</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -613,13 +613,13 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>6.03</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>353</v>
+        <v>12</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -641,13 +641,13 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>446.45</v>
+        <v>163.54</v>
       </c>
       <c r="E8" t="n">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="F8" t="n">
-        <v>861</v>
+        <v>266</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -669,13 +669,13 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>107.42</v>
+        <v>48.75</v>
       </c>
       <c r="E9" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F9" t="n">
-        <v>273</v>
+        <v>106</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -725,13 +725,13 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1435.11</v>
+        <v>1239.86</v>
       </c>
       <c r="E11" t="n">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="F11" t="n">
-        <v>8558</v>
+        <v>6201</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -753,13 +753,13 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>633.1899999999999</v>
+        <v>497.55</v>
       </c>
       <c r="E12" t="n">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="F12" t="n">
-        <v>11315</v>
+        <v>9870</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -809,13 +809,13 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>467.15</v>
+        <v>422.2</v>
       </c>
       <c r="E14" t="n">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="F14" t="n">
-        <v>8915</v>
+        <v>7769</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -837,13 +837,13 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>4517.96</v>
+        <v>4044.21</v>
       </c>
       <c r="E15" t="n">
-        <v>265</v>
+        <v>227</v>
       </c>
       <c r="F15" t="n">
-        <v>14705</v>
+        <v>10679</v>
       </c>
       <c r="G15" t="n">
         <v>2541.52</v>
@@ -893,13 +893,13 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>997.3099999999999</v>
+        <v>512.48</v>
       </c>
       <c r="E17" t="n">
-        <v>114</v>
+        <v>61</v>
       </c>
       <c r="F17" t="n">
-        <v>8084</v>
+        <v>5151</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -1033,19 +1033,19 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>2255.25</v>
+        <v>2160.26</v>
       </c>
       <c r="E22" t="n">
-        <v>418</v>
+        <v>394</v>
       </c>
       <c r="F22" t="n">
-        <v>46549</v>
+        <v>44049</v>
       </c>
       <c r="G22" t="n">
-        <v>2541.52</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -1108,12 +1108,12 @@
       <c r="A25" t="inlineStr"/>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Nexlev - B0DM6BB3VT - Calf Massager - SP - KT - Exact</t>
+          <t>Nexlev - B0DNJP9T35 - Spin Scrubber- SP - PT</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>B0DM6BB3VT</t>
+          <t>B0DNJP9T35</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1123,7 +1123,7 @@
         <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -1136,35 +1136,35 @@
       <c r="A26" t="inlineStr"/>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Nexlev - B0DNJP9T35 - Spin Scrubber- SP - PT</t>
+          <t>Nexlev - B0DNJS23HS - Steam Cleaner - BM</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>B0DNJP9T35</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>3374.3</v>
       </c>
       <c r="E26" t="n">
-        <v>0</v>
+        <v>197</v>
       </c>
       <c r="F26" t="n">
-        <v>4</v>
+        <v>32411</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>10167.8</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr"/>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Nexlev - B0DNJS23HS - Steam Cleaner - BM</t>
+          <t>Nexlev - B0DNJS23HS - Steam Cleaner - CT</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1173,26 +1173,26 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>3489.19</v>
+        <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>204</v>
+        <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>33741</v>
+        <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>10167.8</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr"/>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Nexlev - B0DNJS23HS - Steam Cleaner - CT</t>
+          <t>Nexlev - B0DNJS23HS - Steam Cleaner - CT - On Other</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1220,7 +1220,7 @@
       <c r="A29" t="inlineStr"/>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Nexlev - B0DNJS23HS - Steam Cleaner - CT - On Other</t>
+          <t>Nexlev - B0DNJS23HS - Steam Cleaner - PT</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1248,7 +1248,7 @@
       <c r="A30" t="inlineStr"/>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Nexlev - B0DNJS23HS - Steam Cleaner - PT</t>
+          <t>Nexlev - B0DNJS23HS - Steam Cleaner - Phrase/BM</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1276,35 +1276,35 @@
       <c r="A31" t="inlineStr"/>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Nexlev - B0DNJS23HS - Steam Cleaner - Phrase/BM</t>
+          <t>Nexlev - B0DVC7VJP1 - Stand Mixer - Broad</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0DVC7VJP1</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>0</v>
+        <v>2819.77</v>
       </c>
       <c r="E31" t="n">
-        <v>0</v>
+        <v>190</v>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>28327</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>15251.7</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr"/>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Nexlev - B0DVC7VJP1 - Stand Mixer - Broad</t>
+          <t>Nexlev - B0DVC7VJP1 - Stand Mixer - CT</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1313,26 +1313,26 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>3836.14</v>
+        <v>2072.52</v>
       </c>
       <c r="E32" t="n">
-        <v>263</v>
+        <v>168</v>
       </c>
       <c r="F32" t="n">
-        <v>39183</v>
+        <v>15735</v>
       </c>
       <c r="G32" t="n">
-        <v>20335.6</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr"/>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Nexlev - B0DVC7VJP1 - Stand Mixer - CT</t>
+          <t>Nexlev - B0DVC7VJP1 - Stand Mixer - PT</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1341,26 +1341,26 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>2072.52</v>
+        <v>2082.19</v>
       </c>
       <c r="E33" t="n">
-        <v>168</v>
+        <v>148</v>
       </c>
       <c r="F33" t="n">
-        <v>15735</v>
+        <v>13872</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>30503.4</v>
       </c>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr"/>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Nexlev - B0DVC7VJP1 - Stand Mixer - PT</t>
+          <t>Nexlev - B0DVC7VJP1 - Stand Mixer - PT - SP</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1369,26 +1369,26 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>2082.19</v>
+        <v>433.73</v>
       </c>
       <c r="E34" t="n">
-        <v>148</v>
+        <v>23</v>
       </c>
       <c r="F34" t="n">
-        <v>13872</v>
+        <v>2705</v>
       </c>
       <c r="G34" t="n">
-        <v>30503.4</v>
+        <v>10167.8</v>
       </c>
       <c r="H34" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr"/>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Nexlev - B0DVC7VJP1 - Stand Mixer - PT - SP</t>
+          <t>Nexlev - B0DVC7VJP1 - Stand Mixer - PT -SP</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1397,41 +1397,41 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>433.73</v>
+        <v>89.86</v>
       </c>
       <c r="E35" t="n">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="F35" t="n">
-        <v>2705</v>
+        <v>1659</v>
       </c>
       <c r="G35" t="n">
-        <v>10167.8</v>
+        <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr"/>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Nexlev - B0DVC7VJP1 - Stand Mixer - PT -SP</t>
+          <t>Nexlev - B0F43P6D23 - Steam Cleaner - BM</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>B0DVC7VJP1</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>89.86</v>
+        <v>0</v>
       </c>
       <c r="E36" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F36" t="n">
-        <v>1659</v>
+        <v>0</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -1444,7 +1444,7 @@
       <c r="A37" t="inlineStr"/>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Nexlev - B0F43P6D23 - Steam Cleaner - BM</t>
+          <t>Nexlev - B0F43P6D23 - Steam Cleaner - CT</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1453,26 +1453,26 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>0</v>
+        <v>29.13</v>
       </c>
       <c r="E37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F37" t="n">
-        <v>0</v>
+        <v>201</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>3050</v>
       </c>
       <c r="H37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr"/>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Nexlev - B0F43P6D23 - Steam Cleaner - CT</t>
+          <t>Nexlev - B0F43P6D23 - Steam Cleaner - SP - KT - Exact</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1481,54 +1481,54 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>239.94</v>
+        <v>566.27</v>
       </c>
       <c r="E38" t="n">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="F38" t="n">
-        <v>547</v>
+        <v>1465</v>
       </c>
       <c r="G38" t="n">
-        <v>3050</v>
+        <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr"/>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Nexlev - B0F43P6D23 - Steam Cleaner - SP - KT - Exact</t>
+          <t>Nexlev - B0FS6TB7CP - Portable Blender - BM</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0FS6TB7CP</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>1044.75</v>
+        <v>5361.849999999999</v>
       </c>
       <c r="E39" t="n">
-        <v>51</v>
+        <v>375</v>
       </c>
       <c r="F39" t="n">
-        <v>4018</v>
+        <v>153210</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>22343.25</v>
       </c>
       <c r="H39" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr"/>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Nexlev - B0FS6TB7CP - Portable Blender - BM</t>
+          <t>Nexlev - B0FS6TB7CP - Portable Blender - PT</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1537,26 +1537,26 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>5564.29</v>
+        <v>5041.370000000001</v>
       </c>
       <c r="E40" t="n">
-        <v>390</v>
+        <v>306</v>
       </c>
       <c r="F40" t="n">
-        <v>166017</v>
+        <v>46208</v>
       </c>
       <c r="G40" t="n">
-        <v>24376.3</v>
+        <v>12198.31</v>
       </c>
       <c r="H40" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr"/>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Nexlev - B0FS6TB7CP - Portable Blender - PT</t>
+          <t>Nexlev - B0FS6TB7CP - Portable Blender - PT(1)</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1565,26 +1565,26 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>5785.450000000001</v>
+        <v>374.22</v>
       </c>
       <c r="E41" t="n">
-        <v>355</v>
+        <v>27</v>
       </c>
       <c r="F41" t="n">
-        <v>53375</v>
+        <v>11384</v>
       </c>
       <c r="G41" t="n">
-        <v>14231.36</v>
+        <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr"/>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Nexlev - B0FS6TB7CP - Portable Blender - PT(1)</t>
+          <t>Nexlev - B0FS6TB7CP - Portable Blender - PT(2)</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1593,13 +1593,13 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>374.22</v>
+        <v>178.61</v>
       </c>
       <c r="E42" t="n">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="F42" t="n">
-        <v>11386</v>
+        <v>3174</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -1612,22 +1612,22 @@
       <c r="A43" t="inlineStr"/>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Nexlev - B0FS6TB7CP - Portable Blender - PT(2)</t>
+          <t>Nexlev - B0GN8WW6BC - Stand Mixer with Stainless Steel Bowl  - AT</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>B0FS6TB7CP</t>
+          <t>B0GN8WW6BC</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>178.61</v>
+        <v>331.78</v>
       </c>
       <c r="E43" t="n">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="F43" t="n">
-        <v>3174</v>
+        <v>2694</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -1640,7 +1640,7 @@
       <c r="A44" t="inlineStr"/>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Nexlev - B0GN8WW6BC - Stand Mixer with Stainless Steel Bowl  - AT</t>
+          <t>Nexlev - B0GN8WW6BC - Stand Mixer with Stainless Steel Bowl  - PT</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1649,13 +1649,13 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>331.78</v>
+        <v>466.28</v>
       </c>
       <c r="E44" t="n">
-        <v>39</v>
+        <v>73</v>
       </c>
       <c r="F44" t="n">
-        <v>2694</v>
+        <v>5388</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -1668,7 +1668,7 @@
       <c r="A45" t="inlineStr"/>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Nexlev - B0GN8WW6BC - Stand Mixer with Stainless Steel Bowl  - PT</t>
+          <t>Nexlev - B0GN8WW6BC - Stand Mixer with Stainless Steel Bowl - PT(1)</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1677,13 +1677,13 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>466.28</v>
+        <v>98.14000000000001</v>
       </c>
       <c r="E45" t="n">
-        <v>73</v>
+        <v>10</v>
       </c>
       <c r="F45" t="n">
-        <v>5388</v>
+        <v>1417</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -1696,7 +1696,7 @@
       <c r="A46" t="inlineStr"/>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Nexlev - B0GN8WW6BC - Stand Mixer with Stainless Steel Bowl - PT(1)</t>
+          <t>Nexlev - B0GN8WW6BC - Stand Mixer with Stainless Steel Bowl - Phrase</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1705,13 +1705,13 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>98.14000000000001</v>
+        <v>258.69</v>
       </c>
       <c r="E46" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="F46" t="n">
-        <v>1417</v>
+        <v>7232</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -1724,22 +1724,22 @@
       <c r="A47" t="inlineStr"/>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Nexlev - B0GN8WW6BC - Stand Mixer with Stainless Steel Bowl - Phrase</t>
+          <t>Nexlev - B0GN94YDY2 - Stand Mixer with Digital Timer - AT</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>B0GN8WW6BC</t>
+          <t>B0GN94YDY2</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>258.69</v>
+        <v>427.66</v>
       </c>
       <c r="E47" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="F47" t="n">
-        <v>7232</v>
+        <v>9801</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
@@ -1752,7 +1752,7 @@
       <c r="A48" t="inlineStr"/>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Nexlev - B0GN94YDY2 - Stand Mixer with Digital Timer - AT</t>
+          <t>Nexlev - B0GN94YDY2 - Stand Mixer with Digital Timer - PT</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1761,13 +1761,13 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>427.66</v>
+        <v>180.23</v>
       </c>
       <c r="E48" t="n">
-        <v>46</v>
+        <v>14</v>
       </c>
       <c r="F48" t="n">
-        <v>9801</v>
+        <v>2925</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -1780,35 +1780,35 @@
       <c r="A49" t="inlineStr"/>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Nexlev - B0GN94YDY2 - Stand Mixer with Digital Timer - PT</t>
+          <t>Nexlev - SP- B0GN86G345 -  Car Air Purifier - BM</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>B0GN94YDY2</t>
+          <t>B0GN86G345</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>180.23</v>
+        <v>129.29</v>
       </c>
       <c r="E49" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F49" t="n">
-        <v>2925</v>
+        <v>3138</v>
       </c>
       <c r="G49" t="n">
-        <v>0</v>
+        <v>1948.31</v>
       </c>
       <c r="H49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr"/>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Nexlev - SP- B0GN86G345 -  Car Air Purifier - BM</t>
+          <t>Nexlev - SP- B0GN86G345 -  Car Air Purifier- PT</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1817,41 +1817,41 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>146.73</v>
+        <v>0</v>
       </c>
       <c r="E50" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F50" t="n">
-        <v>3623</v>
+        <v>233</v>
       </c>
       <c r="G50" t="n">
-        <v>1948.31</v>
+        <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr"/>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Nexlev - SP- B0GN86G345 -  Car Air Purifier- PT</t>
+          <t>Nexlev - SP-B0GN94YDY2 - Stand Mixer with Digital Timer - BM</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>B0GN86G345</t>
+          <t>B0GN94YDY2</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>0</v>
+        <v>13.89</v>
       </c>
       <c r="E51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F51" t="n">
-        <v>233</v>
+        <v>590</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -1864,63 +1864,63 @@
       <c r="A52" t="inlineStr"/>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Nexlev - SP-B0GN94YDY2 - Stand Mixer with Digital Timer - BM</t>
+          <t>Nexlev -B0CDPP45BM-Steam Cleaner-SP-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>B0GN94YDY2</t>
+          <t>B0CDPP45BM</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>13.89</v>
+        <v>2657.15</v>
       </c>
       <c r="E52" t="n">
-        <v>1</v>
+        <v>133</v>
       </c>
       <c r="F52" t="n">
-        <v>627</v>
+        <v>10492</v>
       </c>
       <c r="G52" t="n">
-        <v>0</v>
+        <v>7625.42</v>
       </c>
       <c r="H52" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr"/>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Nexlev -B0CDPP45BM-Steam Cleaner-SP-KT-Exact/Phrase</t>
+          <t>Nexlev -B0CYSLCRQS- Vacuum Cleaner -SP-CT</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>B0CDPP45BM</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>9049.040000000001</v>
+        <v>889.72</v>
       </c>
       <c r="E53" t="n">
-        <v>424</v>
+        <v>87</v>
       </c>
       <c r="F53" t="n">
-        <v>30950</v>
+        <v>5343</v>
       </c>
       <c r="G53" t="n">
-        <v>9573.73</v>
+        <v>2880.51</v>
       </c>
       <c r="H53" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr"/>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Nexlev -B0CYSLCRQS- Vacuum Cleaner -SP-CT</t>
+          <t>Nexlev -B0CYSLCRQS- Vacuum Cleaner -SP-PT</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1929,26 +1929,26 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>889.72</v>
+        <v>1476.45</v>
       </c>
       <c r="E54" t="n">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="F54" t="n">
-        <v>5343</v>
+        <v>2012</v>
       </c>
       <c r="G54" t="n">
-        <v>2880.51</v>
+        <v>5083.06</v>
       </c>
       <c r="H54" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr"/>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Nexlev -B0CYSLCRQS- Vacuum Cleaner -SP-PT</t>
+          <t>Nexlev -B0CYSLCRQS- Vacuum Cleaner-SP-KT-Exact</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1957,26 +1957,26 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>1818.86</v>
+        <v>0</v>
       </c>
       <c r="E55" t="n">
-        <v>108</v>
+        <v>0</v>
       </c>
       <c r="F55" t="n">
-        <v>3468</v>
+        <v>0</v>
       </c>
       <c r="G55" t="n">
-        <v>5083.06</v>
+        <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr"/>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Nexlev -B0CYSLCRQS- Vacuum Cleaner-SP-KT-Exact</t>
+          <t>Nexlev -B0CYSLCRQS-Vacuum Cleaner-SP-KT-Broad</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -1985,13 +1985,13 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>0</v>
+        <v>1497.48</v>
       </c>
       <c r="E56" t="n">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="F56" t="n">
-        <v>0</v>
+        <v>2691</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
@@ -2004,63 +2004,63 @@
       <c r="A57" t="inlineStr"/>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Nexlev -B0CYSLCRQS-Vacuum Cleaner-SP-KT-Broad</t>
+          <t>Nexlev -B0DNJS23HS-Steam Cleaner-SP-PT</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>1661.93</v>
+        <v>6575</v>
       </c>
       <c r="E57" t="n">
-        <v>109</v>
+        <v>252</v>
       </c>
       <c r="F57" t="n">
-        <v>3173</v>
+        <v>9114</v>
       </c>
       <c r="G57" t="n">
-        <v>0</v>
+        <v>36518.65</v>
       </c>
       <c r="H57" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr"/>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Nexlev -B0DNJS23HS-Steam Cleaner-SP-PT</t>
+          <t>Nexlev -B0F43P6D23 - Steam Cleaner-SP-KT -Broad</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>7108.27</v>
+        <v>192.92</v>
       </c>
       <c r="E58" t="n">
-        <v>272</v>
+        <v>15</v>
       </c>
       <c r="F58" t="n">
-        <v>9559</v>
+        <v>999</v>
       </c>
       <c r="G58" t="n">
-        <v>31434.75</v>
+        <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr"/>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Nexlev -B0F43P6D23 - Steam Cleaner-SP-KT -Broad</t>
+          <t>Nexlev -B0F43P6D23-Steam Cleaner-SP-PT</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2069,13 +2069,13 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>789.15</v>
+        <v>145.35</v>
       </c>
       <c r="E59" t="n">
-        <v>61</v>
+        <v>9</v>
       </c>
       <c r="F59" t="n">
-        <v>3550</v>
+        <v>198</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
@@ -2088,63 +2088,63 @@
       <c r="A60" t="inlineStr"/>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Nexlev -B0F43P6D23-Steam Cleaner-SP-PT</t>
+          <t>Nexlev -B0FPGDVVCX- Calf Massager-SP-Auto</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0FPGDVVCX</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>432.64</v>
+        <v>637.21</v>
       </c>
       <c r="E60" t="n">
-        <v>28</v>
+        <v>58</v>
       </c>
       <c r="F60" t="n">
-        <v>758</v>
+        <v>4983</v>
       </c>
       <c r="G60" t="n">
-        <v>2541.53</v>
+        <v>7092.629999999999</v>
       </c>
       <c r="H60" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr"/>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Nexlev -B0FPGDVVCX- Calf Massager-SP-Auto</t>
+          <t>Nexlev -B0GKNGWLJ2- Cordless Spin - AT</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>B0FPGDVVCX</t>
+          <t>B0GKNGWLJ2</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>637.21</v>
+        <v>583.04</v>
       </c>
       <c r="E61" t="n">
-        <v>58</v>
+        <v>109</v>
       </c>
       <c r="F61" t="n">
-        <v>4983</v>
+        <v>9027</v>
       </c>
       <c r="G61" t="n">
-        <v>7092.629999999999</v>
+        <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr"/>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Nexlev -B0GKNGWLJ2- Cordless Spin - AT</t>
+          <t>Nexlev -B0GKNGWLJ2- Cordless Spin - CT</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2153,13 +2153,13 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>583.04</v>
+        <v>1246.32</v>
       </c>
       <c r="E62" t="n">
-        <v>109</v>
+        <v>127</v>
       </c>
       <c r="F62" t="n">
-        <v>9027</v>
+        <v>11076</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
@@ -2172,7 +2172,7 @@
       <c r="A63" t="inlineStr"/>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Nexlev -B0GKNGWLJ2- Cordless Spin - CT</t>
+          <t>Nexlev -B0GKNGWLJ2- Cordless Spin -SP-KT-Exact</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2181,13 +2181,13 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>1246.32</v>
+        <v>1035.35</v>
       </c>
       <c r="E63" t="n">
-        <v>127</v>
+        <v>64</v>
       </c>
       <c r="F63" t="n">
-        <v>11077</v>
+        <v>8319</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
@@ -2200,22 +2200,22 @@
       <c r="A64" t="inlineStr"/>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Nexlev -B0GKNGWLJ2- Cordless Spin -SP-KT-Exact</t>
+          <t>Nexlev -SP- B0GN8N96R5 - Smart Air Purifier - BM</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>B0GKNGWLJ2</t>
+          <t>B0GN8N96R5</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>1292</v>
+        <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="F64" t="n">
-        <v>11240</v>
+        <v>1820</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
@@ -2228,22 +2228,22 @@
       <c r="A65" t="inlineStr"/>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Nexlev -Catch All-Tyre Inflator-SP-CT</t>
+          <t>Nexlev -SP- B0GN8N96R5 - Smart Air Purifier - PT</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>B0DJFH6RTL</t>
+          <t>B0GN8N96R5</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>0</v>
+        <v>12.89</v>
       </c>
       <c r="E65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F65" t="n">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
@@ -2256,22 +2256,22 @@
       <c r="A66" t="inlineStr"/>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Nexlev -SP- B0GN8N96R5 - Smart Air Purifier - BM</t>
+          <t>Nexlev-B0CDPP45BM- Steam Cleaner-SP-KT-Exact-Branded</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>B0GN8N96R5</t>
+          <t>B0CDPP45BM</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>0</v>
+        <v>243.63</v>
       </c>
       <c r="E66" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="F66" t="n">
-        <v>2569</v>
+        <v>1226</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
@@ -2284,22 +2284,22 @@
       <c r="A67" t="inlineStr"/>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Nexlev -SP- B0GN8N96R5 - Smart Air Purifier - PT</t>
+          <t>Nexlev-B0CDPP45BM-Steam Cleaner-SP-Auto</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>B0GN8N96R5</t>
+          <t>B0CDPP45BM</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>12.89</v>
+        <v>0</v>
       </c>
       <c r="E67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F67" t="n">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -2312,40 +2312,40 @@
       <c r="A68" t="inlineStr"/>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Nexlev-B0CDPP45BM- Steam Cleaner-SP-KT-Exact-Branded</t>
+          <t>Nexlev-B0CYSLCRQS- Vacuum Cleaner -SP -KT-Exact</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>B0CDPP45BM</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>544.12</v>
+        <v>759.9</v>
       </c>
       <c r="E68" t="n">
-        <v>43</v>
+        <v>89</v>
       </c>
       <c r="F68" t="n">
-        <v>3210</v>
+        <v>9943</v>
       </c>
       <c r="G68" t="n">
-        <v>3812.72</v>
+        <v>5506.77</v>
       </c>
       <c r="H68" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr"/>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Nexlev-B0CDPP45BM-Steam Cleaner-SP-Auto</t>
+          <t>Nexlev-B0CYSLCRQS- Vacuum Cleaner-SP-CT</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>B0CDPP45BM</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2368,7 +2368,7 @@
       <c r="A70" t="inlineStr"/>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Nexlev-B0CYSLCRQS- Vacuum Cleaner -SP -KT-Exact</t>
+          <t>Nexlev-B0CYSLCRQS- Vacuum Cleaner-SP-KT-Phrase/Broad</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2377,26 +2377,26 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>1032.87</v>
+        <v>0</v>
       </c>
       <c r="E70" t="n">
-        <v>115</v>
+        <v>0</v>
       </c>
       <c r="F70" t="n">
-        <v>13123</v>
+        <v>0</v>
       </c>
       <c r="G70" t="n">
-        <v>5506.77</v>
+        <v>0</v>
       </c>
       <c r="H70" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr"/>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Nexlev-B0CYSLCRQS- Vacuum Cleaner-SP-CT</t>
+          <t>Nexlev-B0CYSLCRQS-Sofa Cleaning Machine-SP-CT</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2405,26 +2405,26 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>0</v>
+        <v>2371.47</v>
       </c>
       <c r="E71" t="n">
-        <v>0</v>
+        <v>205</v>
       </c>
       <c r="F71" t="n">
-        <v>0</v>
+        <v>10487</v>
       </c>
       <c r="G71" t="n">
-        <v>0</v>
+        <v>7373.74</v>
       </c>
       <c r="H71" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr"/>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Nexlev-B0CYSLCRQS- Vacuum Cleaner-SP-KT-Phrase/Broad</t>
+          <t>Nexlev-B0CYSLCRQS-Sofa Cleaning Machine-SP-CT-Refine</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2433,26 +2433,26 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>0</v>
+        <v>1816.11</v>
       </c>
       <c r="E72" t="n">
-        <v>0</v>
+        <v>153</v>
       </c>
       <c r="F72" t="n">
-        <v>0</v>
+        <v>6538</v>
       </c>
       <c r="G72" t="n">
-        <v>0</v>
+        <v>7964.41</v>
       </c>
       <c r="H72" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr"/>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Nexlev-B0CYSLCRQS-Sofa Cleaning Machine-SP-CT</t>
+          <t>Nexlev-B0CYSLCRQS-Sofa Cleaning Machine-SP-PT</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2461,26 +2461,26 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>2371.47</v>
+        <v>1700.57</v>
       </c>
       <c r="E73" t="n">
-        <v>205</v>
+        <v>138</v>
       </c>
       <c r="F73" t="n">
-        <v>10487</v>
+        <v>5185</v>
       </c>
       <c r="G73" t="n">
-        <v>7373.74</v>
+        <v>5083.06</v>
       </c>
       <c r="H73" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr"/>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Nexlev-B0CYSLCRQS-Sofa Cleaning Machine-SP-CT-Refine</t>
+          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner -SP-KT-Phrase</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2489,72 +2489,72 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>1816.11</v>
+        <v>1613.29</v>
       </c>
       <c r="E74" t="n">
-        <v>153</v>
+        <v>83</v>
       </c>
       <c r="F74" t="n">
-        <v>6538</v>
+        <v>7421</v>
       </c>
       <c r="G74" t="n">
-        <v>7964.41</v>
+        <v>2541.53</v>
       </c>
       <c r="H74" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr"/>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Nexlev-B0CYSLCRQS-Sofa Cleaning Machine-SP-PT</t>
+          <t>Nexlev-B0D672NXC8-Steam Cleaner-SP-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0D672NXC8</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>1700.57</v>
+        <v>12770.66</v>
       </c>
       <c r="E75" t="n">
-        <v>138</v>
+        <v>370</v>
       </c>
       <c r="F75" t="n">
-        <v>5185</v>
+        <v>82455</v>
       </c>
       <c r="G75" t="n">
-        <v>5083.06</v>
+        <v>40220.35</v>
       </c>
       <c r="H75" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr"/>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner -SP-KT-Phrase</t>
+          <t>Nexlev-B0D672NXC8-Steam Cleaner-SP-PT</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0D672NXC8</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>1907.58</v>
+        <v>321.82</v>
       </c>
       <c r="E76" t="n">
-        <v>100</v>
+        <v>12</v>
       </c>
       <c r="F76" t="n">
-        <v>8292</v>
+        <v>672</v>
       </c>
       <c r="G76" t="n">
-        <v>2541.53</v>
+        <v>6270.34</v>
       </c>
       <c r="H76" t="n">
         <v>1</v>
@@ -2564,218 +2564,218 @@
       <c r="A77" t="inlineStr"/>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Nexlev-B0D2LHNS9B- Callus Remover -SP-CT</t>
+          <t>Nexlev-B0D67727VG-Oil Applicator-SP-KT-Phrase</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>B0D2LHNS9B</t>
+          <t>B0D67727VG</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>0</v>
+        <v>876.8</v>
       </c>
       <c r="E77" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="F77" t="n">
-        <v>0</v>
+        <v>12961</v>
       </c>
       <c r="G77" t="n">
-        <v>0</v>
+        <v>2093.34</v>
       </c>
       <c r="H77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr"/>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Nexlev-B0D672NXC8-Steam Cleaner-SP-KT-Exact/Phrase</t>
+          <t>Nexlev-B0D67727VG-Oil Applicator-SP-PT</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>B0D672NXC8</t>
+          <t>B0D67727VG</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>12770.66</v>
+        <v>137.36</v>
       </c>
       <c r="E78" t="n">
-        <v>370</v>
+        <v>7</v>
       </c>
       <c r="F78" t="n">
-        <v>82457</v>
+        <v>154</v>
       </c>
       <c r="G78" t="n">
-        <v>40220.35</v>
+        <v>1046.67</v>
       </c>
       <c r="H78" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr"/>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Nexlev-B0D672NXC8-Steam Cleaner-SP-PT</t>
+          <t>Nexlev-B0D9KFZYG8- Face Steam-SP-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>B0D672NXC8</t>
+          <t>B0D9KFZYG8</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>321.82</v>
+        <v>1443.11</v>
       </c>
       <c r="E79" t="n">
-        <v>12</v>
+        <v>66</v>
       </c>
       <c r="F79" t="n">
-        <v>672</v>
+        <v>24581</v>
       </c>
       <c r="G79" t="n">
-        <v>6270.34</v>
+        <v>5759.32</v>
       </c>
       <c r="H79" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr"/>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Nexlev-B0D67727VG-Oil Applicator-SP-KT-Phrase</t>
+          <t>Nexlev-B0DCGHVN81-Vacuum Cleaner -Exact</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>B0D67727VG</t>
+          <t>B0DCGHVN81</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>1147.53</v>
+        <v>1235.98</v>
       </c>
       <c r="E80" t="n">
-        <v>95</v>
+        <v>79</v>
       </c>
       <c r="F80" t="n">
-        <v>15725</v>
+        <v>13327</v>
       </c>
       <c r="G80" t="n">
-        <v>3140.01</v>
+        <v>0</v>
       </c>
       <c r="H80" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr"/>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Nexlev-B0D67727VG-Oil Applicator-SP-PT</t>
+          <t>Nexlev-B0DCGHVN81-Vacuum Cleaner -SP-Auto</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>B0D67727VG</t>
+          <t>B0DCGHVN81</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>137.36</v>
+        <v>0</v>
       </c>
       <c r="E81" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F81" t="n">
-        <v>198</v>
+        <v>0</v>
       </c>
       <c r="G81" t="n">
-        <v>1046.67</v>
+        <v>0</v>
       </c>
       <c r="H81" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr"/>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Nexlev-B0D9KFZYG8- Face Steam-SP-KT-Exact/Phrase</t>
+          <t>Nexlev-B0DCK3N2JJ-Hair Straightener--SP-KT-Phrase</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>B0D9KFZYG8</t>
+          <t>B0DCK3N2JJ</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>1772.37</v>
+        <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="F82" t="n">
-        <v>28979</v>
+        <v>87</v>
       </c>
       <c r="G82" t="n">
-        <v>5759.32</v>
+        <v>0</v>
       </c>
       <c r="H82" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr"/>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Nexlev-B0DCGHVN81-Vacuum Cleaner -Exact</t>
+          <t>Nexlev-B0DCK3N2JJ-Hair Straightener-SP-PT</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>B0DCGHVN81</t>
+          <t>B0DCK3N2JJ</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>1435.71</v>
+        <v>303.16</v>
       </c>
       <c r="E83" t="n">
-        <v>94</v>
+        <v>6</v>
       </c>
       <c r="F83" t="n">
-        <v>15068</v>
+        <v>261</v>
       </c>
       <c r="G83" t="n">
-        <v>1814.4</v>
+        <v>0</v>
       </c>
       <c r="H83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr"/>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Nexlev-B0DCGHVN81-Vacuum Cleaner -SP-Auto</t>
+          <t>Nexlev-B0DCK7ZH5P-Sofa Cleaning Machine-SP-PT</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>B0DCGHVN81</t>
+          <t>B0DCK7ZH5P</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>0</v>
+        <v>222.51</v>
       </c>
       <c r="E84" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="F84" t="n">
-        <v>0</v>
+        <v>639</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
@@ -2788,50 +2788,50 @@
       <c r="A85" t="inlineStr"/>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Nexlev-B0DCK3N2JJ-Hair Straightener--SP-KT-Phrase</t>
+          <t>Nexlev-B0DCK7ZH5P-Vacuum Cleaner-SP-KT-Exact</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>B0DCK3N2JJ</t>
+          <t>B0DCK7ZH5P</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>13.89</v>
+        <v>5164.4</v>
       </c>
       <c r="E85" t="n">
+        <v>162</v>
+      </c>
+      <c r="F85" t="n">
+        <v>65779</v>
+      </c>
+      <c r="G85" t="n">
+        <v>5422.04</v>
+      </c>
+      <c r="H85" t="n">
         <v>2</v>
-      </c>
-      <c r="F85" t="n">
-        <v>492</v>
-      </c>
-      <c r="G85" t="n">
-        <v>0</v>
-      </c>
-      <c r="H85" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr"/>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Nexlev-B0DCK3N2JJ-Hair Straightener-SP-PT</t>
+          <t>Nexlev-B0DCK7ZH5P-Vacuum Cleaner-SP-PT</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>B0DCK3N2JJ</t>
+          <t>B0DCK7ZH5P</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>618.76</v>
+        <v>0</v>
       </c>
       <c r="E86" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="F86" t="n">
-        <v>2880</v>
+        <v>0</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -2844,22 +2844,22 @@
       <c r="A87" t="inlineStr"/>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Nexlev-B0DCK7ZH5P-Sofa Cleaning Machine-SP-PT</t>
+          <t>Nexlev-B0DKK15YNJ- Oil Applicator--SP-KT-Phrase</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>B0DCK7ZH5P</t>
+          <t>B0DKK15YNJ</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>222.51</v>
+        <v>0</v>
       </c>
       <c r="E87" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="F87" t="n">
-        <v>639</v>
+        <v>0</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -2872,40 +2872,40 @@
       <c r="A88" t="inlineStr"/>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Nexlev-B0DCK7ZH5P-Vacuum Cleaner-SP-KT-Exact</t>
+          <t>Nexlev-B0DKK15YNJ-Oil Applicator-SP-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>B0DCK7ZH5P</t>
+          <t>B0DKK15YNJ</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>6048.6</v>
+        <v>1100.76</v>
       </c>
       <c r="E88" t="n">
-        <v>192</v>
+        <v>95</v>
       </c>
       <c r="F88" t="n">
-        <v>77522</v>
+        <v>17608</v>
       </c>
       <c r="G88" t="n">
-        <v>8302.549999999999</v>
+        <v>17706.66</v>
       </c>
       <c r="H88" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr"/>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Nexlev-B0DCK7ZH5P-Vacuum Cleaner-SP-PT</t>
+          <t>Nexlev-B0DM6BB3VT-Calf Massager-SP-CT</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>B0DCK7ZH5P</t>
+          <t>B0DM6BB3VT</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -2928,22 +2928,22 @@
       <c r="A90" t="inlineStr"/>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Nexlev-B0DKK15YNJ- Oil Applicator--SP-KT-Phrase</t>
+          <t>Nexlev-B0DNJS23HS -Steam Cleaner-SP-AT</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>B0DKK15YNJ</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>0</v>
+        <v>334.71</v>
       </c>
       <c r="E90" t="n">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="F90" t="n">
-        <v>0</v>
+        <v>6969</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -2956,63 +2956,63 @@
       <c r="A91" t="inlineStr"/>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Nexlev-B0DKK15YNJ-Oil Applicator-SP-KT-Exact/Phrase</t>
+          <t>Nexlev-B0DNJS23HS -Steam Cleaner-SP-KT-Branded</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>B0DKK15YNJ</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>1265.16</v>
+        <v>7322.25</v>
       </c>
       <c r="E91" t="n">
-        <v>109</v>
+        <v>298</v>
       </c>
       <c r="F91" t="n">
-        <v>21367</v>
+        <v>87533</v>
       </c>
       <c r="G91" t="n">
-        <v>20086.66</v>
+        <v>18471.19</v>
       </c>
       <c r="H91" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr"/>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Nexlev-B0DM6BB3VT-Calf Massager-SP-CT</t>
+          <t>Nexlev-B0DNJS23HS- Steam Cleaner-SP-KT-Broad</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>B0DM6BB3VT</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>0</v>
+        <v>4449.06</v>
       </c>
       <c r="E92" t="n">
-        <v>0</v>
+        <v>223</v>
       </c>
       <c r="F92" t="n">
-        <v>0</v>
+        <v>16204</v>
       </c>
       <c r="G92" t="n">
-        <v>0</v>
+        <v>20738.14</v>
       </c>
       <c r="H92" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr"/>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Nexlev-B0DNJS23HS -Steam Cleaner-SP-AT</t>
+          <t>Nexlev-B0DNJS23HS-Steam Cleaner-SP-KT -Exact/Phrase</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3021,26 +3021,26 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>334.71</v>
+        <v>5939.76</v>
       </c>
       <c r="E93" t="n">
-        <v>71</v>
+        <v>212</v>
       </c>
       <c r="F93" t="n">
-        <v>6969</v>
+        <v>32614</v>
       </c>
       <c r="G93" t="n">
-        <v>0</v>
+        <v>10590.68</v>
       </c>
       <c r="H93" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr"/>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Nexlev-B0DNJS23HS -Steam Cleaner-SP-KT-Branded</t>
+          <t>Nexlev-B0DNJS23HS-Steam Mop cleaner-SP-PT</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -3049,405 +3049,405 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>8131.72</v>
+        <v>133</v>
       </c>
       <c r="E94" t="n">
-        <v>335</v>
+        <v>11</v>
       </c>
       <c r="F94" t="n">
-        <v>95678</v>
+        <v>672</v>
       </c>
       <c r="G94" t="n">
-        <v>18471.19</v>
+        <v>0</v>
       </c>
       <c r="H94" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr"/>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Nexlev-B0DNJS23HS- Steam Cleaner-SP-KT-Broad</t>
+          <t>Nexlev-B0DQCWRG3H- Hot Air Brush-SP-KT-Exact</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0DQCWRG3H</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>5784.81</v>
+        <v>1405.3</v>
       </c>
       <c r="E95" t="n">
-        <v>285</v>
+        <v>163</v>
       </c>
       <c r="F95" t="n">
-        <v>18177</v>
+        <v>24995</v>
       </c>
       <c r="G95" t="n">
-        <v>25822.04</v>
+        <v>3507.62</v>
       </c>
       <c r="H95" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr"/>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Nexlev-B0DNJS23HS-Steam Cleaner-SP-KT -Exact/Phrase</t>
+          <t>Nexlev-B0DQCWRG3H-Hot Air Brush- SP-KT-Phrase</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0DQCWRG3H</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>7281.6</v>
+        <v>3604.09</v>
       </c>
       <c r="E96" t="n">
-        <v>250</v>
+        <v>334</v>
       </c>
       <c r="F96" t="n">
-        <v>34262</v>
+        <v>65391</v>
       </c>
       <c r="G96" t="n">
-        <v>15776.27</v>
+        <v>13340.67</v>
       </c>
       <c r="H96" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr"/>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Nexlev-B0DNJS23HS-Steam Mop cleaner-SP-PT</t>
+          <t>Nexlev-B0DVC7VJP1- Stand Mixer- SP-Auto</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0DVC7VJP1</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>133</v>
+        <v>9209.57</v>
       </c>
       <c r="E97" t="n">
-        <v>11</v>
+        <v>747</v>
       </c>
       <c r="F97" t="n">
-        <v>672</v>
+        <v>383946</v>
       </c>
       <c r="G97" t="n">
-        <v>0</v>
+        <v>20335.6</v>
       </c>
       <c r="H97" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr"/>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Nexlev-B0DQCWRG3H- Hot Air Brush-SP-KT-Exact</t>
+          <t>Nexlev-B0DVC7VJP1-Stand Mixer-SP-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>B0DQCWRG3H</t>
+          <t>B0DVC7VJP1</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>1674.73</v>
+        <v>2948.81</v>
       </c>
       <c r="E98" t="n">
-        <v>189</v>
+        <v>208</v>
       </c>
       <c r="F98" t="n">
-        <v>28597</v>
+        <v>40897</v>
       </c>
       <c r="G98" t="n">
-        <v>3507.62</v>
+        <v>20166.11</v>
       </c>
       <c r="H98" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr"/>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Nexlev-B0DQCWRG3H-Hot Air Brush- SP-KT-Phrase</t>
+          <t>Nexlev-B0DVC7VJP1-Stand Mixer-SP-PT</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>B0DQCWRG3H</t>
+          <t>B0DVC7VJP1</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>3939.94</v>
+        <v>0</v>
       </c>
       <c r="E99" t="n">
-        <v>364</v>
+        <v>0</v>
       </c>
       <c r="F99" t="n">
-        <v>70025</v>
+        <v>0</v>
       </c>
       <c r="G99" t="n">
-        <v>11604.23</v>
+        <v>0</v>
       </c>
       <c r="H99" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr"/>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Nexlev-B0DVC7VJP1- Stand Mixer- SP-Auto</t>
+          <t>Nexlev-B0F43P6D23 -Steam Cleaner- SP-KT-Exact</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>B0DVC7VJP1</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>9969.1</v>
+        <v>104.09</v>
       </c>
       <c r="E100" t="n">
-        <v>814</v>
+        <v>4</v>
       </c>
       <c r="F100" t="n">
-        <v>414143</v>
+        <v>415</v>
       </c>
       <c r="G100" t="n">
-        <v>20335.6</v>
+        <v>3050</v>
       </c>
       <c r="H100" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr"/>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Nexlev-B0DVC7VJP1-Stand Mixer-SP-KT-Exact/Phrase</t>
+          <t>Nexlev-B0F43P6D23-Steam Cleaner -SP-CT</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>B0DVC7VJP1</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>3624.66</v>
+        <v>13.7</v>
       </c>
       <c r="E101" t="n">
-        <v>244</v>
+        <v>1</v>
       </c>
       <c r="F101" t="n">
-        <v>46727</v>
+        <v>40</v>
       </c>
       <c r="G101" t="n">
-        <v>35248.31</v>
+        <v>0</v>
       </c>
       <c r="H101" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr"/>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Nexlev-B0DVC7VJP1-Stand Mixer-SP-PT</t>
+          <t>Nexlev-B0F43P6D23-Steam Cleaner-SP-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>B0DVC7VJP1</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>0</v>
+        <v>1130.92</v>
       </c>
       <c r="E102" t="n">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="F102" t="n">
-        <v>0</v>
+        <v>9575</v>
       </c>
       <c r="G102" t="n">
-        <v>0</v>
+        <v>9065.26</v>
       </c>
       <c r="H102" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr"/>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Nexlev-B0F43P6D23 -Steam Cleaner- SP-KT-Exact</t>
+          <t>Nexlev-B0FS6TB7CP-Portable Blender -SP-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0FS6TB7CP</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>404.21</v>
+        <v>5113.99</v>
       </c>
       <c r="E103" t="n">
-        <v>20</v>
+        <v>438</v>
       </c>
       <c r="F103" t="n">
-        <v>1382</v>
+        <v>223190</v>
       </c>
       <c r="G103" t="n">
-        <v>3050</v>
+        <v>6099.15</v>
       </c>
       <c r="H103" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr"/>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Nexlev-B0F43P6D23-Steam Cleaner -SP-CT</t>
+          <t>Nexlev-B0FS6TB7CP-Portable Blender-SP-Auto</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0FS6TB7CP</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>27.66</v>
+        <v>2899.01</v>
       </c>
       <c r="E104" t="n">
-        <v>2</v>
+        <v>299</v>
       </c>
       <c r="F104" t="n">
-        <v>152</v>
+        <v>89289</v>
       </c>
       <c r="G104" t="n">
-        <v>0</v>
+        <v>10250.01</v>
       </c>
       <c r="H104" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr"/>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Nexlev-B0F43P6D23-Steam Cleaner-SP-KT-Exact/Phrase</t>
+          <t>Nexlev-B0GGHZWMVW-Vacuum-BM</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0GGHZWMVW</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>3090.23</v>
+        <v>1300.92</v>
       </c>
       <c r="E105" t="n">
-        <v>150</v>
+        <v>105</v>
       </c>
       <c r="F105" t="n">
-        <v>27343</v>
+        <v>10070</v>
       </c>
       <c r="G105" t="n">
-        <v>9065.26</v>
+        <v>0</v>
       </c>
       <c r="H105" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr"/>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Nexlev-B0FS6TB7CP-Portable Blender -SP-KT-Exact/Phrase</t>
+          <t>Nexlev-B0GGHZWMVW-Vacuum-PT</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>B0FS6TB7CP</t>
+          <t>B0GGHZWMVW</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>5805.17</v>
+        <v>1173.92</v>
       </c>
       <c r="E106" t="n">
-        <v>489</v>
+        <v>79</v>
       </c>
       <c r="F106" t="n">
-        <v>251796</v>
+        <v>3819</v>
       </c>
       <c r="G106" t="n">
-        <v>8132.2</v>
+        <v>0</v>
       </c>
       <c r="H106" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr"/>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Nexlev-B0FS6TB7CP-Portable Blender-SP-Auto</t>
+          <t>Nexlev-B0GGHZWMVW-Vacuum-PT01</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>B0FS6TB7CP</t>
+          <t>B0GGHZWMVW</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>3549.03</v>
+        <v>123.14</v>
       </c>
       <c r="E107" t="n">
-        <v>365</v>
+        <v>9</v>
       </c>
       <c r="F107" t="n">
-        <v>107382</v>
+        <v>536</v>
       </c>
       <c r="G107" t="n">
-        <v>10250.01</v>
+        <v>0</v>
       </c>
       <c r="H107" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr"/>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Nexlev-B0GGHZWMVW-Vacuum-BM</t>
+          <t>Nexlev-B0GKNGWLJ2-Cordless Spin-SP-KT-Exact</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>B0GGHZWMVW</t>
+          <t>B0GKNGWLJ2</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>1300.92</v>
+        <v>521.23</v>
       </c>
       <c r="E108" t="n">
-        <v>105</v>
+        <v>71</v>
       </c>
       <c r="F108" t="n">
-        <v>10070</v>
+        <v>8946</v>
       </c>
       <c r="G108" t="n">
         <v>0</v>
@@ -3460,22 +3460,22 @@
       <c r="A109" t="inlineStr"/>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Nexlev-B0GGHZWMVW-Vacuum-PT</t>
+          <t>Nexlev-B0GKNGWLJ2-Cordless Spin-SP-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>B0GGHZWMVW</t>
+          <t>B0GKNGWLJ2</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>1173.92</v>
+        <v>1923.43</v>
       </c>
       <c r="E109" t="n">
-        <v>79</v>
+        <v>129</v>
       </c>
       <c r="F109" t="n">
-        <v>3819</v>
+        <v>26379</v>
       </c>
       <c r="G109" t="n">
         <v>0</v>
@@ -3488,50 +3488,50 @@
       <c r="A110" t="inlineStr"/>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Nexlev-B0GGHZWMVW-Vacuum-PT01</t>
+          <t>Nexlev-B0GKNGWLJ2-Cordless Spin-SP-KT-PT</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>B0GGHZWMVW</t>
+          <t>B0GKNGWLJ2</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>123.14</v>
+        <v>929.5</v>
       </c>
       <c r="E110" t="n">
-        <v>9</v>
+        <v>68</v>
       </c>
       <c r="F110" t="n">
-        <v>536</v>
+        <v>12870</v>
       </c>
       <c r="G110" t="n">
-        <v>0</v>
+        <v>3304.24</v>
       </c>
       <c r="H110" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr"/>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Nexlev-B0GKNGWLJ2-Cordless Spin-SP-KT-Exact</t>
+          <t>Nexlev-Branded-All Products</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>B0GKNGWLJ2</t>
+          <t>B0CDQ55W2M</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>704.46</v>
+        <v>0</v>
       </c>
       <c r="E111" t="n">
-        <v>99</v>
+        <v>0</v>
       </c>
       <c r="F111" t="n">
-        <v>12751</v>
+        <v>8</v>
       </c>
       <c r="G111" t="n">
         <v>0</v>
@@ -3544,22 +3544,22 @@
       <c r="A112" t="inlineStr"/>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Nexlev-B0GKNGWLJ2-Cordless Spin-SP-KT-Exact/Phrase</t>
+          <t>Nexlev-Branded-All Products</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>B0GKNGWLJ2</t>
+          <t>B0CQX9ZZMH</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>2317.69</v>
+        <v>23.33</v>
       </c>
       <c r="E112" t="n">
-        <v>157</v>
+        <v>3</v>
       </c>
       <c r="F112" t="n">
-        <v>27913</v>
+        <v>612</v>
       </c>
       <c r="G112" t="n">
         <v>0</v>
@@ -3572,28 +3572,28 @@
       <c r="A113" t="inlineStr"/>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Nexlev-B0GKNGWLJ2-Cordless Spin-SP-KT-PT</t>
+          <t>Nexlev-Branded-All Products</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>B0GKNGWLJ2</t>
+          <t>B0CW1JJP9S</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>929.5</v>
+        <v>3.91</v>
       </c>
       <c r="E113" t="n">
-        <v>68</v>
+        <v>1</v>
       </c>
       <c r="F113" t="n">
-        <v>12870</v>
+        <v>275</v>
       </c>
       <c r="G113" t="n">
-        <v>3304.24</v>
+        <v>0</v>
       </c>
       <c r="H113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="114">
@@ -3605,23 +3605,23 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>B0CDQ55W2M</t>
+          <t>B0D25LNDSY</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>0</v>
+        <v>32.16</v>
       </c>
       <c r="E114" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F114" t="n">
-        <v>9</v>
+        <v>305</v>
       </c>
       <c r="G114" t="n">
-        <v>0</v>
+        <v>2031.36</v>
       </c>
       <c r="H114" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="115">
@@ -3633,17 +3633,17 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>B0CQX9ZZMH</t>
+          <t>B0D2LD6BYJ</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>29.45</v>
+        <v>7.7</v>
       </c>
       <c r="E115" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F115" t="n">
-        <v>860</v>
+        <v>25</v>
       </c>
       <c r="G115" t="n">
         <v>0</v>
@@ -3661,17 +3661,17 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>B0CW1JJP9S</t>
+          <t>B0D2LFMY48</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>3.91</v>
+        <v>0</v>
       </c>
       <c r="E116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F116" t="n">
-        <v>290</v>
+        <v>86</v>
       </c>
       <c r="G116" t="n">
         <v>0</v>
@@ -3689,23 +3689,23 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>B0D25LNDSY</t>
+          <t>B0D2LKB4BJ</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>32.16</v>
+        <v>7.69</v>
       </c>
       <c r="E117" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F117" t="n">
-        <v>329</v>
+        <v>91</v>
       </c>
       <c r="G117" t="n">
-        <v>2031.36</v>
+        <v>0</v>
       </c>
       <c r="H117" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="118">
@@ -3717,17 +3717,17 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>B0D2LD6BYJ</t>
+          <t>B0D63FKYZ5</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>7.7</v>
+        <v>13.54</v>
       </c>
       <c r="E118" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F118" t="n">
-        <v>30</v>
+        <v>71</v>
       </c>
       <c r="G118" t="n">
         <v>0</v>
@@ -3745,7 +3745,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>B0D2LFMY48</t>
+          <t>B0D81DLSFT</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -3755,7 +3755,7 @@
         <v>0</v>
       </c>
       <c r="F119" t="n">
-        <v>164</v>
+        <v>69</v>
       </c>
       <c r="G119" t="n">
         <v>0</v>
@@ -3773,17 +3773,17 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>B0D2LKB4BJ</t>
+          <t>B0D83Q7L8W</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>7.69</v>
+        <v>3.26</v>
       </c>
       <c r="E120" t="n">
         <v>1</v>
       </c>
       <c r="F120" t="n">
-        <v>170</v>
+        <v>119</v>
       </c>
       <c r="G120" t="n">
         <v>0</v>
@@ -3801,17 +3801,17 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>B0D63FKYZ5</t>
+          <t>B0D8445KJN</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>23.03</v>
+        <v>11.09</v>
       </c>
       <c r="E121" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F121" t="n">
-        <v>103</v>
+        <v>2614</v>
       </c>
       <c r="G121" t="n">
         <v>0</v>
@@ -3829,17 +3829,17 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>B0D81DLSFT</t>
+          <t>B0D86Y2V7V</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>0</v>
+        <v>7.16</v>
       </c>
       <c r="E122" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F122" t="n">
-        <v>71</v>
+        <v>153</v>
       </c>
       <c r="G122" t="n">
         <v>0</v>
@@ -3857,17 +3857,17 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>B0D83Q7L8W</t>
+          <t>B0D86ZC9YT</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="E123" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F123" t="n">
-        <v>236</v>
+        <v>29</v>
       </c>
       <c r="G123" t="n">
         <v>0</v>
@@ -3885,17 +3885,17 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>B0D8445KJN</t>
+          <t>B0D9KCNVNM</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>23.21</v>
+        <v>0</v>
       </c>
       <c r="E124" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F124" t="n">
-        <v>3037</v>
+        <v>37</v>
       </c>
       <c r="G124" t="n">
         <v>0</v>
@@ -3913,23 +3913,23 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>B0D86Y2V7V</t>
+          <t>B0D9KFP4MG</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>7.16</v>
+        <v>65.72</v>
       </c>
       <c r="E125" t="n">
+        <v>8</v>
+      </c>
+      <c r="F125" t="n">
+        <v>459</v>
+      </c>
+      <c r="G125" t="n">
+        <v>2287.29</v>
+      </c>
+      <c r="H125" t="n">
         <v>1</v>
-      </c>
-      <c r="F125" t="n">
-        <v>163</v>
-      </c>
-      <c r="G125" t="n">
-        <v>0</v>
-      </c>
-      <c r="H125" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="126">
@@ -3941,17 +3941,17 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>B0D86ZC9YT</t>
+          <t>B0D9KFQG8Q</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>7.68</v>
+        <v>7.58</v>
       </c>
       <c r="E126" t="n">
         <v>1</v>
       </c>
       <c r="F126" t="n">
-        <v>38</v>
+        <v>766</v>
       </c>
       <c r="G126" t="n">
         <v>0</v>
@@ -3969,17 +3969,17 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>B0D9KCNVNM</t>
+          <t>B0DCK4DR1B</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>0</v>
+        <v>38.33</v>
       </c>
       <c r="E127" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F127" t="n">
-        <v>53</v>
+        <v>276</v>
       </c>
       <c r="G127" t="n">
         <v>0</v>
@@ -3997,23 +3997,23 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>B0D9KFP4MG</t>
+          <t>B0DFCDKMWR</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>95.3</v>
+        <v>13.65</v>
       </c>
       <c r="E128" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="F128" t="n">
-        <v>500</v>
+        <v>57</v>
       </c>
       <c r="G128" t="n">
-        <v>3938.99</v>
+        <v>0</v>
       </c>
       <c r="H128" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="129">
@@ -4025,17 +4025,17 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>B0D9KFQG8Q</t>
+          <t>B0DFCDZWND</t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>15.28</v>
+        <v>26.23</v>
       </c>
       <c r="E129" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F129" t="n">
-        <v>799</v>
+        <v>127</v>
       </c>
       <c r="G129" t="n">
         <v>0</v>
@@ -4053,17 +4053,17 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>B0DCK4DR1B</t>
+          <t>B0DFCG2VGS</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>38.33</v>
+        <v>116.43</v>
       </c>
       <c r="E130" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="F130" t="n">
-        <v>293</v>
+        <v>1693</v>
       </c>
       <c r="G130" t="n">
         <v>0</v>
@@ -4081,17 +4081,17 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>B0DFCDKMWR</t>
+          <t>B0DFD123P5</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>21.27</v>
+        <v>27.27</v>
       </c>
       <c r="E131" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F131" t="n">
-        <v>89</v>
+        <v>575</v>
       </c>
       <c r="G131" t="n">
         <v>0</v>
@@ -4109,17 +4109,17 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>B0DFCDZWND</t>
+          <t>B0DFM4JZV9</t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>26.23</v>
+        <v>3.13</v>
       </c>
       <c r="E132" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F132" t="n">
-        <v>134</v>
+        <v>3</v>
       </c>
       <c r="G132" t="n">
         <v>0</v>
@@ -4137,17 +4137,17 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>B0DFCG2VGS</t>
+          <t>B0DJFH4K8B</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>124.19</v>
+        <v>0</v>
       </c>
       <c r="E133" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="F133" t="n">
-        <v>2193</v>
+        <v>5</v>
       </c>
       <c r="G133" t="n">
         <v>0</v>
@@ -4165,17 +4165,17 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>B0DFD123P5</t>
+          <t>B0DJFH6RTL</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>40.97</v>
+        <v>3.16</v>
       </c>
       <c r="E134" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F134" t="n">
-        <v>902</v>
+        <v>50</v>
       </c>
       <c r="G134" t="n">
         <v>0</v>
@@ -4193,17 +4193,17 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>B0DFM4JZV9</t>
+          <t>B0DK9LYT4P</t>
         </is>
       </c>
       <c r="D135" t="n">
-        <v>3.13</v>
+        <v>4.03</v>
       </c>
       <c r="E135" t="n">
         <v>1</v>
       </c>
       <c r="F135" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="G135" t="n">
         <v>0</v>
@@ -4221,17 +4221,17 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>B0DJFH4K8B</t>
+          <t>B0DKJSCLBD</t>
         </is>
       </c>
       <c r="D136" t="n">
-        <v>0</v>
+        <v>145.9</v>
       </c>
       <c r="E136" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="F136" t="n">
-        <v>11</v>
+        <v>5143</v>
       </c>
       <c r="G136" t="n">
         <v>0</v>
@@ -4249,17 +4249,17 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>B0DJFH6RTL</t>
+          <t>B0DNJF1BLS</t>
         </is>
       </c>
       <c r="D137" t="n">
-        <v>3.16</v>
+        <v>47.62</v>
       </c>
       <c r="E137" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F137" t="n">
-        <v>52</v>
+        <v>1608</v>
       </c>
       <c r="G137" t="n">
         <v>0</v>
@@ -4277,17 +4277,17 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>B0DK9LYT4P</t>
+          <t>B0DNJJKBKG</t>
         </is>
       </c>
       <c r="D138" t="n">
-        <v>4.03</v>
+        <v>0</v>
       </c>
       <c r="E138" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F138" t="n">
-        <v>14</v>
+        <v>126</v>
       </c>
       <c r="G138" t="n">
         <v>0</v>
@@ -4305,17 +4305,17 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>B0DKJSCLBD</t>
+          <t>B0DNJP9T35</t>
         </is>
       </c>
       <c r="D139" t="n">
-        <v>257.98</v>
+        <v>0</v>
       </c>
       <c r="E139" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="F139" t="n">
-        <v>6080</v>
+        <v>3</v>
       </c>
       <c r="G139" t="n">
         <v>0</v>
@@ -4333,17 +4333,17 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>B0DNJF1BLS</t>
+          <t>B0DT6Y7KJM</t>
         </is>
       </c>
       <c r="D140" t="n">
-        <v>55.32</v>
+        <v>17.54</v>
       </c>
       <c r="E140" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F140" t="n">
-        <v>2577</v>
+        <v>279</v>
       </c>
       <c r="G140" t="n">
         <v>0</v>
@@ -4361,7 +4361,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>B0DNJJKBKG</t>
+          <t>B0DV9CY3XR</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -4371,7 +4371,7 @@
         <v>0</v>
       </c>
       <c r="F141" t="n">
-        <v>137</v>
+        <v>27</v>
       </c>
       <c r="G141" t="n">
         <v>0</v>
@@ -4389,17 +4389,17 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>B0DNJP9T35</t>
+          <t>B0DVC58QPZ</t>
         </is>
       </c>
       <c r="D142" t="n">
-        <v>0</v>
+        <v>18.97</v>
       </c>
       <c r="E142" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F142" t="n">
-        <v>5</v>
+        <v>117</v>
       </c>
       <c r="G142" t="n">
         <v>0</v>
@@ -4417,17 +4417,17 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>B0DT6Y7KJM</t>
+          <t>B0DVC968P1</t>
         </is>
       </c>
       <c r="D143" t="n">
-        <v>17.54</v>
+        <v>0</v>
       </c>
       <c r="E143" t="n">
+        <v>0</v>
+      </c>
+      <c r="F143" t="n">
         <v>2</v>
-      </c>
-      <c r="F143" t="n">
-        <v>299</v>
       </c>
       <c r="G143" t="n">
         <v>0</v>
@@ -4445,7 +4445,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>B0DV9CY3XR</t>
+          <t>B0DVC9PRSD</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -4455,7 +4455,7 @@
         <v>0</v>
       </c>
       <c r="F144" t="n">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="G144" t="n">
         <v>0</v>
@@ -4473,17 +4473,17 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>B0DVC58QPZ</t>
+          <t>B0DVSZ2VVJ</t>
         </is>
       </c>
       <c r="D145" t="n">
-        <v>28.21</v>
+        <v>15.4</v>
       </c>
       <c r="E145" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F145" t="n">
-        <v>165</v>
+        <v>72</v>
       </c>
       <c r="G145" t="n">
         <v>0</v>
@@ -4501,17 +4501,17 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>B0DVC968P1</t>
+          <t>B0F29SZCVF</t>
         </is>
       </c>
       <c r="D146" t="n">
-        <v>0</v>
+        <v>74.20999999999999</v>
       </c>
       <c r="E146" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F146" t="n">
-        <v>3</v>
+        <v>363</v>
       </c>
       <c r="G146" t="n">
         <v>0</v>
@@ -4529,23 +4529,23 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>B0DVC9PRSD</t>
+          <t>B0F2MZ8CG9</t>
         </is>
       </c>
       <c r="D147" t="n">
-        <v>0</v>
+        <v>5.98</v>
       </c>
       <c r="E147" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F147" t="n">
-        <v>25</v>
+        <v>151</v>
       </c>
       <c r="G147" t="n">
-        <v>0</v>
+        <v>676.28</v>
       </c>
       <c r="H147" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="148">
@@ -4557,17 +4557,17 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>B0DVSZ2VVJ</t>
+          <t>B0F2N11VTN</t>
         </is>
       </c>
       <c r="D148" t="n">
-        <v>15.4</v>
+        <v>22.9</v>
       </c>
       <c r="E148" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F148" t="n">
-        <v>126</v>
+        <v>3227</v>
       </c>
       <c r="G148" t="n">
         <v>0</v>
@@ -4585,23 +4585,23 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>B0F29SZCVF</t>
+          <t>B0F2N1HTBT</t>
         </is>
       </c>
       <c r="D149" t="n">
-        <v>98.13</v>
+        <v>42.13</v>
       </c>
       <c r="E149" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="F149" t="n">
-        <v>403</v>
+        <v>1694</v>
       </c>
       <c r="G149" t="n">
-        <v>2856.19</v>
+        <v>0</v>
       </c>
       <c r="H149" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="150">
@@ -4613,23 +4613,23 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>B0F2MZ8CG9</t>
+          <t>B0F2N37819</t>
         </is>
       </c>
       <c r="D150" t="n">
-        <v>13.64</v>
+        <v>0</v>
       </c>
       <c r="E150" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F150" t="n">
-        <v>285</v>
+        <v>154</v>
       </c>
       <c r="G150" t="n">
-        <v>676.28</v>
+        <v>0</v>
       </c>
       <c r="H150" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="151">
@@ -4641,17 +4641,17 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>B0F2N11VTN</t>
+          <t>B0F2N4N83Y</t>
         </is>
       </c>
       <c r="D151" t="n">
-        <v>22.9</v>
+        <v>15.4</v>
       </c>
       <c r="E151" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F151" t="n">
-        <v>4831</v>
+        <v>146</v>
       </c>
       <c r="G151" t="n">
         <v>0</v>
@@ -4669,17 +4669,17 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>B0F2N1HTBT</t>
+          <t>B0F678L8YT</t>
         </is>
       </c>
       <c r="D152" t="n">
-        <v>42.13</v>
+        <v>8</v>
       </c>
       <c r="E152" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F152" t="n">
-        <v>1694</v>
+        <v>589</v>
       </c>
       <c r="G152" t="n">
         <v>0</v>
@@ -4697,7 +4697,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>B0F2N37819</t>
+          <t>B0F678RRCX</t>
         </is>
       </c>
       <c r="D153" t="n">
@@ -4707,7 +4707,7 @@
         <v>0</v>
       </c>
       <c r="F153" t="n">
-        <v>167</v>
+        <v>0</v>
       </c>
       <c r="G153" t="n">
         <v>0</v>
@@ -4725,17 +4725,17 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>B0F2N4N83Y</t>
+          <t>B0F679QJH4</t>
         </is>
       </c>
       <c r="D154" t="n">
-        <v>15.4</v>
+        <v>14.26</v>
       </c>
       <c r="E154" t="n">
         <v>2</v>
       </c>
       <c r="F154" t="n">
-        <v>169</v>
+        <v>4614</v>
       </c>
       <c r="G154" t="n">
         <v>0</v>
@@ -4753,17 +4753,17 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>B0F678L8YT</t>
+          <t>B0F67BSF2R</t>
         </is>
       </c>
       <c r="D155" t="n">
-        <v>8</v>
+        <v>20.28</v>
       </c>
       <c r="E155" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F155" t="n">
-        <v>606</v>
+        <v>15854</v>
       </c>
       <c r="G155" t="n">
         <v>0</v>
@@ -4781,23 +4781,23 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>B0F678RRCX</t>
+          <t>B0F67BW7SF</t>
         </is>
       </c>
       <c r="D156" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="E156" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F156" t="n">
-        <v>0</v>
+        <v>162</v>
       </c>
       <c r="G156" t="n">
-        <v>0</v>
+        <v>931.36</v>
       </c>
       <c r="H156" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="157">
@@ -4809,17 +4809,17 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>B0F679QJH4</t>
+          <t>B0F74DJYG6</t>
         </is>
       </c>
       <c r="D157" t="n">
-        <v>14.26</v>
+        <v>14.52</v>
       </c>
       <c r="E157" t="n">
         <v>2</v>
       </c>
       <c r="F157" t="n">
-        <v>4688</v>
+        <v>1213</v>
       </c>
       <c r="G157" t="n">
         <v>0</v>
@@ -4837,17 +4837,17 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>B0F67BSF2R</t>
+          <t>B0FJ1ZB4G9</t>
         </is>
       </c>
       <c r="D158" t="n">
-        <v>26.64</v>
+        <v>0</v>
       </c>
       <c r="E158" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F158" t="n">
-        <v>17544</v>
+        <v>103</v>
       </c>
       <c r="G158" t="n">
         <v>0</v>
@@ -4865,23 +4865,23 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>B0F67BW7SF</t>
+          <t>B0FJG5PFGQ</t>
         </is>
       </c>
       <c r="D159" t="n">
-        <v>4.33</v>
+        <v>7.32</v>
       </c>
       <c r="E159" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F159" t="n">
-        <v>185</v>
+        <v>343</v>
       </c>
       <c r="G159" t="n">
-        <v>931.36</v>
+        <v>0</v>
       </c>
       <c r="H159" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="160">
@@ -4893,17 +4893,17 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>B0F74DJYG6</t>
+          <t>B0FMF1D9NV</t>
         </is>
       </c>
       <c r="D160" t="n">
-        <v>14.52</v>
+        <v>22.44</v>
       </c>
       <c r="E160" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F160" t="n">
-        <v>1213</v>
+        <v>490</v>
       </c>
       <c r="G160" t="n">
         <v>0</v>
@@ -4921,7 +4921,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>B0FJ1ZB4G9</t>
+          <t>B0FS7T8151</t>
         </is>
       </c>
       <c r="D161" t="n">
@@ -4931,7 +4931,7 @@
         <v>0</v>
       </c>
       <c r="F161" t="n">
-        <v>135</v>
+        <v>30</v>
       </c>
       <c r="G161" t="n">
         <v>0</v>
@@ -4949,17 +4949,17 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>B0FJG5PFGQ</t>
+          <t>B0FYNKYJFN</t>
         </is>
       </c>
       <c r="D162" t="n">
-        <v>7.32</v>
+        <v>7.65</v>
       </c>
       <c r="E162" t="n">
         <v>1</v>
       </c>
       <c r="F162" t="n">
-        <v>384</v>
+        <v>83</v>
       </c>
       <c r="G162" t="n">
         <v>0</v>
@@ -4977,17 +4977,17 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>B0FMF1D9NV</t>
+          <t>B0GGHZWMVW</t>
         </is>
       </c>
       <c r="D163" t="n">
-        <v>22.44</v>
+        <v>244.37</v>
       </c>
       <c r="E163" t="n">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="F163" t="n">
-        <v>518</v>
+        <v>11315</v>
       </c>
       <c r="G163" t="n">
         <v>0</v>
@@ -5000,22 +5000,22 @@
       <c r="A164" t="inlineStr"/>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Nexlev-Branded-All Products</t>
+          <t>Nexlev-Branded-Phrase</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>B0FS7T8151</t>
+          <t>B0DCGHVN81</t>
         </is>
       </c>
       <c r="D164" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="E164" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F164" t="n">
-        <v>37</v>
+        <v>1986</v>
       </c>
       <c r="G164" t="n">
         <v>0</v>
@@ -5028,22 +5028,22 @@
       <c r="A165" t="inlineStr"/>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Nexlev-Branded-All Products</t>
+          <t>Nexlev-Branded-Phrase</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>B0FYNKYJFN</t>
+          <t>B0GGHZWMVW</t>
         </is>
       </c>
       <c r="D165" t="n">
-        <v>15.35</v>
+        <v>0</v>
       </c>
       <c r="E165" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F165" t="n">
-        <v>168</v>
+        <v>288</v>
       </c>
       <c r="G165" t="n">
         <v>0</v>
@@ -5056,22 +5056,22 @@
       <c r="A166" t="inlineStr"/>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Nexlev-Branded-All Products</t>
+          <t>Nexlev-Branded-Phrase</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>B0GGHZWMVW</t>
+          <t>B0GN8WW6BC</t>
         </is>
       </c>
       <c r="D166" t="n">
-        <v>272.17</v>
+        <v>0</v>
       </c>
       <c r="E166" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="F166" t="n">
-        <v>11704</v>
+        <v>8</v>
       </c>
       <c r="G166" t="n">
         <v>0</v>
@@ -5089,17 +5089,17 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>B0DCGHVN81</t>
+          <t>B0GN94YDY2</t>
         </is>
       </c>
       <c r="D167" t="n">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="E167" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F167" t="n">
-        <v>1986</v>
+        <v>11</v>
       </c>
       <c r="G167" t="n">
         <v>0</v>
@@ -5112,12 +5112,12 @@
       <c r="A168" t="inlineStr"/>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Nexlev-Branded-Phrase</t>
+          <t>Nexlev-Catch All-AT</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>B0GGHZWMVW</t>
+          <t>B0CDQ55W2M</t>
         </is>
       </c>
       <c r="D168" t="n">
@@ -5127,7 +5127,7 @@
         <v>0</v>
       </c>
       <c r="F168" t="n">
-        <v>288</v>
+        <v>16</v>
       </c>
       <c r="G168" t="n">
         <v>0</v>
@@ -5140,22 +5140,22 @@
       <c r="A169" t="inlineStr"/>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Nexlev-Branded-Phrase</t>
+          <t>Nexlev-Catch All-AT</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>B0GN8WW6BC</t>
+          <t>B0CQX9ZZMH</t>
         </is>
       </c>
       <c r="D169" t="n">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="E169" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F169" t="n">
-        <v>8</v>
+        <v>251</v>
       </c>
       <c r="G169" t="n">
         <v>0</v>
@@ -5168,22 +5168,22 @@
       <c r="A170" t="inlineStr"/>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Nexlev-Branded-Phrase</t>
+          <t>Nexlev-Catch All-AT</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>B0GN94YDY2</t>
+          <t>B0CW1JJP9S</t>
         </is>
       </c>
       <c r="D170" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="E170" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F170" t="n">
-        <v>11</v>
+        <v>372</v>
       </c>
       <c r="G170" t="n">
         <v>0</v>
@@ -5201,17 +5201,17 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>B0CDQ55W2M</t>
+          <t>B0D25LNDSY</t>
         </is>
       </c>
       <c r="D171" t="n">
-        <v>0</v>
+        <v>72.56999999999999</v>
       </c>
       <c r="E171" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="F171" t="n">
-        <v>24</v>
+        <v>2219</v>
       </c>
       <c r="G171" t="n">
         <v>0</v>
@@ -5229,17 +5229,17 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>B0CQX9ZZMH</t>
+          <t>B0D2LD6BYJ</t>
         </is>
       </c>
       <c r="D172" t="n">
-        <v>3.67</v>
+        <v>4.37</v>
       </c>
       <c r="E172" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F172" t="n">
-        <v>404</v>
+        <v>2425</v>
       </c>
       <c r="G172" t="n">
         <v>0</v>
@@ -5257,17 +5257,17 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>B0CW1JJP9S</t>
+          <t>B0D2LFMY48</t>
         </is>
       </c>
       <c r="D173" t="n">
-        <v>5.1</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="E173" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F173" t="n">
-        <v>424</v>
+        <v>2025</v>
       </c>
       <c r="G173" t="n">
         <v>0</v>
@@ -5285,23 +5285,23 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>B0D25LNDSY</t>
+          <t>B0D2LKB4BJ</t>
         </is>
       </c>
       <c r="D174" t="n">
-        <v>87.84</v>
+        <v>8.33</v>
       </c>
       <c r="E174" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="F174" t="n">
-        <v>2582</v>
+        <v>685</v>
       </c>
       <c r="G174" t="n">
-        <v>677.12</v>
+        <v>0</v>
       </c>
       <c r="H174" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="175">
@@ -5313,17 +5313,17 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>B0D2LD6BYJ</t>
+          <t>B0D63FKYZ5</t>
         </is>
       </c>
       <c r="D175" t="n">
-        <v>8.98</v>
+        <v>1.23</v>
       </c>
       <c r="E175" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F175" t="n">
-        <v>8028</v>
+        <v>645</v>
       </c>
       <c r="G175" t="n">
         <v>0</v>
@@ -5341,17 +5341,17 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>B0D2LFMY48</t>
+          <t>B0D81DLSFT</t>
         </is>
       </c>
       <c r="D176" t="n">
-        <v>12.21</v>
+        <v>4.41</v>
       </c>
       <c r="E176" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F176" t="n">
-        <v>2573</v>
+        <v>1443</v>
       </c>
       <c r="G176" t="n">
         <v>0</v>
@@ -5369,17 +5369,17 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>B0D2LKB4BJ</t>
+          <t>B0D83Q7L8W</t>
         </is>
       </c>
       <c r="D177" t="n">
-        <v>11.52</v>
+        <v>11.85</v>
       </c>
       <c r="E177" t="n">
         <v>4</v>
       </c>
       <c r="F177" t="n">
-        <v>1006</v>
+        <v>456</v>
       </c>
       <c r="G177" t="n">
         <v>0</v>
@@ -5397,17 +5397,17 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>B0D63FKYZ5</t>
+          <t>B0D8445KJN</t>
         </is>
       </c>
       <c r="D178" t="n">
-        <v>4.9</v>
+        <v>16.78</v>
       </c>
       <c r="E178" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F178" t="n">
-        <v>873</v>
+        <v>1861</v>
       </c>
       <c r="G178" t="n">
         <v>0</v>
@@ -5425,17 +5425,17 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>B0D81DLSFT</t>
+          <t>B0D86Y2V7V</t>
         </is>
       </c>
       <c r="D179" t="n">
-        <v>4.41</v>
+        <v>5.98</v>
       </c>
       <c r="E179" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F179" t="n">
-        <v>1685</v>
+        <v>664</v>
       </c>
       <c r="G179" t="n">
         <v>0</v>
@@ -5453,17 +5453,17 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>B0D83Q7L8W</t>
+          <t>B0D86ZC9YT</t>
         </is>
       </c>
       <c r="D180" t="n">
-        <v>16.28</v>
+        <v>11.26</v>
       </c>
       <c r="E180" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F180" t="n">
-        <v>706</v>
+        <v>1047</v>
       </c>
       <c r="G180" t="n">
         <v>0</v>
@@ -5481,17 +5481,17 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>B0D8445KJN</t>
+          <t>B0D9KCNVNM</t>
         </is>
       </c>
       <c r="D181" t="n">
-        <v>16.78</v>
+        <v>1</v>
       </c>
       <c r="E181" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F181" t="n">
-        <v>2170</v>
+        <v>238</v>
       </c>
       <c r="G181" t="n">
         <v>0</v>
@@ -5509,23 +5509,23 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>B0D86Y2V7V</t>
+          <t>B0D9KFP4MG</t>
         </is>
       </c>
       <c r="D182" t="n">
-        <v>9.550000000000001</v>
+        <v>179.4</v>
       </c>
       <c r="E182" t="n">
-        <v>4</v>
+        <v>56</v>
       </c>
       <c r="F182" t="n">
-        <v>795</v>
+        <v>12607</v>
       </c>
       <c r="G182" t="n">
-        <v>0</v>
+        <v>3303.39</v>
       </c>
       <c r="H182" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="183">
@@ -5537,17 +5537,17 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>B0D86ZC9YT</t>
+          <t>B0D9KFQG8Q</t>
         </is>
       </c>
       <c r="D183" t="n">
-        <v>13.46</v>
+        <v>1</v>
       </c>
       <c r="E183" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F183" t="n">
-        <v>1206</v>
+        <v>182</v>
       </c>
       <c r="G183" t="n">
         <v>0</v>
@@ -5565,17 +5565,17 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>B0D9KCNVNM</t>
+          <t>B0DCK4DR1B</t>
         </is>
       </c>
       <c r="D184" t="n">
-        <v>4.67</v>
+        <v>0</v>
       </c>
       <c r="E184" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F184" t="n">
-        <v>395</v>
+        <v>308</v>
       </c>
       <c r="G184" t="n">
         <v>0</v>
@@ -5593,23 +5593,23 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>B0D9KFP4MG</t>
+          <t>B0DFCDKMWR</t>
         </is>
       </c>
       <c r="D185" t="n">
-        <v>200.81</v>
+        <v>3.28</v>
       </c>
       <c r="E185" t="n">
-        <v>62</v>
+        <v>1</v>
       </c>
       <c r="F185" t="n">
-        <v>13718</v>
+        <v>110</v>
       </c>
       <c r="G185" t="n">
-        <v>3303.39</v>
+        <v>0</v>
       </c>
       <c r="H185" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="186">
@@ -5621,17 +5621,17 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>B0D9KFQG8Q</t>
+          <t>B0DFCDZWND</t>
         </is>
       </c>
       <c r="D186" t="n">
-        <v>4.5</v>
+        <v>13.81</v>
       </c>
       <c r="E186" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F186" t="n">
-        <v>298</v>
+        <v>1296</v>
       </c>
       <c r="G186" t="n">
         <v>0</v>
@@ -5649,7 +5649,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>B0DCK4DR1B</t>
+          <t>B0DFCG2VGS</t>
         </is>
       </c>
       <c r="D187" t="n">
@@ -5659,7 +5659,7 @@
         <v>0</v>
       </c>
       <c r="F187" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="G187" t="n">
         <v>0</v>
@@ -5677,23 +5677,23 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>B0DFCDKMWR</t>
+          <t>B0DFD123P5</t>
         </is>
       </c>
       <c r="D188" t="n">
-        <v>3.28</v>
+        <v>537.6900000000001</v>
       </c>
       <c r="E188" t="n">
+        <v>159</v>
+      </c>
+      <c r="F188" t="n">
+        <v>18706</v>
+      </c>
+      <c r="G188" t="n">
+        <v>1771.19</v>
+      </c>
+      <c r="H188" t="n">
         <v>1</v>
-      </c>
-      <c r="F188" t="n">
-        <v>201</v>
-      </c>
-      <c r="G188" t="n">
-        <v>0</v>
-      </c>
-      <c r="H188" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="189">
@@ -5705,17 +5705,17 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>B0DFCDZWND</t>
+          <t>B0DFM4JZV9</t>
         </is>
       </c>
       <c r="D189" t="n">
-        <v>17.48</v>
+        <v>1.3</v>
       </c>
       <c r="E189" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F189" t="n">
-        <v>1494</v>
+        <v>457</v>
       </c>
       <c r="G189" t="n">
         <v>0</v>
@@ -5733,17 +5733,17 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>B0DFCG2VGS</t>
+          <t>B0DJFH4K8B</t>
         </is>
       </c>
       <c r="D190" t="n">
-        <v>0</v>
+        <v>7.99</v>
       </c>
       <c r="E190" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F190" t="n">
-        <v>0</v>
+        <v>1281</v>
       </c>
       <c r="G190" t="n">
         <v>0</v>
@@ -5761,23 +5761,23 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>B0DFD123P5</t>
+          <t>B0DJFH6RTL</t>
         </is>
       </c>
       <c r="D191" t="n">
-        <v>887.36</v>
+        <v>67.03</v>
       </c>
       <c r="E191" t="n">
-        <v>263</v>
+        <v>14</v>
       </c>
       <c r="F191" t="n">
-        <v>31274</v>
+        <v>3120</v>
       </c>
       <c r="G191" t="n">
-        <v>3550</v>
+        <v>1397.46</v>
       </c>
       <c r="H191" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="192">
@@ -5789,17 +5789,17 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>B0DFM4JZV9</t>
+          <t>B0DK9LYT4P</t>
         </is>
       </c>
       <c r="D192" t="n">
-        <v>1.3</v>
+        <v>100.08</v>
       </c>
       <c r="E192" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="F192" t="n">
-        <v>702</v>
+        <v>7646</v>
       </c>
       <c r="G192" t="n">
         <v>0</v>
@@ -5817,23 +5817,23 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>B0DJFH4K8B</t>
+          <t>B0DKJSCLBD</t>
         </is>
       </c>
       <c r="D193" t="n">
-        <v>21.2</v>
+        <v>10.48</v>
       </c>
       <c r="E193" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F193" t="n">
-        <v>2070</v>
+        <v>1758</v>
       </c>
       <c r="G193" t="n">
-        <v>0</v>
+        <v>2117.8</v>
       </c>
       <c r="H193" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="194">
@@ -5845,23 +5845,23 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>B0DJFH6RTL</t>
+          <t>B0DNJF1BLS</t>
         </is>
       </c>
       <c r="D194" t="n">
-        <v>71.53999999999999</v>
+        <v>0</v>
       </c>
       <c r="E194" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F194" t="n">
-        <v>3530</v>
+        <v>0</v>
       </c>
       <c r="G194" t="n">
-        <v>1397.46</v>
+        <v>0</v>
       </c>
       <c r="H194" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="195">
@@ -5873,17 +5873,17 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>B0DK9LYT4P</t>
+          <t>B0DNJJKBKG</t>
         </is>
       </c>
       <c r="D195" t="n">
-        <v>129.08</v>
+        <v>3.8</v>
       </c>
       <c r="E195" t="n">
-        <v>38</v>
+        <v>1</v>
       </c>
       <c r="F195" t="n">
-        <v>19211</v>
+        <v>202</v>
       </c>
       <c r="G195" t="n">
         <v>0</v>
@@ -5901,23 +5901,23 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>B0DKJSCLBD</t>
+          <t>B0DNJP9T35</t>
         </is>
       </c>
       <c r="D196" t="n">
-        <v>23.35</v>
+        <v>0</v>
       </c>
       <c r="E196" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F196" t="n">
-        <v>2780</v>
+        <v>2</v>
       </c>
       <c r="G196" t="n">
-        <v>2117.8</v>
+        <v>0</v>
       </c>
       <c r="H196" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="197">
@@ -5929,17 +5929,17 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>B0DNJF1BLS</t>
+          <t>B0DT6Y7KJM</t>
         </is>
       </c>
       <c r="D197" t="n">
-        <v>0</v>
+        <v>17.65</v>
       </c>
       <c r="E197" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F197" t="n">
-        <v>0</v>
+        <v>977</v>
       </c>
       <c r="G197" t="n">
         <v>0</v>
@@ -5957,17 +5957,17 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>B0DNJJKBKG</t>
+          <t>B0DV9CY3XR</t>
         </is>
       </c>
       <c r="D198" t="n">
-        <v>3.8</v>
+        <v>3.58</v>
       </c>
       <c r="E198" t="n">
         <v>1</v>
       </c>
       <c r="F198" t="n">
-        <v>237</v>
+        <v>65</v>
       </c>
       <c r="G198" t="n">
         <v>0</v>
@@ -5985,23 +5985,23 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>B0DNJP9T35</t>
+          <t>B0DVC58QPZ</t>
         </is>
       </c>
       <c r="D199" t="n">
-        <v>0</v>
+        <v>65.36</v>
       </c>
       <c r="E199" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="F199" t="n">
-        <v>2</v>
+        <v>3673</v>
       </c>
       <c r="G199" t="n">
-        <v>0</v>
+        <v>3558.47</v>
       </c>
       <c r="H199" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="200">
@@ -6013,17 +6013,17 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>B0DT6Y7KJM</t>
+          <t>B0DVC968P1</t>
         </is>
       </c>
       <c r="D200" t="n">
-        <v>21.22</v>
+        <v>0</v>
       </c>
       <c r="E200" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F200" t="n">
-        <v>1141</v>
+        <v>8</v>
       </c>
       <c r="G200" t="n">
         <v>0</v>
@@ -6041,17 +6041,17 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>B0DV9CY3XR</t>
+          <t>B0DVC9PRSD</t>
         </is>
       </c>
       <c r="D201" t="n">
-        <v>3.58</v>
+        <v>14.28</v>
       </c>
       <c r="E201" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F201" t="n">
-        <v>91</v>
+        <v>416</v>
       </c>
       <c r="G201" t="n">
         <v>0</v>
@@ -6069,23 +6069,23 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>B0DVC58QPZ</t>
+          <t>B0DVSZ2VVJ</t>
         </is>
       </c>
       <c r="D202" t="n">
-        <v>68.02000000000001</v>
+        <v>10.34</v>
       </c>
       <c r="E202" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="F202" t="n">
-        <v>4562</v>
+        <v>152</v>
       </c>
       <c r="G202" t="n">
-        <v>3558.47</v>
+        <v>0</v>
       </c>
       <c r="H202" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="203">
@@ -6097,17 +6097,17 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>B0DVC968P1</t>
+          <t>B0F29SZCVF</t>
         </is>
       </c>
       <c r="D203" t="n">
-        <v>0</v>
+        <v>14.93</v>
       </c>
       <c r="E203" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F203" t="n">
-        <v>10</v>
+        <v>286</v>
       </c>
       <c r="G203" t="n">
         <v>0</v>
@@ -6125,23 +6125,23 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>B0DVC9PRSD</t>
+          <t>B0F2MZ8CG9</t>
         </is>
       </c>
       <c r="D204" t="n">
-        <v>14.28</v>
+        <v>1.18</v>
       </c>
       <c r="E204" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F204" t="n">
-        <v>956</v>
+        <v>113</v>
       </c>
       <c r="G204" t="n">
-        <v>0</v>
+        <v>338.14</v>
       </c>
       <c r="H204" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="205">
@@ -6153,17 +6153,17 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>B0DVSZ2VVJ</t>
+          <t>B0F2N11VTN</t>
         </is>
       </c>
       <c r="D205" t="n">
-        <v>10.34</v>
+        <v>8.33</v>
       </c>
       <c r="E205" t="n">
         <v>3</v>
       </c>
       <c r="F205" t="n">
-        <v>259</v>
+        <v>501</v>
       </c>
       <c r="G205" t="n">
         <v>0</v>
@@ -6181,23 +6181,23 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>B0F29SZCVF</t>
+          <t>B0F2N1HTBT</t>
         </is>
       </c>
       <c r="D206" t="n">
-        <v>22.27</v>
+        <v>5.99</v>
       </c>
       <c r="E206" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F206" t="n">
-        <v>331</v>
+        <v>343</v>
       </c>
       <c r="G206" t="n">
-        <v>1380</v>
+        <v>0</v>
       </c>
       <c r="H206" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="207">
@@ -6209,23 +6209,23 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>B0F2MZ8CG9</t>
+          <t>B0F2N37819</t>
         </is>
       </c>
       <c r="D207" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="E207" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F207" t="n">
-        <v>242</v>
+        <v>379</v>
       </c>
       <c r="G207" t="n">
-        <v>338.14</v>
+        <v>0</v>
       </c>
       <c r="H207" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="208">
@@ -6237,17 +6237,17 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>B0F2N11VTN</t>
+          <t>B0F2N4N83Y</t>
         </is>
       </c>
       <c r="D208" t="n">
-        <v>8.33</v>
+        <v>3.63</v>
       </c>
       <c r="E208" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F208" t="n">
-        <v>663</v>
+        <v>165</v>
       </c>
       <c r="G208" t="n">
         <v>0</v>
@@ -6265,17 +6265,17 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>B0F2N1HTBT</t>
+          <t>B0F678L8YT</t>
         </is>
       </c>
       <c r="D209" t="n">
-        <v>5.99</v>
+        <v>6.4</v>
       </c>
       <c r="E209" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F209" t="n">
-        <v>343</v>
+        <v>586</v>
       </c>
       <c r="G209" t="n">
         <v>0</v>
@@ -6293,7 +6293,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>B0F2N37819</t>
+          <t>B0F678RRCX</t>
         </is>
       </c>
       <c r="D210" t="n">
@@ -6303,7 +6303,7 @@
         <v>0</v>
       </c>
       <c r="F210" t="n">
-        <v>390</v>
+        <v>0</v>
       </c>
       <c r="G210" t="n">
         <v>0</v>
@@ -6321,17 +6321,17 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>B0F2N4N83Y</t>
+          <t>B0F679QJH4</t>
         </is>
       </c>
       <c r="D211" t="n">
-        <v>6.49</v>
+        <v>20.31</v>
       </c>
       <c r="E211" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F211" t="n">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="G211" t="n">
         <v>0</v>
@@ -6349,17 +6349,17 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>B0F678L8YT</t>
+          <t>B0F67BSF2R</t>
         </is>
       </c>
       <c r="D212" t="n">
-        <v>10.04</v>
+        <v>17.82</v>
       </c>
       <c r="E212" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F212" t="n">
-        <v>778</v>
+        <v>3090</v>
       </c>
       <c r="G212" t="n">
         <v>0</v>
@@ -6377,17 +6377,17 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>B0F678RRCX</t>
+          <t>B0F67BW7SF</t>
         </is>
       </c>
       <c r="D213" t="n">
-        <v>0</v>
+        <v>4.58</v>
       </c>
       <c r="E213" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F213" t="n">
-        <v>0</v>
+        <v>1332</v>
       </c>
       <c r="G213" t="n">
         <v>0</v>
@@ -6405,17 +6405,17 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>B0F679QJH4</t>
+          <t>B0F74DJYG6</t>
         </is>
       </c>
       <c r="D214" t="n">
-        <v>20.31</v>
+        <v>8.52</v>
       </c>
       <c r="E214" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F214" t="n">
-        <v>265</v>
+        <v>1236</v>
       </c>
       <c r="G214" t="n">
         <v>0</v>
@@ -6433,17 +6433,17 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>B0F67BSF2R</t>
+          <t>B0FJ1ZB4G9</t>
         </is>
       </c>
       <c r="D215" t="n">
-        <v>22.56</v>
+        <v>4.26</v>
       </c>
       <c r="E215" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F215" t="n">
-        <v>3484</v>
+        <v>1163</v>
       </c>
       <c r="G215" t="n">
         <v>0</v>
@@ -6461,17 +6461,17 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>B0F67BW7SF</t>
+          <t>B0FJG5PFGQ</t>
         </is>
       </c>
       <c r="D216" t="n">
-        <v>7.84</v>
+        <v>42.85</v>
       </c>
       <c r="E216" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F216" t="n">
-        <v>1629</v>
+        <v>3836</v>
       </c>
       <c r="G216" t="n">
         <v>0</v>
@@ -6489,23 +6489,23 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>B0F74DJYG6</t>
+          <t>B0FMF1D9NV</t>
         </is>
       </c>
       <c r="D217" t="n">
-        <v>8.52</v>
+        <v>14.85</v>
       </c>
       <c r="E217" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F217" t="n">
-        <v>1236</v>
+        <v>327</v>
       </c>
       <c r="G217" t="n">
-        <v>0</v>
+        <v>8466.1</v>
       </c>
       <c r="H217" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="218">
@@ -6517,17 +6517,17 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>B0FJ1ZB4G9</t>
+          <t>B0FS7T8151</t>
         </is>
       </c>
       <c r="D218" t="n">
-        <v>4.26</v>
+        <v>0</v>
       </c>
       <c r="E218" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F218" t="n">
-        <v>1356</v>
+        <v>237</v>
       </c>
       <c r="G218" t="n">
         <v>0</v>
@@ -6545,17 +6545,17 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>B0FJG5PFGQ</t>
+          <t>B0FYNKYJFN</t>
         </is>
       </c>
       <c r="D219" t="n">
-        <v>46.52</v>
+        <v>1.14</v>
       </c>
       <c r="E219" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="F219" t="n">
-        <v>4450</v>
+        <v>93</v>
       </c>
       <c r="G219" t="n">
         <v>0</v>
@@ -6573,35 +6573,35 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>B0FMF1D9NV</t>
+          <t>B0GGHZWMVW</t>
         </is>
       </c>
       <c r="D220" t="n">
-        <v>18.42</v>
+        <v>218.5</v>
       </c>
       <c r="E220" t="n">
-        <v>5</v>
+        <v>63</v>
       </c>
       <c r="F220" t="n">
-        <v>425</v>
+        <v>9796</v>
       </c>
       <c r="G220" t="n">
-        <v>8466.1</v>
+        <v>0</v>
       </c>
       <c r="H220" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr"/>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-AT</t>
+          <t>Nexlev-Defensive-AT</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>B0FS7T8151</t>
+          <t>B0CQX9ZZMH</t>
         </is>
       </c>
       <c r="D221" t="n">
@@ -6611,7 +6611,7 @@
         <v>0</v>
       </c>
       <c r="F221" t="n">
-        <v>407</v>
+        <v>3</v>
       </c>
       <c r="G221" t="n">
         <v>0</v>
@@ -6624,22 +6624,22 @@
       <c r="A222" t="inlineStr"/>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-AT</t>
+          <t>Nexlev-Defensive-AT</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>B0FYNKYJFN</t>
+          <t>B0CW1JJP9S</t>
         </is>
       </c>
       <c r="D222" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="E222" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F222" t="n">
-        <v>175</v>
+        <v>5</v>
       </c>
       <c r="G222" t="n">
         <v>0</v>
@@ -6652,22 +6652,22 @@
       <c r="A223" t="inlineStr"/>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-AT</t>
+          <t>Nexlev-Defensive-AT</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>B0GGHZWMVW</t>
+          <t>B0D25LNDSY</t>
         </is>
       </c>
       <c r="D223" t="n">
-        <v>276.73</v>
+        <v>0</v>
       </c>
       <c r="E223" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="F223" t="n">
-        <v>10997</v>
+        <v>36</v>
       </c>
       <c r="G223" t="n">
         <v>0</v>
@@ -6685,7 +6685,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>B0CQX9ZZMH</t>
+          <t>B0D2LFMY48</t>
         </is>
       </c>
       <c r="D224" t="n">
@@ -6695,7 +6695,7 @@
         <v>0</v>
       </c>
       <c r="F224" t="n">
-        <v>5</v>
+        <v>89</v>
       </c>
       <c r="G224" t="n">
         <v>0</v>
@@ -6713,7 +6713,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>B0CW1JJP9S</t>
+          <t>B0D2LKB4BJ</t>
         </is>
       </c>
       <c r="D225" t="n">
@@ -6723,7 +6723,7 @@
         <v>0</v>
       </c>
       <c r="F225" t="n">
-        <v>5</v>
+        <v>56</v>
       </c>
       <c r="G225" t="n">
         <v>0</v>
@@ -6741,7 +6741,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>B0D25LNDSY</t>
+          <t>B0D81DLSFT</t>
         </is>
       </c>
       <c r="D226" t="n">
@@ -6751,7 +6751,7 @@
         <v>0</v>
       </c>
       <c r="F226" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="G226" t="n">
         <v>0</v>
@@ -6769,7 +6769,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>B0D2LD6BYJ</t>
+          <t>B0D83Q7L8W</t>
         </is>
       </c>
       <c r="D227" t="n">
@@ -6779,7 +6779,7 @@
         <v>0</v>
       </c>
       <c r="F227" t="n">
-        <v>3</v>
+        <v>74</v>
       </c>
       <c r="G227" t="n">
         <v>0</v>
@@ -6797,7 +6797,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>B0D2LFMY48</t>
+          <t>B0D8445KJN</t>
         </is>
       </c>
       <c r="D228" t="n">
@@ -6807,7 +6807,7 @@
         <v>0</v>
       </c>
       <c r="F228" t="n">
-        <v>115</v>
+        <v>6</v>
       </c>
       <c r="G228" t="n">
         <v>0</v>
@@ -6825,17 +6825,17 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>B0D2LKB4BJ</t>
+          <t>B0D86Y2V7V</t>
         </is>
       </c>
       <c r="D229" t="n">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="E229" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F229" t="n">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G229" t="n">
         <v>0</v>
@@ -6853,7 +6853,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>B0D81DLSFT</t>
+          <t>B0D86ZC9YT</t>
         </is>
       </c>
       <c r="D230" t="n">
@@ -6863,7 +6863,7 @@
         <v>0</v>
       </c>
       <c r="F230" t="n">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="G230" t="n">
         <v>0</v>
@@ -6881,7 +6881,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>B0D83Q7L8W</t>
+          <t>B0D9KCNVNM</t>
         </is>
       </c>
       <c r="D231" t="n">
@@ -6891,7 +6891,7 @@
         <v>0</v>
       </c>
       <c r="F231" t="n">
-        <v>78</v>
+        <v>8</v>
       </c>
       <c r="G231" t="n">
         <v>0</v>
@@ -6909,17 +6909,17 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>B0D8445KJN</t>
+          <t>B0D9KFP4MG</t>
         </is>
       </c>
       <c r="D232" t="n">
-        <v>0</v>
+        <v>11.15</v>
       </c>
       <c r="E232" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F232" t="n">
-        <v>19</v>
+        <v>419</v>
       </c>
       <c r="G232" t="n">
         <v>0</v>
@@ -6937,7 +6937,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>B0D86Y2V7V</t>
+          <t>B0D9KFQG8Q</t>
         </is>
       </c>
       <c r="D233" t="n">
@@ -6947,7 +6947,7 @@
         <v>0</v>
       </c>
       <c r="F233" t="n">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="G233" t="n">
         <v>0</v>
@@ -6965,7 +6965,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>B0D86ZC9YT</t>
+          <t>B0DCK4DR1B</t>
         </is>
       </c>
       <c r="D234" t="n">
@@ -6975,7 +6975,7 @@
         <v>0</v>
       </c>
       <c r="F234" t="n">
-        <v>9</v>
+        <v>38</v>
       </c>
       <c r="G234" t="n">
         <v>0</v>
@@ -6993,7 +6993,7 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>B0D9KCNVNM</t>
+          <t>B0DFCDZWND</t>
         </is>
       </c>
       <c r="D235" t="n">
@@ -7003,7 +7003,7 @@
         <v>0</v>
       </c>
       <c r="F235" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G235" t="n">
         <v>0</v>
@@ -7021,23 +7021,23 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>B0D9KFP4MG</t>
+          <t>B0DFCG2VGS</t>
         </is>
       </c>
       <c r="D236" t="n">
-        <v>15.95</v>
+        <v>24.42</v>
       </c>
       <c r="E236" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F236" t="n">
-        <v>448</v>
+        <v>274</v>
       </c>
       <c r="G236" t="n">
-        <v>1651.69</v>
+        <v>0</v>
       </c>
       <c r="H236" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="237">
@@ -7049,17 +7049,17 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>B0D9KFQG8Q</t>
+          <t>B0DFD123P5</t>
         </is>
       </c>
       <c r="D237" t="n">
-        <v>0</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="E237" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F237" t="n">
-        <v>0</v>
+        <v>147</v>
       </c>
       <c r="G237" t="n">
         <v>0</v>
@@ -7077,7 +7077,7 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>B0DCK4DR1B</t>
+          <t>B0DJFH4K8B</t>
         </is>
       </c>
       <c r="D238" t="n">
@@ -7087,7 +7087,7 @@
         <v>0</v>
       </c>
       <c r="F238" t="n">
-        <v>42</v>
+        <v>1</v>
       </c>
       <c r="G238" t="n">
         <v>0</v>
@@ -7105,7 +7105,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>B0DFCDZWND</t>
+          <t>B0DJFH6RTL</t>
         </is>
       </c>
       <c r="D239" t="n">
@@ -7115,7 +7115,7 @@
         <v>0</v>
       </c>
       <c r="F239" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="G239" t="n">
         <v>0</v>
@@ -7133,17 +7133,17 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>B0DFCG2VGS</t>
+          <t>B0DK9LYT4P</t>
         </is>
       </c>
       <c r="D240" t="n">
-        <v>24.42</v>
+        <v>0</v>
       </c>
       <c r="E240" t="n">
+        <v>0</v>
+      </c>
+      <c r="F240" t="n">
         <v>5</v>
-      </c>
-      <c r="F240" t="n">
-        <v>402</v>
       </c>
       <c r="G240" t="n">
         <v>0</v>
@@ -7161,17 +7161,17 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>B0DFD123P5</t>
+          <t>B0DKJSCLBD</t>
         </is>
       </c>
       <c r="D241" t="n">
-        <v>8.710000000000001</v>
+        <v>6.52</v>
       </c>
       <c r="E241" t="n">
         <v>2</v>
       </c>
       <c r="F241" t="n">
-        <v>250</v>
+        <v>40</v>
       </c>
       <c r="G241" t="n">
         <v>0</v>
@@ -7189,7 +7189,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>B0DJFH4K8B</t>
+          <t>B0DNJF1BLS</t>
         </is>
       </c>
       <c r="D242" t="n">
@@ -7199,7 +7199,7 @@
         <v>0</v>
       </c>
       <c r="F242" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="G242" t="n">
         <v>0</v>
@@ -7217,7 +7217,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>B0DJFH6RTL</t>
+          <t>B0DNJJKBKG</t>
         </is>
       </c>
       <c r="D243" t="n">
@@ -7227,7 +7227,7 @@
         <v>0</v>
       </c>
       <c r="F243" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="G243" t="n">
         <v>0</v>
@@ -7245,7 +7245,7 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>B0DK9LYT4P</t>
+          <t>B0DT6Y7KJM</t>
         </is>
       </c>
       <c r="D244" t="n">
@@ -7255,7 +7255,7 @@
         <v>0</v>
       </c>
       <c r="F244" t="n">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="G244" t="n">
         <v>0</v>
@@ -7273,17 +7273,17 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>B0DKJSCLBD</t>
+          <t>B0DV9CY3XR</t>
         </is>
       </c>
       <c r="D245" t="n">
-        <v>6.52</v>
+        <v>0</v>
       </c>
       <c r="E245" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F245" t="n">
-        <v>60</v>
+        <v>13</v>
       </c>
       <c r="G245" t="n">
         <v>0</v>
@@ -7301,17 +7301,17 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>B0DNJF1BLS</t>
+          <t>B0DVC58QPZ</t>
         </is>
       </c>
       <c r="D246" t="n">
-        <v>4.64</v>
+        <v>0</v>
       </c>
       <c r="E246" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F246" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="G246" t="n">
         <v>0</v>
@@ -7329,7 +7329,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>B0DNJJKBKG</t>
+          <t>B0DVC9PRSD</t>
         </is>
       </c>
       <c r="D247" t="n">
@@ -7339,7 +7339,7 @@
         <v>0</v>
       </c>
       <c r="F247" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="G247" t="n">
         <v>0</v>
@@ -7357,7 +7357,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>B0DT6Y7KJM</t>
+          <t>B0DVSZ2VVJ</t>
         </is>
       </c>
       <c r="D248" t="n">
@@ -7367,7 +7367,7 @@
         <v>0</v>
       </c>
       <c r="F248" t="n">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="G248" t="n">
         <v>0</v>
@@ -7385,7 +7385,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>B0DV9CY3XR</t>
+          <t>B0F29SZCVF</t>
         </is>
       </c>
       <c r="D249" t="n">
@@ -7395,7 +7395,7 @@
         <v>0</v>
       </c>
       <c r="F249" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="G249" t="n">
         <v>0</v>
@@ -7413,7 +7413,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>B0DVC58QPZ</t>
+          <t>B0F2N11VTN</t>
         </is>
       </c>
       <c r="D250" t="n">
@@ -7423,7 +7423,7 @@
         <v>0</v>
       </c>
       <c r="F250" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="G250" t="n">
         <v>0</v>
@@ -7441,7 +7441,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>B0DVC9PRSD</t>
+          <t>B0F2N1HTBT</t>
         </is>
       </c>
       <c r="D251" t="n">
@@ -7451,7 +7451,7 @@
         <v>0</v>
       </c>
       <c r="F251" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G251" t="n">
         <v>0</v>
@@ -7469,17 +7469,17 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>B0DVSZ2VVJ</t>
+          <t>B0F2N37819</t>
         </is>
       </c>
       <c r="D252" t="n">
-        <v>0</v>
+        <v>4.26</v>
       </c>
       <c r="E252" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F252" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G252" t="n">
         <v>0</v>
@@ -7497,7 +7497,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>B0F29SZCVF</t>
+          <t>B0F2N4N83Y</t>
         </is>
       </c>
       <c r="D253" t="n">
@@ -7507,7 +7507,7 @@
         <v>0</v>
       </c>
       <c r="F253" t="n">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="G253" t="n">
         <v>0</v>
@@ -7525,7 +7525,7 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>B0F2N11VTN</t>
+          <t>B0F678L8YT</t>
         </is>
       </c>
       <c r="D254" t="n">
@@ -7535,7 +7535,7 @@
         <v>0</v>
       </c>
       <c r="F254" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="G254" t="n">
         <v>0</v>
@@ -7553,7 +7553,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>B0F2N1HTBT</t>
+          <t>B0F679QJH4</t>
         </is>
       </c>
       <c r="D255" t="n">
@@ -7563,7 +7563,7 @@
         <v>0</v>
       </c>
       <c r="F255" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G255" t="n">
         <v>0</v>
@@ -7581,17 +7581,17 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>B0F2N37819</t>
+          <t>B0F67BSF2R</t>
         </is>
       </c>
       <c r="D256" t="n">
-        <v>4.26</v>
+        <v>0</v>
       </c>
       <c r="E256" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F256" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="G256" t="n">
         <v>0</v>
@@ -7609,7 +7609,7 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>B0F2N4N83Y</t>
+          <t>B0FJ1ZB4G9</t>
         </is>
       </c>
       <c r="D257" t="n">
@@ -7619,7 +7619,7 @@
         <v>0</v>
       </c>
       <c r="F257" t="n">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="G257" t="n">
         <v>0</v>
@@ -7637,17 +7637,17 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>B0F678L8YT</t>
+          <t>B0FJG5PFGQ</t>
         </is>
       </c>
       <c r="D258" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="E258" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F258" t="n">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="G258" t="n">
         <v>0</v>
@@ -7665,7 +7665,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>B0F679QJH4</t>
+          <t>B0FMF1D9NV</t>
         </is>
       </c>
       <c r="D259" t="n">
@@ -7675,7 +7675,7 @@
         <v>0</v>
       </c>
       <c r="F259" t="n">
-        <v>2</v>
+        <v>51</v>
       </c>
       <c r="G259" t="n">
         <v>0</v>
@@ -7693,7 +7693,7 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>B0F67BSF2R</t>
+          <t>B0FS7T8151</t>
         </is>
       </c>
       <c r="D260" t="n">
@@ -7703,7 +7703,7 @@
         <v>0</v>
       </c>
       <c r="F260" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="G260" t="n">
         <v>0</v>
@@ -7721,7 +7721,7 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>B0FJ1ZB4G9</t>
+          <t>B0FYNKYJFN</t>
         </is>
       </c>
       <c r="D261" t="n">
@@ -7731,7 +7731,7 @@
         <v>0</v>
       </c>
       <c r="F261" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="G261" t="n">
         <v>0</v>
@@ -7749,17 +7749,17 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>B0FJG5PFGQ</t>
+          <t>B0GGHZWMVW</t>
         </is>
       </c>
       <c r="D262" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="E262" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F262" t="n">
-        <v>49</v>
+        <v>376</v>
       </c>
       <c r="G262" t="n">
         <v>0</v>
@@ -7772,50 +7772,50 @@
       <c r="A263" t="inlineStr"/>
       <c r="B263" t="inlineStr">
         <is>
-          <t>Nexlev-Defensive-AT</t>
+          <t>Nexlev-Multi Ad Group-Steam Cleaner -SP-KT -Exact/Phrase/Broad</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>B0FMF1D9NV</t>
+          <t>B0CDPP45BM</t>
         </is>
       </c>
       <c r="D263" t="n">
-        <v>1.34</v>
+        <v>867.55</v>
       </c>
       <c r="E263" t="n">
+        <v>29</v>
+      </c>
+      <c r="F263" t="n">
+        <v>7017</v>
+      </c>
+      <c r="G263" t="n">
+        <v>5083.9</v>
+      </c>
+      <c r="H263" t="n">
         <v>1</v>
-      </c>
-      <c r="F263" t="n">
-        <v>56</v>
-      </c>
-      <c r="G263" t="n">
-        <v>0</v>
-      </c>
-      <c r="H263" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr"/>
       <c r="B264" t="inlineStr">
         <is>
-          <t>Nexlev-Defensive-AT</t>
+          <t>Nexlev-SP- B0GN8WW6BC - Stand Mixer with Stainless Steel Bowl - BM</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>B0FS7T8151</t>
+          <t>B0GN8WW6BC</t>
         </is>
       </c>
       <c r="D264" t="n">
-        <v>0</v>
+        <v>12.06</v>
       </c>
       <c r="E264" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F264" t="n">
-        <v>0</v>
+        <v>423</v>
       </c>
       <c r="G264" t="n">
         <v>0</v>
@@ -7828,12 +7828,12 @@
       <c r="A265" t="inlineStr"/>
       <c r="B265" t="inlineStr">
         <is>
-          <t>Nexlev-Defensive-AT</t>
+          <t>Nexlev-Steamer-PT(SEAHELTON)</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>B0FYNKYJFN</t>
+          <t>B0CDPP45BM</t>
         </is>
       </c>
       <c r="D265" t="n">
@@ -7843,7 +7843,7 @@
         <v>0</v>
       </c>
       <c r="F265" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="G265" t="n">
         <v>0</v>
@@ -7856,22 +7856,22 @@
       <c r="A266" t="inlineStr"/>
       <c r="B266" t="inlineStr">
         <is>
-          <t>Nexlev-Defensive-AT</t>
+          <t>Nexlev-Steamer-PT(SEAHELTON)</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>B0GGHZWMVW</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D266" t="n">
-        <v>48.6</v>
+        <v>0</v>
       </c>
       <c r="E266" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="F266" t="n">
-        <v>436</v>
+        <v>14</v>
       </c>
       <c r="G266" t="n">
         <v>0</v>
@@ -7884,7 +7884,7 @@
       <c r="A267" t="inlineStr"/>
       <c r="B267" t="inlineStr">
         <is>
-          <t>Nexlev-Multi Ad Group-Steam Cleaner -SP-KT -Exact/Phrase/Broad</t>
+          <t>Nexlev-steam Cleaner For Home-B0CDPP45BM-BM-SP</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
@@ -7893,41 +7893,41 @@
         </is>
       </c>
       <c r="D267" t="n">
-        <v>2241.97</v>
+        <v>0</v>
       </c>
       <c r="E267" t="n">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="F267" t="n">
-        <v>16749</v>
+        <v>71</v>
       </c>
       <c r="G267" t="n">
-        <v>5083.9</v>
+        <v>0</v>
       </c>
       <c r="H267" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr"/>
       <c r="B268" t="inlineStr">
         <is>
-          <t>Nexlev-SP- B0GN8WW6BC - Stand Mixer with Stainless Steel Bowl - BM</t>
+          <t>Nexliv- Steam Mop-B0D2LJSQXZ-AT-SP</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>B0GN8WW6BC</t>
+          <t>B0D2LJSQXZ</t>
         </is>
       </c>
       <c r="D268" t="n">
-        <v>12.06</v>
+        <v>903.99</v>
       </c>
       <c r="E268" t="n">
-        <v>1</v>
+        <v>93</v>
       </c>
       <c r="F268" t="n">
-        <v>456</v>
+        <v>10272</v>
       </c>
       <c r="G268" t="n">
         <v>0</v>
@@ -7940,35 +7940,35 @@
       <c r="A269" t="inlineStr"/>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Nexlev-Steamer-PT(SEAHELTON)</t>
+          <t>Nexliv- Steam Mop-B0D2LJSQXZ-PT-SP</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>B0CDPP45BM</t>
+          <t>B0D2LJSQXZ</t>
         </is>
       </c>
       <c r="D269" t="n">
-        <v>7.36</v>
+        <v>1151.93</v>
       </c>
       <c r="E269" t="n">
-        <v>1</v>
+        <v>113</v>
       </c>
       <c r="F269" t="n">
-        <v>43</v>
+        <v>12251</v>
       </c>
       <c r="G269" t="n">
-        <v>0</v>
+        <v>19316.94</v>
       </c>
       <c r="H269" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr"/>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Nexlev-Steamer-PT(SEAHELTON)</t>
+          <t>Nexliv--Steam Cleaner--B0F43P6D23-AT-SP</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
@@ -7977,13 +7977,13 @@
         </is>
       </c>
       <c r="D270" t="n">
-        <v>29.2</v>
+        <v>0</v>
       </c>
       <c r="E270" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F270" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="G270" t="n">
         <v>0</v>
@@ -7996,40 +7996,40 @@
       <c r="A271" t="inlineStr"/>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Nexlev-steam Cleaner For Home-B0CDPP45BM-BM-SP</t>
+          <t>Nexliv-2 in 1 Stick Vacuum Cleaner-B0DCGHVN81-AT</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>B0CDPP45BM</t>
+          <t>B0DCGHVN81</t>
         </is>
       </c>
       <c r="D271" t="n">
-        <v>39.51</v>
+        <v>4603.4</v>
       </c>
       <c r="E271" t="n">
-        <v>3</v>
+        <v>604</v>
       </c>
       <c r="F271" t="n">
-        <v>264</v>
+        <v>149925</v>
       </c>
       <c r="G271" t="n">
-        <v>0</v>
+        <v>23922.88</v>
       </c>
       <c r="H271" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr"/>
       <c r="B272" t="inlineStr">
         <is>
-          <t>Nexlev-steam Cleaner For Home-B0CDPP45BM-Exact-SP</t>
+          <t>Nexliv-2 in 1 Stick Vacuum Cleaner-B0DCGHVN81-BM-SP</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>B0CDPP45BM</t>
+          <t>B0DCGHVN81</t>
         </is>
       </c>
       <c r="D272" t="n">
@@ -8039,7 +8039,7 @@
         <v>0</v>
       </c>
       <c r="F272" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G272" t="n">
         <v>0</v>
@@ -8052,22 +8052,22 @@
       <c r="A273" t="inlineStr"/>
       <c r="B273" t="inlineStr">
         <is>
-          <t>Nexliv- Steam Mop-B0D2LJSQXZ-AT-SP</t>
+          <t>Nexliv-2 in 1 Stick Vacuum Cleaner-B0DCGHVN81-PT(2)-SP</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>B0D2LJSQXZ</t>
+          <t>B0DCGHVN81</t>
         </is>
       </c>
       <c r="D273" t="n">
-        <v>1046.83</v>
+        <v>0</v>
       </c>
       <c r="E273" t="n">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="F273" t="n">
-        <v>12544</v>
+        <v>0</v>
       </c>
       <c r="G273" t="n">
         <v>0</v>
@@ -8080,50 +8080,50 @@
       <c r="A274" t="inlineStr"/>
       <c r="B274" t="inlineStr">
         <is>
-          <t>Nexliv- Steam Mop-B0D2LJSQXZ-PT-SP</t>
+          <t>Nexliv-2 in 1 Stick Vacuum Cleaner-B0DCGHVN81-PT-SP</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>B0D2LJSQXZ</t>
+          <t>B0DCGHVN81</t>
         </is>
       </c>
       <c r="D274" t="n">
-        <v>1304.59</v>
+        <v>2312.03</v>
       </c>
       <c r="E274" t="n">
-        <v>130</v>
+        <v>167</v>
       </c>
       <c r="F274" t="n">
-        <v>12945</v>
+        <v>22182</v>
       </c>
       <c r="G274" t="n">
-        <v>19316.94</v>
+        <v>3557.63</v>
       </c>
       <c r="H274" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr"/>
       <c r="B275" t="inlineStr">
         <is>
-          <t>Nexliv--Steam Cleaner--B0F43P6D23-AT-SP</t>
+          <t>Nexliv-2 in 1 Stick Vacuum Cleaner-B0DCGHVN81-PT-SP(1)</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0DCGHVN81</t>
         </is>
       </c>
       <c r="D275" t="n">
-        <v>0</v>
+        <v>129.94</v>
       </c>
       <c r="E275" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F275" t="n">
-        <v>0</v>
+        <v>712</v>
       </c>
       <c r="G275" t="n">
         <v>0</v>
@@ -8136,7 +8136,7 @@
       <c r="A276" t="inlineStr"/>
       <c r="B276" t="inlineStr">
         <is>
-          <t>Nexliv-2 in 1 Stick Vacuum Cleaner-B0DCGHVN81-AT</t>
+          <t>Nexliv-2 in 1 Stick Vacuum Cleaner-B0DCGHVN81-PT-SP(2)</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
@@ -8145,26 +8145,26 @@
         </is>
       </c>
       <c r="D276" t="n">
-        <v>5085.13</v>
+        <v>180.69</v>
       </c>
       <c r="E276" t="n">
-        <v>680</v>
+        <v>14</v>
       </c>
       <c r="F276" t="n">
-        <v>159346</v>
+        <v>1164</v>
       </c>
       <c r="G276" t="n">
-        <v>27480.5</v>
+        <v>0</v>
       </c>
       <c r="H276" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr"/>
       <c r="B277" t="inlineStr">
         <is>
-          <t>Nexliv-2 in 1 Stick Vacuum Cleaner-B0DCGHVN81-BM-SP</t>
+          <t>Nexliv-2 in 1 Stick Vacuum Cleaner-B0DCGHVN81-Phrase-SP(2)</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
@@ -8173,41 +8173,41 @@
         </is>
       </c>
       <c r="D277" t="n">
-        <v>0</v>
+        <v>536.45</v>
       </c>
       <c r="E277" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="F277" t="n">
-        <v>0</v>
+        <v>33099</v>
       </c>
       <c r="G277" t="n">
-        <v>0</v>
+        <v>1778.81</v>
       </c>
       <c r="H277" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr"/>
       <c r="B278" t="inlineStr">
         <is>
-          <t>Nexliv-2 in 1 Stick Vacuum Cleaner-B0DCGHVN81-PT(2)-SP</t>
+          <t>Nexliv-B0D9KDQCCM-Portable Sewing Machine-AT-SP</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>B0DCGHVN81</t>
+          <t>B0D9KDQCCM</t>
         </is>
       </c>
       <c r="D278" t="n">
-        <v>0</v>
+        <v>319.18</v>
       </c>
       <c r="E278" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="F278" t="n">
-        <v>0</v>
+        <v>2975</v>
       </c>
       <c r="G278" t="n">
         <v>0</v>
@@ -8220,50 +8220,50 @@
       <c r="A279" t="inlineStr"/>
       <c r="B279" t="inlineStr">
         <is>
-          <t>Nexliv-2 in 1 Stick Vacuum Cleaner-B0DCGHVN81-PT-SP</t>
+          <t>Nexliv-B0DCK4DR1B-Skin Lift Device-PT-SP</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>B0DCGHVN81</t>
+          <t>B0DCK4DR1B</t>
         </is>
       </c>
       <c r="D279" t="n">
-        <v>2853.03</v>
+        <v>42.2</v>
       </c>
       <c r="E279" t="n">
-        <v>209</v>
+        <v>3</v>
       </c>
       <c r="F279" t="n">
-        <v>26211</v>
+        <v>641</v>
       </c>
       <c r="G279" t="n">
-        <v>3557.63</v>
+        <v>0</v>
       </c>
       <c r="H279" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr"/>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Nexliv-2 in 1 Stick Vacuum Cleaner-B0DCGHVN81-PT-SP(1)</t>
+          <t>Nexliv-B0F43P6D23-KW-SP-Exact(111)</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>B0DCGHVN81</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D280" t="n">
-        <v>129.94</v>
+        <v>0</v>
       </c>
       <c r="E280" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F280" t="n">
-        <v>712</v>
+        <v>0</v>
       </c>
       <c r="G280" t="n">
         <v>0</v>
@@ -8276,22 +8276,22 @@
       <c r="A281" t="inlineStr"/>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Nexliv-2 in 1 Stick Vacuum Cleaner-B0DCGHVN81-PT-SP(2)</t>
+          <t>Nexliv-Electric Food Kettle-B0DFCG2VGS-BM-SP</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>B0DCGHVN81</t>
+          <t>B0DFCG2VGS</t>
         </is>
       </c>
       <c r="D281" t="n">
-        <v>180.69</v>
+        <v>909.96</v>
       </c>
       <c r="E281" t="n">
-        <v>14</v>
+        <v>91</v>
       </c>
       <c r="F281" t="n">
-        <v>1164</v>
+        <v>28450</v>
       </c>
       <c r="G281" t="n">
         <v>0</v>
@@ -8304,134 +8304,134 @@
       <c r="A282" t="inlineStr"/>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Nexliv-2 in 1 Stick Vacuum Cleaner-B0DCGHVN81-Phrase-SP(2)</t>
+          <t>Nexliv-Handheld Steamer-B0D383WQPB-BM-SP</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>B0DCGHVN81</t>
+          <t>B0D383WQPB</t>
         </is>
       </c>
       <c r="D282" t="n">
-        <v>860.7</v>
+        <v>3152.55</v>
       </c>
       <c r="E282" t="n">
-        <v>67</v>
+        <v>123</v>
       </c>
       <c r="F282" t="n">
-        <v>41147</v>
+        <v>15818</v>
       </c>
       <c r="G282" t="n">
-        <v>1778.81</v>
+        <v>6776.28</v>
       </c>
       <c r="H282" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr"/>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Nexliv-B0D9KDQCCM-Portable Sewing Machine-AT-SP</t>
+          <t>Nexliv-Handheld Steamer-B0D383WQPB-CT</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>B0D9KDQCCM</t>
+          <t>B0D383WQPB</t>
         </is>
       </c>
       <c r="D283" t="n">
-        <v>460.82</v>
+        <v>960.8</v>
       </c>
       <c r="E283" t="n">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="F283" t="n">
-        <v>4935</v>
+        <v>14333</v>
       </c>
       <c r="G283" t="n">
-        <v>0</v>
+        <v>2033.05</v>
       </c>
       <c r="H283" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr"/>
       <c r="B284" t="inlineStr">
         <is>
-          <t>Nexliv-B0DCK4DR1B-Skin Lift Device-PT-SP</t>
+          <t>Nexliv-Mattress Sofa-B0CYSLCRQS-AT-SP</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>B0DCK4DR1B</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="D284" t="n">
-        <v>42.2</v>
+        <v>3383.45</v>
       </c>
       <c r="E284" t="n">
+        <v>906</v>
+      </c>
+      <c r="F284" t="n">
+        <v>108442</v>
+      </c>
+      <c r="G284" t="n">
+        <v>7709.320000000001</v>
+      </c>
+      <c r="H284" t="n">
         <v>3</v>
-      </c>
-      <c r="F284" t="n">
-        <v>730</v>
-      </c>
-      <c r="G284" t="n">
-        <v>0</v>
-      </c>
-      <c r="H284" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr"/>
       <c r="B285" t="inlineStr">
         <is>
-          <t>Nexliv-B0F43P6D23-KW-SP-Exact(111)</t>
+          <t>Nexliv-Mattress Sofa-B0CYSLCRQS-Exact-SP</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="D285" t="n">
-        <v>0</v>
+        <v>378.32</v>
       </c>
       <c r="E285" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="F285" t="n">
-        <v>0</v>
+        <v>2788</v>
       </c>
       <c r="G285" t="n">
-        <v>0</v>
+        <v>2541.53</v>
       </c>
       <c r="H285" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr"/>
       <c r="B286" t="inlineStr">
         <is>
-          <t>Nexliv-Electric Food Kettle-B0DFCG2VGS-BM-SP</t>
+          <t>Nexliv-Portable Blender-B0FS6TB7CP-BM</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>B0DFCG2VGS</t>
+          <t>B0FS6TB7CP</t>
         </is>
       </c>
       <c r="D286" t="n">
-        <v>1352.01</v>
+        <v>816.33</v>
       </c>
       <c r="E286" t="n">
-        <v>132</v>
+        <v>57</v>
       </c>
       <c r="F286" t="n">
-        <v>44571</v>
+        <v>9147</v>
       </c>
       <c r="G286" t="n">
         <v>0</v>
@@ -8444,358 +8444,358 @@
       <c r="A287" t="inlineStr"/>
       <c r="B287" t="inlineStr">
         <is>
-          <t>Nexliv-Handheld Steamer-B0D383WQPB-BM-SP</t>
+          <t>Nexliv-Portable Blender-B0FS6TB7CP-CT</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>B0D383WQPB</t>
+          <t>B0FS6TB7CP</t>
         </is>
       </c>
       <c r="D287" t="n">
-        <v>3566.34</v>
+        <v>2808.86</v>
       </c>
       <c r="E287" t="n">
-        <v>142</v>
+        <v>154</v>
       </c>
       <c r="F287" t="n">
-        <v>21343</v>
+        <v>26619</v>
       </c>
       <c r="G287" t="n">
-        <v>6776.28</v>
+        <v>2033.05</v>
       </c>
       <c r="H287" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr"/>
       <c r="B288" t="inlineStr">
         <is>
-          <t>Nexliv-Handheld Steamer-B0D383WQPB-CT</t>
+          <t>Nexliv-Portable Blender-B0FS6TB7CP-PT(2)-SP</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>B0D383WQPB</t>
+          <t>B0FS6TB7CP</t>
         </is>
       </c>
       <c r="D288" t="n">
-        <v>1289.87</v>
+        <v>4697.34</v>
       </c>
       <c r="E288" t="n">
-        <v>64</v>
+        <v>291</v>
       </c>
       <c r="F288" t="n">
-        <v>22946</v>
+        <v>72246</v>
       </c>
       <c r="G288" t="n">
-        <v>2033.05</v>
+        <v>14231.36</v>
       </c>
       <c r="H288" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr"/>
       <c r="B289" t="inlineStr">
         <is>
-          <t>Nexliv-Mattress Sofa-B0CYSLCRQS-AT-SP</t>
+          <t>Nexliv-Portable Blender-B0FS6TB7CP-PT-SP</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B08L46ZKKZ</t>
         </is>
       </c>
       <c r="D289" t="n">
-        <v>3852.53</v>
+        <v>6469.000000000001</v>
       </c>
       <c r="E289" t="n">
-        <v>1036</v>
+        <v>458</v>
       </c>
       <c r="F289" t="n">
-        <v>119294</v>
+        <v>27943</v>
       </c>
       <c r="G289" t="n">
-        <v>7709.320000000001</v>
+        <v>73701</v>
       </c>
       <c r="H289" t="n">
-        <v>3</v>
+        <v>33</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr"/>
       <c r="B290" t="inlineStr">
         <is>
-          <t>Nexliv-Mattress Sofa-B0CYSLCRQS-Exact-SP</t>
+          <t>Nexliv-Portable Blender-B0FS6TB7CP-PT-SP</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0FNQS4RRD</t>
         </is>
       </c>
       <c r="D290" t="n">
-        <v>417.67</v>
+        <v>859.12</v>
       </c>
       <c r="E290" t="n">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="F290" t="n">
-        <v>2973</v>
+        <v>13728</v>
       </c>
       <c r="G290" t="n">
-        <v>2541.53</v>
+        <v>30503.4</v>
       </c>
       <c r="H290" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr"/>
       <c r="B291" t="inlineStr">
         <is>
-          <t>Nexliv-Portable Blender-B0FS6TB7CP-BM</t>
+          <t>Nexliv-Portable Sewing Machine-B0D9KDQCCM-Phrase-SP</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>B0FS6TB7CP</t>
+          <t>B0D9KDQCCM</t>
         </is>
       </c>
       <c r="D291" t="n">
-        <v>1290.96</v>
+        <v>92.46000000000001</v>
       </c>
       <c r="E291" t="n">
-        <v>90</v>
+        <v>10</v>
       </c>
       <c r="F291" t="n">
-        <v>19279</v>
+        <v>1165</v>
       </c>
       <c r="G291" t="n">
-        <v>0</v>
+        <v>970.48</v>
       </c>
       <c r="H291" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr"/>
       <c r="B292" t="inlineStr">
         <is>
-          <t>Nexliv-Portable Blender-B0FS6TB7CP-CT</t>
+          <t>Nexliv-Stand Mixer-B0DVC7VJP1-BM-SP</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>B0FS6TB7CP</t>
+          <t>B0DVC7VJP1</t>
         </is>
       </c>
       <c r="D292" t="n">
-        <v>4307.61</v>
+        <v>3938.36</v>
       </c>
       <c r="E292" t="n">
-        <v>241</v>
+        <v>260</v>
       </c>
       <c r="F292" t="n">
-        <v>48115</v>
+        <v>65331</v>
       </c>
       <c r="G292" t="n">
-        <v>6099.15</v>
+        <v>35587.3</v>
       </c>
       <c r="H292" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr"/>
       <c r="B293" t="inlineStr">
         <is>
-          <t>Nexliv-Portable Blender-B0FS6TB7CP-PT(2)-SP</t>
+          <t>Nexliv-Stand Mixer-B0DVC7VJP1-CT-SP</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>B0FS6TB7CP</t>
+          <t>B0DVC7VJP1</t>
         </is>
       </c>
       <c r="D293" t="n">
-        <v>5619.52</v>
+        <v>753.16</v>
       </c>
       <c r="E293" t="n">
-        <v>347</v>
+        <v>44</v>
       </c>
       <c r="F293" t="n">
-        <v>84528</v>
+        <v>3438</v>
       </c>
       <c r="G293" t="n">
-        <v>18297.46</v>
+        <v>5083.9</v>
       </c>
       <c r="H293" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr"/>
       <c r="B294" t="inlineStr">
         <is>
-          <t>Nexliv-Portable Blender-B0FS6TB7CP-PT-SP</t>
+          <t>Nexliv-Steam Cleaner,B0F43P6D23-KW-SP-Exact</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>B08L46ZKKZ</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D294" t="n">
-        <v>6911.580000000001</v>
+        <v>69.55</v>
       </c>
       <c r="E294" t="n">
-        <v>491</v>
+        <v>4</v>
       </c>
       <c r="F294" t="n">
-        <v>28933</v>
+        <v>876</v>
       </c>
       <c r="G294" t="n">
-        <v>77597.62</v>
+        <v>0</v>
       </c>
       <c r="H294" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr"/>
       <c r="B295" t="inlineStr">
         <is>
-          <t>Nexliv-Portable Blender-B0FS6TB7CP-PT-SP</t>
+          <t>Nexliv-Steam Cleaner---B0F43P6D23-PT-SP</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>B0FNQS4RRD</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D295" t="n">
-        <v>874.3100000000001</v>
+        <v>432.76</v>
       </c>
       <c r="E295" t="n">
-        <v>56</v>
+        <v>23</v>
       </c>
       <c r="F295" t="n">
-        <v>14329</v>
+        <v>3310</v>
       </c>
       <c r="G295" t="n">
-        <v>30503.4</v>
+        <v>0</v>
       </c>
       <c r="H295" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr"/>
       <c r="B296" t="inlineStr">
         <is>
-          <t>Nexliv-Portable Sewing Machine-B0D9KDQCCM-Phrase-SP</t>
+          <t>Nexliv-Steam Cleaner-B0F43P6D23-AT-SP</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>B0D9KDQCCM</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D296" t="n">
-        <v>135.41</v>
+        <v>0</v>
       </c>
       <c r="E296" t="n">
+        <v>0</v>
+      </c>
+      <c r="F296" t="n">
         <v>15</v>
       </c>
-      <c r="F296" t="n">
-        <v>1345</v>
-      </c>
       <c r="G296" t="n">
-        <v>1979.05</v>
+        <v>0</v>
       </c>
       <c r="H296" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr"/>
       <c r="B297" t="inlineStr">
         <is>
-          <t>Nexliv-Stand Mixer-B0DVC7VJP1-BM-SP</t>
+          <t>Nexliv-Steam Cleaner-B0F43P6D23-BM-SP</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>B0DVC7VJP1</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D297" t="n">
-        <v>4513.3</v>
+        <v>152.48</v>
       </c>
       <c r="E297" t="n">
-        <v>300</v>
+        <v>9</v>
       </c>
       <c r="F297" t="n">
-        <v>75045</v>
+        <v>162</v>
       </c>
       <c r="G297" t="n">
-        <v>45755.94</v>
+        <v>0</v>
       </c>
       <c r="H297" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr"/>
       <c r="B298" t="inlineStr">
         <is>
-          <t>Nexliv-Stand Mixer-B0DVC7VJP1-CT-SP</t>
+          <t>Nexliv-Steam Mop Floor Cleaner-B0DNJS23HS- PT</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>B0DVC7VJP1</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D298" t="n">
-        <v>753.16</v>
+        <v>53.73999999999999</v>
       </c>
       <c r="E298" t="n">
-        <v>44</v>
+        <v>4</v>
       </c>
       <c r="F298" t="n">
-        <v>3609</v>
+        <v>240</v>
       </c>
       <c r="G298" t="n">
-        <v>5083.9</v>
+        <v>0</v>
       </c>
       <c r="H298" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr"/>
       <c r="B299" t="inlineStr">
         <is>
-          <t>Nexliv-Steam Cleaner,B0F43P6D23-KW-SP-Exact</t>
+          <t>Nexliv-Steam Mop Floor Cleaner-B0DNJS23HS- PT01</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D299" t="n">
-        <v>79.95999999999999</v>
+        <v>157.17</v>
       </c>
       <c r="E299" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="F299" t="n">
-        <v>1396</v>
+        <v>1624</v>
       </c>
       <c r="G299" t="n">
         <v>0</v>
@@ -8808,22 +8808,22 @@
       <c r="A300" t="inlineStr"/>
       <c r="B300" t="inlineStr">
         <is>
-          <t>Nexliv-Steam Cleaner---B0F43P6D23-PT-SP</t>
+          <t>Nexliv-Steam Mop Floor Cleaner-B0DNJS23HS-BM-and exact-SP</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D300" t="n">
-        <v>950.6900000000001</v>
+        <v>0</v>
       </c>
       <c r="E300" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="F300" t="n">
-        <v>8009</v>
+        <v>0</v>
       </c>
       <c r="G300" t="n">
         <v>0</v>
@@ -8836,50 +8836,50 @@
       <c r="A301" t="inlineStr"/>
       <c r="B301" t="inlineStr">
         <is>
-          <t>Nexliv-Steam Cleaner-B0F43P6D23-AT-SP</t>
+          <t>Nexliv-Steam Mop Floor Cleaner-B0DNJS23HS-CT-SP</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D301" t="n">
-        <v>0</v>
+        <v>3331.27</v>
       </c>
       <c r="E301" t="n">
-        <v>0</v>
+        <v>134</v>
       </c>
       <c r="F301" t="n">
-        <v>15</v>
+        <v>12319</v>
       </c>
       <c r="G301" t="n">
-        <v>0</v>
+        <v>5083.9</v>
       </c>
       <c r="H301" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr"/>
       <c r="B302" t="inlineStr">
         <is>
-          <t>Nexliv-Steam Cleaner-B0F43P6D23-BM-SP</t>
+          <t>Nexliv-Steam Mop Floor Cleaner-B0DNJS23HS-Exact</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D302" t="n">
-        <v>292.84</v>
+        <v>3038.84</v>
       </c>
       <c r="E302" t="n">
-        <v>21</v>
+        <v>148</v>
       </c>
       <c r="F302" t="n">
-        <v>484</v>
+        <v>20005</v>
       </c>
       <c r="G302" t="n">
         <v>0</v>
@@ -8892,22 +8892,22 @@
       <c r="A303" t="inlineStr"/>
       <c r="B303" t="inlineStr">
         <is>
-          <t>Nexliv-Steam Mop Floor Cleaner-B0DNJS23HS- PT</t>
+          <t>Nexliv-Steam Mop-B0D2LJSQXZ-Phrase-SP</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0D2LJSQXZ</t>
         </is>
       </c>
       <c r="D303" t="n">
-        <v>53.73999999999999</v>
+        <v>0</v>
       </c>
       <c r="E303" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F303" t="n">
-        <v>240</v>
+        <v>1</v>
       </c>
       <c r="G303" t="n">
         <v>0</v>
@@ -8920,22 +8920,22 @@
       <c r="A304" t="inlineStr"/>
       <c r="B304" t="inlineStr">
         <is>
-          <t>Nexliv-Steam Mop Floor Cleaner-B0DNJS23HS- PT01</t>
+          <t>Nexliv/Steam Cleaner-B0F43P6D23-Exact(1)-SP</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D304" t="n">
-        <v>157.17</v>
+        <v>0</v>
       </c>
       <c r="E304" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="F304" t="n">
-        <v>1624</v>
+        <v>33</v>
       </c>
       <c r="G304" t="n">
         <v>0</v>
@@ -8948,22 +8948,22 @@
       <c r="A305" t="inlineStr"/>
       <c r="B305" t="inlineStr">
         <is>
-          <t>Nexliv-Steam Mop Floor Cleaner-B0DNJS23HS-BM-and exact-SP</t>
+          <t>Nexlive-Cordless Spin Mop-B0GKNGWLJ2-Exact-SP</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0GKNGWLJ2</t>
         </is>
       </c>
       <c r="D305" t="n">
-        <v>0</v>
+        <v>1011.38</v>
       </c>
       <c r="E305" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="F305" t="n">
-        <v>0</v>
+        <v>13963</v>
       </c>
       <c r="G305" t="n">
         <v>0</v>
@@ -8976,78 +8976,78 @@
       <c r="A306" t="inlineStr"/>
       <c r="B306" t="inlineStr">
         <is>
-          <t>Nexliv-Steam Mop Floor Cleaner-B0DNJS23HS-CT-SP</t>
+          <t>Nexlive-Cordless Spin Mop-B0GKNGWLJ2-PT-SP</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0GKNGWLJ2</t>
         </is>
       </c>
       <c r="D306" t="n">
-        <v>3600.26</v>
+        <v>3585.57</v>
       </c>
       <c r="E306" t="n">
-        <v>147</v>
+        <v>265</v>
       </c>
       <c r="F306" t="n">
-        <v>14290</v>
+        <v>100047</v>
       </c>
       <c r="G306" t="n">
-        <v>5083.9</v>
+        <v>6608.48</v>
       </c>
       <c r="H306" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr"/>
       <c r="B307" t="inlineStr">
         <is>
-          <t>Nexliv-Steam Mop Floor Cleaner-B0DNJS23HS-Exact</t>
+          <t>Nexlive-Oil Applicator Comb-B0DKK15YNJ-PH-SP</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0DKK15YNJ</t>
         </is>
       </c>
       <c r="D307" t="n">
-        <v>3539.2</v>
+        <v>894.98</v>
       </c>
       <c r="E307" t="n">
-        <v>172</v>
+        <v>83</v>
       </c>
       <c r="F307" t="n">
-        <v>22502</v>
+        <v>10086</v>
       </c>
       <c r="G307" t="n">
-        <v>0</v>
+        <v>2380</v>
       </c>
       <c r="H307" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr"/>
       <c r="B308" t="inlineStr">
         <is>
-          <t>Nexliv-Steam Mop-B0D2LJSQXZ-Phrase-SP</t>
+          <t>Nexlive-Steam Mop Flor Cleaner-B0DNJS23HS-PT/-SP</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>B0D2LJSQXZ</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D308" t="n">
-        <v>0</v>
+        <v>341.49</v>
       </c>
       <c r="E308" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="F308" t="n">
-        <v>1</v>
+        <v>2738</v>
       </c>
       <c r="G308" t="n">
         <v>0</v>
@@ -9060,22 +9060,22 @@
       <c r="A309" t="inlineStr"/>
       <c r="B309" t="inlineStr">
         <is>
-          <t>Nexliv/Steam Cleaner-B0F43P6D23-Exact(1)-SP</t>
+          <t>Nexllev-Vacuum Cleaner-B0DCK7ZH5P-Exact</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0DCK7ZH5P</t>
         </is>
       </c>
       <c r="D309" t="n">
-        <v>13.07</v>
+        <v>2166.24</v>
       </c>
       <c r="E309" t="n">
-        <v>1</v>
+        <v>173</v>
       </c>
       <c r="F309" t="n">
-        <v>66</v>
+        <v>22685</v>
       </c>
       <c r="G309" t="n">
         <v>0</v>
@@ -9088,167 +9088,27 @@
       <c r="A310" t="inlineStr"/>
       <c r="B310" t="inlineStr">
         <is>
-          <t>Nexlive-Cordless Spin Mop-B0GKNGWLJ2-Exact-SP</t>
+          <t>nexliv-Mattress Sofa Carpet B0DCK7ZH5P-Phrase-SP</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>B0GKNGWLJ2</t>
+          <t>B0DCK7ZH5P</t>
         </is>
       </c>
       <c r="D310" t="n">
-        <v>1388.04</v>
+        <v>921.28</v>
       </c>
       <c r="E310" t="n">
-        <v>120</v>
+        <v>50</v>
       </c>
       <c r="F310" t="n">
-        <v>20610</v>
+        <v>8109</v>
       </c>
       <c r="G310" t="n">
-        <v>0</v>
+        <v>2880.51</v>
       </c>
       <c r="H310" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="311">
-      <c r="A311" t="inlineStr"/>
-      <c r="B311" t="inlineStr">
-        <is>
-          <t>Nexlive-Cordless Spin Mop-B0GKNGWLJ2-PT-SP</t>
-        </is>
-      </c>
-      <c r="C311" t="inlineStr">
-        <is>
-          <t>B0GKNGWLJ2</t>
-        </is>
-      </c>
-      <c r="D311" t="n">
-        <v>4210.93</v>
-      </c>
-      <c r="E311" t="n">
-        <v>320</v>
-      </c>
-      <c r="F311" t="n">
-        <v>129883</v>
-      </c>
-      <c r="G311" t="n">
-        <v>6608.48</v>
-      </c>
-      <c r="H311" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="312">
-      <c r="A312" t="inlineStr"/>
-      <c r="B312" t="inlineStr">
-        <is>
-          <t>Nexlive-Oil Applicator Comb-B0DKK15YNJ-PH-SP</t>
-        </is>
-      </c>
-      <c r="C312" t="inlineStr">
-        <is>
-          <t>B0DKK15YNJ</t>
-        </is>
-      </c>
-      <c r="D312" t="n">
-        <v>934.27</v>
-      </c>
-      <c r="E312" t="n">
-        <v>87</v>
-      </c>
-      <c r="F312" t="n">
-        <v>11098</v>
-      </c>
-      <c r="G312" t="n">
-        <v>2380</v>
-      </c>
-      <c r="H312" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="313">
-      <c r="A313" t="inlineStr"/>
-      <c r="B313" t="inlineStr">
-        <is>
-          <t>Nexlive-Steam Mop Flor Cleaner-B0DNJS23HS-PT/-SP</t>
-        </is>
-      </c>
-      <c r="C313" t="inlineStr">
-        <is>
-          <t>B0DNJS23HS</t>
-        </is>
-      </c>
-      <c r="D313" t="n">
-        <v>724.8299999999999</v>
-      </c>
-      <c r="E313" t="n">
-        <v>36</v>
-      </c>
-      <c r="F313" t="n">
-        <v>4077</v>
-      </c>
-      <c r="G313" t="n">
-        <v>0</v>
-      </c>
-      <c r="H313" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="314">
-      <c r="A314" t="inlineStr"/>
-      <c r="B314" t="inlineStr">
-        <is>
-          <t>Nexllev-Vacuum Cleaner-B0DCK7ZH5P-Exact</t>
-        </is>
-      </c>
-      <c r="C314" t="inlineStr">
-        <is>
-          <t>B0DCK7ZH5P</t>
-        </is>
-      </c>
-      <c r="D314" t="n">
-        <v>2523.23</v>
-      </c>
-      <c r="E314" t="n">
-        <v>206</v>
-      </c>
-      <c r="F314" t="n">
-        <v>27283</v>
-      </c>
-      <c r="G314" t="n">
-        <v>2880.5</v>
-      </c>
-      <c r="H314" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="315">
-      <c r="A315" t="inlineStr"/>
-      <c r="B315" t="inlineStr">
-        <is>
-          <t>nexliv-Mattress Sofa Carpet B0DCK7ZH5P-Phrase-SP</t>
-        </is>
-      </c>
-      <c r="C315" t="inlineStr">
-        <is>
-          <t>B0DCK7ZH5P</t>
-        </is>
-      </c>
-      <c r="D315" t="n">
-        <v>1215.33</v>
-      </c>
-      <c r="E315" t="n">
-        <v>64</v>
-      </c>
-      <c r="F315" t="n">
-        <v>9481</v>
-      </c>
-      <c r="G315" t="n">
-        <v>2880.51</v>
-      </c>
-      <c r="H315" t="n">
         <v>1</v>
       </c>
     </row>
@@ -10475,7 +10335,7 @@
         <v>23</v>
       </c>
       <c r="F43" t="n">
-        <v>10550</v>
+        <v>9460</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -10699,7 +10559,7 @@
         <v>1</v>
       </c>
       <c r="F51" t="n">
-        <v>1152</v>
+        <v>1106</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -10727,7 +10587,7 @@
         <v>0</v>
       </c>
       <c r="F52" t="n">
-        <v>457</v>
+        <v>286</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -10755,7 +10615,7 @@
         <v>1</v>
       </c>
       <c r="F53" t="n">
-        <v>776</v>
+        <v>580</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
@@ -10777,13 +10637,13 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>28.05</v>
+        <v>16.67</v>
       </c>
       <c r="E54" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F54" t="n">
-        <v>2264</v>
+        <v>2079</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
@@ -10811,7 +10671,7 @@
         <v>0</v>
       </c>
       <c r="F55" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
@@ -10831,7 +10691,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I48"/>
+  <dimension ref="A1:I46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10960,13 +10820,13 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>20496</v>
+        <v>18132</v>
       </c>
       <c r="E4" t="n">
-        <v>151</v>
+        <v>130</v>
       </c>
       <c r="F4" t="n">
-        <v>5605.747620231801</v>
+        <v>4878.071386235461</v>
       </c>
       <c r="G4" t="n">
         <v>3982.2</v>
@@ -10993,13 +10853,13 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>179</v>
+        <v>163</v>
       </c>
       <c r="E5" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F5" t="n">
-        <v>182.0566666666666</v>
+        <v>162.1233333333333</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -11026,13 +10886,13 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>30004</v>
+        <v>26542</v>
       </c>
       <c r="E6" t="n">
-        <v>216</v>
+        <v>186</v>
       </c>
       <c r="F6" t="n">
-        <v>8143.885713101533</v>
+        <v>7085.005280431205</v>
       </c>
       <c r="G6" t="n">
         <v>5845.76</v>
@@ -11059,13 +10919,13 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>8483</v>
+        <v>5781</v>
       </c>
       <c r="E7" t="n">
-        <v>282</v>
+        <v>182</v>
       </c>
       <c r="F7" t="n">
-        <v>2468.59</v>
+        <v>1681.42</v>
       </c>
       <c r="G7" t="n">
         <v>4236.44</v>
@@ -11092,13 +10952,13 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>30136</v>
+        <v>26830</v>
       </c>
       <c r="E8" t="n">
-        <v>171</v>
+        <v>153</v>
       </c>
       <c r="F8" t="n">
-        <v>2311.552196280246</v>
+        <v>2029.462067382764</v>
       </c>
       <c r="G8" t="n">
         <v>8568.570000000002</v>
@@ -11125,13 +10985,13 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>29800</v>
+        <v>26530</v>
       </c>
       <c r="E9" t="n">
-        <v>170</v>
+        <v>152</v>
       </c>
       <c r="F9" t="n">
-        <v>2285.737803719754</v>
+        <v>2006.797932617236</v>
       </c>
       <c r="G9" t="n">
         <v>8472.880000000001</v>
@@ -11158,19 +11018,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>12314</v>
+        <v>11466</v>
       </c>
       <c r="E10" t="n">
-        <v>125</v>
+        <v>114</v>
       </c>
       <c r="F10" t="n">
-        <v>1268.562638524461</v>
+        <v>1172.123436733268</v>
       </c>
       <c r="G10" t="n">
-        <v>4598.475136156199</v>
+        <v>4175.921519920821</v>
       </c>
       <c r="H10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -11191,19 +11051,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>4982</v>
+        <v>6186</v>
       </c>
       <c r="E11" t="n">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="F11" t="n">
-        <v>513.3020649918427</v>
+        <v>632.3717927491593</v>
       </c>
       <c r="G11" t="n">
-        <v>1860.69391571247</v>
+        <v>2252.949557336645</v>
       </c>
       <c r="H11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -11224,19 +11084,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>14000</v>
+        <v>8691</v>
       </c>
       <c r="E12" t="n">
-        <v>142</v>
+        <v>86</v>
       </c>
       <c r="F12" t="n">
-        <v>1442.285296483697</v>
+        <v>888.4247705175727</v>
       </c>
       <c r="G12" t="n">
-        <v>5228.21094813133</v>
+        <v>3165.188922742534</v>
       </c>
       <c r="H12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -11257,13 +11117,13 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>6884</v>
+        <v>6003</v>
       </c>
       <c r="E13" t="n">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="F13" t="n">
-        <v>366.35</v>
+        <v>303.0833333333333</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -11290,13 +11150,13 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>6884</v>
+        <v>6003</v>
       </c>
       <c r="E14" t="n">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="F14" t="n">
-        <v>366.35</v>
+        <v>303.0833333333333</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -11323,13 +11183,13 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>6884</v>
+        <v>6003</v>
       </c>
       <c r="E15" t="n">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="F15" t="n">
-        <v>366.35</v>
+        <v>303.0833333333333</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -11356,16 +11216,16 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>15867</v>
+        <v>13941</v>
       </c>
       <c r="E16" t="n">
-        <v>225</v>
+        <v>204</v>
       </c>
       <c r="F16" t="n">
-        <v>4184.137889877319</v>
+        <v>3957.65</v>
       </c>
       <c r="G16" t="n">
-        <v>17420.61236661249</v>
+        <v>15928.8</v>
       </c>
       <c r="H16" t="n">
         <v>4</v>
@@ -11380,28 +11240,28 @@
       <c r="A17" t="inlineStr"/>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Nexlev-B0CDPP45BM-Steam Cleaner-SBV-KT-Exact/Phrase</t>
+          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner - SBV-PT</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3340</v>
+        <v>4576</v>
       </c>
       <c r="E17" t="n">
-        <v>45</v>
+        <v>74</v>
       </c>
       <c r="F17" t="n">
-        <v>950.0321101226807</v>
+        <v>863.8</v>
       </c>
       <c r="G17" t="n">
-        <v>2320.897633387513</v>
+        <v>5083.05</v>
       </c>
       <c r="H17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -11413,7 +11273,7 @@
       <c r="A18" t="inlineStr"/>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner - SBV-PT</t>
+          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner - SBV-Phrase</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -11422,19 +11282,19 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>4576</v>
+        <v>2608</v>
       </c>
       <c r="E18" t="n">
-        <v>74</v>
+        <v>28</v>
       </c>
       <c r="F18" t="n">
-        <v>863.8</v>
+        <v>319.34</v>
       </c>
       <c r="G18" t="n">
-        <v>5083.05</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -11446,7 +11306,7 @@
       <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner - SBV-Phrase</t>
+          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner - SBV-Phrase01</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -11455,13 +11315,13 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2608</v>
+        <v>5932</v>
       </c>
       <c r="E19" t="n">
-        <v>28</v>
+        <v>51</v>
       </c>
       <c r="F19" t="n">
-        <v>319.34</v>
+        <v>585.65</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -11479,28 +11339,28 @@
       <c r="A20" t="inlineStr"/>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner - SBV-Phrase01</t>
+          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner -SB-KT-Exact</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0DCK7ZH5P</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>5932</v>
+        <v>3512</v>
       </c>
       <c r="E20" t="n">
-        <v>51</v>
+        <v>84</v>
       </c>
       <c r="F20" t="n">
-        <v>585.65</v>
+        <v>911.12</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>5422.030000000001</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -11512,25 +11372,25 @@
       <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner -SB-KT-Exact</t>
+          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner -SB-KT-Phrase(Video)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>B0DCK7ZH5P</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>4095</v>
+        <v>3861</v>
       </c>
       <c r="E21" t="n">
-        <v>106</v>
+        <v>81</v>
       </c>
       <c r="F21" t="n">
-        <v>1107.02</v>
+        <v>921.7</v>
       </c>
       <c r="G21" t="n">
-        <v>5422.030000000001</v>
+        <v>2541.53</v>
       </c>
       <c r="H21" t="n">
         <v>2</v>
@@ -11545,25 +11405,25 @@
       <c r="A22" t="inlineStr"/>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner -SB-KT-Phrase(Video)</t>
+          <t>Nexlev-B0DKK15YNJ- Oil Applicator-SBV-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0DKK15YNJ</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>4485</v>
+        <v>606</v>
       </c>
       <c r="E22" t="n">
-        <v>93</v>
+        <v>20</v>
       </c>
       <c r="F22" t="n">
-        <v>1076.39</v>
+        <v>365.27</v>
       </c>
       <c r="G22" t="n">
-        <v>2541.53</v>
+        <v>4760</v>
       </c>
       <c r="H22" t="n">
         <v>2</v>
@@ -11578,28 +11438,28 @@
       <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Nexlev-B0DKK15YNJ- Oil Applicator-SBV-KT-Exact/Phrase</t>
+          <t>Nexlev-B0DNJS23HS-SBV-Phrase-Mop Cleaner-SP</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>B0DKK15YNJ</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>721</v>
+        <v>92</v>
       </c>
       <c r="E23" t="n">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="F23" t="n">
-        <v>397.27</v>
+        <v>42.07</v>
       </c>
       <c r="G23" t="n">
-        <v>4760</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -11611,28 +11471,28 @@
       <c r="A24" t="inlineStr"/>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Nexlev-B0DNJS23HS-SBV-Phrase-Mop Cleaner-SP</t>
+          <t>Nexlev-B0DNJS23HS-Steam Cleaner - SBV-KT-Exact</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0D2LJSQXZ</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>92</v>
+        <v>3480</v>
       </c>
       <c r="E24" t="n">
-        <v>3</v>
+        <v>107</v>
       </c>
       <c r="F24" t="n">
-        <v>42.07</v>
+        <v>1307.25521503344</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>3219.49</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -11649,20 +11509,20 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>B0D2LJSQXZ</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>2661</v>
+        <v>3296</v>
       </c>
       <c r="E25" t="n">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="F25" t="n">
-        <v>1037.514701556099</v>
+        <v>1238.43478496656</v>
       </c>
       <c r="G25" t="n">
-        <v>4661.135641610127</v>
+        <v>3050</v>
       </c>
       <c r="H25" t="n">
         <v>1</v>
@@ -11677,7 +11537,7 @@
       <c r="A26" t="inlineStr"/>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Nexlev-B0DNJS23HS-Steam Cleaner - SBV-KT-Exact</t>
+          <t>Nexlev-B0DNJS23HS-Steam Mop-SB-KT-BM</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -11686,19 +11546,19 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>4202</v>
+        <v>1010</v>
       </c>
       <c r="E26" t="n">
-        <v>135</v>
+        <v>25</v>
       </c>
       <c r="F26" t="n">
-        <v>1638.34054189982</v>
+        <v>267.5003163991063</v>
       </c>
       <c r="G26" t="n">
-        <v>7360.404128722786</v>
+        <v>5083.9</v>
       </c>
       <c r="H26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -11710,25 +11570,25 @@
       <c r="A27" t="inlineStr"/>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Nexlev-B0DNJS23HS-Steam Cleaner - SBV-KT-Exact</t>
+          <t>Nexlev-B0DNJS23HS-Steam Mop-SB-KT-BM</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0GKNGWLJ2</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>2521</v>
+        <v>656</v>
       </c>
       <c r="E27" t="n">
-        <v>81</v>
+        <v>16</v>
       </c>
       <c r="F27" t="n">
-        <v>982.8947565440808</v>
+        <v>173.8596836008936</v>
       </c>
       <c r="G27" t="n">
-        <v>4415.750229667087</v>
+        <v>3304.24</v>
       </c>
       <c r="H27" t="n">
         <v>1</v>
@@ -11743,28 +11603,28 @@
       <c r="A28" t="inlineStr"/>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Nexlev-B0DNJS23HS-Steam Mop-SB-KT-BM</t>
+          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- PT</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0DVC7VJP1</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>1204</v>
+        <v>5396</v>
       </c>
       <c r="E28" t="n">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="F28" t="n">
-        <v>293.083034260277</v>
+        <v>630.95</v>
       </c>
       <c r="G28" t="n">
-        <v>8165.15987525244</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -11776,28 +11636,28 @@
       <c r="A29" t="inlineStr"/>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Nexlev-B0DNJS23HS-Steam Mop-SB-KT-BM</t>
+          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- PT01</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>B0GKNGWLJ2</t>
+          <t>B0DVC7VJP1</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>782</v>
+        <v>4467</v>
       </c>
       <c r="E29" t="n">
-        <v>18</v>
+        <v>48</v>
       </c>
       <c r="F29" t="n">
-        <v>190.486965739723</v>
+        <v>637.5599999999999</v>
       </c>
       <c r="G29" t="n">
-        <v>5306.88012474756</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -11809,7 +11669,7 @@
       <c r="A30" t="inlineStr"/>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- PT</t>
+          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- Phrase01</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -11818,13 +11678,13 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>5397</v>
+        <v>10430</v>
       </c>
       <c r="E30" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F30" t="n">
-        <v>630.95</v>
+        <v>529.66</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -11842,7 +11702,7 @@
       <c r="A31" t="inlineStr"/>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- PT01</t>
+          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV-phrase</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -11851,13 +11711,13 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>4467</v>
+        <v>10840</v>
       </c>
       <c r="E31" t="n">
         <v>48</v>
       </c>
       <c r="F31" t="n">
-        <v>637.5599999999999</v>
+        <v>509.86</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -11875,28 +11735,28 @@
       <c r="A32" t="inlineStr"/>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- Phrase01</t>
+          <t>Nexlev-B0F43P6D23-Steam Cleaner-SB-KT-Phrase</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>B0DVC7VJP1</t>
+          <t>B0D672NXC8</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>10430</v>
+        <v>13992</v>
       </c>
       <c r="E32" t="n">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="F32" t="n">
-        <v>529.66</v>
+        <v>606.4344991716607</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>8162.514621215101</v>
       </c>
       <c r="H32" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -11908,28 +11768,28 @@
       <c r="A33" t="inlineStr"/>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV-phrase</t>
+          <t>Nexlev-B0F43P6D23-Steam Cleaner-SB-KT-Phrase</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>B0DVC7VJP1</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>10840</v>
+        <v>6995</v>
       </c>
       <c r="E33" t="n">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="F33" t="n">
-        <v>509.86</v>
+        <v>303.1755008283393</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>4080.695378784898</v>
       </c>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -11941,7 +11801,7 @@
       <c r="A34" t="inlineStr"/>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Nexlev-B0F43P6D23-Steam Cleaner-SB-KT-Phrase</t>
+          <t>Nexlev-Catch All-Steam Cleaner -SB-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -11950,19 +11810,19 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>15741</v>
+        <v>11400</v>
       </c>
       <c r="E34" t="n">
-        <v>75</v>
+        <v>99</v>
       </c>
       <c r="F34" t="n">
-        <v>708.1391669398656</v>
+        <v>799.4770612172453</v>
       </c>
       <c r="G34" t="n">
-        <v>8162.514621215101</v>
+        <v>7455.225785130034</v>
       </c>
       <c r="H34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -11974,28 +11834,28 @@
       <c r="A35" t="inlineStr"/>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Nexlev-B0F43P6D23-Steam Cleaner-SB-KT-Phrase</t>
+          <t>Nexlev-Catch All-Steam Cleaner -SB-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>7870</v>
+        <v>27730</v>
       </c>
       <c r="E35" t="n">
-        <v>38</v>
+        <v>241</v>
       </c>
       <c r="F35" t="n">
-        <v>354.0208330601344</v>
+        <v>1944.612938782755</v>
       </c>
       <c r="G35" t="n">
-        <v>4080.695378784898</v>
+        <v>18133.76421486997</v>
       </c>
       <c r="H35" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -12007,28 +11867,28 @@
       <c r="A36" t="inlineStr"/>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-Steam Cleaner -SB-KT-Exact/Phrase</t>
+          <t>Nexlev-Catch All-Vacuum Cleaner-SB-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>B0D672NXC8</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>12012</v>
+        <v>6818</v>
       </c>
       <c r="E36" t="n">
-        <v>111</v>
+        <v>9</v>
       </c>
       <c r="F36" t="n">
-        <v>946.1314232479821</v>
+        <v>233.88</v>
       </c>
       <c r="G36" t="n">
-        <v>7455.225785130034</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -12040,28 +11900,28 @@
       <c r="A37" t="inlineStr"/>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-Steam Cleaner -SB-KT-Exact/Phrase</t>
+          <t>Nexlev-Catch All-Vacuum Cleaner-SB-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0DCK7ZH5P</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>29217</v>
+        <v>6818</v>
       </c>
       <c r="E37" t="n">
-        <v>271</v>
+        <v>9</v>
       </c>
       <c r="F37" t="n">
-        <v>2301.328576752018</v>
+        <v>233.88</v>
       </c>
       <c r="G37" t="n">
-        <v>18133.76421486997</v>
+        <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -12073,28 +11933,28 @@
       <c r="A38" t="inlineStr"/>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-Vacuum Cleaner-SB-KT-Exact/Phrase</t>
+          <t>Nexlev-Steamer-PT(SEAHELTON)-SB</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0CDPP45BM</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>9440</v>
+        <v>3705</v>
       </c>
       <c r="E38" t="n">
-        <v>12</v>
+        <v>214</v>
       </c>
       <c r="F38" t="n">
-        <v>324.805</v>
+        <v>2650.124821536723</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>14496.18887846715</v>
       </c>
       <c r="H38" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -12106,28 +11966,28 @@
       <c r="A39" t="inlineStr"/>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-Vacuum Cleaner-SB-KT-Exact/Phrase</t>
+          <t>Nexlev-Steamer-PT(SEAHELTON)-SB</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>B0DCK7ZH5P</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>9440</v>
+        <v>1635</v>
       </c>
       <c r="E39" t="n">
-        <v>12</v>
+        <v>95</v>
       </c>
       <c r="F39" t="n">
-        <v>324.805</v>
+        <v>1169.237315027467</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>6395.730806581966</v>
       </c>
       <c r="H39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -12144,23 +12004,23 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>B0CDPP45BM</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>3293</v>
+        <v>12505</v>
       </c>
       <c r="E40" t="n">
-        <v>187</v>
+        <v>723</v>
       </c>
       <c r="F40" t="n">
-        <v>2337.229394220671</v>
+        <v>8943.617863435809</v>
       </c>
       <c r="G40" t="n">
-        <v>13979.83487307437</v>
+        <v>48921.61031495088</v>
       </c>
       <c r="H40" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -12172,28 +12032,28 @@
       <c r="A41" t="inlineStr"/>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Nexlev-Steamer-PT(SEAHELTON)-SB</t>
+          <t>Nexlev-Steamers-Branded</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0CDPP45BM</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>4388</v>
+        <v>29</v>
       </c>
       <c r="E41" t="n">
-        <v>249</v>
+        <v>3</v>
       </c>
       <c r="F41" t="n">
-        <v>3114.188948494056</v>
+        <v>19.57333333333333</v>
       </c>
       <c r="G41" t="n">
-        <v>18627.1178050183</v>
+        <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -12205,28 +12065,28 @@
       <c r="A42" t="inlineStr"/>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Nexlev-Steamer-PT(SEAHELTON)-SB</t>
+          <t>Nexlev-Steamers-Branded</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>12761</v>
+        <v>29</v>
       </c>
       <c r="E42" t="n">
-        <v>724</v>
+        <v>3</v>
       </c>
       <c r="F42" t="n">
-        <v>9056.191657285275</v>
+        <v>19.57333333333333</v>
       </c>
       <c r="G42" t="n">
-        <v>54168.43732190733</v>
+        <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -12243,11 +12103,11 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>B0CDPP45BM</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E43" t="n">
         <v>3</v>
@@ -12271,22 +12131,22 @@
       <c r="A44" t="inlineStr"/>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Nexlev-Steamers-Branded</t>
+          <t>Nexlev-Vacuum Cleaner-Branded</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>30</v>
+        <v>1665</v>
       </c>
       <c r="E44" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="F44" t="n">
-        <v>19.57333333333333</v>
+        <v>91.29000000000001</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -12304,22 +12164,22 @@
       <c r="A45" t="inlineStr"/>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Nexlev-Steamers-Branded</t>
+          <t>Nexlev-Vacuum Cleaner-Branded</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0DCK7ZH5P</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>30</v>
+        <v>1665</v>
       </c>
       <c r="E45" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="F45" t="n">
-        <v>19.57333333333333</v>
+        <v>91.29000000000001</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -12342,17 +12202,17 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0DKJSCLBD</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>2314</v>
+        <v>1665</v>
       </c>
       <c r="E46" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F46" t="n">
-        <v>117.4133333333333</v>
+        <v>91.29000000000001</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -12361,72 +12221,6 @@
         <v>0</v>
       </c>
       <c r="I46" t="inlineStr">
-        <is>
-          <t>Nexlev</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr"/>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>Nexlev-Vacuum Cleaner-Branded</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>B0DCK7ZH5P</t>
-        </is>
-      </c>
-      <c r="D47" t="n">
-        <v>2314</v>
-      </c>
-      <c r="E47" t="n">
-        <v>10</v>
-      </c>
-      <c r="F47" t="n">
-        <v>117.4133333333333</v>
-      </c>
-      <c r="G47" t="n">
-        <v>0</v>
-      </c>
-      <c r="H47" t="n">
-        <v>0</v>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>Nexlev</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr"/>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>Nexlev-Vacuum Cleaner-Branded</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>B0DKJSCLBD</t>
-        </is>
-      </c>
-      <c r="D48" t="n">
-        <v>2314</v>
-      </c>
-      <c r="E48" t="n">
-        <v>10</v>
-      </c>
-      <c r="F48" t="n">
-        <v>117.4133333333333</v>
-      </c>
-      <c r="G48" t="n">
-        <v>0</v>
-      </c>
-      <c r="H48" t="n">
-        <v>0</v>
-      </c>
-      <c r="I48" t="inlineStr">
         <is>
           <t>Nexlev</t>
         </is>

--- a/data/ams_weekly_data/Nexlev/ads_report_week23.xlsx
+++ b/data/ams_weekly_data/Nexlev/ads_report_week23.xlsx
@@ -10691,7 +10691,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I46"/>
+  <dimension ref="A1:I37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11108,7 +11108,7 @@
       <c r="A13" t="inlineStr"/>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Nexlev-B0CDPP45BM-Cleaning Machine-SB-PT</t>
+          <t>Nexlev-B0CDPP45BM-Steam Cleaner-SBV-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -11117,19 +11117,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>6003</v>
+        <v>13941</v>
       </c>
       <c r="E13" t="n">
-        <v>27</v>
+        <v>204</v>
       </c>
       <c r="F13" t="n">
-        <v>303.0833333333333</v>
+        <v>3957.65</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>15928.8</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -11141,28 +11141,28 @@
       <c r="A14" t="inlineStr"/>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Nexlev-B0CDPP45BM-Cleaning Machine-SB-PT</t>
+          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner - SBV-PT</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>B0D672NXC8</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>6003</v>
+        <v>4576</v>
       </c>
       <c r="E14" t="n">
-        <v>27</v>
+        <v>74</v>
       </c>
       <c r="F14" t="n">
-        <v>303.0833333333333</v>
+        <v>863.8</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>5083.05</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -11174,22 +11174,22 @@
       <c r="A15" t="inlineStr"/>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Nexlev-B0CDPP45BM-Cleaning Machine-SB-PT</t>
+          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner - SBV-Phrase</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>6003</v>
+        <v>2608</v>
       </c>
       <c r="E15" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F15" t="n">
-        <v>303.0833333333333</v>
+        <v>319.34</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -11207,28 +11207,28 @@
       <c r="A16" t="inlineStr"/>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Nexlev-B0CDPP45BM-Steam Cleaner-SBV-KT-Exact/Phrase</t>
+          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner - SBV-Phrase01</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>B0CDPP45BM</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>13941</v>
+        <v>5932</v>
       </c>
       <c r="E16" t="n">
-        <v>204</v>
+        <v>51</v>
       </c>
       <c r="F16" t="n">
-        <v>3957.65</v>
+        <v>585.65</v>
       </c>
       <c r="G16" t="n">
-        <v>15928.8</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -11240,25 +11240,25 @@
       <c r="A17" t="inlineStr"/>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner - SBV-PT</t>
+          <t>Nexlev-B0DKK15YNJ- Oil Applicator-SBV-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0DKK15YNJ</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>4576</v>
+        <v>606</v>
       </c>
       <c r="E17" t="n">
-        <v>74</v>
+        <v>20</v>
       </c>
       <c r="F17" t="n">
-        <v>863.8</v>
+        <v>365.27</v>
       </c>
       <c r="G17" t="n">
-        <v>5083.05</v>
+        <v>4760</v>
       </c>
       <c r="H17" t="n">
         <v>2</v>
@@ -11273,22 +11273,22 @@
       <c r="A18" t="inlineStr"/>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner - SBV-Phrase</t>
+          <t>Nexlev-B0DNJS23HS-SBV-Phrase-Mop Cleaner-SP</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>2608</v>
+        <v>92</v>
       </c>
       <c r="E18" t="n">
-        <v>28</v>
+        <v>3</v>
       </c>
       <c r="F18" t="n">
-        <v>319.34</v>
+        <v>42.07</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -11306,28 +11306,28 @@
       <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner - SBV-Phrase01</t>
+          <t>Nexlev-B0DNJS23HS-Steam Cleaner - SBV-KT-Exact</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0D2LJSQXZ</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>5932</v>
+        <v>3480</v>
       </c>
       <c r="E19" t="n">
-        <v>51</v>
+        <v>107</v>
       </c>
       <c r="F19" t="n">
-        <v>585.65</v>
+        <v>1307.25521503344</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>3219.49</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -11339,28 +11339,28 @@
       <c r="A20" t="inlineStr"/>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner -SB-KT-Exact</t>
+          <t>Nexlev-B0DNJS23HS-Steam Cleaner - SBV-KT-Exact</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>B0DCK7ZH5P</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>3512</v>
+        <v>3296</v>
       </c>
       <c r="E20" t="n">
-        <v>84</v>
+        <v>102</v>
       </c>
       <c r="F20" t="n">
-        <v>911.12</v>
+        <v>1238.43478496656</v>
       </c>
       <c r="G20" t="n">
-        <v>5422.030000000001</v>
+        <v>3050</v>
       </c>
       <c r="H20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -11372,28 +11372,28 @@
       <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner -SB-KT-Phrase(Video)</t>
+          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- PT</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0DVC7VJP1</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>3861</v>
+        <v>5396</v>
       </c>
       <c r="E21" t="n">
-        <v>81</v>
+        <v>50</v>
       </c>
       <c r="F21" t="n">
-        <v>921.7</v>
+        <v>630.95</v>
       </c>
       <c r="G21" t="n">
-        <v>2541.53</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -11405,28 +11405,28 @@
       <c r="A22" t="inlineStr"/>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Nexlev-B0DKK15YNJ- Oil Applicator-SBV-KT-Exact/Phrase</t>
+          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- PT01</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>B0DKK15YNJ</t>
+          <t>B0DVC7VJP1</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>606</v>
+        <v>4467</v>
       </c>
       <c r="E22" t="n">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="F22" t="n">
-        <v>365.27</v>
+        <v>637.5599999999999</v>
       </c>
       <c r="G22" t="n">
-        <v>4760</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -11438,22 +11438,22 @@
       <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Nexlev-B0DNJS23HS-SBV-Phrase-Mop Cleaner-SP</t>
+          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- Phrase01</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0DVC7VJP1</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>92</v>
+        <v>10430</v>
       </c>
       <c r="E23" t="n">
-        <v>3</v>
+        <v>49</v>
       </c>
       <c r="F23" t="n">
-        <v>42.07</v>
+        <v>529.66</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -11471,28 +11471,28 @@
       <c r="A24" t="inlineStr"/>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Nexlev-B0DNJS23HS-Steam Cleaner - SBV-KT-Exact</t>
+          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV-phrase</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>B0D2LJSQXZ</t>
+          <t>B0DVC7VJP1</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>3480</v>
+        <v>10840</v>
       </c>
       <c r="E24" t="n">
-        <v>107</v>
+        <v>48</v>
       </c>
       <c r="F24" t="n">
-        <v>1307.25521503344</v>
+        <v>509.86</v>
       </c>
       <c r="G24" t="n">
-        <v>3219.49</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -11504,25 +11504,25 @@
       <c r="A25" t="inlineStr"/>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Nexlev-B0DNJS23HS-Steam Cleaner - SBV-KT-Exact</t>
+          <t>Nexlev-Catch All-Steam Cleaner -SB-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0D672NXC8</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>3296</v>
+        <v>11400</v>
       </c>
       <c r="E25" t="n">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="F25" t="n">
-        <v>1238.43478496656</v>
+        <v>799.4770612172453</v>
       </c>
       <c r="G25" t="n">
-        <v>3050</v>
+        <v>7455.225785130034</v>
       </c>
       <c r="H25" t="n">
         <v>1</v>
@@ -11537,7 +11537,7 @@
       <c r="A26" t="inlineStr"/>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Nexlev-B0DNJS23HS-Steam Mop-SB-KT-BM</t>
+          <t>Nexlev-Catch All-Steam Cleaner -SB-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -11546,19 +11546,19 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>1010</v>
+        <v>27730</v>
       </c>
       <c r="E26" t="n">
-        <v>25</v>
+        <v>241</v>
       </c>
       <c r="F26" t="n">
-        <v>267.5003163991063</v>
+        <v>1944.612938782755</v>
       </c>
       <c r="G26" t="n">
-        <v>5083.9</v>
+        <v>18133.76421486997</v>
       </c>
       <c r="H26" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -11570,28 +11570,28 @@
       <c r="A27" t="inlineStr"/>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Nexlev-B0DNJS23HS-Steam Mop-SB-KT-BM</t>
+          <t>Nexlev-Catch All-Vacuum Cleaner-SB-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>B0GKNGWLJ2</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>656</v>
+        <v>6818</v>
       </c>
       <c r="E27" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="F27" t="n">
-        <v>173.8596836008936</v>
+        <v>233.88</v>
       </c>
       <c r="G27" t="n">
-        <v>3304.24</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -11603,22 +11603,22 @@
       <c r="A28" t="inlineStr"/>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- PT</t>
+          <t>Nexlev-Catch All-Vacuum Cleaner-SB-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>B0DVC7VJP1</t>
+          <t>B0DCK7ZH5P</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>5396</v>
+        <v>6818</v>
       </c>
       <c r="E28" t="n">
-        <v>50</v>
+        <v>9</v>
       </c>
       <c r="F28" t="n">
-        <v>630.95</v>
+        <v>233.88</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -11636,28 +11636,28 @@
       <c r="A29" t="inlineStr"/>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- PT01</t>
+          <t>Nexlev-Steamer-PT(SEAHELTON)-SB</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>B0DVC7VJP1</t>
+          <t>B0CDPP45BM</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>4467</v>
+        <v>3705</v>
       </c>
       <c r="E29" t="n">
-        <v>48</v>
+        <v>214</v>
       </c>
       <c r="F29" t="n">
-        <v>637.5599999999999</v>
+        <v>2650.124821536723</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>14496.18887846715</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -11669,28 +11669,28 @@
       <c r="A30" t="inlineStr"/>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- Phrase01</t>
+          <t>Nexlev-Steamer-PT(SEAHELTON)-SB</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>B0DVC7VJP1</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>10430</v>
+        <v>1635</v>
       </c>
       <c r="E30" t="n">
-        <v>49</v>
+        <v>95</v>
       </c>
       <c r="F30" t="n">
-        <v>529.66</v>
+        <v>1169.237315027467</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>6395.730806581966</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -11702,28 +11702,28 @@
       <c r="A31" t="inlineStr"/>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV-phrase</t>
+          <t>Nexlev-Steamer-PT(SEAHELTON)-SB</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>B0DVC7VJP1</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>10840</v>
+        <v>12505</v>
       </c>
       <c r="E31" t="n">
-        <v>48</v>
+        <v>723</v>
       </c>
       <c r="F31" t="n">
-        <v>509.86</v>
+        <v>8943.617863435809</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>48921.61031495088</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -11735,28 +11735,28 @@
       <c r="A32" t="inlineStr"/>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Nexlev-B0F43P6D23-Steam Cleaner-SB-KT-Phrase</t>
+          <t>Nexlev-Steamers-Branded</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>B0D672NXC8</t>
+          <t>B0CDPP45BM</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13992</v>
+        <v>29</v>
       </c>
       <c r="E32" t="n">
-        <v>65</v>
+        <v>3</v>
       </c>
       <c r="F32" t="n">
-        <v>606.4344991716607</v>
+        <v>19.57333333333333</v>
       </c>
       <c r="G32" t="n">
-        <v>8162.514621215101</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -11768,28 +11768,28 @@
       <c r="A33" t="inlineStr"/>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Nexlev-B0F43P6D23-Steam Cleaner-SB-KT-Phrase</t>
+          <t>Nexlev-Steamers-Branded</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>6995</v>
+        <v>29</v>
       </c>
       <c r="E33" t="n">
-        <v>32</v>
+        <v>3</v>
       </c>
       <c r="F33" t="n">
-        <v>303.1755008283393</v>
+        <v>19.57333333333333</v>
       </c>
       <c r="G33" t="n">
-        <v>4080.695378784898</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -11801,28 +11801,28 @@
       <c r="A34" t="inlineStr"/>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-Steam Cleaner -SB-KT-Exact/Phrase</t>
+          <t>Nexlev-Steamers-Branded</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>B0D672NXC8</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>11400</v>
+        <v>29</v>
       </c>
       <c r="E34" t="n">
-        <v>99</v>
+        <v>3</v>
       </c>
       <c r="F34" t="n">
-        <v>799.4770612172453</v>
+        <v>19.57333333333333</v>
       </c>
       <c r="G34" t="n">
-        <v>7455.225785130034</v>
+        <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -11834,28 +11834,28 @@
       <c r="A35" t="inlineStr"/>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-Steam Cleaner -SB-KT-Exact/Phrase</t>
+          <t>Nexlev-Vacuum Cleaner-Branded</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>27730</v>
+        <v>1665</v>
       </c>
       <c r="E35" t="n">
-        <v>241</v>
+        <v>8</v>
       </c>
       <c r="F35" t="n">
-        <v>1944.612938782755</v>
+        <v>91.29000000000001</v>
       </c>
       <c r="G35" t="n">
-        <v>18133.76421486997</v>
+        <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -11867,22 +11867,22 @@
       <c r="A36" t="inlineStr"/>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-Vacuum Cleaner-SB-KT-Exact/Phrase</t>
+          <t>Nexlev-Vacuum Cleaner-Branded</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0DCK7ZH5P</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>6818</v>
+        <v>1665</v>
       </c>
       <c r="E36" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F36" t="n">
-        <v>233.88</v>
+        <v>91.29000000000001</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -11900,22 +11900,22 @@
       <c r="A37" t="inlineStr"/>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-Vacuum Cleaner-SB-KT-Exact/Phrase</t>
+          <t>Nexlev-Vacuum Cleaner-Branded</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>B0DCK7ZH5P</t>
+          <t>B0DKJSCLBD</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>6818</v>
+        <v>1665</v>
       </c>
       <c r="E37" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F37" t="n">
-        <v>233.88</v>
+        <v>91.29000000000001</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -11924,303 +11924,6 @@
         <v>0</v>
       </c>
       <c r="I37" t="inlineStr">
-        <is>
-          <t>Nexlev</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr"/>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Nexlev-Steamer-PT(SEAHELTON)-SB</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>B0CDPP45BM</t>
-        </is>
-      </c>
-      <c r="D38" t="n">
-        <v>3705</v>
-      </c>
-      <c r="E38" t="n">
-        <v>214</v>
-      </c>
-      <c r="F38" t="n">
-        <v>2650.124821536723</v>
-      </c>
-      <c r="G38" t="n">
-        <v>14496.18887846715</v>
-      </c>
-      <c r="H38" t="n">
-        <v>4</v>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>Nexlev</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr"/>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Nexlev-Steamer-PT(SEAHELTON)-SB</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>B0DNJS23HS</t>
-        </is>
-      </c>
-      <c r="D39" t="n">
-        <v>1635</v>
-      </c>
-      <c r="E39" t="n">
-        <v>95</v>
-      </c>
-      <c r="F39" t="n">
-        <v>1169.237315027467</v>
-      </c>
-      <c r="G39" t="n">
-        <v>6395.730806581966</v>
-      </c>
-      <c r="H39" t="n">
-        <v>2</v>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>Nexlev</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr"/>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Nexlev-Steamer-PT(SEAHELTON)-SB</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>B0F43P6D23</t>
-        </is>
-      </c>
-      <c r="D40" t="n">
-        <v>12505</v>
-      </c>
-      <c r="E40" t="n">
-        <v>723</v>
-      </c>
-      <c r="F40" t="n">
-        <v>8943.617863435809</v>
-      </c>
-      <c r="G40" t="n">
-        <v>48921.61031495088</v>
-      </c>
-      <c r="H40" t="n">
-        <v>15</v>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>Nexlev</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr"/>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Nexlev-Steamers-Branded</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>B0CDPP45BM</t>
-        </is>
-      </c>
-      <c r="D41" t="n">
-        <v>29</v>
-      </c>
-      <c r="E41" t="n">
-        <v>3</v>
-      </c>
-      <c r="F41" t="n">
-        <v>19.57333333333333</v>
-      </c>
-      <c r="G41" t="n">
-        <v>0</v>
-      </c>
-      <c r="H41" t="n">
-        <v>0</v>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>Nexlev</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr"/>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Nexlev-Steamers-Branded</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>B0DNJS23HS</t>
-        </is>
-      </c>
-      <c r="D42" t="n">
-        <v>29</v>
-      </c>
-      <c r="E42" t="n">
-        <v>3</v>
-      </c>
-      <c r="F42" t="n">
-        <v>19.57333333333333</v>
-      </c>
-      <c r="G42" t="n">
-        <v>0</v>
-      </c>
-      <c r="H42" t="n">
-        <v>0</v>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>Nexlev</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr"/>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Nexlev-Steamers-Branded</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>B0F43P6D23</t>
-        </is>
-      </c>
-      <c r="D43" t="n">
-        <v>29</v>
-      </c>
-      <c r="E43" t="n">
-        <v>3</v>
-      </c>
-      <c r="F43" t="n">
-        <v>19.57333333333333</v>
-      </c>
-      <c r="G43" t="n">
-        <v>0</v>
-      </c>
-      <c r="H43" t="n">
-        <v>0</v>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>Nexlev</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr"/>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Nexlev-Vacuum Cleaner-Branded</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>B0CYSLCRQS</t>
-        </is>
-      </c>
-      <c r="D44" t="n">
-        <v>1665</v>
-      </c>
-      <c r="E44" t="n">
-        <v>8</v>
-      </c>
-      <c r="F44" t="n">
-        <v>91.29000000000001</v>
-      </c>
-      <c r="G44" t="n">
-        <v>0</v>
-      </c>
-      <c r="H44" t="n">
-        <v>0</v>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>Nexlev</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr"/>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Nexlev-Vacuum Cleaner-Branded</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>B0DCK7ZH5P</t>
-        </is>
-      </c>
-      <c r="D45" t="n">
-        <v>1665</v>
-      </c>
-      <c r="E45" t="n">
-        <v>8</v>
-      </c>
-      <c r="F45" t="n">
-        <v>91.29000000000001</v>
-      </c>
-      <c r="G45" t="n">
-        <v>0</v>
-      </c>
-      <c r="H45" t="n">
-        <v>0</v>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>Nexlev</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr"/>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>Nexlev-Vacuum Cleaner-Branded</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>B0DKJSCLBD</t>
-        </is>
-      </c>
-      <c r="D46" t="n">
-        <v>1665</v>
-      </c>
-      <c r="E46" t="n">
-        <v>8</v>
-      </c>
-      <c r="F46" t="n">
-        <v>91.29000000000001</v>
-      </c>
-      <c r="G46" t="n">
-        <v>0</v>
-      </c>
-      <c r="H46" t="n">
-        <v>0</v>
-      </c>
-      <c r="I46" t="inlineStr">
         <is>
           <t>Nexlev</t>
         </is>

--- a/data/ams_weekly_data/Nexlev/ads_report_week23.xlsx
+++ b/data/ams_weekly_data/Nexlev/ads_report_week23.xlsx
@@ -10691,7 +10691,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I37"/>
+  <dimension ref="A1:I46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11108,7 +11108,7 @@
       <c r="A13" t="inlineStr"/>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Nexlev-B0CDPP45BM-Steam Cleaner-SBV-KT-Exact/Phrase</t>
+          <t>Nexlev-B0CDPP45BM-Cleaning Machine-SB-PT</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -11117,19 +11117,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13941</v>
+        <v>6003</v>
       </c>
       <c r="E13" t="n">
-        <v>204</v>
+        <v>27</v>
       </c>
       <c r="F13" t="n">
-        <v>3957.65</v>
+        <v>303.0833333333333</v>
       </c>
       <c r="G13" t="n">
-        <v>15928.8</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -11141,28 +11141,28 @@
       <c r="A14" t="inlineStr"/>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner - SBV-PT</t>
+          <t>Nexlev-B0CDPP45BM-Cleaning Machine-SB-PT</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0D672NXC8</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4576</v>
+        <v>6003</v>
       </c>
       <c r="E14" t="n">
-        <v>74</v>
+        <v>27</v>
       </c>
       <c r="F14" t="n">
-        <v>863.8</v>
+        <v>303.0833333333333</v>
       </c>
       <c r="G14" t="n">
-        <v>5083.05</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -11174,22 +11174,22 @@
       <c r="A15" t="inlineStr"/>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner - SBV-Phrase</t>
+          <t>Nexlev-B0CDPP45BM-Cleaning Machine-SB-PT</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>2608</v>
+        <v>6003</v>
       </c>
       <c r="E15" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F15" t="n">
-        <v>319.34</v>
+        <v>303.0833333333333</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -11207,28 +11207,28 @@
       <c r="A16" t="inlineStr"/>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner - SBV-Phrase01</t>
+          <t>Nexlev-B0CDPP45BM-Steam Cleaner-SBV-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0CDPP45BM</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>5932</v>
+        <v>13941</v>
       </c>
       <c r="E16" t="n">
-        <v>51</v>
+        <v>204</v>
       </c>
       <c r="F16" t="n">
-        <v>585.65</v>
+        <v>3957.65</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>15928.8</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -11240,25 +11240,25 @@
       <c r="A17" t="inlineStr"/>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Nexlev-B0DKK15YNJ- Oil Applicator-SBV-KT-Exact/Phrase</t>
+          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner - SBV-PT</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>B0DKK15YNJ</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>606</v>
+        <v>4576</v>
       </c>
       <c r="E17" t="n">
-        <v>20</v>
+        <v>74</v>
       </c>
       <c r="F17" t="n">
-        <v>365.27</v>
+        <v>863.8</v>
       </c>
       <c r="G17" t="n">
-        <v>4760</v>
+        <v>5083.05</v>
       </c>
       <c r="H17" t="n">
         <v>2</v>
@@ -11273,22 +11273,22 @@
       <c r="A18" t="inlineStr"/>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Nexlev-B0DNJS23HS-SBV-Phrase-Mop Cleaner-SP</t>
+          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner - SBV-Phrase</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>92</v>
+        <v>2608</v>
       </c>
       <c r="E18" t="n">
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="F18" t="n">
-        <v>42.07</v>
+        <v>319.34</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -11306,28 +11306,28 @@
       <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Nexlev-B0DNJS23HS-Steam Cleaner - SBV-KT-Exact</t>
+          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner - SBV-Phrase01</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>B0D2LJSQXZ</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>3480</v>
+        <v>5932</v>
       </c>
       <c r="E19" t="n">
-        <v>107</v>
+        <v>51</v>
       </c>
       <c r="F19" t="n">
-        <v>1307.25521503344</v>
+        <v>585.65</v>
       </c>
       <c r="G19" t="n">
-        <v>3219.49</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -11339,28 +11339,28 @@
       <c r="A20" t="inlineStr"/>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Nexlev-B0DNJS23HS-Steam Cleaner - SBV-KT-Exact</t>
+          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner -SB-KT-Exact</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0DCK7ZH5P</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>3296</v>
+        <v>3512</v>
       </c>
       <c r="E20" t="n">
-        <v>102</v>
+        <v>84</v>
       </c>
       <c r="F20" t="n">
-        <v>1238.43478496656</v>
+        <v>911.12</v>
       </c>
       <c r="G20" t="n">
-        <v>3050</v>
+        <v>5422.030000000001</v>
       </c>
       <c r="H20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -11372,28 +11372,28 @@
       <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- PT</t>
+          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner -SB-KT-Phrase(Video)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>B0DVC7VJP1</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>5396</v>
+        <v>3861</v>
       </c>
       <c r="E21" t="n">
-        <v>50</v>
+        <v>81</v>
       </c>
       <c r="F21" t="n">
-        <v>630.95</v>
+        <v>921.7</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>2541.53</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -11405,28 +11405,28 @@
       <c r="A22" t="inlineStr"/>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- PT01</t>
+          <t>Nexlev-B0DKK15YNJ- Oil Applicator-SBV-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>B0DVC7VJP1</t>
+          <t>B0DKK15YNJ</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>4467</v>
+        <v>606</v>
       </c>
       <c r="E22" t="n">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="F22" t="n">
-        <v>637.5599999999999</v>
+        <v>365.27</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>4760</v>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -11438,22 +11438,22 @@
       <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- Phrase01</t>
+          <t>Nexlev-B0DNJS23HS-SBV-Phrase-Mop Cleaner-SP</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>B0DVC7VJP1</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>10430</v>
+        <v>92</v>
       </c>
       <c r="E23" t="n">
-        <v>49</v>
+        <v>3</v>
       </c>
       <c r="F23" t="n">
-        <v>529.66</v>
+        <v>42.07</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -11471,28 +11471,28 @@
       <c r="A24" t="inlineStr"/>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV-phrase</t>
+          <t>Nexlev-B0DNJS23HS-Steam Cleaner - SBV-KT-Exact</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>B0DVC7VJP1</t>
+          <t>B0D2LJSQXZ</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>10840</v>
+        <v>3480</v>
       </c>
       <c r="E24" t="n">
-        <v>48</v>
+        <v>107</v>
       </c>
       <c r="F24" t="n">
-        <v>509.86</v>
+        <v>1307.25521503344</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>3219.49</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -11504,25 +11504,25 @@
       <c r="A25" t="inlineStr"/>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-Steam Cleaner -SB-KT-Exact/Phrase</t>
+          <t>Nexlev-B0DNJS23HS-Steam Cleaner - SBV-KT-Exact</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>B0D672NXC8</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>11400</v>
+        <v>3296</v>
       </c>
       <c r="E25" t="n">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="F25" t="n">
-        <v>799.4770612172453</v>
+        <v>1238.43478496656</v>
       </c>
       <c r="G25" t="n">
-        <v>7455.225785130034</v>
+        <v>3050</v>
       </c>
       <c r="H25" t="n">
         <v>1</v>
@@ -11537,7 +11537,7 @@
       <c r="A26" t="inlineStr"/>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-Steam Cleaner -SB-KT-Exact/Phrase</t>
+          <t>Nexlev-B0DNJS23HS-Steam Mop-SB-KT-BM</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -11546,19 +11546,19 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>27730</v>
+        <v>1010</v>
       </c>
       <c r="E26" t="n">
-        <v>241</v>
+        <v>25</v>
       </c>
       <c r="F26" t="n">
-        <v>1944.612938782755</v>
+        <v>267.5003163991063</v>
       </c>
       <c r="G26" t="n">
-        <v>18133.76421486997</v>
+        <v>5083.9</v>
       </c>
       <c r="H26" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -11570,28 +11570,28 @@
       <c r="A27" t="inlineStr"/>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-Vacuum Cleaner-SB-KT-Exact/Phrase</t>
+          <t>Nexlev-B0DNJS23HS-Steam Mop-SB-KT-BM</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0GKNGWLJ2</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>6818</v>
+        <v>656</v>
       </c>
       <c r="E27" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="F27" t="n">
-        <v>233.88</v>
+        <v>173.8596836008936</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>3304.24</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -11603,22 +11603,22 @@
       <c r="A28" t="inlineStr"/>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-Vacuum Cleaner-SB-KT-Exact/Phrase</t>
+          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- PT</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>B0DCK7ZH5P</t>
+          <t>B0DVC7VJP1</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>6818</v>
+        <v>5396</v>
       </c>
       <c r="E28" t="n">
-        <v>9</v>
+        <v>50</v>
       </c>
       <c r="F28" t="n">
-        <v>233.88</v>
+        <v>630.95</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -11636,28 +11636,28 @@
       <c r="A29" t="inlineStr"/>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Nexlev-Steamer-PT(SEAHELTON)-SB</t>
+          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- PT01</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>B0CDPP45BM</t>
+          <t>B0DVC7VJP1</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>3705</v>
+        <v>4467</v>
       </c>
       <c r="E29" t="n">
-        <v>214</v>
+        <v>48</v>
       </c>
       <c r="F29" t="n">
-        <v>2650.124821536723</v>
+        <v>637.5599999999999</v>
       </c>
       <c r="G29" t="n">
-        <v>14496.18887846715</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -11669,28 +11669,28 @@
       <c r="A30" t="inlineStr"/>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Nexlev-Steamer-PT(SEAHELTON)-SB</t>
+          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- Phrase01</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0DVC7VJP1</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>1635</v>
+        <v>10430</v>
       </c>
       <c r="E30" t="n">
-        <v>95</v>
+        <v>49</v>
       </c>
       <c r="F30" t="n">
-        <v>1169.237315027467</v>
+        <v>529.66</v>
       </c>
       <c r="G30" t="n">
-        <v>6395.730806581966</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -11702,28 +11702,28 @@
       <c r="A31" t="inlineStr"/>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Nexlev-Steamer-PT(SEAHELTON)-SB</t>
+          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV-phrase</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0DVC7VJP1</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>12505</v>
+        <v>10840</v>
       </c>
       <c r="E31" t="n">
-        <v>723</v>
+        <v>48</v>
       </c>
       <c r="F31" t="n">
-        <v>8943.617863435809</v>
+        <v>509.86</v>
       </c>
       <c r="G31" t="n">
-        <v>48921.61031495088</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -11735,28 +11735,28 @@
       <c r="A32" t="inlineStr"/>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Nexlev-Steamers-Branded</t>
+          <t>Nexlev-B0F43P6D23-Steam Cleaner-SB-KT-Phrase</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>B0CDPP45BM</t>
+          <t>B0D672NXC8</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>29</v>
+        <v>13992</v>
       </c>
       <c r="E32" t="n">
-        <v>3</v>
+        <v>65</v>
       </c>
       <c r="F32" t="n">
-        <v>19.57333333333333</v>
+        <v>606.4344991716607</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>8162.514621215101</v>
       </c>
       <c r="H32" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -11768,28 +11768,28 @@
       <c r="A33" t="inlineStr"/>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Nexlev-Steamers-Branded</t>
+          <t>Nexlev-B0F43P6D23-Steam Cleaner-SB-KT-Phrase</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>29</v>
+        <v>6995</v>
       </c>
       <c r="E33" t="n">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="F33" t="n">
-        <v>19.57333333333333</v>
+        <v>303.1755008283393</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>4080.695378784898</v>
       </c>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -11801,28 +11801,28 @@
       <c r="A34" t="inlineStr"/>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Nexlev-Steamers-Branded</t>
+          <t>Nexlev-Catch All-Steam Cleaner -SB-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0D672NXC8</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>29</v>
+        <v>11400</v>
       </c>
       <c r="E34" t="n">
-        <v>3</v>
+        <v>99</v>
       </c>
       <c r="F34" t="n">
-        <v>19.57333333333333</v>
+        <v>799.4770612172453</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>7455.225785130034</v>
       </c>
       <c r="H34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -11834,28 +11834,28 @@
       <c r="A35" t="inlineStr"/>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Nexlev-Vacuum Cleaner-Branded</t>
+          <t>Nexlev-Catch All-Steam Cleaner -SB-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>1665</v>
+        <v>27730</v>
       </c>
       <c r="E35" t="n">
-        <v>8</v>
+        <v>241</v>
       </c>
       <c r="F35" t="n">
-        <v>91.29000000000001</v>
+        <v>1944.612938782755</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>18133.76421486997</v>
       </c>
       <c r="H35" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -11867,22 +11867,22 @@
       <c r="A36" t="inlineStr"/>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Nexlev-Vacuum Cleaner-Branded</t>
+          <t>Nexlev-Catch All-Vacuum Cleaner-SB-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>B0DCK7ZH5P</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>1665</v>
+        <v>6818</v>
       </c>
       <c r="E36" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F36" t="n">
-        <v>91.29000000000001</v>
+        <v>233.88</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -11900,30 +11900,327 @@
       <c r="A37" t="inlineStr"/>
       <c r="B37" t="inlineStr">
         <is>
+          <t>Nexlev-Catch All-Vacuum Cleaner-SB-KT-Exact/Phrase</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>B0DCK7ZH5P</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>6818</v>
+      </c>
+      <c r="E37" t="n">
+        <v>9</v>
+      </c>
+      <c r="F37" t="n">
+        <v>233.88</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr"/>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Nexlev-Steamer-PT(SEAHELTON)-SB</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>B0CDPP45BM</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>3705</v>
+      </c>
+      <c r="E38" t="n">
+        <v>214</v>
+      </c>
+      <c r="F38" t="n">
+        <v>2650.124821536723</v>
+      </c>
+      <c r="G38" t="n">
+        <v>14496.18887846715</v>
+      </c>
+      <c r="H38" t="n">
+        <v>4</v>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr"/>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Nexlev-Steamer-PT(SEAHELTON)-SB</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>B0DNJS23HS</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>1635</v>
+      </c>
+      <c r="E39" t="n">
+        <v>95</v>
+      </c>
+      <c r="F39" t="n">
+        <v>1169.237315027467</v>
+      </c>
+      <c r="G39" t="n">
+        <v>6395.730806581966</v>
+      </c>
+      <c r="H39" t="n">
+        <v>2</v>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr"/>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Nexlev-Steamer-PT(SEAHELTON)-SB</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>B0F43P6D23</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>12505</v>
+      </c>
+      <c r="E40" t="n">
+        <v>723</v>
+      </c>
+      <c r="F40" t="n">
+        <v>8943.617863435809</v>
+      </c>
+      <c r="G40" t="n">
+        <v>48921.61031495088</v>
+      </c>
+      <c r="H40" t="n">
+        <v>15</v>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr"/>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Nexlev-Steamers-Branded</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>B0CDPP45BM</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>29</v>
+      </c>
+      <c r="E41" t="n">
+        <v>3</v>
+      </c>
+      <c r="F41" t="n">
+        <v>19.57333333333333</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr"/>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Nexlev-Steamers-Branded</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>B0DNJS23HS</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>29</v>
+      </c>
+      <c r="E42" t="n">
+        <v>3</v>
+      </c>
+      <c r="F42" t="n">
+        <v>19.57333333333333</v>
+      </c>
+      <c r="G42" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr"/>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Nexlev-Steamers-Branded</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>B0F43P6D23</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>29</v>
+      </c>
+      <c r="E43" t="n">
+        <v>3</v>
+      </c>
+      <c r="F43" t="n">
+        <v>19.57333333333333</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr"/>
+      <c r="B44" t="inlineStr">
+        <is>
           <t>Nexlev-Vacuum Cleaner-Branded</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>B0CYSLCRQS</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>1665</v>
+      </c>
+      <c r="E44" t="n">
+        <v>8</v>
+      </c>
+      <c r="F44" t="n">
+        <v>91.29000000000001</v>
+      </c>
+      <c r="G44" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr"/>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Nexlev-Vacuum Cleaner-Branded</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>B0DCK7ZH5P</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>1665</v>
+      </c>
+      <c r="E45" t="n">
+        <v>8</v>
+      </c>
+      <c r="F45" t="n">
+        <v>91.29000000000001</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr"/>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Nexlev-Vacuum Cleaner-Branded</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
         <is>
           <t>B0DKJSCLBD</t>
         </is>
       </c>
-      <c r="D37" t="n">
+      <c r="D46" t="n">
         <v>1665</v>
       </c>
-      <c r="E37" t="n">
+      <c r="E46" t="n">
         <v>8</v>
       </c>
-      <c r="F37" t="n">
+      <c r="F46" t="n">
         <v>91.29000000000001</v>
       </c>
-      <c r="G37" t="n">
-        <v>0</v>
-      </c>
-      <c r="H37" t="n">
-        <v>0</v>
-      </c>
-      <c r="I37" t="inlineStr">
+      <c r="G46" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" t="inlineStr">
         <is>
           <t>Nexlev</t>
         </is>

--- a/data/ams_weekly_data/Nexlev/ads_report_week23.xlsx
+++ b/data/ams_weekly_data/Nexlev/ads_report_week23.xlsx
@@ -10691,7 +10691,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I46"/>
+  <dimension ref="A1:I47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10820,16 +10820,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18132</v>
+        <v>14946</v>
       </c>
       <c r="E4" t="n">
-        <v>130</v>
+        <v>109</v>
       </c>
       <c r="F4" t="n">
-        <v>4878.071386235461</v>
+        <v>4041.733333333334</v>
       </c>
       <c r="G4" t="n">
-        <v>3982.2</v>
+        <v>3275.986666666666</v>
       </c>
       <c r="H4" t="n">
         <v>1</v>
@@ -10853,19 +10853,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>163</v>
+        <v>14946</v>
       </c>
       <c r="E5" t="n">
-        <v>11</v>
+        <v>109</v>
       </c>
       <c r="F5" t="n">
-        <v>162.1233333333333</v>
+        <v>4041.733333333334</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>3275.986666666666</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -10886,19 +10886,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>26542</v>
+        <v>14946</v>
       </c>
       <c r="E6" t="n">
-        <v>186</v>
+        <v>109</v>
       </c>
       <c r="F6" t="n">
-        <v>7085.005280431205</v>
+        <v>4041.733333333334</v>
       </c>
       <c r="G6" t="n">
-        <v>5845.76</v>
+        <v>3275.986666666666</v>
       </c>
       <c r="H6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -10915,23 +10915,23 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>B0FPGDVVCX</t>
+          <t>B0DM6BB3VT</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>5781</v>
+        <v>2890</v>
       </c>
       <c r="E7" t="n">
-        <v>182</v>
+        <v>91</v>
       </c>
       <c r="F7" t="n">
-        <v>1681.42</v>
+        <v>840.71</v>
       </c>
       <c r="G7" t="n">
-        <v>4236.44</v>
+        <v>2118.22</v>
       </c>
       <c r="H7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -10943,28 +10943,28 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Nexlev -Catch All-  Calf Massager -SB-KT-Exact/Phrase</t>
+          <t>Nexlev -B0DM6BB3VT-Calf Massager-SBV -KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>B0DM6BB3VT</t>
+          <t>B0FPGDVVCX</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>26830</v>
+        <v>2890</v>
       </c>
       <c r="E8" t="n">
-        <v>153</v>
+        <v>91</v>
       </c>
       <c r="F8" t="n">
-        <v>2029.462067382764</v>
+        <v>840.71</v>
       </c>
       <c r="G8" t="n">
-        <v>8568.570000000002</v>
+        <v>2118.22</v>
       </c>
       <c r="H8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -10981,20 +10981,20 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>B0FPGDVVCX</t>
+          <t>B0DM6BB3VT</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>26530</v>
+        <v>17787</v>
       </c>
       <c r="E9" t="n">
-        <v>152</v>
+        <v>102</v>
       </c>
       <c r="F9" t="n">
-        <v>2006.797932617236</v>
+        <v>1345.42</v>
       </c>
       <c r="G9" t="n">
-        <v>8472.880000000001</v>
+        <v>5680.483333333334</v>
       </c>
       <c r="H9" t="n">
         <v>2</v>
@@ -11009,28 +11009,28 @@
       <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Nexlev -Catch All- Scalp Massager-SB-KT-Exact/Phrase</t>
+          <t>Nexlev -Catch All-  Calf Massager -SB-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>B0D67727VG</t>
+          <t>B0DVSZ2VVJ</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>11466</v>
+        <v>17787</v>
       </c>
       <c r="E10" t="n">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="F10" t="n">
-        <v>1172.123436733268</v>
+        <v>1345.42</v>
       </c>
       <c r="G10" t="n">
-        <v>4175.921519920821</v>
+        <v>5680.483333333334</v>
       </c>
       <c r="H10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -11042,25 +11042,25 @@
       <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Nexlev -Catch All- Scalp Massager-SB-KT-Exact/Phrase</t>
+          <t>Nexlev -Catch All-  Calf Massager -SB-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>B0DCGHKRXX</t>
+          <t>B0FPGDVVCX</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6186</v>
+        <v>17787</v>
       </c>
       <c r="E11" t="n">
-        <v>62</v>
+        <v>102</v>
       </c>
       <c r="F11" t="n">
-        <v>632.3717927491593</v>
+        <v>1345.42</v>
       </c>
       <c r="G11" t="n">
-        <v>2252.949557336645</v>
+        <v>5680.483333333334</v>
       </c>
       <c r="H11" t="n">
         <v>2</v>
@@ -11080,20 +11080,20 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>B0DKK15YNJ</t>
+          <t>B0D67727VG</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>8691</v>
+        <v>8781</v>
       </c>
       <c r="E12" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F12" t="n">
-        <v>888.4247705175727</v>
+        <v>897.64</v>
       </c>
       <c r="G12" t="n">
-        <v>3165.188922742534</v>
+        <v>3198.02</v>
       </c>
       <c r="H12" t="n">
         <v>2</v>
@@ -11108,28 +11108,28 @@
       <c r="A13" t="inlineStr"/>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Nexlev-B0CDPP45BM-Cleaning Machine-SB-PT</t>
+          <t>Nexlev -Catch All- Scalp Massager-SB-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>B0CDPP45BM</t>
+          <t>B0DCGHKRXX</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>6003</v>
+        <v>8781</v>
       </c>
       <c r="E13" t="n">
-        <v>27</v>
+        <v>87</v>
       </c>
       <c r="F13" t="n">
-        <v>303.0833333333333</v>
+        <v>897.64</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>3198.02</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -11141,28 +11141,28 @@
       <c r="A14" t="inlineStr"/>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Nexlev-B0CDPP45BM-Cleaning Machine-SB-PT</t>
+          <t>Nexlev -Catch All- Scalp Massager-SB-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>B0D672NXC8</t>
+          <t>B0DKK15YNJ</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>6003</v>
+        <v>8781</v>
       </c>
       <c r="E14" t="n">
-        <v>27</v>
+        <v>87</v>
       </c>
       <c r="F14" t="n">
-        <v>303.0833333333333</v>
+        <v>897.64</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>3198.02</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -11179,17 +11179,17 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0CDPP45BM</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>6003</v>
+        <v>18010</v>
       </c>
       <c r="E15" t="n">
-        <v>27</v>
+        <v>82</v>
       </c>
       <c r="F15" t="n">
-        <v>303.0833333333333</v>
+        <v>909.25</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -11410,23 +11410,23 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>B0DKK15YNJ</t>
+          <t>B0D67727VG</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>606</v>
+        <v>303</v>
       </c>
       <c r="E22" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F22" t="n">
-        <v>365.27</v>
+        <v>182.635</v>
       </c>
       <c r="G22" t="n">
-        <v>4760</v>
+        <v>2380</v>
       </c>
       <c r="H22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -11438,28 +11438,28 @@
       <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Nexlev-B0DNJS23HS-SBV-Phrase-Mop Cleaner-SP</t>
+          <t>Nexlev-B0DKK15YNJ- Oil Applicator-SBV-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0DKK15YNJ</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>92</v>
+        <v>303</v>
       </c>
       <c r="E23" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F23" t="n">
-        <v>42.07</v>
+        <v>182.635</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>2380</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -11471,28 +11471,28 @@
       <c r="A24" t="inlineStr"/>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Nexlev-B0DNJS23HS-Steam Cleaner - SBV-KT-Exact</t>
+          <t>Nexlev-B0DNJS23HS-SBV-Phrase-Mop Cleaner-SP</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>B0D2LJSQXZ</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>3480</v>
+        <v>92</v>
       </c>
       <c r="E24" t="n">
-        <v>107</v>
+        <v>3</v>
       </c>
       <c r="F24" t="n">
-        <v>1307.25521503344</v>
+        <v>42.07</v>
       </c>
       <c r="G24" t="n">
-        <v>3219.49</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -11509,23 +11509,23 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>3296</v>
+        <v>6776</v>
       </c>
       <c r="E25" t="n">
-        <v>102</v>
+        <v>209</v>
       </c>
       <c r="F25" t="n">
-        <v>1238.43478496656</v>
+        <v>2545.69</v>
       </c>
       <c r="G25" t="n">
-        <v>3050</v>
+        <v>6269.49</v>
       </c>
       <c r="H25" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -11806,23 +11806,23 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>B0D672NXC8</t>
+          <t>B0CDPP45BM</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>11400</v>
+        <v>13043</v>
       </c>
       <c r="E34" t="n">
-        <v>99</v>
+        <v>113</v>
       </c>
       <c r="F34" t="n">
-        <v>799.4770612172453</v>
+        <v>914.6966666666667</v>
       </c>
       <c r="G34" t="n">
-        <v>7455.225785130034</v>
+        <v>8529.663333333334</v>
       </c>
       <c r="H34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -11843,19 +11843,19 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>27730</v>
+        <v>13043</v>
       </c>
       <c r="E35" t="n">
-        <v>241</v>
+        <v>113</v>
       </c>
       <c r="F35" t="n">
-        <v>1944.612938782755</v>
+        <v>914.6966666666667</v>
       </c>
       <c r="G35" t="n">
-        <v>18133.76421486997</v>
+        <v>8529.663333333334</v>
       </c>
       <c r="H35" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -11867,28 +11867,28 @@
       <c r="A36" t="inlineStr"/>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-Vacuum Cleaner-SB-KT-Exact/Phrase</t>
+          <t>Nexlev-Catch All-Steam Cleaner -SB-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>6818</v>
+        <v>13043</v>
       </c>
       <c r="E36" t="n">
-        <v>9</v>
+        <v>113</v>
       </c>
       <c r="F36" t="n">
-        <v>233.88</v>
+        <v>914.6966666666667</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>8529.663333333334</v>
       </c>
       <c r="H36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -11905,7 +11905,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>B0DCK7ZH5P</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -11933,28 +11933,28 @@
       <c r="A38" t="inlineStr"/>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Nexlev-Steamer-PT(SEAHELTON)-SB</t>
+          <t>Nexlev-Catch All-Vacuum Cleaner-SB-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>B0CDPP45BM</t>
+          <t>B0DCK7ZH5P</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>3705</v>
+        <v>6818</v>
       </c>
       <c r="E38" t="n">
-        <v>214</v>
+        <v>9</v>
       </c>
       <c r="F38" t="n">
-        <v>2650.124821536723</v>
+        <v>233.88</v>
       </c>
       <c r="G38" t="n">
-        <v>14496.18887846715</v>
+        <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -11971,23 +11971,23 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0CDPP45BM</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>1635</v>
+        <v>5948</v>
       </c>
       <c r="E39" t="n">
-        <v>95</v>
+        <v>344</v>
       </c>
       <c r="F39" t="n">
-        <v>1169.237315027467</v>
+        <v>4254.326666666667</v>
       </c>
       <c r="G39" t="n">
-        <v>6395.730806581966</v>
+        <v>23271.17666666667</v>
       </c>
       <c r="H39" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -12004,23 +12004,23 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>12505</v>
+        <v>5948</v>
       </c>
       <c r="E40" t="n">
-        <v>723</v>
+        <v>344</v>
       </c>
       <c r="F40" t="n">
-        <v>8943.617863435809</v>
+        <v>4254.326666666667</v>
       </c>
       <c r="G40" t="n">
-        <v>48921.61031495088</v>
+        <v>23271.17666666667</v>
       </c>
       <c r="H40" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -12032,28 +12032,28 @@
       <c r="A41" t="inlineStr"/>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Nexlev-Steamers-Branded</t>
+          <t>Nexlev-Steamer-PT(SEAHELTON)-SB</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>B0CDPP45BM</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>29</v>
+        <v>5948</v>
       </c>
       <c r="E41" t="n">
-        <v>3</v>
+        <v>344</v>
       </c>
       <c r="F41" t="n">
-        <v>19.57333333333333</v>
+        <v>4254.326666666667</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>23271.17666666667</v>
       </c>
       <c r="H41" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -12070,7 +12070,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0CDPP45BM</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -12103,7 +12103,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -12131,22 +12131,22 @@
       <c r="A44" t="inlineStr"/>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Nexlev-Vacuum Cleaner-Branded</t>
+          <t>Nexlev-Steamers-Branded</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>1665</v>
+        <v>29</v>
       </c>
       <c r="E44" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F44" t="n">
-        <v>91.29000000000001</v>
+        <v>19.57333333333333</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -12169,7 +12169,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>B0DCK7ZH5P</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -12202,7 +12202,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>B0DKJSCLBD</t>
+          <t>B0DCK7ZH5P</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -12221,6 +12221,39 @@
         <v>0</v>
       </c>
       <c r="I46" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr"/>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Nexlev-Vacuum Cleaner-Branded</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>B0DKJSCLBD</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>1665</v>
+      </c>
+      <c r="E47" t="n">
+        <v>8</v>
+      </c>
+      <c r="F47" t="n">
+        <v>91.29000000000001</v>
+      </c>
+      <c r="G47" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0</v>
+      </c>
+      <c r="I47" t="inlineStr">
         <is>
           <t>Nexlev</t>
         </is>
